--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
@@ -447,7 +447,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
@@ -447,7 +447,7 @@
     <t>,,</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
     <t>(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9383" uniqueCount="2041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9561" uniqueCount="2143">
   <si>
     <t>ID</t>
   </si>
@@ -365,307 +365,307 @@
     <t>C0076</t>
   </si>
   <si>
-    <t>campaign--469310ef-4094-4e7c-9c67-f45b0aaa8547</t>
-  </si>
-  <si>
-    <t>campaign--1da9ae08-d4bb-4d3f-ac74-ec943ba5eaea</t>
-  </si>
-  <si>
-    <t>campaign--06564046-4d40-460a-97a4-3ed307685e40</t>
-  </si>
-  <si>
-    <t>campaign--f35b3b1e-3566-45f5-bffd-36b87158a0a8</t>
-  </si>
-  <si>
-    <t>campaign--1ed15b75-60c6-4d37-9d70-217b0e2c459f</t>
-  </si>
-  <si>
-    <t>campaign--37f47ace-f541-4346-bc8d-914ef07293a2</t>
-  </si>
-  <si>
-    <t>campaign--a7b14767-cae0-4491-88c0-9f89c9121a90</t>
-  </si>
-  <si>
-    <t>campaign--fbc5edd1-be5a-43d9-b787-a616fa2715dc</t>
-  </si>
-  <si>
-    <t>campaign--57bc5e5f-ccdc-40e4-afad-02434f0b2fb6</t>
-  </si>
-  <si>
-    <t>campaign--92d836df-311b-4605-9795-446b644815bb</t>
-  </si>
-  <si>
-    <t>campaign--96476361-e0d6-4535-b346-9c3b912bd9e3</t>
-  </si>
-  <si>
-    <t>campaign--a9efd6f6-ecda-44af-b7fc-43a9dc8ccd12</t>
-  </si>
-  <si>
-    <t>campaign--2d54bb22-7db2-4405-9c6b-03591652ceb7</t>
-  </si>
-  <si>
-    <t>campaign--babba679-aee3-44e3-b357-607640fb6ac5</t>
-  </si>
-  <si>
-    <t>campaign--a1e496e7-7199-4d75-83ef-a86810a706b0</t>
-  </si>
-  <si>
-    <t>campaign--02829ff9-ab24-4d0b-8fd1-50d95a2c675a</t>
-  </si>
-  <si>
-    <t>campaign--c075447d-3770-4539-8fa3-c78e83db5533</t>
-  </si>
-  <si>
-    <t>campaign--0b6e405c-a036-47dd-8c12-ec160b0ebf20</t>
-  </si>
-  <si>
-    <t>campaign--9ee49c05-78a5-441d-b6b6-3803e9cf6b2e</t>
-  </si>
-  <si>
-    <t>campaign--bbdb7af2-2478-4231-bf88-140096111cf0</t>
-  </si>
-  <si>
-    <t>campaign--7ed527f9-2a59-48e7-84fa-2207c3867e21</t>
-  </si>
-  <si>
-    <t>campaign--878cb2cf-11b1-450d-8240-874e6cee55db</t>
-  </si>
-  <si>
-    <t>campaign--31b050af-e3bb-418b-ba1f-3e3900d3b5c1</t>
-  </si>
-  <si>
-    <t>campaign--b58bf5e2-8288-406d-873a-d6c557000725</t>
-  </si>
-  <si>
-    <t>campaign--b47a06ee-5194-4931-ae87-651748ad7ba6</t>
-  </si>
-  <si>
-    <t>campaign--d058c586-e582-45f0-b4e2-194c6599f119</t>
-  </si>
-  <si>
-    <t>campaign--a4cd4a1b-d1c5-45c5-bb7d-3018adbdeaaa</t>
-  </si>
-  <si>
-    <t>campaign--9f1c9c14-749e-4471-96a6-36e2a8ce16f3</t>
-  </si>
-  <si>
-    <t>campaign--138818ae-7e8e-4838-858a-fc252dff9953</t>
-  </si>
-  <si>
-    <t>campaign--5eeb401c-84e2-46fd-b61f-f0f6a3b8942a</t>
-  </si>
-  <si>
-    <t>campaign--94dae670-09c9-4e10-a03e-bace8ecddebb</t>
-  </si>
-  <si>
-    <t>campaign--1bd11010-5386-41c3-aa33-79321c801f6d</t>
-  </si>
-  <si>
-    <t>campaign--351bcd52-1012-4ba8-9014-071de5495f66</t>
-  </si>
-  <si>
-    <t>campaign--e2ddf00a-7479-4e93-92ef-75f49f3e574e</t>
-  </si>
-  <si>
-    <t>campaign--979cdf7e-8431-4d0e-9edf-97c67a396fab</t>
-  </si>
-  <si>
-    <t>campaign--61eacb32-a063-44cc-acba-9691d4504970</t>
-  </si>
-  <si>
-    <t>campaign--0f123e76-dbd9-42e8-83fa-94c42ab45546</t>
-  </si>
-  <si>
-    <t>campaign--a4e9875b-4377-4409-8e0d-ba4bf6817fe1</t>
-  </si>
-  <si>
-    <t>campaign--ffcd0dcc-ce70-4d9a-b06e-ad29c6a5faa7</t>
-  </si>
-  <si>
-    <t>campaign--9d75ac21-abcf-4195-9c50-287324e7013e</t>
-  </si>
-  <si>
-    <t>campaign--1be51ecb-8994-4135-b846-3a4d2fc03bbc</t>
-  </si>
-  <si>
-    <t>campaign--0ff0500d-6a60-465d-ad50-d1f1c3b9bb2f</t>
-  </si>
-  <si>
-    <t>campaign--b7427601-e8ad-4808-86ad-e348d4d8e8e8</t>
-  </si>
-  <si>
-    <t>campaign--23562267-63c1-45f6-a2e5-2c8be7dea1ca</t>
-  </si>
-  <si>
-    <t>campaign--ccd6e591-b2f6-401c-9432-d880013c9109</t>
-  </si>
-  <si>
-    <t>campaign--4375f375-22bc-45fa-a6a1-647d169ca8d2</t>
-  </si>
-  <si>
-    <t>campaign--00e9c967-4b34-4582-addc-71e4e7138765</t>
-  </si>
-  <si>
-    <t>campaign--39681d6f-63c5-4f46-b65d-e9e278c89ffd</t>
-  </si>
-  <si>
-    <t>campaign--579698e2-118e-4ece-9ae6-68677abbfcfb</t>
-  </si>
-  <si>
-    <t>campaign--85ed260f-1c25-4943-94cb-7889f41f7e49</t>
-  </si>
-  <si>
-    <t>campaign--3120da56-f8d8-4bfe-820e-a5c81422a643</t>
-  </si>
-  <si>
-    <t>campaign--1a4c53de-829f-4e74-98d2-669ac8260fa5</t>
-  </si>
-  <si>
-    <t>campaign--d25530f7-12c2-4aa6-93dd-6eb9e3e64e45</t>
-  </si>
-  <si>
-    <t>campaign--d2388221-289a-4666-8ea7-09aa68582270</t>
-  </si>
-  <si>
-    <t>campaign--0824f4a5-da79-4989-bde2-a1cd6d32bbb0</t>
-  </si>
-  <si>
-    <t>campaign--2e6f6e3e-6481-4991-8daa-f31bbd1ddcd4</t>
-  </si>
-  <si>
-    <t>campaign--19eabd02-641a-470f-ba96-16bd2e8fbb7c</t>
-  </si>
-  <si>
-    <t>campaign--31a84130-e0f4-4b6a-b733-a13fe388aca1</t>
-  </si>
-  <si>
-    <t>campaign--7ad99995-4346-4b9f-8ee6-7456085ee8f4</t>
-  </si>
-  <si>
-    <t>campaign--6a417d5d-08fd-494a-8e38-a849469200d5</t>
-  </si>
-  <si>
-    <t>campaign--80cc78f4-303a-4e14-b362-205a0455754d</t>
-  </si>
-  <si>
-    <t>campaign--41aeb17b-6211-408d-b7d2-38119809d10e</t>
-  </si>
-  <si>
-    <t>campaign--f05ed4f4-f2e3-4913-a735-82027728ce05</t>
-  </si>
-  <si>
-    <t>campaign--d1e226e3-fc33-499c-a10e-cf0a09450014</t>
-  </si>
-  <si>
-    <t>campaign--0fe96e75-417a-47b7-892d-e68565b241b6</t>
-  </si>
-  <si>
-    <t>campaign--df7c84da-94a8-4648-9f1c-6c33cfe71f0c</t>
-  </si>
-  <si>
-    <t>campaign--a85fa0a4-c62b-4a2d-89ab-350311b71890</t>
-  </si>
-  <si>
-    <t>campaign--3fc95fda-cd5c-4e2a-8075-55803606d10e</t>
-  </si>
-  <si>
-    <t>campaign--4eacde73-d9c1-4355-afec-7d8f87610f1f</t>
-  </si>
-  <si>
-    <t>campaign--5dad886c-01bc-4d38-8168-6177fd6a7349</t>
-  </si>
-  <si>
-    <t>campaign--548b6a19-f9f3-4763-bdbc-1c12c12267ae</t>
-  </si>
-  <si>
-    <t>campaign--221ad627-69c6-436e-bd69-70f81103fcc4</t>
-  </si>
-  <si>
-    <t>campaign--b1c0f594-4c32-4525-a394-f0cfa965e9df</t>
-  </si>
-  <si>
-    <t>campaign--b64e83f5-f457-4774-9be1-66c261e50854</t>
-  </si>
-  <si>
-    <t>campaign--790d7f8e-2c25-48b5-8533-65b3f8ac2b9b</t>
-  </si>
-  <si>
-    <t>campaign--4e7c9498-5134-492c-8a41-ad881a983a77</t>
-  </si>
-  <si>
-    <t>campaign--de5f6586-4723-47b4-bea0-fc192727aebd</t>
-  </si>
-  <si>
-    <t>campaign--a21034da-0578-4297-bffe-b1f389435ff6</t>
-  </si>
-  <si>
-    <t>campaign--ccfe0a05-ff11-4dfd-8f07-e5c961c2afcd</t>
-  </si>
-  <si>
-    <t>campaign--fe66cc4f-a868-42fc-898d-619bdfe66830</t>
-  </si>
-  <si>
-    <t>campaign--ed294a47-7e87-40fa-993e-de2cb99245bb</t>
-  </si>
-  <si>
-    <t>campaign--d9465ad8-c135-4770-ab09-965c31194f8a</t>
-  </si>
-  <si>
-    <t>campaign--953fcd6f-5a7f-4ddd-9a05-c1d081d3febd</t>
-  </si>
-  <si>
-    <t>campaign--e7714c89-03d9-4e0f-8667-cb52fb36e11b</t>
-  </si>
-  <si>
-    <t>campaign--05051bcd-4e18-474e-a19a-a127de638f55</t>
-  </si>
-  <si>
-    <t>campaign--74724121-ec58-4506-a35d-f9b712da7b67</t>
-  </si>
-  <si>
-    <t>campaign--d6cabbf1-27c3-45d6-9c3c-1cec382515d8</t>
-  </si>
-  <si>
-    <t>campaign--67d98968-5982-4041-9eb1-b366e631d16f</t>
-  </si>
-  <si>
-    <t>campaign--04131151-85c0-4189-9ffd-9508eb1a253d</t>
-  </si>
-  <si>
-    <t>campaign--f4378eab-dead-40c5-a510-fca43c057d18</t>
-  </si>
-  <si>
-    <t>campaign--98342c99-3a98-4b8f-b49e-7e00b435bd99</t>
-  </si>
-  <si>
-    <t>campaign--8893f759-a738-4bd4-9a5b-12ee22480623</t>
-  </si>
-  <si>
-    <t>campaign--3a522944-77dd-4455-99bd-9bb3662762c6</t>
-  </si>
-  <si>
-    <t>campaign--f00cb9d8-2806-467d-9675-3953a6f7998c</t>
-  </si>
-  <si>
-    <t>campaign--ebbf432f-457f-4477-be87-0dd1c7ba2b06</t>
-  </si>
-  <si>
-    <t>campaign--fafde296-b6ea-4b0a-8c05-fae5907ad781</t>
-  </si>
-  <si>
-    <t>campaign--97b9ca95-4c48-46e3-9c0c-69a1c2a83695</t>
-  </si>
-  <si>
-    <t>campaign--7d79a2a7-6f18-45c3-ad5b-a726a4fb6e93</t>
-  </si>
-  <si>
-    <t>campaign--b3ebfffc-4e30-4091-83e3-6ad673c7e2d4</t>
-  </si>
-  <si>
-    <t>campaign--22c4105c-6aba-421f-933e-40a47b6a0ce0</t>
-  </si>
-  <si>
-    <t>campaign--ec0283ed-3be9-48ad-b31f-4ac278e8e07a</t>
+    <t>campaign--6cb77d0a-3451-4de8-87da-b018068dfb90</t>
+  </si>
+  <si>
+    <t>campaign--8b42609d-df97-4863-be72-6956976733bf</t>
+  </si>
+  <si>
+    <t>campaign--9a411991-5759-4401-bf8b-1d035755a82e</t>
+  </si>
+  <si>
+    <t>campaign--87f90c81-65f7-408a-869c-13c15763058d</t>
+  </si>
+  <si>
+    <t>campaign--79792109-8930-4868-a0d5-c36b7e4d35d2</t>
+  </si>
+  <si>
+    <t>campaign--a2a50721-74ad-4a1b-8f10-4729fe218d77</t>
+  </si>
+  <si>
+    <t>campaign--e0b2ee1f-02d9-420b-95ec-c5e69e7683ba</t>
+  </si>
+  <si>
+    <t>campaign--f1f99961-521b-4e4c-ad7b-41a7f7fbb47d</t>
+  </si>
+  <si>
+    <t>campaign--b00634c3-5732-436e-b8ac-a379eb11a3a5</t>
+  </si>
+  <si>
+    <t>campaign--79f52559-e2ab-4202-825d-6c93ef0450f8</t>
+  </si>
+  <si>
+    <t>campaign--946006e7-080a-4089-846c-570e294df9de</t>
+  </si>
+  <si>
+    <t>campaign--120e2810-9671-4bbd-89dd-fdd5e5664bd8</t>
+  </si>
+  <si>
+    <t>campaign--e31eeb50-d21f-4f54-94fc-7a1265e3f422</t>
+  </si>
+  <si>
+    <t>campaign--4b4c6c32-adfd-4839-a189-784041b133e3</t>
+  </si>
+  <si>
+    <t>campaign--bbf4f7b4-df46-40fb-9560-91bbccaa69dd</t>
+  </si>
+  <si>
+    <t>campaign--d71c0044-37aa-487b-a348-d665b548d364</t>
+  </si>
+  <si>
+    <t>campaign--db3cd6c5-fdee-4f60-a49a-78a6842a0bdd</t>
+  </si>
+  <si>
+    <t>campaign--76bb2459-6ee0-4d14-9d96-4608d7fb554f</t>
+  </si>
+  <si>
+    <t>campaign--6763e8dc-524b-4121-9c95-1badc8d4ac5e</t>
+  </si>
+  <si>
+    <t>campaign--f7092c6b-af00-4ffc-bbc9-d41fdc3d22c0</t>
+  </si>
+  <si>
+    <t>campaign--02c01b67-1582-41d8-9cb8-89286d93e772</t>
+  </si>
+  <si>
+    <t>campaign--aedfaa2b-061a-4e70-8824-e88b30dbe4c4</t>
+  </si>
+  <si>
+    <t>campaign--452ec2f1-3adb-4883-a2a6-240c40bc70bc</t>
+  </si>
+  <si>
+    <t>campaign--467c7d12-8c86-49b3-accf-f377d0d7d0cc</t>
+  </si>
+  <si>
+    <t>campaign--a124adf3-a386-46f5-ab54-3b856f8a8bad</t>
+  </si>
+  <si>
+    <t>campaign--b25b509c-ab0c-4256-8f81-968d821c5915</t>
+  </si>
+  <si>
+    <t>campaign--18b1943c-1241-40fe-aae3-033c9ffa418c</t>
+  </si>
+  <si>
+    <t>campaign--50f07b8d-3a52-4520-9e5a-1f1eb1e83dea</t>
+  </si>
+  <si>
+    <t>campaign--05ca5326-ae3e-481b-ad1b-07a246c88714</t>
+  </si>
+  <si>
+    <t>campaign--5263d574-5eed-4573-a592-aff86805b317</t>
+  </si>
+  <si>
+    <t>campaign--87b0aff4-b9bb-4edb-b847-a3eb826f374e</t>
+  </si>
+  <si>
+    <t>campaign--4b8f603c-2beb-40c6-9db9-d9823f6e0437</t>
+  </si>
+  <si>
+    <t>campaign--45fafe35-cd3c-444a-a268-46b6a7370a63</t>
+  </si>
+  <si>
+    <t>campaign--4f403031-7401-483e-8eed-57761453596d</t>
+  </si>
+  <si>
+    <t>campaign--8cae9b2b-74d5-4ad1-9fea-e453ecc7f425</t>
+  </si>
+  <si>
+    <t>campaign--040c2b9c-df77-4197-bd95-495a7034b4c1</t>
+  </si>
+  <si>
+    <t>campaign--c7253f1e-c38d-4816-aa0b-fcd9f8dbbc27</t>
+  </si>
+  <si>
+    <t>campaign--d706a65d-715e-48ed-967a-3f237212463e</t>
+  </si>
+  <si>
+    <t>campaign--c3ef8acc-0599-468f-8956-3b91f3f30511</t>
+  </si>
+  <si>
+    <t>campaign--9a4f57ab-6a5e-462f-9d19-5421174ca868</t>
+  </si>
+  <si>
+    <t>campaign--3eab6e53-2449-478f-bf55-dd8afe89a40f</t>
+  </si>
+  <si>
+    <t>campaign--66baf89b-527e-4143-b19f-5621e74abb52</t>
+  </si>
+  <si>
+    <t>campaign--d33f72f9-20ea-4c43-a97d-85d6b536eda0</t>
+  </si>
+  <si>
+    <t>campaign--bebaab35-7783-4d15-b58b-ad2b0da41e64</t>
+  </si>
+  <si>
+    <t>campaign--1d62a197-4c67-4f24-8a41-5890204c4c85</t>
+  </si>
+  <si>
+    <t>campaign--ab5f7d10-2bd1-4ecb-b899-e478c9e2bedd</t>
+  </si>
+  <si>
+    <t>campaign--f9faba2b-2963-4108-975a-2425bcf557ff</t>
+  </si>
+  <si>
+    <t>campaign--d99a23fc-75f2-454e-a013-ef34ceee1c09</t>
+  </si>
+  <si>
+    <t>campaign--f36b045a-dea2-4a27-9a7e-dd439efff501</t>
+  </si>
+  <si>
+    <t>campaign--b93d1b44-3dc6-4818-b008-6748d0af33e9</t>
+  </si>
+  <si>
+    <t>campaign--2152c27e-8fb6-4d17-9545-ece61b0abb3d</t>
+  </si>
+  <si>
+    <t>campaign--da5bc58c-582e-4e35-83a7-a7616031ccf5</t>
+  </si>
+  <si>
+    <t>campaign--25d28320-21cd-47c2-8697-a1311d1d96f7</t>
+  </si>
+  <si>
+    <t>campaign--9232f8d3-d677-410c-9237-89f745f0288d</t>
+  </si>
+  <si>
+    <t>campaign--4b2262cd-ff27-411a-979d-6212f210b82d</t>
+  </si>
+  <si>
+    <t>campaign--9b0bbb08-af99-4a34-b75d-4014845f167d</t>
+  </si>
+  <si>
+    <t>campaign--29d1bd6c-71fb-4d83-862b-cbd6746a86b0</t>
+  </si>
+  <si>
+    <t>campaign--8d7e51bc-58cf-4cf3-891f-e30a45c03432</t>
+  </si>
+  <si>
+    <t>campaign--767abf96-8a3c-4500-9ec1-0d0a1fb32a88</t>
+  </si>
+  <si>
+    <t>campaign--009b3fbb-eb3e-4dd6-a04c-a439731c1854</t>
+  </si>
+  <si>
+    <t>campaign--210bd249-aeb2-4415-8206-e60090b574d1</t>
+  </si>
+  <si>
+    <t>campaign--142059e7-8457-48d4-8716-7aa6b587ab1b</t>
+  </si>
+  <si>
+    <t>campaign--6bb7b821-0e8b-4422-ad1b-764fff0a37e9</t>
+  </si>
+  <si>
+    <t>campaign--a7570eea-ac8a-4869-a00b-367790a7b200</t>
+  </si>
+  <si>
+    <t>campaign--9d9fbae1-5595-4a19-bd8c-7ddd1e2168ec</t>
+  </si>
+  <si>
+    <t>campaign--08748419-8e5d-40dc-aaff-c88e0fff5983</t>
+  </si>
+  <si>
+    <t>campaign--bbc072e6-4905-4dc0-a250-6a9d2dc9d66b</t>
+  </si>
+  <si>
+    <t>campaign--e30cc2e9-1add-4397-876e-067e0ede49ff</t>
+  </si>
+  <si>
+    <t>campaign--d787d857-4e39-4e4a-8103-3f6a4562de40</t>
+  </si>
+  <si>
+    <t>campaign--3c84c661-3fb6-44a6-ab75-7b4399e54925</t>
+  </si>
+  <si>
+    <t>campaign--33b91be6-6f1e-4aa6-ae4b-0099423adbf4</t>
+  </si>
+  <si>
+    <t>campaign--c8a3e3e3-0e8c-491a-b935-3ee30c72989d</t>
+  </si>
+  <si>
+    <t>campaign--9ed45ec0-7d71-4336-ba95-741c9cb1c4ad</t>
+  </si>
+  <si>
+    <t>campaign--c655b524-c56f-484c-b29f-132f99d873d6</t>
+  </si>
+  <si>
+    <t>campaign--256cf231-0b45-47ef-8398-143a78d0dbbf</t>
+  </si>
+  <si>
+    <t>campaign--ee36ce57-051f-4c20-8a09-69d43a2c1de6</t>
+  </si>
+  <si>
+    <t>campaign--b7e2e05a-2a56-49bf-af17-f86e431bece0</t>
+  </si>
+  <si>
+    <t>campaign--5cb4ced0-dedd-48cf-82cb-86724811997b</t>
+  </si>
+  <si>
+    <t>campaign--22649a71-e98f-4dce-a1cc-ed19d9c75cee</t>
+  </si>
+  <si>
+    <t>campaign--b3642930-149d-4b8d-ad0d-64d9d7c22e31</t>
+  </si>
+  <si>
+    <t>campaign--41303f5c-3cb5-48f0-afe0-1b97bae4f54b</t>
+  </si>
+  <si>
+    <t>campaign--2d672617-e7ff-4186-b99a-6c0e59b2069d</t>
+  </si>
+  <si>
+    <t>campaign--065b7c0a-b8f7-4351-9b58-96cb67b5bacb</t>
+  </si>
+  <si>
+    <t>campaign--4929ab8d-cac2-4c99-a2b4-d3012a155cfd</t>
+  </si>
+  <si>
+    <t>campaign--168b36b5-425a-4f37-8a93-b1b55d5a1da7</t>
+  </si>
+  <si>
+    <t>campaign--144ec9d9-444e-43fe-9d0e-3a2394ee8b53</t>
+  </si>
+  <si>
+    <t>campaign--65523a6a-2868-4b87-be5d-4ae9b29134b1</t>
+  </si>
+  <si>
+    <t>campaign--fe715480-d6ee-406e-ac1c-97428a212e65</t>
+  </si>
+  <si>
+    <t>campaign--88abdeab-1534-4131-aa37-73e84eb546ae</t>
+  </si>
+  <si>
+    <t>campaign--1c35fcdc-a6e6-4112-aa74-de7560d1bba3</t>
+  </si>
+  <si>
+    <t>campaign--ee0f26e4-d128-460c-9682-7492020544fb</t>
+  </si>
+  <si>
+    <t>campaign--0e177b96-42bc-49d8-a7a4-87d001a7b97d</t>
+  </si>
+  <si>
+    <t>campaign--09aa5cdd-2b55-4270-9ede-505fce974966</t>
+  </si>
+  <si>
+    <t>campaign--4a354ca0-b612-41ae-a22d-d5c6fb7a028a</t>
+  </si>
+  <si>
+    <t>campaign--01263d76-7a3e-4516-b993-39c444830762</t>
+  </si>
+  <si>
+    <t>campaign--513a8978-9c37-43cb-852f-88eaf99d3f6d</t>
+  </si>
+  <si>
+    <t>campaign--e667332a-68bc-4c3b-8f13-e19634de4d9f</t>
+  </si>
+  <si>
+    <t>campaign--65767352-3a24-4af7-a88e-481714d18d9c</t>
+  </si>
+  <si>
+    <t>campaign--54b232b3-84e1-4abc-a84d-f4855390eec4</t>
+  </si>
+  <si>
+    <t>campaign--2750145d-cbe0-49fc-b789-75f9234b1e96</t>
+  </si>
+  <si>
+    <t>campaign--8f92c47c-028b-41e2-b632-00565ffce2c8</t>
   </si>
   <si>
     <t>«Вечный мир» с Польшей (1686)</t>
@@ -974,7 +974,7 @@
     <t>Юридическая легитимация раздела территорий между Московским царством и Речью Посполитой за спиной Гетманщины, окончательно превратившая Украину в бесправный объект торгов. «В 1686 году Россия и Польша подписывают очередной так называемый «вечный мир», по которому уже официально делят Украину между собой. Для Мазепы и всех украинцев это колоссальное унижение». Сделка была закреплена финансово: «Чтобы Польша признала Киев российским навсегда, в 1686 году Москва выплатила ей 146 тысяч рублей серебром» (Citation: Война и наказание: Как Россия уничтожала Украину 2023).</t>
   </si>
   <si>
-    <t>Апогей репрессий при В. Щербицком. Массовые аресты членов Украинской Хельсинкской группы и диссидентов. Для нейтрализации инакомыслящих массово применялась карательная психиатрия — объявление здоровых людей сумасшедшими для их бессрочной изоляции и медикаментозных пыток. Многие правозащитники, включая В. Стуса, так и не вышли на свободу, погибнув в лагерях особого режима. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026)</t>
+    <t>Апогей репрессий при В. Щербицком. Массовые аресты членов Украинской Хельсинкской группы и диссидентов. Для нейтрализации инакомыслящих массово применялась карательная психиатрия — объявление здоровых людей сумасшедшими для их бессрочной изоляции и медикаментозных пыток. Многие правозащитники, включая В. Стуса, так и не вышли на свободу, погибнув в лагерях особого режима. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
   </si>
   <si>
     <t>Исполнение секретных инструкций Екатерины II по институциональной и культурной ассимиляции края. Ликвидация полкового устройства, введение имперских наместничеств, конфискация монастырских земель и окончательное закрепощение свободных украинских крестьян (Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)(Citation: Друга Малоросійська колегія — Вікіпедія 2026).</t>
@@ -2114,22 +2114,22 @@
     <t>31 January 1924</t>
   </si>
   <si>
-    <t>(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Азовські походи (1695—1696),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Азовські походи (1695—1696),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Азовські походи (1695—1696)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026)</t>
+    <t>(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -2150,10 +2150,10 @@
     <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Ліквідація Запорозької Січі (1775)</t>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775)</t>
   </si>
   <si>
     <t>(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026)</t>
@@ -2162,7 +2162,7 @@
     <t>(Citation: Перепис населення Російської імперії (1897),(Citation: Перепис населення Російської імперії (1897),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897)</t>
   </si>
   <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026)</t>
@@ -2171,7 +2171,7 @@
     <t>(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023),(Citation: РАШИЗМ ЗВІР З БЕЗОДНІ 2023)</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: «Рашизм: Звір з безодні» 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: «Рашизм: Звір з безодні» 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Киевский синопсис — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026)</t>
@@ -2180,22 +2180,22 @@
     <t>(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
   </si>
   <si>
-    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
+    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007)</t>
   </si>
   <si>
     <t>(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
   </si>
   <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Крымская война — Википедия 2026),(Citation: Крымская война — Википедия 2026),(Citation: Київська козаччина — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026)</t>
+    <t>(Citation: Крымская война — Википедия 2026),(Citation: Київська козаччина — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Крымская война — Википедия 2026)</t>
   </si>
   <si>
     <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
@@ -2204,7 +2204,7 @@
     <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
+    <t>(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
@@ -2240,7 +2240,7 @@
     <t>(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026)</t>
+    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
   </si>
   <si>
     <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026)</t>
@@ -2255,13 +2255,13 @@
     <t>(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Антикріпосницький рух в Україні (1789-1861)</t>
   </si>
   <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864)</t>
-  </si>
-  <si>
-    <t>(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Норильское восстание - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864)</t>
+  </si>
+  <si>
+    <t>(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Норильское восстание - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026)</t>
@@ -2273,10 +2273,10 @@
     <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна й українці в постімперську добу (1917–1939)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: «Рашизм: Звір з безодні» 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Російсько-українська війна (з 2014),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939)</t>
+  </si>
+  <si>
+    <t>(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
@@ -2294,10 +2294,10 @@
     <t>(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1768—1774)</t>
   </si>
   <si>
-    <t>(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Російсько-турецька війна (1806—1812)</t>
+  </si>
+  <si>
+    <t>(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026)</t>
@@ -2324,7 +2324,7 @@
     <t>(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна й українці в постімперську добу (1917–1939)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Україна й українці в постімперську добу (1917–1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917–1939)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -2441,43 +2441,43 @@
     <t>Имперские Коллегии</t>
   </si>
   <si>
-    <t>tool--0cab0eb6-aab8-491e-87e0-90065cad619f</t>
-  </si>
-  <si>
-    <t>tool--2be11800-685c-4062-97e0-08a0312813c2</t>
-  </si>
-  <si>
-    <t>tool--49b4cf66-92e2-4bfe-9ee7-c7836c48f1bd</t>
-  </si>
-  <si>
-    <t>tool--508817a5-f547-4738-b33f-2073c7e7bb46</t>
-  </si>
-  <si>
-    <t>tool--c318b583-5c74-4d4c-af96-44d2a38cc28b</t>
-  </si>
-  <si>
-    <t>tool--be70b110-ba24-40a9-a494-db8bbac83de8</t>
-  </si>
-  <si>
-    <t>tool--07ed755a-398c-4330-8349-2f5ed4ca4c1c</t>
-  </si>
-  <si>
-    <t>tool--13c02cc3-f597-4c27-b187-bb691a376e8d</t>
-  </si>
-  <si>
-    <t>tool--a284d8f6-38fa-45a8-b856-19580195c4b5</t>
-  </si>
-  <si>
-    <t>tool--8dee1f22-2f1a-49e4-9cd7-3ad55f270afa</t>
-  </si>
-  <si>
-    <t>tool--093e831e-738d-4d35-a139-a2c858be92a3</t>
-  </si>
-  <si>
-    <t>tool--8584cec6-6377-4946-ac42-132e7d9dfc47</t>
-  </si>
-  <si>
-    <t>tool--63c492b1-88b1-4df6-8737-003e09b95b91</t>
+    <t>tool--cdc507d7-2b86-4fd9-9a01-b0172cfc5205</t>
+  </si>
+  <si>
+    <t>tool--229ccd55-af8b-4954-9d37-c01c7b007daf</t>
+  </si>
+  <si>
+    <t>tool--f889d8a2-0000-47c9-b8b3-1a12089eec06</t>
+  </si>
+  <si>
+    <t>tool--ea14cd7b-585a-494b-88e8-d9f8da2455eb</t>
+  </si>
+  <si>
+    <t>tool--88321b03-b598-459c-b69c-53b4cb0ebb20</t>
+  </si>
+  <si>
+    <t>tool--4556118e-edf6-43e4-9cee-24e270ae451e</t>
+  </si>
+  <si>
+    <t>tool--f772df95-d66e-4e57-8645-b8020a451f65</t>
+  </si>
+  <si>
+    <t>tool--72e7409f-63c7-43bd-9414-02a61e50b0b2</t>
+  </si>
+  <si>
+    <t>tool--60e274fe-60d9-44b4-b2e2-19ab1948bd5e</t>
+  </si>
+  <si>
+    <t>tool--f74fade6-c2ba-4cbc-8833-3daf6cc482ae</t>
+  </si>
+  <si>
+    <t>tool--f69553b2-8023-4d84-b754-92e67a665955</t>
+  </si>
+  <si>
+    <t>tool--29369b13-242b-4f23-92f0-f8c810bc8cd4</t>
+  </si>
+  <si>
+    <t>tool--f92083ef-3b0a-455a-a6ca-fc137cb4a6c0</t>
   </si>
   <si>
     <t>software</t>
@@ -2486,7 +2486,7 @@
     <t>Юридическая фиксация раскола страны на две части с превращением Правобережья в буферную зону: «По условиям Вечного мира Правобережье осталось за Польшей... договорили и постановили, что те места оставатись имеют пусты, так как ныне суть» (Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)(Citation: Мазепа 2007).</t>
   </si>
   <si>
-    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026)</t>
+    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
   </si>
   <si>
     <t>Массовые аресты членов Украинской Хельсинкской группы и фабрикация уголовных дел, приведшие к длительной изоляции и гибели видных диссидентов (в том числе Василя Стуса) в лагерях особого режима. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -2630,7 +2630,7 @@
     <t>Публикация В. Путиным манифеста «Об историческом единстве русских и украинцев» (июль 2021), в котором конструируется псевдоисторический миф о том, что современную Украину якобы «создал Ленин», а историческая Россия была искусственно расчленена большевиками. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Тотальная индоктринация российского общества идеями философа И. Ильина (так называемый «белый фашизм») и превращение концепта «Русского мира» в государственную идеологию (рашизм), обосновывающую культурное превосходство и экзистенциальное право метрополии на насилие над соседями. (Citation: «Рашизм: Звір з безодні» 2023)</t>
+    <t>Тотальная индоктринация российского общества идеями философа И. Ильина (так называемый «белый фашизм») и превращение концепта «Русского мира» в государственную идеологию (рашизм), обосновывающую культурное превосходство и экзистенциальное право метрополии на насилие над соседями. (Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
     <t>Для идеологического обоснования захвата и расчленения территорий московские власти инициировали создание нового исторического канона, призванного легитимизировать оккупацию задним числом: «Синопсис, или Краткое собрание от различных летописцев о начале славяно-росийского народа и первоначальных князьях богоспасаемого града Киева» (Citation: Киевский синопсис — Википедия 2026).</t>
@@ -2768,7 +2768,7 @@
     <t>Принудительная инкорпорация автохтонных вооруженных сил в имперскую армию: «перетворення полків на регулярні гусарські» (Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Целенаправленные аресты новой украинской интеллигенции, диссидентов и участников протестов (в т.ч. после премьеры «Теней забытых предков») для подавления зарождающегося сопротивления. (Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) - ХПГ 2026)</t>
+    <t>Целенаправленные аресты новой украинской интеллигенции, диссидентов и участников протестов (в т.ч. после премьеры «Теней забытых предков») для подавления зарождающегося сопротивления. (Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026)</t>
   </si>
   <si>
     <t>Тотальная зачистка украинских институтов на оккупированных территориях Галичины: закрытие газет, преследование деятелей движения, арест и высылка Михаила Грушевского (Citation: Історія України — Вікіпедія 2026) (Citation: Україна в Першій світовій війні — Вікіпедія 2026).</t>
@@ -2804,7 +2804,7 @@
     <t>Использование регулярной армии для силового подавления [Январского восстания](https://ru.wikipedia.org/wiki/Польское_восстание_(1863—1864)). Российское правительство решает силой «искоренить любые предпосылки к самостоятельности» (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Польское восстание (1863—1864) — Википедия 2026).</t>
   </si>
   <si>
-    <t>Зачистка гражданских сообществ: запрет деятельности украинских просветительских громад на Правобережье после подавления восстания (Citation: Історія України — Вікіпедія 2026).</t>
+    <t>Зачистка гражданских сообществ: запрет деятельности украинских просветительских громад на Правобережье после подавления восстания (Citation: Історія України — Вікіпедія 2026).</t>
   </si>
   <si>
     <t>Применение регулярных войск и танков для подавления масштабных бунтов украинских политзаключенных в системе концлагерей (в частности, в Кенгире). (Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
@@ -3017,538 +3017,538 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917–1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--1cdfd3f0-541c-46ef-bbb7-57a694bb8048</t>
-  </si>
-  <si>
-    <t>relationship--d495d79d-34f6-49d9-9a53-82b1b44b932e</t>
-  </si>
-  <si>
-    <t>relationship--c3a1ebf2-6376-41a0-8da9-9559ab938f54</t>
-  </si>
-  <si>
-    <t>relationship--4275b59a-eb45-4ef4-8326-636a04a0ac05</t>
-  </si>
-  <si>
-    <t>relationship--17d269a7-f021-4844-ba97-285385aa5a05</t>
-  </si>
-  <si>
-    <t>relationship--8ff83813-6c82-4ab8-9564-9a97297a517b</t>
-  </si>
-  <si>
-    <t>relationship--e86385b6-78ef-4f5b-b86a-3451ef4fb67a</t>
-  </si>
-  <si>
-    <t>relationship--e7e68ba5-bf1c-4e7b-b4b9-fce42d55812e</t>
-  </si>
-  <si>
-    <t>relationship--4f3a2482-9355-4569-b86a-336d346b028f</t>
-  </si>
-  <si>
-    <t>relationship--d7f85bae-60a9-4a89-962e-bdca90445fd7</t>
-  </si>
-  <si>
-    <t>relationship--f5887284-ec26-4787-96de-d48cb0bdfc1f</t>
-  </si>
-  <si>
-    <t>relationship--11fe4de9-dec3-4e00-b181-ead6b952fe0c</t>
-  </si>
-  <si>
-    <t>relationship--ecf760dd-1173-412c-ad70-81d9e69c6948</t>
-  </si>
-  <si>
-    <t>relationship--1aaa7ddc-9a79-4ed7-85c2-be1a33b6a156</t>
-  </si>
-  <si>
-    <t>relationship--c85a9687-a983-4bbf-ad54-1d226493a38f</t>
-  </si>
-  <si>
-    <t>relationship--fe47f8f9-3736-4608-b9d0-5893ad2c1a20</t>
-  </si>
-  <si>
-    <t>relationship--d5ac8e63-17dd-47cd-81f7-ed9630d5c3ac</t>
-  </si>
-  <si>
-    <t>relationship--3abd1255-9cd6-478b-8fcd-86fa79d7a7d7</t>
-  </si>
-  <si>
-    <t>relationship--b62ca932-d26f-4ee7-ac33-a5a511103bcb</t>
-  </si>
-  <si>
-    <t>relationship--b5699099-cc20-45f1-b5ce-c03e07c2717a</t>
-  </si>
-  <si>
-    <t>relationship--6e2f5430-1f89-48c3-a07b-4a3bf4a5c063</t>
-  </si>
-  <si>
-    <t>relationship--2a69c0df-229f-4cb1-ac1f-3238e18c9baf</t>
-  </si>
-  <si>
-    <t>relationship--a82b5c09-7ce9-44fc-8754-1f4b7c6d6b33</t>
-  </si>
-  <si>
-    <t>relationship--69431d70-4fef-408c-a215-aacb1d4d004d</t>
-  </si>
-  <si>
-    <t>relationship--038a681e-750f-4a0a-b5cb-f0dcef35c08f</t>
-  </si>
-  <si>
-    <t>relationship--1ba8353d-9752-48c5-bf67-b4d140483403</t>
-  </si>
-  <si>
-    <t>relationship--2bc1ff86-36cf-42b9-844b-05f25c23c468</t>
-  </si>
-  <si>
-    <t>relationship--ecc7b820-6f33-43ab-ab90-c682a1be8336</t>
-  </si>
-  <si>
-    <t>relationship--93d90a0a-63ee-4661-8f45-7edc33476ee4</t>
-  </si>
-  <si>
-    <t>relationship--32d85f0d-22c0-41aa-9a04-009cbec9908d</t>
-  </si>
-  <si>
-    <t>relationship--eeaaf694-091d-4a77-a389-8ce77831e4a2</t>
-  </si>
-  <si>
-    <t>relationship--8dbe975d-70a2-4dbf-bc37-047267e4cd6f</t>
-  </si>
-  <si>
-    <t>relationship--b9cae21b-21a4-442b-a5e0-a4177c3e1890</t>
-  </si>
-  <si>
-    <t>relationship--91a138d5-48e6-4841-81f9-f0cfe4e51eb1</t>
-  </si>
-  <si>
-    <t>relationship--5003f1ac-cf34-41b5-b829-f13c40a2e702</t>
-  </si>
-  <si>
-    <t>relationship--88e13235-bafa-4ec6-91bc-c39b564b85da</t>
-  </si>
-  <si>
-    <t>relationship--a0860cd0-758f-4062-be11-c20b22d79471</t>
-  </si>
-  <si>
-    <t>relationship--7ebf24ab-cbe1-436a-afe9-5c16fb858ecf</t>
-  </si>
-  <si>
-    <t>relationship--ea64dad1-2022-47bd-b2a8-b9d96756e301</t>
-  </si>
-  <si>
-    <t>relationship--bb8e0007-4bcb-430c-8611-f195c41eb35a</t>
-  </si>
-  <si>
-    <t>relationship--3e18b328-12eb-4972-9cfe-bd5b4518bba0</t>
-  </si>
-  <si>
-    <t>relationship--46fd9d5f-a9ec-45a6-b954-0759b6c20a85</t>
-  </si>
-  <si>
-    <t>relationship--c24ba103-dbdf-4f6c-9ac9-82676d6029d4</t>
-  </si>
-  <si>
-    <t>relationship--902c7b16-7751-4272-802f-b60a53d1527f</t>
-  </si>
-  <si>
-    <t>relationship--967afc2b-34b6-42e4-b19f-ff55d27f154f</t>
-  </si>
-  <si>
-    <t>relationship--f440f70b-b325-40f3-a514-7388745133c9</t>
-  </si>
-  <si>
-    <t>relationship--633ca8be-925a-4e14-97f8-4994f1ee83e6</t>
-  </si>
-  <si>
-    <t>relationship--780d743b-1356-4890-b4d5-f4b8d0834b72</t>
-  </si>
-  <si>
-    <t>relationship--60f31cc5-629b-4d37-9a05-00641db8c720</t>
-  </si>
-  <si>
-    <t>relationship--cdc12329-4f34-4ad3-8299-fa8f7ce39bc4</t>
-  </si>
-  <si>
-    <t>relationship--d70cd8dc-7476-4c3e-8cfa-ac68ca5d402e</t>
-  </si>
-  <si>
-    <t>relationship--fdc13399-0dc4-42c2-a70c-764aa1293fc0</t>
-  </si>
-  <si>
-    <t>relationship--47e10c42-9a84-45f5-b104-fb5324ebf8c7</t>
-  </si>
-  <si>
-    <t>relationship--a1220d18-cbde-4f2e-9889-a8a2e18f394b</t>
-  </si>
-  <si>
-    <t>relationship--34433281-ac06-431b-bd5f-2213d1e4da91</t>
-  </si>
-  <si>
-    <t>relationship--c5abc27a-dc5a-405b-ae79-769efb4e10e9</t>
-  </si>
-  <si>
-    <t>relationship--0e6f0900-a388-4c25-a11d-378f3cae1130</t>
-  </si>
-  <si>
-    <t>relationship--b5cd62b4-dea8-4068-a0fa-e55b018ea237</t>
-  </si>
-  <si>
-    <t>relationship--9404262b-dc1c-4696-be6c-fad1aa7554c7</t>
-  </si>
-  <si>
-    <t>relationship--276a166b-5637-43b3-aeb9-77c877438848</t>
-  </si>
-  <si>
-    <t>relationship--f2c4cec2-d81e-4dca-a191-e35842b29fd2</t>
-  </si>
-  <si>
-    <t>relationship--87a894f3-208c-452c-862e-a9d9b4c102b2</t>
-  </si>
-  <si>
-    <t>relationship--66bbd274-033a-4f63-a101-1a6ab18b7bd2</t>
-  </si>
-  <si>
-    <t>relationship--c80e0195-3fbb-45e9-b72d-74a151137581</t>
-  </si>
-  <si>
-    <t>relationship--60f800c4-5d5d-4d39-bfb8-ca8aa4638e4b</t>
-  </si>
-  <si>
-    <t>relationship--c0644e3b-a1a9-485d-ad11-82c755d2687b</t>
-  </si>
-  <si>
-    <t>relationship--b58d72ea-68d4-4083-9fa3-a22add914005</t>
-  </si>
-  <si>
-    <t>relationship--eebe6013-7f34-4d64-9822-b18a454d0d10</t>
-  </si>
-  <si>
-    <t>relationship--c0baffae-39e5-4ca8-85e9-bc702c8dcfba</t>
-  </si>
-  <si>
-    <t>relationship--695a9636-88ca-4dd3-b589-942963e4156f</t>
-  </si>
-  <si>
-    <t>relationship--e88bdaef-60f1-4119-964e-01f69f60bb51</t>
-  </si>
-  <si>
-    <t>relationship--b1c69f86-8c7c-4af6-88d3-b19e3c5e2fba</t>
-  </si>
-  <si>
-    <t>relationship--dffb6d3f-25b1-4514-83ae-cc167e523d72</t>
-  </si>
-  <si>
-    <t>relationship--11029e5c-57ac-46ae-8f08-6bca2acbc93e</t>
-  </si>
-  <si>
-    <t>relationship--7ce5ed6e-610b-4ae3-b4be-bbf7dfc9e166</t>
-  </si>
-  <si>
-    <t>relationship--61ae46e5-0b72-42ac-be14-0b1ea28d9423</t>
-  </si>
-  <si>
-    <t>relationship--434436ae-32d9-47bc-b0dd-22bec94579cc</t>
-  </si>
-  <si>
-    <t>relationship--f0488f83-03a7-4d16-9837-511b214e8ec9</t>
-  </si>
-  <si>
-    <t>relationship--50900495-ce2f-4374-8aac-dc046af7894d</t>
-  </si>
-  <si>
-    <t>relationship--56c2e33c-ff02-45cf-997e-e185fb8284d5</t>
-  </si>
-  <si>
-    <t>relationship--cd07c225-e684-4721-87a0-cca930a0df0b</t>
-  </si>
-  <si>
-    <t>relationship--625be509-1c87-4659-96ea-444501a59ebc</t>
-  </si>
-  <si>
-    <t>relationship--f8dcd5fe-c1b4-44ca-b402-373dfc5417ae</t>
-  </si>
-  <si>
-    <t>relationship--4e783095-de36-446d-831c-48bb2b0b1b02</t>
-  </si>
-  <si>
-    <t>relationship--0b74edca-140c-4e19-b47d-aa12c64ed50b</t>
-  </si>
-  <si>
-    <t>relationship--130424c7-894e-4b77-a1b6-7d68a7fbb786</t>
-  </si>
-  <si>
-    <t>relationship--914ac410-74b1-4d63-95d9-6dd9b8c71eca</t>
-  </si>
-  <si>
-    <t>relationship--79050ddd-6640-4e75-b080-e475b0d8975b</t>
-  </si>
-  <si>
-    <t>relationship--ce1bf1e0-dc9f-40bb-a42c-30efd808e3b1</t>
-  </si>
-  <si>
-    <t>relationship--e74de5ee-3f90-4b88-8422-e3ba16f5bdf6</t>
-  </si>
-  <si>
-    <t>relationship--506a1a08-e298-4edf-b8c0-5657fc9e45a7</t>
-  </si>
-  <si>
-    <t>relationship--c07440af-65cd-4234-a5e8-d42c0529a636</t>
-  </si>
-  <si>
-    <t>relationship--210deede-586f-494b-a4f2-7a313d2e5469</t>
-  </si>
-  <si>
-    <t>relationship--aa93a03f-3dd5-4f2e-b15e-db1651483c9b</t>
-  </si>
-  <si>
-    <t>relationship--2051de94-1c9d-4463-98aa-438798808410</t>
-  </si>
-  <si>
-    <t>relationship--51f7a69a-2e4a-4d10-a03d-11900999275c</t>
-  </si>
-  <si>
-    <t>relationship--46546620-8293-410c-ad64-a773cab1f209</t>
-  </si>
-  <si>
-    <t>relationship--ad420e9a-6920-4f5f-925d-523ea56a45e9</t>
-  </si>
-  <si>
-    <t>relationship--7acc1852-4ef0-40ef-b37c-c8f2f9fac56e</t>
-  </si>
-  <si>
-    <t>relationship--758e247d-f39c-46ac-8cef-bdddf76bc9d9</t>
-  </si>
-  <si>
-    <t>relationship--bd03b7b2-94b0-4219-9416-bf901b225690</t>
-  </si>
-  <si>
-    <t>relationship--42fb59ab-4d4c-41bf-926d-4a4bc95bf45c</t>
-  </si>
-  <si>
-    <t>relationship--cacfc402-9f00-4407-a735-ab09e75094a4</t>
-  </si>
-  <si>
-    <t>relationship--87d649c2-7d7e-4f10-b90b-ed6475279488</t>
-  </si>
-  <si>
-    <t>relationship--6f1756f2-1539-43cb-9996-33580fb9e881</t>
-  </si>
-  <si>
-    <t>relationship--153a2818-cc0b-4f35-9cc4-0a2e217995e6</t>
-  </si>
-  <si>
-    <t>relationship--6d8a5ae3-cc8f-40c3-8811-6a3bf10f557e</t>
-  </si>
-  <si>
-    <t>relationship--60a19e2e-729e-4de3-a802-826a2782bb59</t>
-  </si>
-  <si>
-    <t>relationship--ee60bad0-c865-4880-b61d-cd448625421c</t>
-  </si>
-  <si>
-    <t>relationship--c3785308-59c1-4f4e-ba70-1882ca413e0f</t>
-  </si>
-  <si>
-    <t>relationship--475be7dc-0bc6-4a77-a1d9-a878992a9f19</t>
-  </si>
-  <si>
-    <t>relationship--e2206cb5-af2c-49e8-ba91-2f4054442efc</t>
-  </si>
-  <si>
-    <t>relationship--3ef2fca5-cdc7-468a-8d50-f31920d1fee4</t>
-  </si>
-  <si>
-    <t>relationship--646d6b42-11a6-45fd-8542-6d2b46c09280</t>
-  </si>
-  <si>
-    <t>relationship--d4e46347-6d3c-4959-8927-94fd180da28d</t>
-  </si>
-  <si>
-    <t>relationship--32e0e1bf-6626-47ca-a8d0-c2372e080abe</t>
-  </si>
-  <si>
-    <t>relationship--e9e83d95-bffe-40a5-b5ba-aa0ec6dca05f</t>
-  </si>
-  <si>
-    <t>relationship--2951b2fa-de71-492a-9d6f-80e5a9f1d972</t>
-  </si>
-  <si>
-    <t>relationship--2e4721a4-2bde-486a-858e-0db6024a79b1</t>
-  </si>
-  <si>
-    <t>relationship--8b7392e1-b6ba-4cd8-8ca3-e7682da3c3d2</t>
-  </si>
-  <si>
-    <t>relationship--07e1f68a-0a5c-48b2-86a9-e2c9da36c3f6</t>
-  </si>
-  <si>
-    <t>relationship--7a9605db-5367-4646-bddc-3c9c4a4845e3</t>
-  </si>
-  <si>
-    <t>relationship--ad4315eb-e04b-4f42-b869-d0b9c5583b24</t>
-  </si>
-  <si>
-    <t>relationship--f0715d2a-127e-4a91-8afa-eb98e9855e0d</t>
-  </si>
-  <si>
-    <t>relationship--e1ca466a-14e1-4bdc-a9b4-3a82d16573b2</t>
-  </si>
-  <si>
-    <t>relationship--c5b841c9-1fbc-47f5-ac79-d1ee7a652b27</t>
-  </si>
-  <si>
-    <t>relationship--bc9989b6-c70a-4741-aee6-eadad2f7f632</t>
-  </si>
-  <si>
-    <t>relationship--21e5d65f-f85b-4717-b1d3-ba74ff6f0752</t>
-  </si>
-  <si>
-    <t>relationship--b90729d8-7dd4-4708-8496-8418c70e4971</t>
-  </si>
-  <si>
-    <t>relationship--40de2cbe-a25c-482e-9c27-44904b5ecb02</t>
-  </si>
-  <si>
-    <t>relationship--0b2249dd-99ec-4fc6-85bc-fbc274f259e5</t>
-  </si>
-  <si>
-    <t>relationship--6798be57-0f6e-47c8-b8d2-f58d9d149764</t>
-  </si>
-  <si>
-    <t>relationship--ba31761f-897b-4f8f-968a-e59925f8d6fa</t>
-  </si>
-  <si>
-    <t>relationship--91aa061c-0ed0-46c3-abc1-441bcb58d942</t>
-  </si>
-  <si>
-    <t>relationship--9bb17497-5ced-46d4-8e49-19478609770e</t>
-  </si>
-  <si>
-    <t>relationship--f32b2650-c2d7-4d69-8d67-18d8b776f9e8</t>
-  </si>
-  <si>
-    <t>relationship--a7cc2842-95fa-49f7-afc5-e5fba2503da4</t>
-  </si>
-  <si>
-    <t>relationship--f9481fe5-2017-4a84-9bc1-d2e3d995b101</t>
-  </si>
-  <si>
-    <t>relationship--26b8177c-dc31-4935-b650-c23f16e1961a</t>
-  </si>
-  <si>
-    <t>relationship--6844cf1e-add2-4a34-bfe0-3347bafc0a9f</t>
-  </si>
-  <si>
-    <t>relationship--e5b5c765-82fe-4964-aead-5414f522b718</t>
-  </si>
-  <si>
-    <t>relationship--c5af5ee1-c2d4-40cc-b7b6-ae4abaff53b6</t>
-  </si>
-  <si>
-    <t>relationship--a7e785d3-d07b-4e9a-bb4d-ef89ea1a9f5f</t>
-  </si>
-  <si>
-    <t>relationship--ee6d5d17-128a-440b-af31-6ae771a8292d</t>
-  </si>
-  <si>
-    <t>relationship--e9778606-9150-4f14-b119-01e6b1e85502</t>
-  </si>
-  <si>
-    <t>relationship--14a32943-f91e-48c3-8ee9-8ad808687bc1</t>
-  </si>
-  <si>
-    <t>relationship--12cd06be-5eff-42d6-acbb-a89a987992dc</t>
-  </si>
-  <si>
-    <t>relationship--d0ebd6a9-9219-480c-beac-b1fe4801880b</t>
-  </si>
-  <si>
-    <t>relationship--194539c1-2cf8-4240-bcbf-24a8064f6b8b</t>
-  </si>
-  <si>
-    <t>relationship--84f966a1-0e37-4246-ab85-33e30d8439bf</t>
-  </si>
-  <si>
-    <t>relationship--af457245-7456-45e2-b0f5-ffb032c38189</t>
-  </si>
-  <si>
-    <t>relationship--74e76fa7-fa51-41c4-9307-dfcd67a3fff5</t>
-  </si>
-  <si>
-    <t>relationship--b4b9ece4-7fca-4d13-b796-f780283e170c</t>
-  </si>
-  <si>
-    <t>relationship--cb18f39c-b72f-434d-b0ba-2f9469c2e3a9</t>
-  </si>
-  <si>
-    <t>relationship--f1ce89a9-70cd-4b29-945c-3f0e75e93323</t>
-  </si>
-  <si>
-    <t>relationship--94c1394f-ff7d-4eec-b6be-47b1198c0831</t>
-  </si>
-  <si>
-    <t>relationship--4dafb5e2-1c32-48fd-a176-ff2384d8ad4c</t>
-  </si>
-  <si>
-    <t>relationship--75dfd531-7cf6-4fcd-a4a5-bc9b434c5929</t>
-  </si>
-  <si>
-    <t>relationship--005eea82-2f46-4916-8974-19efe9a0a2db</t>
-  </si>
-  <si>
-    <t>relationship--84ad2176-58e3-46ac-b6b8-c13c7003204c</t>
-  </si>
-  <si>
-    <t>relationship--062e6e55-26ed-441a-9fb9-12a14eee63a8</t>
-  </si>
-  <si>
-    <t>relationship--510d4bcb-7a47-493f-ba01-cb1758383dc6</t>
-  </si>
-  <si>
-    <t>relationship--847ad2f4-da00-4510-a9c3-2c433ac3c7af</t>
-  </si>
-  <si>
-    <t>relationship--9b53807b-e85c-4c3e-b896-741f3120f8f8</t>
-  </si>
-  <si>
-    <t>relationship--159acf55-c89e-4b96-ac79-c109e70b6d50</t>
-  </si>
-  <si>
-    <t>relationship--085707c3-a1f3-49ed-96a6-925b6a1df8a3</t>
-  </si>
-  <si>
-    <t>relationship--3a3ad8b1-a0c1-4f39-a1f6-6e363ff281ad</t>
-  </si>
-  <si>
-    <t>relationship--c75a8d56-a880-48b5-b10b-3cca05274dae</t>
-  </si>
-  <si>
-    <t>relationship--10f99ae2-c75c-47da-893b-cfd21283673b</t>
-  </si>
-  <si>
-    <t>relationship--c0ee9936-c01c-454c-b1d4-ea76e1334b76</t>
-  </si>
-  <si>
-    <t>relationship--c51902d5-3216-4c0a-92d4-755ba6e18971</t>
-  </si>
-  <si>
-    <t>relationship--74e4be03-35a9-4b2b-bb31-5ee352fbfe4b</t>
-  </si>
-  <si>
-    <t>relationship--e14de57d-3551-48b7-b7fa-4f0c4f9c8ad6</t>
-  </si>
-  <si>
-    <t>relationship--026a5211-c9ca-427e-b85b-31369a0515b5</t>
-  </si>
-  <si>
-    <t>relationship--0fa3717a-abec-48e7-bf72-de0846014da8</t>
-  </si>
-  <si>
-    <t>relationship--787e5842-1c07-4a27-a240-39e502105e39</t>
-  </si>
-  <si>
-    <t>relationship--9e8b6ddb-22d8-48dd-a284-a1fc3fb4f706</t>
-  </si>
-  <si>
-    <t>relationship--6c36f8a8-3b33-43c5-bce4-9e382648a9fa</t>
+    <t>relationship--441881a9-009f-4fee-a84f-69e4dab72d5c</t>
+  </si>
+  <si>
+    <t>relationship--407bea55-52b8-4513-b233-41b08397fbe1</t>
+  </si>
+  <si>
+    <t>relationship--fc7d4fd2-bc39-4034-9208-2c0620054b59</t>
+  </si>
+  <si>
+    <t>relationship--c558e80f-a8c2-437d-9ade-a0f376fe7e79</t>
+  </si>
+  <si>
+    <t>relationship--9b0fbe4c-0035-4a4b-a8d7-10f2cce3df63</t>
+  </si>
+  <si>
+    <t>relationship--b0694f7a-56c9-4c82-a43a-81af0a4f3bb9</t>
+  </si>
+  <si>
+    <t>relationship--d6d8e6e8-b3e8-46ca-b8ac-642e0a298f3a</t>
+  </si>
+  <si>
+    <t>relationship--4b7a94b8-42f2-49cd-a391-8e8f4e99c93b</t>
+  </si>
+  <si>
+    <t>relationship--961f8807-6832-4dc3-a94c-cb50484d6d4f</t>
+  </si>
+  <si>
+    <t>relationship--57e2158b-8a11-4f88-b7be-e2145f4a8414</t>
+  </si>
+  <si>
+    <t>relationship--7612f698-4e79-4079-bb58-7f9dd7632c89</t>
+  </si>
+  <si>
+    <t>relationship--e50a2e6b-8ff6-45d0-a644-acbe67737007</t>
+  </si>
+  <si>
+    <t>relationship--7e1ed3b9-48bc-440f-9642-35a01ae689d0</t>
+  </si>
+  <si>
+    <t>relationship--b644ebfa-43b6-4469-accc-7b28e9870fdd</t>
+  </si>
+  <si>
+    <t>relationship--a2676ea5-5fb6-4831-bed3-0c639585820a</t>
+  </si>
+  <si>
+    <t>relationship--5b45a746-3a8b-4c4e-a51c-dce4b3364093</t>
+  </si>
+  <si>
+    <t>relationship--7273265b-2eeb-42fc-a808-8abcf8b2b615</t>
+  </si>
+  <si>
+    <t>relationship--3838bffd-1e3e-4887-aa0b-14734c4ec124</t>
+  </si>
+  <si>
+    <t>relationship--e60441a0-fec1-41d5-a7d7-2c45407cac67</t>
+  </si>
+  <si>
+    <t>relationship--5b876a2f-7dd3-4088-bf8f-bd2b1edf7028</t>
+  </si>
+  <si>
+    <t>relationship--3011500f-0a55-413c-8d8c-9d7caf1bfc3b</t>
+  </si>
+  <si>
+    <t>relationship--a138e90f-cfd8-4675-933a-666be4ce0dfd</t>
+  </si>
+  <si>
+    <t>relationship--6321420c-7f8a-4134-ac3a-24cd8e083e27</t>
+  </si>
+  <si>
+    <t>relationship--57fb9d6f-4241-4202-9128-7d51c0385fbc</t>
+  </si>
+  <si>
+    <t>relationship--d9487cc0-d30b-42b0-933f-7daa67a4d305</t>
+  </si>
+  <si>
+    <t>relationship--781440d6-1c17-413a-b7dc-ca8a39850699</t>
+  </si>
+  <si>
+    <t>relationship--4bef0001-77f5-465c-abf3-0d402b77ace8</t>
+  </si>
+  <si>
+    <t>relationship--c7486468-93f2-4754-a50c-16283298d211</t>
+  </si>
+  <si>
+    <t>relationship--f9dd9271-ea96-4ff7-b724-681af78a04e7</t>
+  </si>
+  <si>
+    <t>relationship--dbd9631b-2f68-4370-9b80-c1089da85d5d</t>
+  </si>
+  <si>
+    <t>relationship--a7bdb3f3-64fc-45f0-b3a9-1ba82698426d</t>
+  </si>
+  <si>
+    <t>relationship--00bb7bc3-1a65-49d9-91b3-2450fc194238</t>
+  </si>
+  <si>
+    <t>relationship--2fad882f-decd-4932-a722-ef77eb92437c</t>
+  </si>
+  <si>
+    <t>relationship--b6eb1c53-17ef-4a3b-a873-cf14b724f163</t>
+  </si>
+  <si>
+    <t>relationship--6175913f-69fb-4a98-b3b8-bbaa760f13be</t>
+  </si>
+  <si>
+    <t>relationship--a6368f7a-9b39-4475-84d7-276b0d039abe</t>
+  </si>
+  <si>
+    <t>relationship--60bebbf9-8e9f-4a42-9491-0bc43bbf4d17</t>
+  </si>
+  <si>
+    <t>relationship--f4604e84-a2b2-4f14-91ff-195750ee404e</t>
+  </si>
+  <si>
+    <t>relationship--74e179a8-6abe-4ea7-af21-b6592b6b8890</t>
+  </si>
+  <si>
+    <t>relationship--f5f2de92-6fc7-42bd-b3a8-217af9374e86</t>
+  </si>
+  <si>
+    <t>relationship--83cdbbf8-7a00-4751-9447-3833cb0cacfc</t>
+  </si>
+  <si>
+    <t>relationship--8b91af60-3fee-4992-9550-3e9e979cf5b2</t>
+  </si>
+  <si>
+    <t>relationship--813b29fc-9542-49f0-b7d6-d85caac81af1</t>
+  </si>
+  <si>
+    <t>relationship--b3283625-fa86-4cf5-aa10-0ded7dbcb529</t>
+  </si>
+  <si>
+    <t>relationship--0811f3c0-1321-4781-802f-97b87c5afaa3</t>
+  </si>
+  <si>
+    <t>relationship--1d8d1b56-f5f2-4999-920a-cfb7f9f56594</t>
+  </si>
+  <si>
+    <t>relationship--751638bf-cebc-4abf-860a-a7c1c08da3c0</t>
+  </si>
+  <si>
+    <t>relationship--0f0c0423-83ee-4518-9de1-30d4302248d4</t>
+  </si>
+  <si>
+    <t>relationship--b7b482f4-4d21-44c5-9ce6-c605f47bdde4</t>
+  </si>
+  <si>
+    <t>relationship--917b2898-4587-4f51-a21f-6ff22db57b1e</t>
+  </si>
+  <si>
+    <t>relationship--2825feda-f6cd-42e9-b930-ee0e52daf77a</t>
+  </si>
+  <si>
+    <t>relationship--1ac52934-fe96-4ed7-86fe-e3ee711af5e9</t>
+  </si>
+  <si>
+    <t>relationship--c8737263-bf11-425d-91dd-55d0f549bfcb</t>
+  </si>
+  <si>
+    <t>relationship--07b70a83-2609-4c90-8909-9baa1f31f740</t>
+  </si>
+  <si>
+    <t>relationship--cbbd604a-0e5d-42e5-98c5-d38f4719f206</t>
+  </si>
+  <si>
+    <t>relationship--9136c6c2-0744-4a54-8d09-5f4caecb5cde</t>
+  </si>
+  <si>
+    <t>relationship--2868298e-2343-4014-a92f-2d33a27f0baa</t>
+  </si>
+  <si>
+    <t>relationship--b612f9af-4857-41e8-a956-2eca718f33df</t>
+  </si>
+  <si>
+    <t>relationship--8af6a667-ed82-4d95-9a4d-1607edd3f8a1</t>
+  </si>
+  <si>
+    <t>relationship--f5d1dea0-93dc-4ac9-b4ce-accf7602a45f</t>
+  </si>
+  <si>
+    <t>relationship--3ad90ba9-4488-46e0-a3ec-17bd34367b66</t>
+  </si>
+  <si>
+    <t>relationship--0daf0622-2f9b-4ac7-9aef-053994bded64</t>
+  </si>
+  <si>
+    <t>relationship--9f2d31c8-f2d9-4759-b736-d11d86178f4f</t>
+  </si>
+  <si>
+    <t>relationship--890d8899-b99a-479e-be08-dfb3daca60da</t>
+  </si>
+  <si>
+    <t>relationship--d404fecc-e9e3-404b-b30d-f00b42103b51</t>
+  </si>
+  <si>
+    <t>relationship--07f4735b-2a05-4307-97ad-0ff4415765a0</t>
+  </si>
+  <si>
+    <t>relationship--f1f57dce-f052-4f8e-a2f5-03d7751c58fa</t>
+  </si>
+  <si>
+    <t>relationship--93f11158-e77e-4fa4-bd95-5728ab2a8113</t>
+  </si>
+  <si>
+    <t>relationship--5df2074b-c8a0-4157-b089-75337e602753</t>
+  </si>
+  <si>
+    <t>relationship--f447b07a-9053-4453-aaf8-9c9ea45c45c5</t>
+  </si>
+  <si>
+    <t>relationship--be1b4978-dc1b-4f3c-8662-47ff662c36d6</t>
+  </si>
+  <si>
+    <t>relationship--b5841b12-d9f7-403a-8a50-78a27bfb9637</t>
+  </si>
+  <si>
+    <t>relationship--9afdae70-50ff-49fb-8225-e5b90c0b7a58</t>
+  </si>
+  <si>
+    <t>relationship--9b2ebf13-bbfd-4b19-a9e7-af835e586c97</t>
+  </si>
+  <si>
+    <t>relationship--9780392f-c787-47d4-9a1e-e1c1cf64ac87</t>
+  </si>
+  <si>
+    <t>relationship--e322cdd6-030e-4540-a15c-8d503576b6b9</t>
+  </si>
+  <si>
+    <t>relationship--4c6f4f3e-53d8-4424-af5c-ccd1a3a988b3</t>
+  </si>
+  <si>
+    <t>relationship--5e4dae36-7bf6-4af9-9c2e-d5352b1d6114</t>
+  </si>
+  <si>
+    <t>relationship--8697ca8e-9f1f-4407-925d-a68046c1c2c8</t>
+  </si>
+  <si>
+    <t>relationship--718f9d9c-6317-4a19-b6bd-8d258d006860</t>
+  </si>
+  <si>
+    <t>relationship--da549cde-da67-4e1f-915f-09b238dc04ec</t>
+  </si>
+  <si>
+    <t>relationship--bb8a48ae-aa01-4454-a12e-ed18437b96a8</t>
+  </si>
+  <si>
+    <t>relationship--3dcb809b-592f-4127-ac8c-8de9bc67cec6</t>
+  </si>
+  <si>
+    <t>relationship--4c540dc0-b860-4ac0-b792-993e3cd0aab8</t>
+  </si>
+  <si>
+    <t>relationship--a0826615-5551-4d3d-9f6b-e703807aae14</t>
+  </si>
+  <si>
+    <t>relationship--132041e5-ed6d-4e6c-aade-210229974629</t>
+  </si>
+  <si>
+    <t>relationship--67096cdb-92e3-4272-b1e8-546a902485c0</t>
+  </si>
+  <si>
+    <t>relationship--9e8f67e4-47db-449a-b6f7-a63170c53dc7</t>
+  </si>
+  <si>
+    <t>relationship--46b68874-1f2f-43a7-863c-90e55d9734bd</t>
+  </si>
+  <si>
+    <t>relationship--abb7e5c8-7b40-42fb-90e2-9bc557f5f67f</t>
+  </si>
+  <si>
+    <t>relationship--5c36eb4a-457e-4a46-ab2d-4cc902dda01e</t>
+  </si>
+  <si>
+    <t>relationship--762b0536-840f-46d5-86c2-97e1f4487006</t>
+  </si>
+  <si>
+    <t>relationship--2e12471b-3432-438d-adf1-9e2ab4053a60</t>
+  </si>
+  <si>
+    <t>relationship--2ac7264f-d24c-4c49-9ce7-c27d0b872ab6</t>
+  </si>
+  <si>
+    <t>relationship--5638a773-0cb3-4bbb-b24c-273c8817a364</t>
+  </si>
+  <si>
+    <t>relationship--12960d4d-8926-4ac5-af99-14db2dd9cee8</t>
+  </si>
+  <si>
+    <t>relationship--78e20bd1-2285-4dae-b5b2-a7983a786965</t>
+  </si>
+  <si>
+    <t>relationship--d3e23368-e5d8-4f94-aa52-413d60355cc5</t>
+  </si>
+  <si>
+    <t>relationship--dd230c6e-165b-4696-bdf3-782fd5285305</t>
+  </si>
+  <si>
+    <t>relationship--6d29f5ca-d360-43b4-a3ed-250c47e735ef</t>
+  </si>
+  <si>
+    <t>relationship--b09e905f-2b9c-4372-8c3e-fb2b49a913f5</t>
+  </si>
+  <si>
+    <t>relationship--90c464bb-bc62-4073-85ba-a201cb8b595e</t>
+  </si>
+  <si>
+    <t>relationship--4925bc85-a414-4035-832d-1d33ac5fa39e</t>
+  </si>
+  <si>
+    <t>relationship--4a65083f-36e3-4f13-a4d8-be9b52bf5fc0</t>
+  </si>
+  <si>
+    <t>relationship--304e95a0-6dd4-47ff-934b-4f0d7348b944</t>
+  </si>
+  <si>
+    <t>relationship--d2bdc03f-4476-4881-a541-1588fba0f385</t>
+  </si>
+  <si>
+    <t>relationship--805cc33d-f3ec-4c22-a0c5-5df17b7cbfb9</t>
+  </si>
+  <si>
+    <t>relationship--2abda4bd-6317-4cb6-924f-4e224e08ac1e</t>
+  </si>
+  <si>
+    <t>relationship--b43f380a-aa32-481a-9b24-037eb5b38f99</t>
+  </si>
+  <si>
+    <t>relationship--52675a0d-26a3-4b64-aa61-52a2056ae15c</t>
+  </si>
+  <si>
+    <t>relationship--e510f063-e11d-4317-ba14-1f87a6460b67</t>
+  </si>
+  <si>
+    <t>relationship--55591725-3491-422a-af15-c02e3bc5fb94</t>
+  </si>
+  <si>
+    <t>relationship--2dd7c50e-1819-46ca-9396-51cdb484f7aa</t>
+  </si>
+  <si>
+    <t>relationship--caf85b66-0b95-4d45-8ac1-84b6e4ebf785</t>
+  </si>
+  <si>
+    <t>relationship--288214cb-c73d-4f1e-927b-05a37e2453b0</t>
+  </si>
+  <si>
+    <t>relationship--6aa37a01-a801-45f0-a20a-7751db643b6d</t>
+  </si>
+  <si>
+    <t>relationship--0d1fc3e4-d8b3-4e98-a93d-fd3f90915d36</t>
+  </si>
+  <si>
+    <t>relationship--22623415-7c83-4632-bc56-9caeb313f36c</t>
+  </si>
+  <si>
+    <t>relationship--a9e00f4b-a679-4509-a041-87a902b91e02</t>
+  </si>
+  <si>
+    <t>relationship--3409df06-8599-4282-8ed0-e820a152383b</t>
+  </si>
+  <si>
+    <t>relationship--86bf5a2e-684d-4fd7-9477-de3c9a619a4a</t>
+  </si>
+  <si>
+    <t>relationship--d576c757-7f1f-43e8-bc1b-f8cb73428c43</t>
+  </si>
+  <si>
+    <t>relationship--04e7c1ff-1012-404b-b3ad-e98d8843ffa2</t>
+  </si>
+  <si>
+    <t>relationship--36b34d55-9914-4c75-b7fc-565891a12cc2</t>
+  </si>
+  <si>
+    <t>relationship--cf73e4cc-b8ff-44d1-9c57-3e82caeef378</t>
+  </si>
+  <si>
+    <t>relationship--f585c65b-6983-48f9-a53b-2f7fb7d68f36</t>
+  </si>
+  <si>
+    <t>relationship--5e4f1d76-4a8e-44d9-a9d7-48b44bfc73cb</t>
+  </si>
+  <si>
+    <t>relationship--d14dbb7c-7a09-4a21-8b8d-98a33df3e20d</t>
+  </si>
+  <si>
+    <t>relationship--3210750f-ed45-4edc-ac7e-cc55c042046b</t>
+  </si>
+  <si>
+    <t>relationship--cb4ddc60-71cd-4eac-8132-94f3468d8fe6</t>
+  </si>
+  <si>
+    <t>relationship--8d4cdc65-64eb-4e30-b6e4-a0ec6a72f846</t>
+  </si>
+  <si>
+    <t>relationship--c98e2e93-8511-4dc3-ac72-4b0903d5ccc1</t>
+  </si>
+  <si>
+    <t>relationship--da032b93-902c-49d4-b8cb-9d1553699b74</t>
+  </si>
+  <si>
+    <t>relationship--25889eda-19fb-4ed7-803c-763e1a7a7b26</t>
+  </si>
+  <si>
+    <t>relationship--e84bf0ea-af23-4787-a5a6-a72d0d16f927</t>
+  </si>
+  <si>
+    <t>relationship--7bd172c9-3e04-42c6-9602-d5f2158880c7</t>
+  </si>
+  <si>
+    <t>relationship--3a61fd94-bc71-47e3-a578-ff29a1decaef</t>
+  </si>
+  <si>
+    <t>relationship--0391717a-029b-486d-80c8-08787e305aef</t>
+  </si>
+  <si>
+    <t>relationship--79180226-0bf3-49ee-8c4d-cba479e72236</t>
+  </si>
+  <si>
+    <t>relationship--cdaaeb34-75ee-42a4-9666-f14f74502646</t>
+  </si>
+  <si>
+    <t>relationship--a737ce26-ab27-43ee-9cb0-431b3cdffaf4</t>
+  </si>
+  <si>
+    <t>relationship--21301ffa-1e23-47af-aa68-a3450f199bfa</t>
+  </si>
+  <si>
+    <t>relationship--37682e0d-76fa-487b-8bc0-ae6238b763ee</t>
+  </si>
+  <si>
+    <t>relationship--dfaa1d89-6e3b-4130-b1f8-11cbb0027e79</t>
+  </si>
+  <si>
+    <t>relationship--92c9ff8e-3781-4d02-9662-d6991e6e9d37</t>
+  </si>
+  <si>
+    <t>relationship--be07c2e6-6261-44d2-bc83-e6e04630c204</t>
+  </si>
+  <si>
+    <t>relationship--da8dd423-80b8-41fc-9a3b-89b56d0c70f7</t>
+  </si>
+  <si>
+    <t>relationship--3a5d0d2f-eae1-4c3d-9e82-831b8e45fe96</t>
+  </si>
+  <si>
+    <t>relationship--58da3d5c-9f22-4eb1-8fa0-9e3839a8c93d</t>
+  </si>
+  <si>
+    <t>relationship--57091e5d-9bba-4e83-bbcb-cf292c2ff158</t>
+  </si>
+  <si>
+    <t>relationship--7c88bce6-dd2e-4328-889a-991ca4996a38</t>
+  </si>
+  <si>
+    <t>relationship--aad938fe-6411-4b9c-bea1-46f98ee0686e</t>
+  </si>
+  <si>
+    <t>relationship--48e1bb2c-4c2b-43f9-9f02-6fbe777e68b7</t>
+  </si>
+  <si>
+    <t>relationship--7059bef7-58be-4188-96b9-50a70f8cb9e2</t>
+  </si>
+  <si>
+    <t>relationship--3398d3d3-0037-4f35-bb48-2088250200e2</t>
+  </si>
+  <si>
+    <t>relationship--bc841a9c-6502-4865-91c5-00ba71e7da19</t>
+  </si>
+  <si>
+    <t>relationship--4d058eb2-0689-44d7-9be7-4d3a0bae4ef1</t>
+  </si>
+  <si>
+    <t>relationship--28a8b3b6-c862-456c-b28a-d5333961be22</t>
+  </si>
+  <si>
+    <t>relationship--e8fe1d3d-d0d9-4f86-9c5d-6284b4ec4182</t>
+  </si>
+  <si>
+    <t>relationship--0039a511-54e6-4a57-8a3b-05ab6a13e667</t>
+  </si>
+  <si>
+    <t>relationship--6ec2c473-2c58-49c4-b086-380209da8aef</t>
+  </si>
+  <si>
+    <t>relationship--767b6cc7-96f4-4fbe-aec0-eaf007da9ff5</t>
+  </si>
+  <si>
+    <t>relationship--50bda0bd-4368-43b2-ac17-04d8f46d2a05</t>
+  </si>
+  <si>
+    <t>relationship--22540bd2-e90f-4607-b488-32eb394d3a2d</t>
+  </si>
+  <si>
+    <t>relationship--315f5761-3336-4dbd-9ad9-8445740126ee</t>
+  </si>
+  <si>
+    <t>relationship--6a92abcc-0bfb-407e-b7d1-e532b4036cb3</t>
+  </si>
+  <si>
+    <t>relationship--2caf81eb-8f2e-451c-a2bb-1c894ae2afa9</t>
+  </si>
+  <si>
+    <t>relationship--3fb41385-b9bf-4494-b268-fc212e3f9685</t>
+  </si>
+  <si>
+    <t>relationship--4b5e9197-0b24-4317-9dbb-5d23d1614316</t>
+  </si>
+  <si>
+    <t>relationship--33ca54ea-b2f3-4ffd-a547-e2f67737c98a</t>
+  </si>
+  <si>
+    <t>relationship--7bb0e65b-ac66-4bb1-be32-6b6967e8695e</t>
+  </si>
+  <si>
+    <t>relationship--ce68e232-5128-4316-8b29-26a268892c48</t>
+  </si>
+  <si>
+    <t>relationship--06badfd9-eea9-40b1-98a5-0a5e6d8a1751</t>
+  </si>
+  <si>
+    <t>relationship--76498daa-ef4a-4043-9dd9-2b4b26e1d087</t>
+  </si>
+  <si>
+    <t>relationship--012253ee-0b1b-4c2f-a160-3bf410c37184</t>
+  </si>
+  <si>
+    <t>relationship--ad3bfa98-f3de-4c9e-98dd-e49f5db0d59f</t>
+  </si>
+  <si>
+    <t>relationship--a622899b-6756-442b-80ef-e57635e6056f</t>
+  </si>
+  <si>
+    <t>relationship--13b95caf-63ea-4fc2-abc9-e3569fbb4ae1</t>
   </si>
   <si>
     <t>T0030</t>
@@ -4031,244 +4031,244 @@
     <t>Смена алфавита родного языка</t>
   </si>
   <si>
-    <t>attack-pattern--6e7e75e1-0db0-4d82-b49a-0d53a8377673</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2e968ce-b955-4609-885e-9a94a97d9bc9</t>
-  </si>
-  <si>
-    <t>attack-pattern--5dcc3a96-1d9f-421c-ac46-9c396f68ea34</t>
-  </si>
-  <si>
-    <t>attack-pattern--e9e41389-66eb-43b4-9cdf-f5b0ac2dc057</t>
-  </si>
-  <si>
-    <t>attack-pattern--3886a528-955b-4e5e-a31a-a297076adfd2</t>
-  </si>
-  <si>
-    <t>attack-pattern--be992ef6-3881-4236-9c72-93ad885fecf9</t>
-  </si>
-  <si>
-    <t>attack-pattern--792c75be-6b88-40e7-8dbb-df0dd4841993</t>
-  </si>
-  <si>
-    <t>attack-pattern--65fb49b6-79ef-40ce-89c4-ff952b19011b</t>
-  </si>
-  <si>
-    <t>attack-pattern--919d30d7-6892-423a-a8bb-8fbe7d66e8ff</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1eb4ee9-8cf3-491b-bf9e-62b29e6ee4bf</t>
-  </si>
-  <si>
-    <t>attack-pattern--90055235-0572-4542-b108-29375451d387</t>
-  </si>
-  <si>
-    <t>attack-pattern--e3fb11b9-94a3-4399-b897-c0f602fcd3d7</t>
-  </si>
-  <si>
-    <t>attack-pattern--f220f5b7-f3f0-4fef-86af-ade60ec7305a</t>
-  </si>
-  <si>
-    <t>attack-pattern--07b87f7d-539f-40f7-be97-6078fae34324</t>
-  </si>
-  <si>
-    <t>attack-pattern--c5770ebc-aaeb-40b0-af29-fd3d63ca97a2</t>
-  </si>
-  <si>
-    <t>attack-pattern--103f63dc-a6d5-4ba1-abc7-0184491b5271</t>
-  </si>
-  <si>
-    <t>attack-pattern--dbed37eb-3e38-48b6-98f6-1a9aac1076d5</t>
-  </si>
-  <si>
-    <t>attack-pattern--e56f5dcd-3983-435f-93da-a93a60ca1e47</t>
-  </si>
-  <si>
-    <t>attack-pattern--d353ed6f-c3e5-4632-9f6d-9fd389c16231</t>
-  </si>
-  <si>
-    <t>attack-pattern--70479515-9b93-4ec1-ba31-632cd23e4574</t>
-  </si>
-  <si>
-    <t>attack-pattern--fdf6886c-4a4e-4067-9cac-a018da349cc1</t>
-  </si>
-  <si>
-    <t>attack-pattern--23b6daf2-9f20-46eb-8671-920d60e4176b</t>
-  </si>
-  <si>
-    <t>attack-pattern--7a4074d0-24b3-4fd5-b768-e156c78db7db</t>
-  </si>
-  <si>
-    <t>attack-pattern--a15399bd-925c-44e3-a75c-cb1b53d8c074</t>
-  </si>
-  <si>
-    <t>attack-pattern--44ad371d-f921-4b4d-9334-2dce2da4aaaf</t>
-  </si>
-  <si>
-    <t>attack-pattern--22fb0501-e69d-4266-9e11-6d271bcd7c5d</t>
-  </si>
-  <si>
-    <t>attack-pattern--cb4b534f-b8a9-4926-baa3-b078694b8519</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae6f538f-2867-497c-b74a-c0bb0726a49f</t>
-  </si>
-  <si>
-    <t>attack-pattern--4026908a-0f17-4fb5-a50a-e8c8a747c58e</t>
-  </si>
-  <si>
-    <t>attack-pattern--9fbabf63-9dce-4492-b220-0d1e461df010</t>
-  </si>
-  <si>
-    <t>attack-pattern--e2637ab4-aa90-4f26-9f0c-643026911644</t>
-  </si>
-  <si>
-    <t>attack-pattern--e5f42ecf-13cd-4984-af2e-f1a5fbd73b22</t>
-  </si>
-  <si>
-    <t>attack-pattern--6a1c7124-cdb4-497c-9174-c8b73fd00307</t>
-  </si>
-  <si>
-    <t>attack-pattern--ad1006c7-69a5-4235-9644-77a665afffaf</t>
-  </si>
-  <si>
-    <t>attack-pattern--63ec97cd-e76f-4242-855c-65e2ce960aff</t>
-  </si>
-  <si>
-    <t>attack-pattern--9164d0d6-f747-40be-b2ab-c64baa5cd6e8</t>
-  </si>
-  <si>
-    <t>attack-pattern--14882788-8da6-4e89-8b0a-369f6b46aac1</t>
-  </si>
-  <si>
-    <t>attack-pattern--3e70f8b3-4681-42f1-8a6b-a1baece08ac6</t>
-  </si>
-  <si>
-    <t>attack-pattern--074400fc-9c8c-409c-96e6-91b0f42eb110</t>
-  </si>
-  <si>
-    <t>attack-pattern--ccb1c983-8262-4840-a946-316971a55893</t>
-  </si>
-  <si>
-    <t>attack-pattern--9de68747-f426-4db4-b51f-b53282321fe1</t>
-  </si>
-  <si>
-    <t>attack-pattern--4202af9f-2d34-4e0c-a33f-e3bab246965b</t>
-  </si>
-  <si>
-    <t>attack-pattern--bd51216b-c2ed-44fe-947f-259544f66886</t>
-  </si>
-  <si>
-    <t>attack-pattern--f73d8a36-0521-4724-927a-92af6f36e696</t>
-  </si>
-  <si>
-    <t>attack-pattern--ee5bb8e1-fee2-4e46-a264-77b6fca28401</t>
-  </si>
-  <si>
-    <t>attack-pattern--dff3ad94-5c20-4925-a7b9-a62b37efeb45</t>
-  </si>
-  <si>
-    <t>attack-pattern--9452fecd-32ce-4960-851a-e7805c6edbc3</t>
-  </si>
-  <si>
-    <t>attack-pattern--147076ae-f3b0-4e8d-a3f2-6018cfab8120</t>
-  </si>
-  <si>
-    <t>attack-pattern--57c19e77-979f-4af9-8f76-b8842e0eccc9</t>
-  </si>
-  <si>
-    <t>attack-pattern--ffef9fde-b807-4346-848c-fd66677fc503</t>
-  </si>
-  <si>
-    <t>attack-pattern--86ca32e1-923d-4a0c-8dab-76cc249df7bb</t>
-  </si>
-  <si>
-    <t>attack-pattern--69f3396d-7553-450c-9443-80126d293837</t>
-  </si>
-  <si>
-    <t>attack-pattern--6b474b4b-ff3a-40f7-8aa2-f96235b52ef8</t>
-  </si>
-  <si>
-    <t>attack-pattern--da34d411-6ba3-4e4d-a8c3-a9fd1ff0adcd</t>
-  </si>
-  <si>
-    <t>attack-pattern--2534c0c4-3a14-4ef3-9ec3-e1ce52e4c596</t>
-  </si>
-  <si>
-    <t>attack-pattern--1c8963ba-44f5-4619-bfbe-d74b9db41464</t>
-  </si>
-  <si>
-    <t>attack-pattern--317902b3-2928-42ce-aab1-77bf6464d029</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2671755-9e9d-4f4b-a531-cb8e290024f8</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d6a8a93-d876-4698-a4cd-c7cfcc14197c</t>
-  </si>
-  <si>
-    <t>attack-pattern--a211ed94-8a7b-4e48-b03d-c43ec7c2c14b</t>
-  </si>
-  <si>
-    <t>attack-pattern--2595f410-b103-4103-99dc-7cc1b896315b</t>
-  </si>
-  <si>
-    <t>attack-pattern--170785ac-cac2-48cd-8acf-e8c5bc941503</t>
-  </si>
-  <si>
-    <t>attack-pattern--5eee076f-a070-4da8-b6e4-9a8f68bb602e</t>
-  </si>
-  <si>
-    <t>attack-pattern--e2267790-f642-490c-9da2-d96e13dff98b</t>
-  </si>
-  <si>
-    <t>attack-pattern--6ad16641-500b-4819-acbe-66e0bbd9553e</t>
-  </si>
-  <si>
-    <t>attack-pattern--bfef93ab-ace2-46de-ba41-96702238ef93</t>
-  </si>
-  <si>
-    <t>attack-pattern--5bd16692-e9de-4fb0-aaf2-203c5654c3be</t>
-  </si>
-  <si>
-    <t>attack-pattern--ffd8d85d-efff-4145-a4f3-d46d5c558bb8</t>
-  </si>
-  <si>
-    <t>attack-pattern--aac436e7-dadf-43f1-8cda-44882c19612a</t>
-  </si>
-  <si>
-    <t>attack-pattern--f3d8f555-581e-4ed0-add2-4dddb1b28f8a</t>
-  </si>
-  <si>
-    <t>attack-pattern--08d8cad1-e1cc-4796-a3a1-6d4762590e75</t>
-  </si>
-  <si>
-    <t>attack-pattern--d2d6833f-93e2-47c4-9ed5-6cc66a10e99c</t>
-  </si>
-  <si>
-    <t>attack-pattern--42950ff4-99e9-43e0-9c84-fca26222c4c1</t>
-  </si>
-  <si>
-    <t>attack-pattern--e28fa69e-65b0-418e-a24e-461b222259e6</t>
-  </si>
-  <si>
-    <t>attack-pattern--c75bc202-aba2-48a6-add2-b139f4c14017</t>
-  </si>
-  <si>
-    <t>attack-pattern--0baf716e-a678-48a1-a89f-01fae4b785c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--d21a2253-ea3b-42b9-9bd2-5d602c76bed0</t>
-  </si>
-  <si>
-    <t>attack-pattern--d175845f-f2f1-4e62-b02f-758d61f90f48</t>
-  </si>
-  <si>
-    <t>attack-pattern--07476ac0-71a4-44ac-8a17-b01278057e19</t>
-  </si>
-  <si>
-    <t>attack-pattern--17d9ac61-a2aa-417e-b5ea-4de8b5986439</t>
+    <t>attack-pattern--9f3fdc90-cca7-485e-b78b-eefe2753dc95</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d84c262-0100-44cc-9fd7-a698ee3776dc</t>
+  </si>
+  <si>
+    <t>attack-pattern--9336c78d-5a9f-4d5b-b674-0e344c73b809</t>
+  </si>
+  <si>
+    <t>attack-pattern--91f8404d-6987-41b7-b7a9-df79fe77afe5</t>
+  </si>
+  <si>
+    <t>attack-pattern--8056b7be-c173-4a65-8710-6ea8194a3741</t>
+  </si>
+  <si>
+    <t>attack-pattern--ae2812e0-2ac6-48c0-aaf1-8a649e218bd7</t>
+  </si>
+  <si>
+    <t>attack-pattern--a4deb5e5-f8da-46dc-91ed-17f22df9d9f1</t>
+  </si>
+  <si>
+    <t>attack-pattern--eb3aa6f0-74f5-4e0a-861e-a2c82ffc0798</t>
+  </si>
+  <si>
+    <t>attack-pattern--ecf3feb7-137c-4f53-9e1c-2e1181947f3c</t>
+  </si>
+  <si>
+    <t>attack-pattern--a83e27a1-55ce-4327-8003-590d22630ae9</t>
+  </si>
+  <si>
+    <t>attack-pattern--d080b90a-f3a6-4503-8b13-e422b7a47265</t>
+  </si>
+  <si>
+    <t>attack-pattern--69a3d9fe-d220-4cc1-ac9e-0eb3c8da7a10</t>
+  </si>
+  <si>
+    <t>attack-pattern--e0246bcc-9820-45fa-bfea-862bed9dd573</t>
+  </si>
+  <si>
+    <t>attack-pattern--cd8bb5ae-5aff-4b70-8d6f-31ac36eadbde</t>
+  </si>
+  <si>
+    <t>attack-pattern--952c089f-d14e-4e35-a31d-95ebc0496362</t>
+  </si>
+  <si>
+    <t>attack-pattern--f98477fa-369f-4d0d-8064-a2180d75714c</t>
+  </si>
+  <si>
+    <t>attack-pattern--0ef67418-f9c5-4e0f-9e36-0747bc8f210c</t>
+  </si>
+  <si>
+    <t>attack-pattern--262ba99b-f4f8-41cb-b5cd-5b08f6bb8bd3</t>
+  </si>
+  <si>
+    <t>attack-pattern--e236beed-9135-4388-92da-004919b6e1c8</t>
+  </si>
+  <si>
+    <t>attack-pattern--972bf47e-c0f5-4dae-97cd-9451c7bc4603</t>
+  </si>
+  <si>
+    <t>attack-pattern--cc247977-b994-472a-a92f-a82cf26cbbe2</t>
+  </si>
+  <si>
+    <t>attack-pattern--5a357495-f376-4a5e-a3f7-0066f362328b</t>
+  </si>
+  <si>
+    <t>attack-pattern--ff63c265-0310-4574-82ad-3dc8a99c3488</t>
+  </si>
+  <si>
+    <t>attack-pattern--f09d31c3-1ef9-4f13-9587-c5645517cfe0</t>
+  </si>
+  <si>
+    <t>attack-pattern--55fed0eb-37e3-4ce6-b9a3-a924f2578368</t>
+  </si>
+  <si>
+    <t>attack-pattern--a46ec1d7-5bdd-4e55-a04f-a6f259b5e12e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c3384966-9c95-434d-bcf2-3be46383e578</t>
+  </si>
+  <si>
+    <t>attack-pattern--af2dabb3-15cb-4c7a-87ae-6953c2686480</t>
+  </si>
+  <si>
+    <t>attack-pattern--7b14e908-93a7-43b6-a8d4-ef9881f7b070</t>
+  </si>
+  <si>
+    <t>attack-pattern--53cb5b45-acd8-45ad-8e44-a1db86632a2d</t>
+  </si>
+  <si>
+    <t>attack-pattern--48d4b99e-6c35-41df-9bca-54744d0eb5bd</t>
+  </si>
+  <si>
+    <t>attack-pattern--d7da24f0-8fe5-4136-85ff-12c3f911587f</t>
+  </si>
+  <si>
+    <t>attack-pattern--e99f7a3a-594c-4175-9d82-5b5c75db890d</t>
+  </si>
+  <si>
+    <t>attack-pattern--4a7ebe15-e0c5-424d-8581-ba13a207baf0</t>
+  </si>
+  <si>
+    <t>attack-pattern--154481f0-8068-45c2-9e46-31ae7dc6853a</t>
+  </si>
+  <si>
+    <t>attack-pattern--281579e8-e28f-4e62-9971-a18fab84e0af</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7e4beb6-0682-47aa-acf9-03c1ca5d415a</t>
+  </si>
+  <si>
+    <t>attack-pattern--09a18447-c729-43f1-8ceb-2d48687eac97</t>
+  </si>
+  <si>
+    <t>attack-pattern--8209784f-cde9-413a-bc2b-2ad5da2f0bba</t>
+  </si>
+  <si>
+    <t>attack-pattern--896791e3-5b2d-426b-a067-e6e79c492c4a</t>
+  </si>
+  <si>
+    <t>attack-pattern--65b7c386-1376-4ee1-a83e-d9a77c643142</t>
+  </si>
+  <si>
+    <t>attack-pattern--c0383ad6-d98f-4336-963f-37398fe3c9a3</t>
+  </si>
+  <si>
+    <t>attack-pattern--57e6c6c4-a591-4903-9985-4d284b4eaf64</t>
+  </si>
+  <si>
+    <t>attack-pattern--61b8a224-eb09-443f-822a-8009280fcdc5</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7c2ef21-3827-4a2e-91f2-e658ba4e6fa5</t>
+  </si>
+  <si>
+    <t>attack-pattern--22a5b731-e091-4444-bc84-5e60eba2a2bb</t>
+  </si>
+  <si>
+    <t>attack-pattern--c9e6ccf7-a8ae-4556-bede-76dbb5670f16</t>
+  </si>
+  <si>
+    <t>attack-pattern--024d1d49-921a-479d-b8c4-90d4f7f94d35</t>
+  </si>
+  <si>
+    <t>attack-pattern--5111de41-6dbf-4ce2-ab89-beaa810e1cf7</t>
+  </si>
+  <si>
+    <t>attack-pattern--e64e3ca3-6b6e-482c-bdb2-3d3a64794457</t>
+  </si>
+  <si>
+    <t>attack-pattern--1d927ea8-3d2b-413f-8459-9786ccf5b725</t>
+  </si>
+  <si>
+    <t>attack-pattern--7d791de3-2e04-431d-ba88-dbdde6add3f4</t>
+  </si>
+  <si>
+    <t>attack-pattern--25092de4-9a0b-4dbc-8b23-6d1a000a5f42</t>
+  </si>
+  <si>
+    <t>attack-pattern--a0d79fcb-de29-4b04-ab91-078640aa7942</t>
+  </si>
+  <si>
+    <t>attack-pattern--20693395-073f-458c-b2a1-7be782d97354</t>
+  </si>
+  <si>
+    <t>attack-pattern--7aa1b36a-86ff-4f8b-b158-ee648a9ef31a</t>
+  </si>
+  <si>
+    <t>attack-pattern--d5f1412a-2885-40f5-a71f-f39ad84178c0</t>
+  </si>
+  <si>
+    <t>attack-pattern--a903cd8c-c914-4408-ae0a-c915df961d3b</t>
+  </si>
+  <si>
+    <t>attack-pattern--b66ac526-6f64-4e32-9922-2d68e51631b1</t>
+  </si>
+  <si>
+    <t>attack-pattern--3cb79497-d461-4586-860f-71737528f775</t>
+  </si>
+  <si>
+    <t>attack-pattern--953bf0ac-d5ae-4b33-a124-4c223463b0fa</t>
+  </si>
+  <si>
+    <t>attack-pattern--cffadcf5-6a6b-4e1f-8b87-85adf27c9f9c</t>
+  </si>
+  <si>
+    <t>attack-pattern--49a44b3e-87a2-4cf6-a4f0-fd58d82d63ea</t>
+  </si>
+  <si>
+    <t>attack-pattern--f3ce3c11-3e28-4d6e-b4f2-426f987041f8</t>
+  </si>
+  <si>
+    <t>attack-pattern--ecc01b5f-5093-4549-972c-ff73588df011</t>
+  </si>
+  <si>
+    <t>attack-pattern--a45e2a90-8a79-47a9-ad3e-2c1f33b089f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--dba55821-e44f-42a3-b519-056650fee6a3</t>
+  </si>
+  <si>
+    <t>attack-pattern--85ac27b3-8e0a-481a-8960-03146d6387b9</t>
+  </si>
+  <si>
+    <t>attack-pattern--50d263b4-e04e-4942-a7d4-026ee3dd7f03</t>
+  </si>
+  <si>
+    <t>attack-pattern--816d2931-33e2-4dde-a98f-1bdcd38931b3</t>
+  </si>
+  <si>
+    <t>attack-pattern--f4ee8a5d-0fb9-42f8-8046-04b5e02d18be</t>
+  </si>
+  <si>
+    <t>attack-pattern--e5c43fec-3847-47e6-aad1-56f38d6c0723</t>
+  </si>
+  <si>
+    <t>attack-pattern--9dfb75d7-34d0-4b59-a463-4300cf5493a6</t>
+  </si>
+  <si>
+    <t>attack-pattern--ba2aee33-7edc-416e-921b-2aece2032428</t>
+  </si>
+  <si>
+    <t>attack-pattern--404cbad7-d4cf-4dfa-a2d5-f7e771b4c804</t>
+  </si>
+  <si>
+    <t>attack-pattern--e27e053b-85f7-4f3b-9caa-70ba91cc3a44</t>
+  </si>
+  <si>
+    <t>attack-pattern--4de692cb-753a-45d3-ac80-34255162bcaf</t>
+  </si>
+  <si>
+    <t>attack-pattern--bf051bf8-cc3b-4bed-921d-d093e17d11b6</t>
+  </si>
+  <si>
+    <t>attack-pattern--46228d06-6a20-4748-9cdb-8155982fdceb</t>
+  </si>
+  <si>
+    <t>attack-pattern--3fb03caa-0900-45aa-b166-8e7282b52a60</t>
   </si>
   <si>
     <t>technique</t>
@@ -4283,7 +4283,7 @@
     <t>Раздел сфер влияния за спиной украинского союзника, сопровождавшийся финансовой сделкой за территорию: Москва официально заплатила за уступку Киева огромную сумму серебром (Citation: Война и наказание: Как Россия уничтожала Украину 2023)(Citation: Мазепа 2007)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? - Riddle Russia 2026)</t>
+    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
   </si>
   <si>
     <t>Секуляризация и конфискация в имперскую казну земель украинских православных монастырей (1786 год), лишившая локальную церковь экономической базы (Citation: Друга Малоросійська колегія — Вікіпедія 2026).</t>
@@ -4601,7 +4601,7 @@
     <t>Использование подконтрольной спецслужбам хакерской группировки Fancy Bear для взлома программного обеспечения украинских артиллеристов (через заражение приложения Ярослава Шерстюка) с целью получения геолокационных данных и уничтожения артиллерии ВСУ. (Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>Целенаправленные кибератаки российских спецслужб на распределительные подстанции украинской энергосети зимой 2015 и 2016 годов с целью массового отключения электроэнергии для гражданского населения. (Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®) (Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®)</t>
+    <t>Целенаправленные кибератаки российских спецслужб на распределительные подстанции украинской энергосети зимой 2015 и 2016 годов с целью массового отключения электроэнергии для гражданского населения. (Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023) (Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023)</t>
   </si>
   <si>
     <t>Физическое устранение легитимных представителей местной власти, оказывавших открытое политическое сопротивление оккупации (в частности, жестокое убийство депутата горловского горсовета В. Рыбака за попытку вернуть украинский флаг). (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -4616,10 +4616,10 @@
     <t>Систематическое применение пыток и физического насилия к гражданским лицам на оккупированных территориях за любую демонстрацию украинской символики и проукраинскую позицию. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Разжигание вооруженных столкновений в Одессе 2 мая 2014 года силами пророссийских активистов («антимайдана») с целью дестабилизации Юга Украины, что переросло в уличные бои и привело к массовым жертвам в Доме профсоюзов. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>Привлечение к боевым действиям российских неонацистских группировок (таких как ДРГ «Русич» под командованием А. Мильчакова), главари которых открыто призывали к немотивированному садистскому насилию над гражданскими («Режь бомжей, щенков и детей!»). (Citation: «Рашизм: Звір з безодні» 2023)</t>
+    <t>Разжигание вооруженных столкновений в Одессе 2 мая 2014 года силами пророссийских активистов («антимайдана») с целью дестабилизации Юга Украины, что переросло в уличные бои и привело к массовым жертвам в Доме профсоюзов. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>Привлечение к боевым действиям российских неонацистских группировок (таких как ДРГ «Русич» под командованием А. Мильчакова), главари которых открыто призывали к немотивированному садистскому насилию над гражданскими («Режь бомжей, щенков и детей!»). (Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
     <t>Вербовка ФСК кадровых военнослужащих Кантемировской и Таманской дивизий и снабжение оппозиции десятками танков для штурма Грозного 26 ноября 1994 года (Citation: Хроника первой российской войны в Чечне 2026).</t>
@@ -4718,979 +4718,979 @@
     <t>Изъятие у УССР контроля над внешней политикой, армией, внешней торговлей, транспортом и связью через Конституцию СССР 1924 года с передачей их в ведение союзных наркоматов. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--fe81bdc2-fb65-4491-aa3a-44d75444dd06</t>
-  </si>
-  <si>
-    <t>relationship--ab503d43-2880-46aa-a946-3403b6728626</t>
-  </si>
-  <si>
-    <t>relationship--bf3ddc72-9e25-4cfa-9c5c-9c111077193b</t>
-  </si>
-  <si>
-    <t>relationship--fcfe3d53-832a-41af-8c72-16cca38a60fa</t>
-  </si>
-  <si>
-    <t>relationship--b065a97f-cf1b-4283-b259-8b950b166dfe</t>
-  </si>
-  <si>
-    <t>relationship--645f7c96-1911-403c-951d-e019a6719a01</t>
-  </si>
-  <si>
-    <t>relationship--11158ebc-0b03-43a1-b313-ac38d8f051d1</t>
-  </si>
-  <si>
-    <t>relationship--6b687f62-f45d-4690-bafa-209ffe344c28</t>
-  </si>
-  <si>
-    <t>relationship--4df55bd7-04b7-4218-b5b7-dc264d79bc0c</t>
-  </si>
-  <si>
-    <t>relationship--927e8bfd-2d99-4eb5-9066-aeb6f1fa2728</t>
-  </si>
-  <si>
-    <t>relationship--464b11af-1365-4de9-a6e5-e4e25eb4cbd2</t>
-  </si>
-  <si>
-    <t>relationship--d31e84d5-bce8-46bc-a885-a108dae98fe1</t>
-  </si>
-  <si>
-    <t>relationship--6ce2a3f3-8535-40e4-96ee-0bd1b9ac52dc</t>
-  </si>
-  <si>
-    <t>relationship--42b869a9-68ff-423a-ad84-f19a43bdbe54</t>
-  </si>
-  <si>
-    <t>relationship--3137e944-5681-4b80-99a7-3eb1b02ea140</t>
-  </si>
-  <si>
-    <t>relationship--8343eea4-11a8-4129-8fd0-c7d65fdda02e</t>
-  </si>
-  <si>
-    <t>relationship--7e840be6-8397-427a-a4d2-db201848de4b</t>
-  </si>
-  <si>
-    <t>relationship--573c703b-578f-4f9f-8dc4-083037ff5a56</t>
-  </si>
-  <si>
-    <t>relationship--f9b29ccb-0a2d-40f8-81c6-c92a16e0fa0c</t>
-  </si>
-  <si>
-    <t>relationship--179479ad-6037-444d-b630-db8a1ab2a843</t>
-  </si>
-  <si>
-    <t>relationship--3bb0dbf1-c7c2-4ba9-bcc2-b54c05545d8f</t>
-  </si>
-  <si>
-    <t>relationship--e4117033-ad9e-46e7-8566-86891580219d</t>
-  </si>
-  <si>
-    <t>relationship--de95722f-a356-4b1d-837e-cb55369c7d8c</t>
-  </si>
-  <si>
-    <t>relationship--9e6b7e40-3818-42c4-9577-3833f41e615d</t>
-  </si>
-  <si>
-    <t>relationship--a0c2eefb-8a87-48d5-b414-1bb57e9ca4a6</t>
-  </si>
-  <si>
-    <t>relationship--cd10b91e-8ad9-431b-8e55-ffc63e01dd11</t>
-  </si>
-  <si>
-    <t>relationship--703172da-07fd-45df-9d31-d2f4bd3895a3</t>
-  </si>
-  <si>
-    <t>relationship--0247aed9-4200-4a52-a55f-730181e3bee0</t>
-  </si>
-  <si>
-    <t>relationship--fc1ad78c-e556-41bd-a13a-1b64b8995563</t>
-  </si>
-  <si>
-    <t>relationship--2f54637f-c3bc-49d9-a748-a2c27cbbd117</t>
-  </si>
-  <si>
-    <t>relationship--8a91cf3c-d910-4f3c-81c4-42029fe695f4</t>
-  </si>
-  <si>
-    <t>relationship--35716e7b-3f6f-4c0a-8dcb-c645f64019f5</t>
-  </si>
-  <si>
-    <t>relationship--32035de9-5d1d-4d94-a194-9529b2d98ec3</t>
-  </si>
-  <si>
-    <t>relationship--939b9e84-712c-4a37-ae73-66462a4d6cc9</t>
-  </si>
-  <si>
-    <t>relationship--37371b99-42ac-4734-9bd2-e0ad5232c9ce</t>
-  </si>
-  <si>
-    <t>relationship--10780957-0222-4ae3-b3f7-454f2ca79de7</t>
-  </si>
-  <si>
-    <t>relationship--3970823d-85b6-4a57-9d5d-799cd48ba1e9</t>
-  </si>
-  <si>
-    <t>relationship--3f4019e3-2e5c-4431-9067-d099050dc711</t>
-  </si>
-  <si>
-    <t>relationship--f9e5665e-d6df-4917-8f54-df8b4a07b365</t>
-  </si>
-  <si>
-    <t>relationship--acd1a355-b8be-4337-bf0d-c8133f815de0</t>
-  </si>
-  <si>
-    <t>relationship--cf80e058-0bc7-4252-909f-40adbaa4bca0</t>
-  </si>
-  <si>
-    <t>relationship--3d6b86ed-58b4-4e2f-8e4d-07ff96fbcc65</t>
-  </si>
-  <si>
-    <t>relationship--b4356b31-fcb3-45a7-8a6f-1b231716f5e2</t>
-  </si>
-  <si>
-    <t>relationship--c0789b16-4de5-4322-88ee-902f3c381be5</t>
-  </si>
-  <si>
-    <t>relationship--42086e12-5363-49f6-ba92-c06db5333223</t>
-  </si>
-  <si>
-    <t>relationship--541d56a0-874f-4758-8d90-3ad7c129313f</t>
-  </si>
-  <si>
-    <t>relationship--7d3838e2-ec4f-45c1-94eb-a80a732ed7cc</t>
-  </si>
-  <si>
-    <t>relationship--63480807-8332-460c-8a43-a2c17f051a75</t>
-  </si>
-  <si>
-    <t>relationship--206a56c3-53fc-4c9f-9013-756b14f1457d</t>
-  </si>
-  <si>
-    <t>relationship--4689bc88-86a1-4ef1-81f8-95eb72ca6756</t>
-  </si>
-  <si>
-    <t>relationship--89034db7-f8fe-4d50-bd46-131fdf843dbd</t>
-  </si>
-  <si>
-    <t>relationship--bca608f9-459c-4a0a-991c-27fe3715de17</t>
-  </si>
-  <si>
-    <t>relationship--7040c013-4f18-4c07-bb5e-86dd9f17f8f3</t>
-  </si>
-  <si>
-    <t>relationship--b1808a6d-649f-4c22-bcc8-1b9fc3b42dc3</t>
-  </si>
-  <si>
-    <t>relationship--b8dc28a7-d577-45a5-91e3-e7b3a7b62c84</t>
-  </si>
-  <si>
-    <t>relationship--fe10999f-3385-480a-9b96-2225c2933266</t>
-  </si>
-  <si>
-    <t>relationship--5632a625-0e99-42ff-a571-7d8469dde809</t>
-  </si>
-  <si>
-    <t>relationship--fc6d3b53-b3a2-4f6f-b075-574810e43953</t>
-  </si>
-  <si>
-    <t>relationship--242fa20a-b1b9-4f04-ab21-31ccce61fa32</t>
-  </si>
-  <si>
-    <t>relationship--21da539f-ef77-4a2d-8c5e-16ae2eb9f213</t>
-  </si>
-  <si>
-    <t>relationship--bcddc11f-0521-4ad7-af40-57e84ce5ae4e</t>
-  </si>
-  <si>
-    <t>relationship--dfa78ebd-17dd-43e9-92ff-1bfb73f74501</t>
-  </si>
-  <si>
-    <t>relationship--5f698e6b-754c-49c5-ae7f-d92019aabc49</t>
-  </si>
-  <si>
-    <t>relationship--60afa905-a813-4335-9492-d0a06ec1f407</t>
-  </si>
-  <si>
-    <t>relationship--1e39d456-ab22-471a-9970-cbce64a72b4d</t>
-  </si>
-  <si>
-    <t>relationship--bb2367b4-bbb0-4f4b-acd6-4663c2ca6314</t>
-  </si>
-  <si>
-    <t>relationship--337702fa-4ef1-44db-847d-7bf7a6ae96d7</t>
-  </si>
-  <si>
-    <t>relationship--438a3acf-b3b3-47d2-a2a4-274310096934</t>
-  </si>
-  <si>
-    <t>relationship--94662ef5-6ee1-43da-bda2-68b9e2c1be3f</t>
-  </si>
-  <si>
-    <t>relationship--b030cbe9-a02e-4508-bfe8-7783062e5ed9</t>
-  </si>
-  <si>
-    <t>relationship--c1b37147-ebf4-49f5-bbad-4baa4730beeb</t>
-  </si>
-  <si>
-    <t>relationship--0a30848e-608c-4861-9856-fada413922c3</t>
-  </si>
-  <si>
-    <t>relationship--e2b88a14-e76d-4573-95f5-12a763824544</t>
-  </si>
-  <si>
-    <t>relationship--6a338b7e-4e8c-4537-9a17-0fd25dacdc44</t>
-  </si>
-  <si>
-    <t>relationship--98af85f2-eeeb-4700-bb53-b7a45ddecd0e</t>
-  </si>
-  <si>
-    <t>relationship--861f62c6-c9d7-4d19-bc19-cd77d0152b42</t>
-  </si>
-  <si>
-    <t>relationship--b169f3c9-aab2-499e-8e59-76ffe354d573</t>
-  </si>
-  <si>
-    <t>relationship--9420186a-9362-45a5-90f8-7e8ae1c96cee</t>
-  </si>
-  <si>
-    <t>relationship--da6c8af0-7a3c-4938-adbf-d5af5e750243</t>
-  </si>
-  <si>
-    <t>relationship--f9913e4a-bd8d-4539-8e0c-4149b3ce1a20</t>
-  </si>
-  <si>
-    <t>relationship--2ef813a4-3004-4ab9-8d4d-2086754414e7</t>
-  </si>
-  <si>
-    <t>relationship--0a9c55c5-60ba-4268-9daa-01fe4edf655b</t>
-  </si>
-  <si>
-    <t>relationship--c0934933-f67a-439a-8ebd-ca38fab7fa82</t>
-  </si>
-  <si>
-    <t>relationship--c10af67a-b9bf-4cff-a637-247dd90035c1</t>
-  </si>
-  <si>
-    <t>relationship--a70f4086-6485-4df8-aa85-3dab9b94ff23</t>
-  </si>
-  <si>
-    <t>relationship--d6700a11-ca14-4032-973d-ffde05a51216</t>
-  </si>
-  <si>
-    <t>relationship--856ed095-d2a7-4e37-8a0c-19e26c033302</t>
-  </si>
-  <si>
-    <t>relationship--5735c03c-9c7d-4a05-b12b-5132e41aec11</t>
-  </si>
-  <si>
-    <t>relationship--0275d445-b6a4-4206-90f7-6465e7e3563b</t>
-  </si>
-  <si>
-    <t>relationship--bbcce0b7-b3f6-4073-a116-9898740fd0b9</t>
-  </si>
-  <si>
-    <t>relationship--66dcd5f6-759b-490d-8b7f-e5b9d71f3c45</t>
-  </si>
-  <si>
-    <t>relationship--cad37de2-a175-40c9-aef5-1fb763b2e3e3</t>
-  </si>
-  <si>
-    <t>relationship--02c50bfa-bef8-4dfc-839c-dc26d1fe3d66</t>
-  </si>
-  <si>
-    <t>relationship--dc9607c0-f66b-470e-aa9d-0e3a55c9f3c7</t>
-  </si>
-  <si>
-    <t>relationship--4b2187d9-4f74-48ab-a856-2340a95db7c5</t>
-  </si>
-  <si>
-    <t>relationship--15997e44-a0ea-4a54-a297-e8a4aac3ad57</t>
-  </si>
-  <si>
-    <t>relationship--518ea525-c27d-4ffd-b28f-5bc14b4be0e5</t>
-  </si>
-  <si>
-    <t>relationship--879d4bfe-4d5b-4e8e-8223-55122aa759c6</t>
-  </si>
-  <si>
-    <t>relationship--b77a0e87-091f-40df-9b62-5d446bcdd01f</t>
-  </si>
-  <si>
-    <t>relationship--48bc212a-3bdf-4d7d-91f4-5e215b1077fb</t>
-  </si>
-  <si>
-    <t>relationship--bf5cd67e-9dd8-4a16-8560-ceb655c8cb36</t>
-  </si>
-  <si>
-    <t>relationship--6c51fdfc-6f8a-4350-9c33-aa001d70d3da</t>
-  </si>
-  <si>
-    <t>relationship--b8c96436-e1a8-4bd3-8a2b-86b4c2a25b21</t>
-  </si>
-  <si>
-    <t>relationship--27d774f2-3fc9-4fe0-abee-6cd87761ed3c</t>
-  </si>
-  <si>
-    <t>relationship--71ca3e38-25f4-42c8-9e8b-e873823a31b7</t>
-  </si>
-  <si>
-    <t>relationship--a1a7f54b-0332-44e1-95ee-27d3852d441a</t>
-  </si>
-  <si>
-    <t>relationship--8dd344cc-ec9d-42c6-a7b5-086749d37c94</t>
-  </si>
-  <si>
-    <t>relationship--1ec59c0d-f056-4162-8e8b-2da597408037</t>
-  </si>
-  <si>
-    <t>relationship--1022cbb9-9614-4178-82b1-2e1909982691</t>
-  </si>
-  <si>
-    <t>relationship--f69cc2a9-a96a-45f0-aa8a-6189e7923e0e</t>
-  </si>
-  <si>
-    <t>relationship--b8b87e2a-6e49-401b-918b-f4dd97c9710d</t>
-  </si>
-  <si>
-    <t>relationship--04fd71ef-4916-455c-84e6-8097e09cf0a6</t>
-  </si>
-  <si>
-    <t>relationship--cd1d0ff4-9e2b-411d-b5fe-84a72e0e104f</t>
-  </si>
-  <si>
-    <t>relationship--56606830-23e3-47b9-baff-839d4d3c1d49</t>
-  </si>
-  <si>
-    <t>relationship--8a9b6e43-5364-4890-9c90-76d47214a038</t>
-  </si>
-  <si>
-    <t>relationship--6c7acd99-5792-42b4-a868-acb4b8f5a766</t>
-  </si>
-  <si>
-    <t>relationship--ca533a27-e7fc-4557-a11d-5262950532a9</t>
-  </si>
-  <si>
-    <t>relationship--9dba5ea8-08b3-4b34-bc06-3f04fbc851fc</t>
-  </si>
-  <si>
-    <t>relationship--176a7f3e-13d6-43d4-aa61-df4675cdd451</t>
-  </si>
-  <si>
-    <t>relationship--92f33b4a-c9be-4e08-9b2a-0268783e922c</t>
-  </si>
-  <si>
-    <t>relationship--5cfb4b45-de6f-4fcc-a358-e4dcb1d72d57</t>
-  </si>
-  <si>
-    <t>relationship--c2b4720c-1b47-46be-a243-050e3027af2c</t>
-  </si>
-  <si>
-    <t>relationship--1b9233f4-7657-4234-bab8-1959ab88c32d</t>
-  </si>
-  <si>
-    <t>relationship--37f774bd-3f2b-4834-8619-6e43bd728552</t>
-  </si>
-  <si>
-    <t>relationship--ca03b65c-e52f-496d-8f81-8486d100a76f</t>
-  </si>
-  <si>
-    <t>relationship--07b3f237-2d0e-4f0b-a055-e069c6218c25</t>
-  </si>
-  <si>
-    <t>relationship--5d84b0ef-d33a-48e9-bf70-d81b141a59c9</t>
-  </si>
-  <si>
-    <t>relationship--addec42e-9235-4acb-9665-96826cb10408</t>
-  </si>
-  <si>
-    <t>relationship--9eaa08df-4f4f-4f6a-9ea5-d1a482540f08</t>
-  </si>
-  <si>
-    <t>relationship--faad56d1-bb8e-4d05-a867-bfa1ac8bf935</t>
-  </si>
-  <si>
-    <t>relationship--bcd57400-e081-448e-b1d9-97b617b2ebac</t>
-  </si>
-  <si>
-    <t>relationship--337d0118-86df-431e-b759-6a0269c759ee</t>
-  </si>
-  <si>
-    <t>relationship--68732d52-ab09-49c7-b960-056b3bed6615</t>
-  </si>
-  <si>
-    <t>relationship--0fa4d2ef-59ec-4f91-99d4-cc6b99a6ece2</t>
-  </si>
-  <si>
-    <t>relationship--77da9625-ef9e-4748-8028-d293af9aaf6b</t>
-  </si>
-  <si>
-    <t>relationship--882112d4-85a8-4f84-ad31-2246195877cb</t>
-  </si>
-  <si>
-    <t>relationship--be15b354-4c50-453a-ba24-af0150576573</t>
-  </si>
-  <si>
-    <t>relationship--cded6212-8f97-411b-9b2f-26cf7b88ec75</t>
-  </si>
-  <si>
-    <t>relationship--9b101cce-035b-4768-aa50-6a77ac941e49</t>
-  </si>
-  <si>
-    <t>relationship--e37647b6-f5d2-42d1-ace1-ae2ec652e4d8</t>
-  </si>
-  <si>
-    <t>relationship--9afad85d-7287-4120-84ba-c3071ec0cf05</t>
-  </si>
-  <si>
-    <t>relationship--f92d8a2c-ca36-46d3-9617-0bdd39c6c8a9</t>
-  </si>
-  <si>
-    <t>relationship--2eb37d25-cd63-42bb-b769-88bbbc9e42a0</t>
-  </si>
-  <si>
-    <t>relationship--a50a9d92-ae3f-4b2d-b7aa-b872ba3504b9</t>
-  </si>
-  <si>
-    <t>relationship--d8f60731-3d47-4c52-8361-8fcbc51e75e6</t>
-  </si>
-  <si>
-    <t>relationship--d5ed462b-45a6-41fb-b616-c91b7fd2d1fe</t>
-  </si>
-  <si>
-    <t>relationship--8f5db833-c94a-42df-9424-8d95791e1ebc</t>
-  </si>
-  <si>
-    <t>relationship--a4ef7742-dc6f-4766-8e13-3dd28cb18b01</t>
-  </si>
-  <si>
-    <t>relationship--cfe54ffd-a7ef-4a02-b33a-ad01b60edaff</t>
-  </si>
-  <si>
-    <t>relationship--9373c913-2adb-4e9c-aac4-2caa620560ea</t>
-  </si>
-  <si>
-    <t>relationship--0d9b9fae-f367-465a-a495-5a67081625c1</t>
-  </si>
-  <si>
-    <t>relationship--64a298dd-955e-4162-9f13-794c9354a782</t>
-  </si>
-  <si>
-    <t>relationship--e4c59a2d-a22b-4cd2-960c-c39c83fb80a9</t>
-  </si>
-  <si>
-    <t>relationship--4e96d8c5-c720-454b-ba66-0008145a0335</t>
-  </si>
-  <si>
-    <t>relationship--de6cf1e1-f764-4c43-a0ba-6651e551d4b4</t>
-  </si>
-  <si>
-    <t>relationship--79721904-27e8-4db7-a378-90196244d95a</t>
-  </si>
-  <si>
-    <t>relationship--2aea632b-362c-44cb-ae4a-22b4abf8bc4e</t>
-  </si>
-  <si>
-    <t>relationship--98c5ad14-3436-4f3a-8ac9-57707f05a5cf</t>
-  </si>
-  <si>
-    <t>relationship--b07a7160-d56b-43a2-9892-d291bc0dcd46</t>
-  </si>
-  <si>
-    <t>relationship--a915e1c1-c7e7-47ed-b91b-aee8756552db</t>
-  </si>
-  <si>
-    <t>relationship--582d9559-533d-4d7e-8f3e-a41c41ac6b78</t>
-  </si>
-  <si>
-    <t>relationship--29acdcfa-233e-485f-9d51-c482277a0e41</t>
-  </si>
-  <si>
-    <t>relationship--632ee11f-6d39-45a6-892e-fc11d8254356</t>
-  </si>
-  <si>
-    <t>relationship--13988107-c5ec-4fc8-98b1-397409e17bd3</t>
-  </si>
-  <si>
-    <t>relationship--b04434ca-32ed-4338-9a49-ac157e9b0314</t>
-  </si>
-  <si>
-    <t>relationship--1437adb0-dabf-4875-a0a1-478cc6fc26c9</t>
-  </si>
-  <si>
-    <t>relationship--5f3f2346-b89d-4f02-a479-4bfec8b46329</t>
-  </si>
-  <si>
-    <t>relationship--8ba9ce12-f05e-48f7-aef1-d3ea9cedd1b8</t>
-  </si>
-  <si>
-    <t>relationship--50d884e4-405a-49a8-858a-79c67f7936f4</t>
-  </si>
-  <si>
-    <t>relationship--f7c3adef-d66a-45bb-b8e5-77a0a672b371</t>
-  </si>
-  <si>
-    <t>relationship--d22f72a7-e3fb-459d-b88d-9d01dceefb6a</t>
-  </si>
-  <si>
-    <t>relationship--a37babda-0bd0-484c-9a7f-9900af65e27d</t>
-  </si>
-  <si>
-    <t>relationship--5c4a2d32-7db4-47dc-b86e-ac30b1cb2bdb</t>
-  </si>
-  <si>
-    <t>relationship--98407efd-2843-4db2-9116-e8e5623d6dab</t>
-  </si>
-  <si>
-    <t>relationship--4c625156-2820-494e-80ab-5ff43a6cdf77</t>
-  </si>
-  <si>
-    <t>relationship--889685a9-345b-4394-b501-b666d0c0a34a</t>
-  </si>
-  <si>
-    <t>relationship--0cd293e9-2988-4f5e-853f-0a8480615b34</t>
-  </si>
-  <si>
-    <t>relationship--0f609a7c-e171-49bf-9d46-953339884185</t>
-  </si>
-  <si>
-    <t>relationship--8e03b2f6-e274-473b-98bf-60857e3d5191</t>
-  </si>
-  <si>
-    <t>relationship--af706863-89f1-4d24-8e80-3ae1162e35b2</t>
-  </si>
-  <si>
-    <t>relationship--f4b2d139-9fe4-4470-8919-e3bb5e858c5a</t>
-  </si>
-  <si>
-    <t>relationship--6c3804db-68fe-4459-8ca6-573debe9556b</t>
-  </si>
-  <si>
-    <t>relationship--5318676c-aec5-496d-a160-449ddc9e7066</t>
-  </si>
-  <si>
-    <t>relationship--e6f18b52-83a2-407c-ab69-f595cc21a77e</t>
-  </si>
-  <si>
-    <t>relationship--dd1fdde9-fd2c-435c-ac37-7320627dd630</t>
-  </si>
-  <si>
-    <t>relationship--9a8273b4-57a7-4b05-a34c-292d7a3dbda6</t>
-  </si>
-  <si>
-    <t>relationship--e1fd0cd6-f6f8-44a4-8e8a-61bc6481f652</t>
-  </si>
-  <si>
-    <t>relationship--5930eb75-d28c-45fb-abf1-f4e7774600f8</t>
-  </si>
-  <si>
-    <t>relationship--12e88647-6039-487b-abf0-bfd692a69ebf</t>
-  </si>
-  <si>
-    <t>relationship--6a36079a-3126-46cd-b6f6-ee96fa6e67fd</t>
-  </si>
-  <si>
-    <t>relationship--04753551-3335-4d90-b95d-5d00e3c7fed7</t>
-  </si>
-  <si>
-    <t>relationship--532a5ad5-896d-4525-8f53-c15768abc161</t>
-  </si>
-  <si>
-    <t>relationship--d8db378e-61dc-4219-bd1f-e8d26884ec36</t>
-  </si>
-  <si>
-    <t>relationship--2b4986d8-4bbd-4b27-8bb8-41e5b1ca50be</t>
-  </si>
-  <si>
-    <t>relationship--6ccfe6a2-3dce-4060-b30b-3471da929e9c</t>
-  </si>
-  <si>
-    <t>relationship--510ac61a-e168-4cbb-a901-c3e77e0cd71d</t>
-  </si>
-  <si>
-    <t>relationship--254ff631-72b5-4c85-9304-3506f391201e</t>
-  </si>
-  <si>
-    <t>relationship--d97fe5a5-6923-46da-924d-e7d2f54a02f1</t>
-  </si>
-  <si>
-    <t>relationship--7fc69a0a-8a13-4aa7-86c9-4e02aefadd8d</t>
-  </si>
-  <si>
-    <t>relationship--822c3e9f-02d5-4d87-bacd-12b7553ccf34</t>
-  </si>
-  <si>
-    <t>relationship--5622e528-21a5-464d-ac22-d6b1dc817825</t>
-  </si>
-  <si>
-    <t>relationship--8c185aba-d191-4c16-a78b-4a70439b8dba</t>
-  </si>
-  <si>
-    <t>relationship--69db0c66-b98d-466b-a158-80f039acc575</t>
-  </si>
-  <si>
-    <t>relationship--70811b17-d816-48f1-916b-7563abc67ed1</t>
-  </si>
-  <si>
-    <t>relationship--c5223ca3-a2b3-4f76-8aa5-cc815c00dd02</t>
-  </si>
-  <si>
-    <t>relationship--8777ea25-9c47-443e-9064-341247bca46d</t>
-  </si>
-  <si>
-    <t>relationship--e2697c62-0a45-46d4-8f29-88bdd6a6a654</t>
-  </si>
-  <si>
-    <t>relationship--83639fac-a388-459a-a007-2f37a29f3132</t>
-  </si>
-  <si>
-    <t>relationship--5816d6d4-028b-46d5-a822-f2f313821c0d</t>
-  </si>
-  <si>
-    <t>relationship--aef53683-e7b3-4cf5-baf4-2551a67b711f</t>
-  </si>
-  <si>
-    <t>relationship--346d2632-2869-4758-a55f-425513c4ebf9</t>
-  </si>
-  <si>
-    <t>relationship--778b0b71-2a2d-4e1e-b73a-d9656b2da939</t>
-  </si>
-  <si>
-    <t>relationship--fead602a-c20a-4b62-9f51-29e95af140ac</t>
-  </si>
-  <si>
-    <t>relationship--4b68b4e7-de18-454e-99b4-5564e6f6d067</t>
-  </si>
-  <si>
-    <t>relationship--da22465e-4c1c-41a6-a660-451487fbd48b</t>
-  </si>
-  <si>
-    <t>relationship--648800dd-dccf-4f75-aad1-876d199d8c3e</t>
-  </si>
-  <si>
-    <t>relationship--6437d19c-8e7a-4ebb-b331-a63f29246800</t>
-  </si>
-  <si>
-    <t>relationship--27cd2bc8-4826-4e63-9c07-6b27ecd1068e</t>
-  </si>
-  <si>
-    <t>relationship--6519f8b9-32f4-4c82-94bb-41c5797a8e44</t>
-  </si>
-  <si>
-    <t>relationship--1b2da7a2-2707-4bec-85a5-1c092565800e</t>
-  </si>
-  <si>
-    <t>relationship--f4cff325-6200-4edb-86c8-1e6d67d1e094</t>
-  </si>
-  <si>
-    <t>relationship--c915631b-4f85-4672-8bae-0a00dc311419</t>
-  </si>
-  <si>
-    <t>relationship--eca70bf9-dab9-4926-99fb-c8f6212062ee</t>
-  </si>
-  <si>
-    <t>relationship--bc25030a-6428-4c73-b88e-975235e48b1d</t>
-  </si>
-  <si>
-    <t>relationship--701fd665-a476-43a7-983c-f64354856926</t>
-  </si>
-  <si>
-    <t>relationship--16986988-7b4a-40d7-bbfa-63c6352de60c</t>
-  </si>
-  <si>
-    <t>relationship--80e3a18b-292f-4e83-bc10-dba09afe08d2</t>
-  </si>
-  <si>
-    <t>relationship--8deb7d87-633f-465f-adf2-b27607240bbf</t>
-  </si>
-  <si>
-    <t>relationship--27bbaa5e-fb0c-49d4-8294-ac44c3d911cd</t>
-  </si>
-  <si>
-    <t>relationship--bcb5e164-3598-4fd5-9393-92791bb06cb8</t>
-  </si>
-  <si>
-    <t>relationship--c4d07db7-6c47-4719-b44d-e2a813cf8bad</t>
-  </si>
-  <si>
-    <t>relationship--3033037c-fef3-4d96-813e-d8a7980b99e5</t>
-  </si>
-  <si>
-    <t>relationship--143addc8-05a7-4bee-86b9-3337a863ec39</t>
-  </si>
-  <si>
-    <t>relationship--8a78bdcb-4e44-42e2-a34b-50b8384f9f73</t>
-  </si>
-  <si>
-    <t>relationship--0f4f7d1c-4bb1-41b0-a38a-be78290b16ad</t>
-  </si>
-  <si>
-    <t>relationship--0b36e1b9-6afa-4d2f-99f0-f25e3b07db0e</t>
-  </si>
-  <si>
-    <t>relationship--e63e4d7b-c694-4745-b962-5d8996eb4c8b</t>
-  </si>
-  <si>
-    <t>relationship--ecd45553-0574-48e3-9d62-a8b3a2c7e8f1</t>
-  </si>
-  <si>
-    <t>relationship--412888ef-d3ea-4be2-b8e1-dcc669ce48d6</t>
-  </si>
-  <si>
-    <t>relationship--30e59906-de9f-4474-aeec-79047286892c</t>
-  </si>
-  <si>
-    <t>relationship--902336a4-a692-4b3e-a361-69f8a1c28740</t>
-  </si>
-  <si>
-    <t>relationship--3eee01b4-8a80-45a4-a3f3-90feba416a59</t>
-  </si>
-  <si>
-    <t>relationship--3ce40bd5-b872-4904-95cc-f299025737c8</t>
-  </si>
-  <si>
-    <t>relationship--925bf850-b760-433d-8723-d2bc3b636e74</t>
-  </si>
-  <si>
-    <t>relationship--31c37f52-a3e2-4f8f-9f99-dc343cbdad21</t>
-  </si>
-  <si>
-    <t>relationship--2c3bd1b7-40a5-4521-be24-0c22e547dbf1</t>
-  </si>
-  <si>
-    <t>relationship--b87c67f3-127e-40e5-86d5-f91b2be3b539</t>
-  </si>
-  <si>
-    <t>relationship--991ece69-cc42-4b59-9990-2efca8dbf30e</t>
-  </si>
-  <si>
-    <t>relationship--3ef64c26-e295-4bd2-b674-b6281b71840f</t>
-  </si>
-  <si>
-    <t>relationship--43b0d444-f418-41c5-8790-f3439d8cd88c</t>
-  </si>
-  <si>
-    <t>relationship--33672ceb-3671-49e5-83f7-dcbe7559c300</t>
-  </si>
-  <si>
-    <t>relationship--c91891ac-a92e-4cf8-a452-542b7352d145</t>
-  </si>
-  <si>
-    <t>relationship--6d216d85-ad66-46fc-b661-d32bff224cd6</t>
-  </si>
-  <si>
-    <t>relationship--2e4becea-8336-41f3-ad54-737f34ef26a8</t>
-  </si>
-  <si>
-    <t>relationship--32fb1611-c6a5-4a0d-9819-46e8698d769e</t>
-  </si>
-  <si>
-    <t>relationship--761f15a5-eb0c-4f1e-9e73-3d0596fe07e8</t>
-  </si>
-  <si>
-    <t>relationship--4ea0d623-932e-4e48-af98-f1e6ba2e5b17</t>
-  </si>
-  <si>
-    <t>relationship--6886f1eb-05f0-4023-ba8d-f81e518675cd</t>
-  </si>
-  <si>
-    <t>relationship--d4afa407-2dd2-479c-8708-1f90c8f4bdb8</t>
-  </si>
-  <si>
-    <t>relationship--947991a0-245d-4a51-927b-8d61740b26f0</t>
-  </si>
-  <si>
-    <t>relationship--015c68e0-2447-4052-ab4f-48a7a243eb3e</t>
-  </si>
-  <si>
-    <t>relationship--68256c4c-b1f7-44ec-8f56-3f85de397fff</t>
-  </si>
-  <si>
-    <t>relationship--18746c33-0368-476b-be25-fa41d2a7f485</t>
-  </si>
-  <si>
-    <t>relationship--b4912da7-0874-4dd6-b2dd-1635eaed8fcd</t>
-  </si>
-  <si>
-    <t>relationship--5bb29cd9-00b8-41ee-bea7-f6c74b0d32e2</t>
-  </si>
-  <si>
-    <t>relationship--7d253c66-0f12-45fd-8ff9-aa011da24823</t>
-  </si>
-  <si>
-    <t>relationship--8cba890a-6fcd-4b5e-b4b5-96094f268ef3</t>
-  </si>
-  <si>
-    <t>relationship--16b6d2c5-e363-4d21-a7db-2b97f1bf70cc</t>
-  </si>
-  <si>
-    <t>relationship--b8930c35-bb1f-472e-9b98-68b5c31bf601</t>
-  </si>
-  <si>
-    <t>relationship--6476c7ec-1aa8-4f13-bb4a-81e18691f424</t>
-  </si>
-  <si>
-    <t>relationship--995c2a4f-87f2-4994-a5b6-fe0e96f25048</t>
-  </si>
-  <si>
-    <t>relationship--86ebcf64-0e77-4cf8-89d3-4e5b050a03b1</t>
-  </si>
-  <si>
-    <t>relationship--5ab853b7-55d3-494d-9ffe-ae92bc46cf55</t>
-  </si>
-  <si>
-    <t>relationship--751c8764-eb2b-4703-af80-4fc25f16732d</t>
-  </si>
-  <si>
-    <t>relationship--7217709d-b258-4678-8762-2bacb28f39d6</t>
-  </si>
-  <si>
-    <t>relationship--cf145d53-ef3a-4459-b9d0-7a196c9286ef</t>
-  </si>
-  <si>
-    <t>relationship--3d845794-54d8-4533-aa90-f0bb4c2ad893</t>
-  </si>
-  <si>
-    <t>relationship--4c19aef1-bf9d-4288-a5b7-9ea10ffce5ef</t>
-  </si>
-  <si>
-    <t>relationship--ca826c66-7588-4851-a7d1-b45343e9555e</t>
-  </si>
-  <si>
-    <t>relationship--a8358b26-7527-4037-8a4b-4923288f0087</t>
-  </si>
-  <si>
-    <t>relationship--f64dc46c-7643-4ccd-94d1-8528179eba98</t>
-  </si>
-  <si>
-    <t>relationship--d98b4866-7e16-47f5-b387-0c0626b03f9b</t>
-  </si>
-  <si>
-    <t>relationship--22229d83-2ac9-4edb-b2c5-b854b3f88ab4</t>
-  </si>
-  <si>
-    <t>relationship--3cb23b20-9cc7-4653-adbc-7368e57f16c3</t>
-  </si>
-  <si>
-    <t>relationship--229efd10-98e7-4a11-9155-51b71aa157c6</t>
-  </si>
-  <si>
-    <t>relationship--d94e4896-296d-413b-b8a5-aaae58b8c227</t>
-  </si>
-  <si>
-    <t>relationship--1591890b-bb90-40a9-acdb-67d083855908</t>
-  </si>
-  <si>
-    <t>relationship--8ca9e6b6-3e2e-4d6c-9e0e-c9add8273970</t>
-  </si>
-  <si>
-    <t>relationship--1c5c1a59-b734-44d6-8b3f-9c235f2c5bfd</t>
-  </si>
-  <si>
-    <t>relationship--f8a05993-9ed7-43a9-ac7c-68fd7b3312da</t>
-  </si>
-  <si>
-    <t>relationship--dff41b02-1d66-4150-9261-253d25ba0fd4</t>
-  </si>
-  <si>
-    <t>relationship--44ef8e57-59ed-4c70-8fc2-1a0d7703ff1f</t>
-  </si>
-  <si>
-    <t>relationship--edcaab56-cfda-406e-9d54-6000819b7781</t>
-  </si>
-  <si>
-    <t>relationship--f43cad46-206e-48ac-8caf-1f114f79a146</t>
-  </si>
-  <si>
-    <t>relationship--0b3e9744-af12-43ae-8ed3-0da51ac28ecb</t>
-  </si>
-  <si>
-    <t>relationship--a0476600-c757-4e35-a618-6fbc922264e0</t>
-  </si>
-  <si>
-    <t>relationship--1367b947-1a96-4495-86c1-fc23b17fb31e</t>
-  </si>
-  <si>
-    <t>relationship--eaab5c2a-ba23-4acd-a57a-08fd0938d8a6</t>
-  </si>
-  <si>
-    <t>relationship--7167e1e3-c7ff-42e6-9c07-044833456057</t>
-  </si>
-  <si>
-    <t>relationship--9a93efc6-a38f-4ee5-884d-ec95078750de</t>
-  </si>
-  <si>
-    <t>relationship--5d8f7aee-ac7d-45b1-9256-3b131cedfda8</t>
-  </si>
-  <si>
-    <t>relationship--47630274-0db8-4183-8fc0-87ec8e6b718b</t>
-  </si>
-  <si>
-    <t>relationship--f0494bf1-fe40-494c-818f-5b5e467f388d</t>
-  </si>
-  <si>
-    <t>relationship--8297ffa0-03ac-47eb-bb16-c2f8b9607e13</t>
-  </si>
-  <si>
-    <t>relationship--b60e5de2-8c56-4a3a-afa2-7fb34a165cf1</t>
-  </si>
-  <si>
-    <t>relationship--7c20a5a3-fecc-4b29-a1da-7b1c901c8e19</t>
-  </si>
-  <si>
-    <t>relationship--f2ea6d1e-7570-4168-bb67-0dc33e5a3f61</t>
-  </si>
-  <si>
-    <t>relationship--5ddcc75d-d2f4-48cf-b379-8ddf2f0f606a</t>
-  </si>
-  <si>
-    <t>relationship--20bea039-6851-4b81-a045-a23fdce4d506</t>
-  </si>
-  <si>
-    <t>relationship--4674608e-f570-453f-aebe-b9b4475cf4fc</t>
-  </si>
-  <si>
-    <t>relationship--efe7d12b-ca4d-4f02-8c7f-b09e2a5d2c1e</t>
-  </si>
-  <si>
-    <t>relationship--13498d2d-83e7-455e-99dd-d83f05e32d5e</t>
-  </si>
-  <si>
-    <t>relationship--2edbb763-d1c0-40e1-a56c-2d0ccd6b50ee</t>
-  </si>
-  <si>
-    <t>relationship--165f81ae-e0b9-4677-8404-de09964c0ba0</t>
-  </si>
-  <si>
-    <t>relationship--b5d52bba-f379-4ee8-993e-2fb423d4ad86</t>
-  </si>
-  <si>
-    <t>relationship--c6a75f1a-b1df-4d90-a771-a9639fa6bb89</t>
-  </si>
-  <si>
-    <t>relationship--8d43b917-8749-4354-925e-6c4778d35f8c</t>
-  </si>
-  <si>
-    <t>relationship--b9322a2e-94ac-4e4a-aa96-2d42bf0cb09b</t>
-  </si>
-  <si>
-    <t>relationship--64c61bba-81d1-4a2c-951f-1f018d2bdf00</t>
-  </si>
-  <si>
-    <t>relationship--126bd1e1-a5dd-4707-9314-bae241a94d3d</t>
-  </si>
-  <si>
-    <t>relationship--819e6ffd-13a0-4029-be94-1a58cadc5591</t>
-  </si>
-  <si>
-    <t>relationship--69aad23c-6d19-4a08-86fd-d978b7d49691</t>
-  </si>
-  <si>
-    <t>relationship--e3b0f38a-d667-4764-a684-e3a62e862f5a</t>
-  </si>
-  <si>
-    <t>relationship--5f12a18d-e834-4804-8692-c50197fed795</t>
-  </si>
-  <si>
-    <t>relationship--2434c1c4-7978-41b7-a9c0-2c24cf00f15b</t>
+    <t>relationship--d1d83ac8-0e25-4bdd-b15b-95cc168bb4c2</t>
+  </si>
+  <si>
+    <t>relationship--6b1bda47-c8f5-4e82-97d9-ce1d70abac84</t>
+  </si>
+  <si>
+    <t>relationship--bf8fb95c-7dcf-48e1-ac39-092b8c09ef22</t>
+  </si>
+  <si>
+    <t>relationship--ed3611c8-15b3-4fd9-b556-0da6f31c3f95</t>
+  </si>
+  <si>
+    <t>relationship--0333ad4f-93ae-4b60-b120-c0c25e136b7d</t>
+  </si>
+  <si>
+    <t>relationship--12e78d5d-98a9-452c-956f-05b920dfed00</t>
+  </si>
+  <si>
+    <t>relationship--ca9e3222-93f6-471d-adf7-f626b6380847</t>
+  </si>
+  <si>
+    <t>relationship--9bfe7ed5-0e6f-4ec4-b223-1c7bf1dc501f</t>
+  </si>
+  <si>
+    <t>relationship--cd887f53-86f1-44a6-a32c-93938867f265</t>
+  </si>
+  <si>
+    <t>relationship--e1233097-29bf-4a0c-8704-bd04567404f4</t>
+  </si>
+  <si>
+    <t>relationship--6f83af4b-2012-4508-967e-21e688d7705c</t>
+  </si>
+  <si>
+    <t>relationship--772fe196-85c9-410e-ad3d-096bcf4edc32</t>
+  </si>
+  <si>
+    <t>relationship--4e4da0bf-de90-4f61-ad14-ca2715784f3a</t>
+  </si>
+  <si>
+    <t>relationship--246145bc-64f3-41fe-96ec-1f6b95a86eb9</t>
+  </si>
+  <si>
+    <t>relationship--ccb7229e-9e17-4cca-ae1d-f4561a0c12d7</t>
+  </si>
+  <si>
+    <t>relationship--43ba5a67-5c11-4053-9400-da8aa3cba390</t>
+  </si>
+  <si>
+    <t>relationship--94657d33-1fa9-4c28-ad03-99335ebc4684</t>
+  </si>
+  <si>
+    <t>relationship--e15d31c8-27ef-4533-b79f-856edfeb3fac</t>
+  </si>
+  <si>
+    <t>relationship--bb41156c-c4c6-4002-8c34-f6ee5284bee4</t>
+  </si>
+  <si>
+    <t>relationship--1276c8a8-dabc-4d0a-b1f4-46013ed61d49</t>
+  </si>
+  <si>
+    <t>relationship--92f2ed6e-cdf8-4be7-b023-7b0e306c5fcd</t>
+  </si>
+  <si>
+    <t>relationship--4ba92107-af63-4626-9a8c-c0d764d8e697</t>
+  </si>
+  <si>
+    <t>relationship--c509caa3-b103-4496-ad4f-d94919392e87</t>
+  </si>
+  <si>
+    <t>relationship--9c542c60-6015-4dad-b3f2-7a0cf84239c3</t>
+  </si>
+  <si>
+    <t>relationship--32ee9ec6-8762-44cd-bb6c-c3114cbe7b36</t>
+  </si>
+  <si>
+    <t>relationship--5da1b46c-17bb-455b-b34d-74ea0cc8665d</t>
+  </si>
+  <si>
+    <t>relationship--2f96354e-152f-448f-a90d-4b7887e95aee</t>
+  </si>
+  <si>
+    <t>relationship--36b8a861-90fa-4ffd-a9b0-63c270c2f778</t>
+  </si>
+  <si>
+    <t>relationship--0b372773-6497-4b0e-9f1d-4dc24b4781da</t>
+  </si>
+  <si>
+    <t>relationship--838664aa-2132-45f7-be9a-966f5c0f0436</t>
+  </si>
+  <si>
+    <t>relationship--e756619b-3edc-4f9d-87e4-041fa8d9b9e1</t>
+  </si>
+  <si>
+    <t>relationship--e33b718e-2bce-4f6c-a4ff-54b324bb829d</t>
+  </si>
+  <si>
+    <t>relationship--bb817c1d-eff0-4142-b03a-bd8b45a64393</t>
+  </si>
+  <si>
+    <t>relationship--e8039964-d4f6-4900-b51e-d0811ca7b8bc</t>
+  </si>
+  <si>
+    <t>relationship--0124e380-8d02-42e4-ab40-c6bd79bd81ed</t>
+  </si>
+  <si>
+    <t>relationship--a30c4afe-a72a-477b-96c7-7cf3b5447579</t>
+  </si>
+  <si>
+    <t>relationship--4b28e17b-5512-4a2a-a1b2-0df7a5c8e9d1</t>
+  </si>
+  <si>
+    <t>relationship--398fc58c-31f3-4c3f-9f29-b7cbf75834d6</t>
+  </si>
+  <si>
+    <t>relationship--28369a62-f753-4996-8b25-64f7692ad365</t>
+  </si>
+  <si>
+    <t>relationship--f30c2820-d2fa-42ee-8782-861b4db8d055</t>
+  </si>
+  <si>
+    <t>relationship--5b420453-d8c4-43ae-ad19-0af007aa14f8</t>
+  </si>
+  <si>
+    <t>relationship--c3ac11bf-df0f-4c5f-82cf-f30288612326</t>
+  </si>
+  <si>
+    <t>relationship--289edc59-ba1f-4126-a45b-0dd6ad7b9489</t>
+  </si>
+  <si>
+    <t>relationship--c63b664d-b6e1-4a78-bacf-feb72a849a79</t>
+  </si>
+  <si>
+    <t>relationship--5e2ee969-6a0a-4687-8ad1-89c12f0b9d2b</t>
+  </si>
+  <si>
+    <t>relationship--fda754fa-d99a-4932-82ba-98de7f53c027</t>
+  </si>
+  <si>
+    <t>relationship--9a37c9fb-0802-43db-9618-f2d7a26ce90e</t>
+  </si>
+  <si>
+    <t>relationship--42a66c9f-70c5-4a47-ab34-97a2ccdfb367</t>
+  </si>
+  <si>
+    <t>relationship--51e41bd9-4beb-4928-9e8e-1889a9129e3a</t>
+  </si>
+  <si>
+    <t>relationship--fd590fab-8bb6-4092-ad60-6cb3cb076984</t>
+  </si>
+  <si>
+    <t>relationship--4227a317-653b-4ee7-a078-32685904a678</t>
+  </si>
+  <si>
+    <t>relationship--3e5cd5ec-e680-483f-92f7-17c872f823ca</t>
+  </si>
+  <si>
+    <t>relationship--e560cf6c-5a39-4046-88a1-401d1e2da616</t>
+  </si>
+  <si>
+    <t>relationship--7d2776f3-eda6-40bb-baa6-223ea41cb1e6</t>
+  </si>
+  <si>
+    <t>relationship--cf686984-8370-4fff-8150-22078049ff5a</t>
+  </si>
+  <si>
+    <t>relationship--5cf8fcc2-17bb-40dc-866c-a5cb479e99f7</t>
+  </si>
+  <si>
+    <t>relationship--2e8fec67-bd59-4314-a9f2-f3eb527c2dde</t>
+  </si>
+  <si>
+    <t>relationship--d49bc92a-830b-4a36-a140-96091480946c</t>
+  </si>
+  <si>
+    <t>relationship--493d2886-0dec-4aba-874a-bf90a4636b78</t>
+  </si>
+  <si>
+    <t>relationship--ad18a4a7-bc9d-43a8-b3d4-6657c00a0622</t>
+  </si>
+  <si>
+    <t>relationship--961e92e0-224b-4d0d-a100-05c55bbe2df0</t>
+  </si>
+  <si>
+    <t>relationship--fda0dc9f-c73a-49a1-93a8-ec70f716c59c</t>
+  </si>
+  <si>
+    <t>relationship--09098c09-cd36-4d6c-8243-7bc65e4eab5e</t>
+  </si>
+  <si>
+    <t>relationship--825181a6-6f22-461d-b00b-53a5c0486d06</t>
+  </si>
+  <si>
+    <t>relationship--451dda86-097e-4d6b-b678-6cba4a5be2b7</t>
+  </si>
+  <si>
+    <t>relationship--2c9f9096-52e3-407f-82b2-e1349f213147</t>
+  </si>
+  <si>
+    <t>relationship--2e159f79-6818-4dfa-8920-6f671d8f7122</t>
+  </si>
+  <si>
+    <t>relationship--e5f16b72-a632-4b28-8359-4969c7a335c4</t>
+  </si>
+  <si>
+    <t>relationship--615e816e-2e68-4aa8-a6d9-4b87e430dc3c</t>
+  </si>
+  <si>
+    <t>relationship--43aa00e0-975d-4b63-b31b-6e26b974f22a</t>
+  </si>
+  <si>
+    <t>relationship--2c8c0aa1-1f93-4566-92d9-af16a72c0f09</t>
+  </si>
+  <si>
+    <t>relationship--71368caa-7c1a-4521-bd44-3aa0b133a333</t>
+  </si>
+  <si>
+    <t>relationship--fa623641-9464-4e79-996c-5668a540ba9b</t>
+  </si>
+  <si>
+    <t>relationship--73e5a790-93ea-4629-80f4-54c3e617144e</t>
+  </si>
+  <si>
+    <t>relationship--dc92657f-b6f7-4520-8b76-f94b5578f7c4</t>
+  </si>
+  <si>
+    <t>relationship--4cd522f2-efb9-466f-ba80-c9259a222e1a</t>
+  </si>
+  <si>
+    <t>relationship--7946bf70-900f-4783-a0aa-c928764cce0f</t>
+  </si>
+  <si>
+    <t>relationship--e6a1dd08-774b-44f0-85c6-6ed7c759faf0</t>
+  </si>
+  <si>
+    <t>relationship--386c7245-2809-4337-8f75-6189cbcd7b57</t>
+  </si>
+  <si>
+    <t>relationship--a1594bcd-c85c-496f-9f37-993db53ab577</t>
+  </si>
+  <si>
+    <t>relationship--d539761c-1508-4a59-b6e1-815850c37c4d</t>
+  </si>
+  <si>
+    <t>relationship--8e3c9748-267e-46f2-af3d-4304533f4b9d</t>
+  </si>
+  <si>
+    <t>relationship--077ae38e-76d0-4d4c-80a7-46ad0cf7325d</t>
+  </si>
+  <si>
+    <t>relationship--083ff325-7e2c-4726-af93-9a3423883278</t>
+  </si>
+  <si>
+    <t>relationship--fd2cdff6-df64-4e6b-aa55-524e80db0871</t>
+  </si>
+  <si>
+    <t>relationship--886b2d02-fc5d-4be8-b914-d126d7f59041</t>
+  </si>
+  <si>
+    <t>relationship--742e58ab-e583-43c2-90e3-7a9f42cb4aa3</t>
+  </si>
+  <si>
+    <t>relationship--fd491e7a-af8d-4a0f-a93b-0b68b4ec5ef8</t>
+  </si>
+  <si>
+    <t>relationship--0a74b93c-6f7b-49d3-a8f2-1a4dfe3fd1e8</t>
+  </si>
+  <si>
+    <t>relationship--a650661b-c8f0-422a-ac66-6b362797e8c8</t>
+  </si>
+  <si>
+    <t>relationship--2e9efbf3-3a02-476a-983a-0842963ffdd3</t>
+  </si>
+  <si>
+    <t>relationship--98ee9481-4eef-44c5-b0a5-78e65858cda4</t>
+  </si>
+  <si>
+    <t>relationship--d0c699e7-f7e1-4f4e-8d30-95711d36cd8e</t>
+  </si>
+  <si>
+    <t>relationship--915a971b-e570-4cf0-bf5a-262b77524af7</t>
+  </si>
+  <si>
+    <t>relationship--9547c90d-2cdb-474b-af37-7815387746ce</t>
+  </si>
+  <si>
+    <t>relationship--95fd47a1-66c4-4cb2-a50b-a54a425cfb22</t>
+  </si>
+  <si>
+    <t>relationship--03d10c28-5853-4702-80d5-89d337266bb1</t>
+  </si>
+  <si>
+    <t>relationship--c5d53ea2-69dd-46eb-bce2-9e940e1a1095</t>
+  </si>
+  <si>
+    <t>relationship--24f7dc64-f10b-4a7d-a641-09421e22d5db</t>
+  </si>
+  <si>
+    <t>relationship--af80af2a-a71e-44a4-8ef5-53e5e946f850</t>
+  </si>
+  <si>
+    <t>relationship--e95ab25e-eae2-4d51-82b8-47948fb7be92</t>
+  </si>
+  <si>
+    <t>relationship--c5c59cc8-26ad-45ba-b653-4c90e2ac9df3</t>
+  </si>
+  <si>
+    <t>relationship--2ae1dde1-0799-4f76-b6c3-98063921d479</t>
+  </si>
+  <si>
+    <t>relationship--b833f03b-e6a3-4dd6-9f80-57a93883ce7d</t>
+  </si>
+  <si>
+    <t>relationship--ff1b5e58-d274-46ce-9a39-18114ef275ca</t>
+  </si>
+  <si>
+    <t>relationship--738bc5da-8c04-4a6e-8b53-738407fa0538</t>
+  </si>
+  <si>
+    <t>relationship--785206e9-653e-456d-a858-539339c3497b</t>
+  </si>
+  <si>
+    <t>relationship--7673f50d-865a-453f-a6d0-34bf1344ffbb</t>
+  </si>
+  <si>
+    <t>relationship--618c31dc-1b31-48dd-954d-884f670969ab</t>
+  </si>
+  <si>
+    <t>relationship--9decedad-c8c0-407e-9e61-7262e5faec22</t>
+  </si>
+  <si>
+    <t>relationship--2d17d162-049d-4542-8355-3c771bd149bb</t>
+  </si>
+  <si>
+    <t>relationship--e339a4ba-45ed-43e7-afa1-f4d988393f96</t>
+  </si>
+  <si>
+    <t>relationship--1a15d373-ae2f-4812-9915-c361b2d5ca02</t>
+  </si>
+  <si>
+    <t>relationship--85d3516c-6941-4107-95f0-acc7e505a48f</t>
+  </si>
+  <si>
+    <t>relationship--164d37cc-bd42-4def-a68d-584685c1d39f</t>
+  </si>
+  <si>
+    <t>relationship--b1e35c8d-e9d8-44c5-a48d-f651e8b70c62</t>
+  </si>
+  <si>
+    <t>relationship--803f590e-f696-4323-b661-7d62919241ae</t>
+  </si>
+  <si>
+    <t>relationship--8126cac9-53bf-4b0e-a5db-bdfaed7d2468</t>
+  </si>
+  <si>
+    <t>relationship--5a452beb-c150-43a0-a23e-bee2129bba7c</t>
+  </si>
+  <si>
+    <t>relationship--0038576b-ad37-4829-9cee-3b07824b5183</t>
+  </si>
+  <si>
+    <t>relationship--432c4baa-c3cc-47d8-8730-0401b123587f</t>
+  </si>
+  <si>
+    <t>relationship--3b2fc822-39e2-48cf-9975-1f31e8f29a6b</t>
+  </si>
+  <si>
+    <t>relationship--f080199d-5ed4-4182-b8e4-fd54d3a1b7b3</t>
+  </si>
+  <si>
+    <t>relationship--c34e6b22-8dc9-486b-afb3-d1787c6b312d</t>
+  </si>
+  <si>
+    <t>relationship--05b1d861-e15d-40db-9e95-57ffd84da00c</t>
+  </si>
+  <si>
+    <t>relationship--c6b6b450-f8dd-4884-8e86-fdc9aaba6548</t>
+  </si>
+  <si>
+    <t>relationship--3343aeb7-6c2b-41dd-835e-276c452f9413</t>
+  </si>
+  <si>
+    <t>relationship--dbdf93c6-45ea-484c-a36d-c0cf71e819d2</t>
+  </si>
+  <si>
+    <t>relationship--d521aa14-0004-4718-9969-4c0d948bf862</t>
+  </si>
+  <si>
+    <t>relationship--dd5a7368-3ab0-4263-b115-27276f5bf765</t>
+  </si>
+  <si>
+    <t>relationship--1ad7045d-2bff-4bf2-8f5f-f4ac8b9ab69a</t>
+  </si>
+  <si>
+    <t>relationship--544bf625-076e-44df-aff0-4a7ddee73181</t>
+  </si>
+  <si>
+    <t>relationship--b81a6028-70ee-4c17-8e6b-908f30227b29</t>
+  </si>
+  <si>
+    <t>relationship--1f4a010b-078b-46a1-90f0-f810af387ef9</t>
+  </si>
+  <si>
+    <t>relationship--035a5b2f-00e0-4491-aa10-769745b28122</t>
+  </si>
+  <si>
+    <t>relationship--030ea514-ae1a-4a51-8ab0-6d4cee4bd910</t>
+  </si>
+  <si>
+    <t>relationship--105d1e70-ccc5-4aeb-aa4b-3a6a9d868e57</t>
+  </si>
+  <si>
+    <t>relationship--c94af27a-fd95-4e3a-87fd-427db96cd89c</t>
+  </si>
+  <si>
+    <t>relationship--539d3d5c-1f47-4549-a4bf-eb6d1cc18158</t>
+  </si>
+  <si>
+    <t>relationship--980ca3cd-bebf-4b61-81ba-8d4e16fd531c</t>
+  </si>
+  <si>
+    <t>relationship--d0f30a13-b14d-49c1-87d0-7a3352009c84</t>
+  </si>
+  <si>
+    <t>relationship--ac5f836e-f0d8-43d7-98e8-82df545a6383</t>
+  </si>
+  <si>
+    <t>relationship--9c247288-da5e-4364-a991-c2df2fcbef82</t>
+  </si>
+  <si>
+    <t>relationship--9643a4e3-4478-4172-9b10-2a8908404ac8</t>
+  </si>
+  <si>
+    <t>relationship--660a1d88-ae37-4bb8-b4f7-d8e47ee43d6e</t>
+  </si>
+  <si>
+    <t>relationship--60c5bbec-2e1f-41f5-941f-38245acb2c3c</t>
+  </si>
+  <si>
+    <t>relationship--718904b7-6d34-4e19-82e8-80ecd0288e7a</t>
+  </si>
+  <si>
+    <t>relationship--da00ddb9-5b8d-4944-8776-c63074652ded</t>
+  </si>
+  <si>
+    <t>relationship--fae8efb4-73e8-481c-9e2b-3bc97970eb09</t>
+  </si>
+  <si>
+    <t>relationship--3db7f257-b1c2-4516-8e03-c308dddca80e</t>
+  </si>
+  <si>
+    <t>relationship--590d09fc-1c18-4d7f-82eb-858e976d2d34</t>
+  </si>
+  <si>
+    <t>relationship--cad5117a-19ed-4276-ae16-3459de3cafaa</t>
+  </si>
+  <si>
+    <t>relationship--fb1a8dc9-9c6f-4c5c-81cc-b8beecfe2f95</t>
+  </si>
+  <si>
+    <t>relationship--59208651-47b9-479d-9218-d2b9a6be55e6</t>
+  </si>
+  <si>
+    <t>relationship--056e5ab5-5cd2-4155-ad00-b9b25e9ed4c0</t>
+  </si>
+  <si>
+    <t>relationship--1fd12b6e-338f-4ba4-8aab-3e125e332365</t>
+  </si>
+  <si>
+    <t>relationship--0c4624f9-aebb-445d-83fb-d5beca048c4f</t>
+  </si>
+  <si>
+    <t>relationship--26a21cd9-b6ed-4376-a465-990e47c4679f</t>
+  </si>
+  <si>
+    <t>relationship--ff2d811b-4899-449c-9d5b-1f8c7bf3181f</t>
+  </si>
+  <si>
+    <t>relationship--8fb2422e-2ee8-4c8a-b5c8-ba0c49bee662</t>
+  </si>
+  <si>
+    <t>relationship--8666d4aa-5d31-410e-963c-85247ae40b50</t>
+  </si>
+  <si>
+    <t>relationship--aa2c19c7-f295-4ae2-ae24-f58f5c1c291d</t>
+  </si>
+  <si>
+    <t>relationship--a4acfd54-5036-4903-959b-657fe1d89b88</t>
+  </si>
+  <si>
+    <t>relationship--953285c6-7360-401e-ba21-f0e8256b087b</t>
+  </si>
+  <si>
+    <t>relationship--14b8bd10-9560-4896-9a8d-63b904117d8d</t>
+  </si>
+  <si>
+    <t>relationship--15509597-3596-412c-bab6-beb0c5c0e940</t>
+  </si>
+  <si>
+    <t>relationship--02bdccaa-b995-41f1-95e9-304f0b87553e</t>
+  </si>
+  <si>
+    <t>relationship--54c09e78-74d9-4aec-838b-7da4ae40bb27</t>
+  </si>
+  <si>
+    <t>relationship--54a73fa9-c095-4ad0-977d-1981fd285365</t>
+  </si>
+  <si>
+    <t>relationship--73a26884-8e1f-4ea0-ad5f-c7ae54d7b353</t>
+  </si>
+  <si>
+    <t>relationship--34bccc2c-e7f2-48a0-8bfb-36783eb1cb15</t>
+  </si>
+  <si>
+    <t>relationship--37664c50-f0ea-495b-bbc0-23fa83db3d4e</t>
+  </si>
+  <si>
+    <t>relationship--4df1c14a-2ab5-455b-856d-776e734e0fa6</t>
+  </si>
+  <si>
+    <t>relationship--2d347c81-7b87-491d-9182-542bace23ca0</t>
+  </si>
+  <si>
+    <t>relationship--6c11bd59-b127-442c-892b-b2bc63d25534</t>
+  </si>
+  <si>
+    <t>relationship--c37dd277-dd17-4f01-934d-7db013b0f903</t>
+  </si>
+  <si>
+    <t>relationship--35147246-29e1-4d4d-9498-e76d0ad616a4</t>
+  </si>
+  <si>
+    <t>relationship--d6708d60-1811-4991-b6d2-e6cd488640eb</t>
+  </si>
+  <si>
+    <t>relationship--38362761-d7e6-45ad-ab47-2d44282f4162</t>
+  </si>
+  <si>
+    <t>relationship--f8db3b7a-c558-4319-b98d-b244ec6fb986</t>
+  </si>
+  <si>
+    <t>relationship--ed905254-ca0c-4d44-a138-182ac87ece98</t>
+  </si>
+  <si>
+    <t>relationship--8d493615-f90b-4252-bdcb-ff9e0c8d2f7f</t>
+  </si>
+  <si>
+    <t>relationship--cd22f3ba-28d1-4d68-8e5a-ba2d1f4eefac</t>
+  </si>
+  <si>
+    <t>relationship--44a19956-97e2-4c8e-8189-00f62314df6d</t>
+  </si>
+  <si>
+    <t>relationship--45003d69-4d4e-46cd-99c9-802c4e2ec000</t>
+  </si>
+  <si>
+    <t>relationship--7ebc03e0-3726-4ea1-900b-a27a5b164a68</t>
+  </si>
+  <si>
+    <t>relationship--cc016a60-e59c-4d69-b687-c7c5f3b205d7</t>
+  </si>
+  <si>
+    <t>relationship--b3ad7d67-1f2b-4093-a560-81f1d25a7689</t>
+  </si>
+  <si>
+    <t>relationship--3fcb8197-e536-4f80-8d7e-98442b97d9d2</t>
+  </si>
+  <si>
+    <t>relationship--00acbf85-ab54-4a73-a858-fabd7c8f4f18</t>
+  </si>
+  <si>
+    <t>relationship--7365713a-afc8-440d-820d-32efec8bc1d1</t>
+  </si>
+  <si>
+    <t>relationship--09b2571b-5c56-4580-b590-7ccea05dc6e6</t>
+  </si>
+  <si>
+    <t>relationship--2ab05e8a-a1b9-49ee-a095-4b3aeba61101</t>
+  </si>
+  <si>
+    <t>relationship--67963316-9796-4de4-8d36-b24118e1e6e5</t>
+  </si>
+  <si>
+    <t>relationship--4791b0b6-0a4a-4b45-bb95-c9c38e179f20</t>
+  </si>
+  <si>
+    <t>relationship--8f47af4f-e378-4438-9624-8ddbbe1692a3</t>
+  </si>
+  <si>
+    <t>relationship--fcacbf3d-8711-4978-b841-0a7d9c7aa95b</t>
+  </si>
+  <si>
+    <t>relationship--804aad46-ea85-4238-9989-711bd7aad718</t>
+  </si>
+  <si>
+    <t>relationship--dc19a1cf-cd7b-4ed4-833a-e0221f9b0d06</t>
+  </si>
+  <si>
+    <t>relationship--68e15c27-41a7-463d-9e55-238ed91a7d94</t>
+  </si>
+  <si>
+    <t>relationship--34e64631-b56a-4993-86ce-662b8012f987</t>
+  </si>
+  <si>
+    <t>relationship--c65d9633-a79d-47b5-963d-d32530cadfc7</t>
+  </si>
+  <si>
+    <t>relationship--007ad286-9577-492d-b5a6-750fd01e425d</t>
+  </si>
+  <si>
+    <t>relationship--ff489e5f-746f-46d1-979b-31c9caeba2cf</t>
+  </si>
+  <si>
+    <t>relationship--a5d36949-e228-45de-bae2-74ae94d6c7e5</t>
+  </si>
+  <si>
+    <t>relationship--3bebe1d5-7871-46cb-9e77-6633b26f30ea</t>
+  </si>
+  <si>
+    <t>relationship--9b2211ad-9c77-4291-b931-e1507c956e35</t>
+  </si>
+  <si>
+    <t>relationship--b25a1a09-40ff-4f55-bd45-f4862dbe3c2a</t>
+  </si>
+  <si>
+    <t>relationship--750bec3c-54b8-4a76-9d83-033c41a7a366</t>
+  </si>
+  <si>
+    <t>relationship--130e6e26-2be5-486e-8366-9b56df79c96b</t>
+  </si>
+  <si>
+    <t>relationship--6f160130-4dab-4146-958f-46a9e7472acd</t>
+  </si>
+  <si>
+    <t>relationship--7441b775-79a6-4c9e-8f64-380970498feb</t>
+  </si>
+  <si>
+    <t>relationship--c79d9f8c-f9c0-49d7-ad80-e9c6506937c6</t>
+  </si>
+  <si>
+    <t>relationship--9cbb9ca8-02eb-48b8-a091-5bad167657b4</t>
+  </si>
+  <si>
+    <t>relationship--07a13764-ce3f-4e54-9635-21bc32366133</t>
+  </si>
+  <si>
+    <t>relationship--c4277db4-7df5-41e4-8800-ef41583deb86</t>
+  </si>
+  <si>
+    <t>relationship--b51f5bae-6fa0-41fb-a593-12423ffc6878</t>
+  </si>
+  <si>
+    <t>relationship--19fce589-5471-4c99-ae55-1955c6b1b3f9</t>
+  </si>
+  <si>
+    <t>relationship--ea410aa6-fcf2-4279-bf0a-8d6252a84f03</t>
+  </si>
+  <si>
+    <t>relationship--f483415c-eb78-44e1-b880-8bc543f6147d</t>
+  </si>
+  <si>
+    <t>relationship--d8213eda-e5a8-44f6-a706-ef5fda70ce5c</t>
+  </si>
+  <si>
+    <t>relationship--9a63f716-ca63-46d4-93a8-070c3931b652</t>
+  </si>
+  <si>
+    <t>relationship--c8526d69-3050-498f-8bf7-82afc708551c</t>
+  </si>
+  <si>
+    <t>relationship--19400f99-1350-4b02-aeee-d99544909ce4</t>
+  </si>
+  <si>
+    <t>relationship--9b83c94f-6256-4b7e-b6ae-a56405818995</t>
+  </si>
+  <si>
+    <t>relationship--28894c0e-d5a0-4c6d-8bcf-256bb6494582</t>
+  </si>
+  <si>
+    <t>relationship--002ae658-ca18-435b-ba2e-66b1a72fb550</t>
+  </si>
+  <si>
+    <t>relationship--4177ff94-92d2-4f73-8d73-fea1375301f7</t>
+  </si>
+  <si>
+    <t>relationship--6cb741e9-c511-4eac-9f1f-bd5f8cc4c61c</t>
+  </si>
+  <si>
+    <t>relationship--0503052b-ba5f-43a7-b6c1-21c7889a8953</t>
+  </si>
+  <si>
+    <t>relationship--8e6ca00a-ee88-4d7b-98f6-62dbbf2adcbd</t>
+  </si>
+  <si>
+    <t>relationship--b4b24e90-0b8f-4b4a-95c8-ea5a60223b71</t>
+  </si>
+  <si>
+    <t>relationship--dd14d1a2-2767-47b0-bf8e-332b715cee5c</t>
+  </si>
+  <si>
+    <t>relationship--fb41999e-0496-45ab-b7cb-55275c251463</t>
+  </si>
+  <si>
+    <t>relationship--fc430164-5dcc-434a-a63b-47a516df2e31</t>
+  </si>
+  <si>
+    <t>relationship--04ba1965-fb10-410d-b4e8-f409a00e1cb8</t>
+  </si>
+  <si>
+    <t>relationship--bfbd0972-36d5-4903-9870-51b52d60b023</t>
+  </si>
+  <si>
+    <t>relationship--127d02cd-cce5-466d-b20d-8d39acfbf7c5</t>
+  </si>
+  <si>
+    <t>relationship--f73351fc-0bfc-4007-a528-086610528b7c</t>
+  </si>
+  <si>
+    <t>relationship--dba17948-9368-4501-8ab8-35c38ba77ae5</t>
+  </si>
+  <si>
+    <t>relationship--b18d4bb8-2787-4440-ab0a-ce1c07b59ab5</t>
+  </si>
+  <si>
+    <t>relationship--f2eccc39-e1d3-4ada-8a3a-0c34530cb193</t>
+  </si>
+  <si>
+    <t>relationship--09d6a952-c45b-4ceb-aa0e-0b180e5f5a5e</t>
+  </si>
+  <si>
+    <t>relationship--01cb16c4-fdae-453e-afb6-e9a687d7c306</t>
+  </si>
+  <si>
+    <t>relationship--6c7b8ce8-9c08-4ae6-8949-88f480aba78a</t>
+  </si>
+  <si>
+    <t>relationship--91510bf5-d4dc-42a8-bef8-7a3aad6b5569</t>
+  </si>
+  <si>
+    <t>relationship--b050efcf-13c4-4cda-9bdd-1482a443c413</t>
+  </si>
+  <si>
+    <t>relationship--33a91efa-fedb-4999-a33c-abe6dcc4bf62</t>
+  </si>
+  <si>
+    <t>relationship--8dac4f0e-12bc-4eb9-9435-7bf3ff9a3b3f</t>
+  </si>
+  <si>
+    <t>relationship--e1a93e10-0537-4b7e-9ecd-30cd8bb57d29</t>
+  </si>
+  <si>
+    <t>relationship--58ca9597-78bc-4561-83ab-61115672c5cb</t>
+  </si>
+  <si>
+    <t>relationship--77cc1ecd-4bbc-4e3e-a803-33bd60a0c56c</t>
+  </si>
+  <si>
+    <t>relationship--5feb5631-feaa-4fe2-949c-d148e858d700</t>
+  </si>
+  <si>
+    <t>relationship--88189f63-8931-4e11-8925-ff54238d14c2</t>
+  </si>
+  <si>
+    <t>relationship--fea76153-5995-4436-9b9b-594ce5d8ee1d</t>
+  </si>
+  <si>
+    <t>relationship--df171c0b-0668-49c1-9b0e-05564534b0e3</t>
+  </si>
+  <si>
+    <t>relationship--5dc62290-5aae-476d-8a98-3aadd9a6245b</t>
+  </si>
+  <si>
+    <t>relationship--30e0c95d-d69e-4c63-b873-79eac6065267</t>
+  </si>
+  <si>
+    <t>relationship--ac5dbe35-18e8-4255-b087-5eef54b0839d</t>
+  </si>
+  <si>
+    <t>relationship--cc8e78f6-b12e-40e1-999f-f98555d21486</t>
+  </si>
+  <si>
+    <t>relationship--5f95d7f1-60e3-460a-acd4-5ca4d9c94580</t>
+  </si>
+  <si>
+    <t>relationship--017cdc2e-16ae-4bc2-8c23-57704b4167fa</t>
+  </si>
+  <si>
+    <t>relationship--9130a5bc-135a-4eca-bfd6-9024a69618ce</t>
+  </si>
+  <si>
+    <t>relationship--89e7fef0-0475-42db-bd2e-2575c6ec27c9</t>
+  </si>
+  <si>
+    <t>relationship--f5b7ae97-ae81-4b47-84d3-76954a828044</t>
+  </si>
+  <si>
+    <t>relationship--18386dc8-62e0-4061-bf78-4a6e3114483e</t>
+  </si>
+  <si>
+    <t>relationship--adbf1673-7c9f-4a39-85f0-bf9ab6551d8f</t>
+  </si>
+  <si>
+    <t>relationship--c74ae4fd-2865-440d-8f8c-1a4e3ee022fb</t>
+  </si>
+  <si>
+    <t>relationship--d1c805c8-6986-43a5-9703-d1bc1aa61e0b</t>
+  </si>
+  <si>
+    <t>relationship--c8201063-2bb2-48a9-ad6d-7df705eebd3c</t>
+  </si>
+  <si>
+    <t>relationship--7fb9f635-f360-4d2b-885b-8e8355e627bc</t>
+  </si>
+  <si>
+    <t>relationship--633a2219-dabd-4478-b064-c1cd77ff1054</t>
+  </si>
+  <si>
+    <t>relationship--238c9a08-e185-4c27-91bf-70e1182fc4a7</t>
+  </si>
+  <si>
+    <t>relationship--280fa33c-b6ce-4d59-ac2b-90a6dc548dfd</t>
+  </si>
+  <si>
+    <t>relationship--0eaad395-d7d0-4593-aa1d-e05d33814e06</t>
+  </si>
+  <si>
+    <t>relationship--4c14ab18-c81f-4e1b-912c-3679449aa5b4</t>
+  </si>
+  <si>
+    <t>relationship--9b6e4a33-bd7b-400c-9843-b0ddbc3774a4</t>
+  </si>
+  <si>
+    <t>relationship--c93099a0-8e35-4e78-99b2-c96c432e19e7</t>
+  </si>
+  <si>
+    <t>relationship--858c5a81-6c3f-4e99-a4b0-8ee08dc34911</t>
+  </si>
+  <si>
+    <t>relationship--6f5bc71e-d2b5-4b00-aa8f-f3e78f434165</t>
+  </si>
+  <si>
+    <t>relationship--4aad8248-3467-4b1f-b9a5-cb9203827c2f</t>
+  </si>
+  <si>
+    <t>relationship--f21c29f4-05f9-4949-b31e-bc2677a08893</t>
+  </si>
+  <si>
+    <t>relationship--774adc3c-869e-47db-a61f-075b6ab50218</t>
+  </si>
+  <si>
+    <t>relationship--3f648681-a0f4-48ae-b66b-67ed3f1c1ba9</t>
+  </si>
+  <si>
+    <t>relationship--9ba43696-429e-480f-a91b-0d634599e34d</t>
+  </si>
+  <si>
+    <t>relationship--9ffa0fd9-e82f-47df-85dd-9932b555eeec</t>
+  </si>
+  <si>
+    <t>relationship--f3b78dea-530c-4654-ae45-46952b6da479</t>
+  </si>
+  <si>
+    <t>relationship--72bb71a2-8cf5-4c36-87e5-afceeb11b790</t>
+  </si>
+  <si>
+    <t>relationship--209045cc-db6a-4a72-82be-d347c10a97ce</t>
+  </si>
+  <si>
+    <t>relationship--156a7a90-0c2a-4c9f-94e8-da0e453b16a7</t>
+  </si>
+  <si>
+    <t>relationship--5ef52a45-9bf2-42fe-a1fa-cc5a0d8d22fb</t>
+  </si>
+  <si>
+    <t>relationship--95dba43b-6e19-41df-a0a4-1cc83bb421e2</t>
+  </si>
+  <si>
+    <t>relationship--3c66f5cf-357c-4e9b-9ce7-444165f3b2d7</t>
+  </si>
+  <si>
+    <t>relationship--9eff6cb2-0ffc-436c-ac33-649fc6d55982</t>
+  </si>
+  <si>
+    <t>relationship--216b6b0a-21aa-4e66-9e36-d791afba56cb</t>
+  </si>
+  <si>
+    <t>relationship--d744b5e8-b444-4664-bbfa-1f4c60530ef6</t>
+  </si>
+  <si>
+    <t>relationship--7141cceb-aadc-4cdb-a74e-d0573bf7e4fe</t>
+  </si>
+  <si>
+    <t>relationship--d7a1b142-b1dc-4ba6-9177-7e76c9e883c5</t>
+  </si>
+  <si>
+    <t>relationship--5e4d4203-65a1-456e-842a-10f6072b2a3b</t>
+  </si>
+  <si>
+    <t>relationship--e443c467-6868-4eb4-9116-e6408b709546</t>
+  </si>
+  <si>
+    <t>relationship--e53a2b88-0ebc-4a16-a577-d112606d66dc</t>
+  </si>
+  <si>
+    <t>relationship--bebdb2d7-bb38-4005-8102-1a5e4cd87fe5</t>
+  </si>
+  <si>
+    <t>relationship--40da80ea-51de-4c88-b37b-4a5454a28fc6</t>
+  </si>
+  <si>
+    <t>relationship--d8aed0a6-ae04-4d23-b68c-e2cb3e8679e2</t>
+  </si>
+  <si>
+    <t>relationship--6c4ad300-bfc1-4639-8cad-cd3831945f63</t>
+  </si>
+  <si>
+    <t>relationship--11257966-4e63-4bd8-8160-ce75de1b35f0</t>
+  </si>
+  <si>
+    <t>relationship--bb8f24f8-9812-4689-ba58-61f48597956f</t>
+  </si>
+  <si>
+    <t>relationship--cd09ba18-72b1-4865-a079-43e70f6c8fde</t>
+  </si>
+  <si>
+    <t>relationship--29065fcd-4bcd-456e-a3ba-4843744bda2e</t>
+  </si>
+  <si>
+    <t>relationship--58d0d22f-c1ec-42f4-93e5-f7964a7743ae</t>
+  </si>
+  <si>
+    <t>relationship--e0d6becd-14f0-4e74-a3ed-39e21e6121f9</t>
+  </si>
+  <si>
+    <t>relationship--7c083924-dbf0-44e0-8acb-468a157e9860</t>
+  </si>
+  <si>
+    <t>relationship--fc64ba9d-1c13-41fe-b318-cbd1181c88f7</t>
+  </si>
+  <si>
+    <t>relationship--a11663d7-88f0-4a16-8fe0-27ba4c2dd379</t>
+  </si>
+  <si>
+    <t>relationship--2bc40996-d1fd-442e-8f96-c0f5d7ea360c</t>
+  </si>
+  <si>
+    <t>relationship--4daee390-683a-4c26-87e6-274b631b7b34</t>
+  </si>
+  <si>
+    <t>relationship--d3ada701-8ad3-4e0c-9582-04433749efc5</t>
+  </si>
+  <si>
+    <t>relationship--c6c1f4e1-8dfe-4a7f-9c72-ff8ed473d8f1</t>
+  </si>
+  <si>
+    <t>relationship--8a862091-f5c2-4cd0-a9b3-767a61f5899a</t>
+  </si>
+  <si>
+    <t>relationship--d04d6a0f-fc60-4e07-9d6e-6403c0ba67aa</t>
+  </si>
+  <si>
+    <t>relationship--4fe1e396-5634-4bdc-ab59-439f1b8f30ef</t>
+  </si>
+  <si>
+    <t>relationship--a5921f8a-453f-4174-8c49-98d0584706ab</t>
+  </si>
+  <si>
+    <t>relationship--e051d46c-9004-4849-be37-66208a4e255c</t>
+  </si>
+  <si>
+    <t>relationship--3ff56c54-ed31-4936-8334-e64efbf2b214</t>
+  </si>
+  <si>
+    <t>relationship--f38fa377-93a8-4dfe-8438-208b8cfbe45f</t>
   </si>
   <si>
     <t>attributed-to</t>
@@ -5732,22 +5732,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--17a091f6-8db4-4483-acf7-a69fd4cc7457</t>
-  </si>
-  <si>
-    <t>intrusion-set--468d1617-0966-4f71-bc4e-0a45dacd6316</t>
-  </si>
-  <si>
-    <t>intrusion-set--6981af28-a9ac-4529-a24e-b9b57a3b8686</t>
-  </si>
-  <si>
-    <t>intrusion-set--ac141584-6691-4008-b480-83deaf636398</t>
-  </si>
-  <si>
-    <t>intrusion-set--f2ca30a8-03bd-4610-b8a2-0148c877e608</t>
-  </si>
-  <si>
-    <t>intrusion-set--27b388cb-7c36-4aca-b91e-792abce31837</t>
+    <t>intrusion-set--d02a2528-4983-49ba-9958-e3dca5f57c1a</t>
+  </si>
+  <si>
+    <t>intrusion-set--a6148444-d09e-4aa5-8c32-50da2bd25525</t>
+  </si>
+  <si>
+    <t>intrusion-set--7077cfc8-f533-42d0-bc5a-a2bbebf847e1</t>
+  </si>
+  <si>
+    <t>intrusion-set--8837e6ef-c6bb-4b41-b8c6-c0588be2db1c</t>
+  </si>
+  <si>
+    <t>intrusion-set--764cac65-3338-4105-9501-152d67a8fc5b</t>
+  </si>
+  <si>
+    <t>intrusion-set--43830a9b-2a24-4049-8b19-d210028de96e</t>
   </si>
   <si>
     <t>group</t>
@@ -5756,310 +5756,310 @@
     <t>Вторжение войск генерала Деникина под лозунгом восстановления «единой и неделимой России» и вооруженное вытеснение украинских частей из освобожденного ими Киева 31 августа 1919 года («Киевская катастрофа»), приведшее к развалу фронта. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--460be75c-3ad5-4bf4-a5c2-7f82b9db6601</t>
-  </si>
-  <si>
-    <t>relationship--e739178a-96b6-4da5-a885-0709960c43cc</t>
-  </si>
-  <si>
-    <t>relationship--c621eb17-4495-4598-8304-7155a176f6d7</t>
-  </si>
-  <si>
-    <t>relationship--f7f4288a-3312-4d68-a865-c2c9c14d9c3e</t>
-  </si>
-  <si>
-    <t>relationship--0089b9ed-25ca-4e4f-b57e-7ce39a04da5b</t>
-  </si>
-  <si>
-    <t>relationship--d0fbaf12-2c5e-4682-99ee-41e5fe7e85cf</t>
-  </si>
-  <si>
-    <t>relationship--691fff9c-01e9-4a98-ae09-225ff331dac4</t>
-  </si>
-  <si>
-    <t>relationship--b6a52714-d16b-444a-8470-cd43335e0cd2</t>
-  </si>
-  <si>
-    <t>relationship--82c31da8-dbe7-4fb4-a4fd-fee93f6eef0a</t>
-  </si>
-  <si>
-    <t>relationship--34892e96-44b8-441f-975a-2e3054b02634</t>
-  </si>
-  <si>
-    <t>relationship--813f11e9-eb36-41da-8626-8ce8120390c2</t>
-  </si>
-  <si>
-    <t>relationship--beee49e6-d7cd-472b-ab78-9b805a53154b</t>
-  </si>
-  <si>
-    <t>relationship--307b3c94-bc1f-47a2-9f0a-3359b85ba4b7</t>
-  </si>
-  <si>
-    <t>relationship--8b1049f5-edf8-45ed-b83c-07e229e1bbd9</t>
-  </si>
-  <si>
-    <t>relationship--2f461d63-49c2-48ac-9c69-43de703e2023</t>
-  </si>
-  <si>
-    <t>relationship--9ba6c77b-a292-4a52-aff7-65ff6df82489</t>
-  </si>
-  <si>
-    <t>relationship--e9836478-20f8-43dd-ae2c-ee8d1cf72d53</t>
-  </si>
-  <si>
-    <t>relationship--9467b34a-adb3-4cea-ba1e-2dae64e36249</t>
-  </si>
-  <si>
-    <t>relationship--a23fd531-4440-44a7-9216-09e48bb43099</t>
-  </si>
-  <si>
-    <t>relationship--27da54f1-ce03-4231-8d9a-2899657b0700</t>
-  </si>
-  <si>
-    <t>relationship--f7994b39-d8d1-4e6a-b562-3be2533cfd2c</t>
-  </si>
-  <si>
-    <t>relationship--5109690b-fa3e-4562-b3fc-a2da6acbbd77</t>
-  </si>
-  <si>
-    <t>relationship--03dbbf99-ef9b-47bc-bcd3-ca87a218f206</t>
-  </si>
-  <si>
-    <t>relationship--ecf39881-4cfd-4dfd-8a55-da7fb9ea2b9a</t>
-  </si>
-  <si>
-    <t>relationship--6e092940-010d-4312-9c49-980c665a05fd</t>
-  </si>
-  <si>
-    <t>relationship--5e199e95-10ba-4f6b-bfea-9aff008c8283</t>
-  </si>
-  <si>
-    <t>relationship--5f893864-4e4d-405f-8377-0bcf69525759</t>
-  </si>
-  <si>
-    <t>relationship--a0231a97-936b-4af6-9b0a-419bf6d733b1</t>
-  </si>
-  <si>
-    <t>relationship--4b8b74a6-6d8e-4273-942f-2a6e3646c91d</t>
-  </si>
-  <si>
-    <t>relationship--75f53d0b-1826-4584-9b31-4c22742f94ed</t>
-  </si>
-  <si>
-    <t>relationship--219f0370-9d7b-4292-b3d5-6b3ba2233f6d</t>
-  </si>
-  <si>
-    <t>relationship--119ac3aa-228b-44a3-a54a-cd1dcf268155</t>
-  </si>
-  <si>
-    <t>relationship--0d29615a-2ec9-4f5f-ab4a-92f6249645d2</t>
-  </si>
-  <si>
-    <t>relationship--2694c872-3e63-479e-89f6-9e2af13fd1b1</t>
-  </si>
-  <si>
-    <t>relationship--f8de1c22-7cb9-444b-9b64-8a6aa3bd4287</t>
-  </si>
-  <si>
-    <t>relationship--a68b9a0d-632c-45f6-823f-b599a57cb5e1</t>
-  </si>
-  <si>
-    <t>relationship--8f08e983-b02e-40c6-bd4d-5a5d1f750c56</t>
-  </si>
-  <si>
-    <t>relationship--0af0860e-a406-4503-b360-2fe5e815381f</t>
-  </si>
-  <si>
-    <t>relationship--7fc5f097-970f-4d89-b7ff-ad7b4545f60f</t>
-  </si>
-  <si>
-    <t>relationship--c4a00367-e77a-4ba7-baac-1d805af730f0</t>
-  </si>
-  <si>
-    <t>relationship--a4615315-a6a9-4ea0-a175-8c5883934b23</t>
-  </si>
-  <si>
-    <t>relationship--4840ad50-55ea-4835-9d61-8b6ec7eaba03</t>
-  </si>
-  <si>
-    <t>relationship--93056257-3766-4a52-bc2f-11e96817b86f</t>
-  </si>
-  <si>
-    <t>relationship--b2a7becd-67da-4a19-b8dd-6f9bb4239e5b</t>
-  </si>
-  <si>
-    <t>relationship--7939df1f-195c-4182-afe6-01c07f80bf71</t>
-  </si>
-  <si>
-    <t>relationship--ba0883c1-6d3c-4536-a025-845f5cb42907</t>
-  </si>
-  <si>
-    <t>relationship--cd59bdfa-d9ee-4b24-b644-1df1836f26e1</t>
-  </si>
-  <si>
-    <t>relationship--6eeb84bf-67aa-4088-ade8-4555190bb69e</t>
-  </si>
-  <si>
-    <t>relationship--f7b1b04d-8ee4-456f-b69f-18cb3fe32e67</t>
-  </si>
-  <si>
-    <t>relationship--1ffbf2c5-625d-4cd2-b8a8-c6eee53ada43</t>
-  </si>
-  <si>
-    <t>relationship--9e6273de-0cd9-4d9d-b605-452a20189f6d</t>
-  </si>
-  <si>
-    <t>relationship--b1a285bc-37cf-4a0b-9d9a-b12dcfa5d8d2</t>
-  </si>
-  <si>
-    <t>relationship--2628aee7-5ff1-4cab-ac41-170f55fa2571</t>
-  </si>
-  <si>
-    <t>relationship--e631c2db-adee-4771-beda-32eba963b2ce</t>
-  </si>
-  <si>
-    <t>relationship--62545ab9-3b51-4b9a-89d6-6f6500c4b2f0</t>
-  </si>
-  <si>
-    <t>relationship--b803ff31-0d9e-43bf-b723-67bf96618a68</t>
-  </si>
-  <si>
-    <t>relationship--141080f4-8be9-4597-8f3b-abff4d4b21a2</t>
-  </si>
-  <si>
-    <t>relationship--5f7d2c05-5dcd-485f-affd-57bad50a51a2</t>
-  </si>
-  <si>
-    <t>relationship--453a6e64-6c03-4016-87cb-19276f03bf99</t>
-  </si>
-  <si>
-    <t>relationship--6ebfa1c0-618a-47b7-8ee1-d9dd9a7757b9</t>
-  </si>
-  <si>
-    <t>relationship--7ba0ff11-382b-4206-acd2-b8ebb861fb4c</t>
-  </si>
-  <si>
-    <t>relationship--93bf0427-97c0-405e-8505-97192d70f5bb</t>
-  </si>
-  <si>
-    <t>relationship--d372ac39-5651-4a7c-8c14-54e3e1475c25</t>
-  </si>
-  <si>
-    <t>relationship--64c91be4-1ea4-484a-802b-c8776f012ed9</t>
-  </si>
-  <si>
-    <t>relationship--4f590fc6-2c0d-4d9c-a64c-7a709daf8872</t>
-  </si>
-  <si>
-    <t>relationship--90fa1c4d-5707-45c3-995c-76286faadc2e</t>
-  </si>
-  <si>
-    <t>relationship--d0a0d87c-46b2-4d8e-b3f5-0299ab3b0b88</t>
-  </si>
-  <si>
-    <t>relationship--0e025094-74fd-4c1f-a5d2-540c3021f581</t>
-  </si>
-  <si>
-    <t>relationship--22167f6f-42b8-4cfc-b883-01a554c1a049</t>
-  </si>
-  <si>
-    <t>relationship--30f85270-fa1c-43a0-aecf-ef2f9cd6a7ed</t>
-  </si>
-  <si>
-    <t>relationship--33a54dc6-ff5a-4dfd-9b98-af2566758506</t>
-  </si>
-  <si>
-    <t>relationship--76a6557d-f467-45c0-94f1-d1d1dbe5595c</t>
-  </si>
-  <si>
-    <t>relationship--4732bc27-5c35-44be-b389-ffed5a0c1eed</t>
-  </si>
-  <si>
-    <t>relationship--b5ea3184-78a6-4d3c-9967-3a6a92aa503b</t>
-  </si>
-  <si>
-    <t>relationship--4ba9dee2-da12-4946-924b-64885b206114</t>
-  </si>
-  <si>
-    <t>relationship--7eef1496-ebfd-4fc7-8170-bd114c496509</t>
-  </si>
-  <si>
-    <t>relationship--4b28cc87-d3f4-49ca-8c79-cf9ffc871673</t>
-  </si>
-  <si>
-    <t>relationship--695eecfc-63f5-4b73-9fab-44d1531736e9</t>
-  </si>
-  <si>
-    <t>relationship--e2a8da7b-577b-414e-90b7-fe1f9aa1a611</t>
-  </si>
-  <si>
-    <t>relationship--7187224f-2fdb-444d-8464-d7537b8c5e94</t>
-  </si>
-  <si>
-    <t>relationship--d40e6fba-d303-4285-986b-9b8f5120a142</t>
-  </si>
-  <si>
-    <t>relationship--61f7abcd-ee01-4167-972a-b9f55536e6b0</t>
-  </si>
-  <si>
-    <t>relationship--d46404cf-43b7-4840-927a-774f468a353c</t>
-  </si>
-  <si>
-    <t>relationship--cb567410-6b9c-4dec-b666-0eb15ed60809</t>
-  </si>
-  <si>
-    <t>relationship--1c38f89e-baaf-4c42-8120-d37491e8aaab</t>
-  </si>
-  <si>
-    <t>relationship--98fc8e5e-a82c-4466-aca9-6fb45a774b5b</t>
-  </si>
-  <si>
-    <t>relationship--8636b8dc-ede2-406a-ac94-d680170f80e0</t>
-  </si>
-  <si>
-    <t>relationship--ecac1301-29a9-4d52-a84b-e97e90d852b8</t>
-  </si>
-  <si>
-    <t>relationship--d181304d-a742-4a43-8614-f6d3c852707d</t>
-  </si>
-  <si>
-    <t>relationship--d424aae3-98cb-47f4-aadb-72f5b20dd769</t>
-  </si>
-  <si>
-    <t>relationship--9860983b-4bfa-4784-b876-bf986826e00d</t>
-  </si>
-  <si>
-    <t>relationship--d355da2f-846a-4625-9afd-9958a0e3e6c5</t>
-  </si>
-  <si>
-    <t>relationship--ba3af7e4-23df-4af8-8b45-769fb484cd48</t>
-  </si>
-  <si>
-    <t>relationship--f4dccceb-2ada-4137-911e-edc9ca8e9ada</t>
-  </si>
-  <si>
-    <t>relationship--910d6a19-3805-4556-ab83-84b3c7bbd63c</t>
-  </si>
-  <si>
-    <t>relationship--5ebf36d4-8505-4753-9ff2-b1b30a8a98bf</t>
-  </si>
-  <si>
-    <t>relationship--e025d045-10e0-430c-ae3c-0e8c2571409f</t>
-  </si>
-  <si>
-    <t>relationship--f7dffc32-dbc9-49a2-8797-152cddca072e</t>
-  </si>
-  <si>
-    <t>relationship--4c374272-1581-4749-948d-6243805759c0</t>
-  </si>
-  <si>
-    <t>relationship--45802b11-78d7-411b-8881-63b6ef7ba5b5</t>
-  </si>
-  <si>
-    <t>relationship--a0b97b5f-eddc-48a0-9871-9877022f9dff</t>
-  </si>
-  <si>
-    <t>relationship--ba84c874-2861-4371-9408-67b3bd715c9b</t>
+    <t>relationship--382fcb97-4f41-46e4-bb60-34c2ae61e243</t>
+  </si>
+  <si>
+    <t>relationship--4495adfe-a3e7-45bd-8dd4-3592a6569138</t>
+  </si>
+  <si>
+    <t>relationship--9225e21e-7c93-49c2-8027-237b8e463ac1</t>
+  </si>
+  <si>
+    <t>relationship--eb953dbb-8e6f-40d4-be23-9cda1f740475</t>
+  </si>
+  <si>
+    <t>relationship--dd066db1-d38e-40a6-a63e-ac40ea62ccf8</t>
+  </si>
+  <si>
+    <t>relationship--61b8e545-b323-4b47-ab5a-7a9a3bcac4f1</t>
+  </si>
+  <si>
+    <t>relationship--d1126afd-11e5-4fd8-9ca4-aef38e5474ee</t>
+  </si>
+  <si>
+    <t>relationship--36fdff9f-fc5c-482e-9de7-6da2088cb90d</t>
+  </si>
+  <si>
+    <t>relationship--7483aed6-f3af-415b-8a8d-2c3c5df83162</t>
+  </si>
+  <si>
+    <t>relationship--55707eee-feda-43e1-9663-98427e22c425</t>
+  </si>
+  <si>
+    <t>relationship--8d1f50e8-5d19-401b-8f5f-e546f4f06f4b</t>
+  </si>
+  <si>
+    <t>relationship--d66ec916-3d0c-4de2-b7be-5df665df503f</t>
+  </si>
+  <si>
+    <t>relationship--da504b5e-7045-48b4-86e9-79c5ca91c4ed</t>
+  </si>
+  <si>
+    <t>relationship--8a2151b1-85a2-4de8-8404-b5359eee6472</t>
+  </si>
+  <si>
+    <t>relationship--8768eabd-8d6b-4420-aeea-54339ed9baf0</t>
+  </si>
+  <si>
+    <t>relationship--49274bca-c396-4e35-9bac-8a77e42bbe37</t>
+  </si>
+  <si>
+    <t>relationship--8856c1b0-3c97-4a08-8129-1ca06a9aa77e</t>
+  </si>
+  <si>
+    <t>relationship--e45bcd17-fc61-4997-ba9d-dd9350c19fcf</t>
+  </si>
+  <si>
+    <t>relationship--a681f9c6-75fb-48b1-a518-4ae4693469cf</t>
+  </si>
+  <si>
+    <t>relationship--a2ae0fcd-d5a3-48f2-9648-94c6a578996b</t>
+  </si>
+  <si>
+    <t>relationship--2169d14e-dccd-4fcb-8089-596e31f992be</t>
+  </si>
+  <si>
+    <t>relationship--85c2a1ef-0476-4dc7-b04b-c7ab04d1551d</t>
+  </si>
+  <si>
+    <t>relationship--2e69f83c-b3d0-428e-8e0e-83f2622be4fe</t>
+  </si>
+  <si>
+    <t>relationship--6196146c-172f-40bd-939e-a3e86f47fccc</t>
+  </si>
+  <si>
+    <t>relationship--bdf151f8-928d-4d5e-9c05-e3d5db94fc73</t>
+  </si>
+  <si>
+    <t>relationship--28d66b03-24f5-4e5c-97e4-02822aa8ccf7</t>
+  </si>
+  <si>
+    <t>relationship--c4d58b25-d138-401b-a8f1-7b6c3070c24f</t>
+  </si>
+  <si>
+    <t>relationship--e63320e3-64b9-476c-8ffd-9b697bbdd1ca</t>
+  </si>
+  <si>
+    <t>relationship--5db7d86a-c6c2-4edf-976f-a8b386b7c52f</t>
+  </si>
+  <si>
+    <t>relationship--88bdfc29-6fee-47c4-8531-4dd2c50addc3</t>
+  </si>
+  <si>
+    <t>relationship--c1bc7a48-1f0d-4b5d-95e3-d41a262fdcb3</t>
+  </si>
+  <si>
+    <t>relationship--8499a70c-630a-494f-9336-2f1763b1bbdc</t>
+  </si>
+  <si>
+    <t>relationship--23806f4b-ec1d-457f-9917-6db807392b7d</t>
+  </si>
+  <si>
+    <t>relationship--efa0724d-5137-40f1-8b31-515732cdb62a</t>
+  </si>
+  <si>
+    <t>relationship--77aab65f-58a4-4e9d-a54d-83a8ee32c799</t>
+  </si>
+  <si>
+    <t>relationship--044095aa-fae1-49c3-b301-5342abc40196</t>
+  </si>
+  <si>
+    <t>relationship--1cbd029d-e0d4-48d3-9d4b-6728e01611c9</t>
+  </si>
+  <si>
+    <t>relationship--49c17912-3b07-4b38-bf9b-a72bd56dc4ca</t>
+  </si>
+  <si>
+    <t>relationship--b5279e93-6c2d-4ef7-b0a2-abee935c2f67</t>
+  </si>
+  <si>
+    <t>relationship--2873c7d0-b4e5-46e7-a4eb-237fb5ab2d86</t>
+  </si>
+  <si>
+    <t>relationship--4e4832dc-e64f-412d-8a26-0e93f91c542c</t>
+  </si>
+  <si>
+    <t>relationship--dc690243-0da4-4460-82ad-9965ac7c3f9e</t>
+  </si>
+  <si>
+    <t>relationship--1589557c-674b-42a6-9d79-140dd54c57a9</t>
+  </si>
+  <si>
+    <t>relationship--23aedab9-87d8-4155-950b-80af2f045330</t>
+  </si>
+  <si>
+    <t>relationship--101c7f49-2c04-4b8a-9556-b4c26783bfe2</t>
+  </si>
+  <si>
+    <t>relationship--1aca5862-5cf0-4da7-be63-d773e5b14e6c</t>
+  </si>
+  <si>
+    <t>relationship--1734101c-ef7a-4948-8a3b-0a0905ca1f1d</t>
+  </si>
+  <si>
+    <t>relationship--db41c035-7acc-4a92-9eac-aead465c5a2c</t>
+  </si>
+  <si>
+    <t>relationship--07f6f446-cb45-4775-bc19-4ca62911421c</t>
+  </si>
+  <si>
+    <t>relationship--23635f40-42e0-4aab-93e5-7839900aa645</t>
+  </si>
+  <si>
+    <t>relationship--e9fd6b3f-16bf-4479-92ec-5caab1d1e0e9</t>
+  </si>
+  <si>
+    <t>relationship--18910b2c-ba23-486c-985b-b109124d1b3e</t>
+  </si>
+  <si>
+    <t>relationship--0ccfc730-fb82-4744-8e1d-322140f19e9a</t>
+  </si>
+  <si>
+    <t>relationship--eee05d7c-ae7b-4053-8875-afcf211b76ed</t>
+  </si>
+  <si>
+    <t>relationship--8aa0ca1b-3f7c-4c32-8a7c-45b31ce910ae</t>
+  </si>
+  <si>
+    <t>relationship--b7259905-9d80-494f-b98c-475f9626877c</t>
+  </si>
+  <si>
+    <t>relationship--94fdda67-bf68-47b8-8de2-34e48e939fc1</t>
+  </si>
+  <si>
+    <t>relationship--590a6244-8e58-46d8-b696-1c5d8e0625b3</t>
+  </si>
+  <si>
+    <t>relationship--bbb202d4-6a82-4e71-820a-a7a10f749fa8</t>
+  </si>
+  <si>
+    <t>relationship--e082139a-4d63-42e3-a9ab-22704289063c</t>
+  </si>
+  <si>
+    <t>relationship--3b287c44-edb0-493f-b089-4c8e9b742c1e</t>
+  </si>
+  <si>
+    <t>relationship--af6c11a0-1a81-4476-9133-418e237512ff</t>
+  </si>
+  <si>
+    <t>relationship--4765f79a-41a8-48a0-9df1-2008ca7b0f99</t>
+  </si>
+  <si>
+    <t>relationship--cb521445-1143-4d52-8855-527fd205f9f8</t>
+  </si>
+  <si>
+    <t>relationship--fdf48b58-3ad9-4551-9e50-af554a5b42ad</t>
+  </si>
+  <si>
+    <t>relationship--ffb95292-95f1-4871-991d-7c92aa317f0b</t>
+  </si>
+  <si>
+    <t>relationship--505e1362-9b73-4bb0-b4c2-e6d1b039e4e4</t>
+  </si>
+  <si>
+    <t>relationship--20298c0f-6237-45dc-af9d-f56d893f7259</t>
+  </si>
+  <si>
+    <t>relationship--9a23d323-20c6-4635-aadb-67dd78a2f01a</t>
+  </si>
+  <si>
+    <t>relationship--61a7038d-63a6-4b13-8a2d-0caca2bc8325</t>
+  </si>
+  <si>
+    <t>relationship--aeb42ea0-3a92-4e4a-8b4b-7f232833f401</t>
+  </si>
+  <si>
+    <t>relationship--da2a7062-df67-4afa-8567-858795e0c382</t>
+  </si>
+  <si>
+    <t>relationship--14f872e6-ada3-4196-ad9c-211a9ce327bb</t>
+  </si>
+  <si>
+    <t>relationship--7b9cbfa7-d262-4ff2-b520-b459f9b562f9</t>
+  </si>
+  <si>
+    <t>relationship--c46aab24-4e0f-41b8-9b97-46505ddae0ae</t>
+  </si>
+  <si>
+    <t>relationship--9a947244-79a8-4ed8-b542-832c9c926e6d</t>
+  </si>
+  <si>
+    <t>relationship--6d836384-f648-4400-8095-c213d21fda1d</t>
+  </si>
+  <si>
+    <t>relationship--e2e535e7-756f-4444-b330-8001d5906d93</t>
+  </si>
+  <si>
+    <t>relationship--d6a4f28f-89a5-4b6e-8bdb-50c6acb9ea4b</t>
+  </si>
+  <si>
+    <t>relationship--d75b0862-802b-4770-9fd6-3426a5d767c7</t>
+  </si>
+  <si>
+    <t>relationship--0350c612-d784-4b91-99a7-cbaac48b11cf</t>
+  </si>
+  <si>
+    <t>relationship--7189b336-e5d2-491b-b8f8-e94a9b52a4e5</t>
+  </si>
+  <si>
+    <t>relationship--c12be137-9cae-44dd-8092-aeee8a1963f4</t>
+  </si>
+  <si>
+    <t>relationship--24b777c8-f739-463f-b8ef-a86cf6aa4f34</t>
+  </si>
+  <si>
+    <t>relationship--05decf97-2ade-44f2-96b0-30b40a6246cf</t>
+  </si>
+  <si>
+    <t>relationship--e7216d3e-de30-4410-9c3f-c022eed6a6d2</t>
+  </si>
+  <si>
+    <t>relationship--e5771421-67f9-443e-873a-3472d1f67ef0</t>
+  </si>
+  <si>
+    <t>relationship--08caa687-cc83-4bc5-8fc3-e2ac19d8c83e</t>
+  </si>
+  <si>
+    <t>relationship--e0ca1f77-bd5b-411a-b57f-6813c65a46ac</t>
+  </si>
+  <si>
+    <t>relationship--62d3fe94-11cc-4584-ad49-257cae10cd2c</t>
+  </si>
+  <si>
+    <t>relationship--f5c60d72-2433-4f5f-b65e-aca6af57ad7e</t>
+  </si>
+  <si>
+    <t>relationship--bdd5cf36-5fe9-40eb-9590-e32ec89eac25</t>
+  </si>
+  <si>
+    <t>relationship--677a1907-f669-4245-89a3-2afbc2911210</t>
+  </si>
+  <si>
+    <t>relationship--5cb58ec3-0569-4768-b0e0-afa765845d2f</t>
+  </si>
+  <si>
+    <t>relationship--ee63d5d7-bc76-42a4-ae67-cea3bfe1cc8d</t>
+  </si>
+  <si>
+    <t>relationship--4e768b23-0fe0-4104-b97e-f19cf0a96cc3</t>
+  </si>
+  <si>
+    <t>relationship--2a5e61b4-05d8-4d14-9de4-2b9c61d56326</t>
+  </si>
+  <si>
+    <t>relationship--7a5abd80-9d01-4a4d-8206-9b79ba60a02d</t>
+  </si>
+  <si>
+    <t>relationship--23bab217-d7a8-4ba9-b0cd-2d38801cfc47</t>
+  </si>
+  <si>
+    <t>relationship--bbbd33ce-ba16-49d8-908c-9d2fc8c86474</t>
+  </si>
+  <si>
+    <t>relationship--764bbf19-51ca-465d-81a9-f43abc274c3e</t>
+  </si>
+  <si>
+    <t>relationship--d11a6c57-9820-4859-a256-286d04380747</t>
   </si>
   <si>
     <t>reference</t>
@@ -6068,79 +6068,385 @@
     <t>citation</t>
   </si>
   <si>
+    <t>2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
+  </si>
+  <si>
+    <t>2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
+  </si>
+  <si>
+    <t>Історія України — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
+    <t>Всесоюзний референдум про збереження СРСР — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Дезінформація під час російсько-української війни — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Друга Малоросійська колегія — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Задунайська Січ — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Запорозька Січ — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
+    <t>Карательная психиатрия в России: назад в СССР? 2026</t>
+  </si>
+  <si>
+    <t>Кенгирское восстание заключённых - Википедия 2026</t>
+  </si>
+  <si>
     <t>Киевский синопсис — Википедия 2026</t>
   </si>
   <si>
+    <t>Кирило-Мефодіївське товариство — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Київська козаччина — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Конотопські статті — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Крымская война — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Лубенський договір — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Ліквідація автономії Гетьманщини — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Мазепа 2007</t>
   </si>
   <si>
+    <t>Малоросійське генерал-губернаторство — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Малоросійський приказ — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Народний рух України — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Норильское восстание - Википедия 2026</t>
+  </si>
+  <si>
     <t>Переяславська рада — Вікіпедія 2026</t>
   </si>
   <si>
-    <t>РАШИЗМ ЗВІР З БЕЗОДНІ 2023</t>
+    <t>Письмо-протест 139 - Википедия 2026</t>
+  </si>
+  <si>
+    <t>Поділи Речі Посполитої — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Правління гетьманського уряду — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Рашизм: Звір з безодні 2023</t>
+  </si>
+  <si>
+    <t>Решетилівські статті — Вікіпедія 2026</t>
   </si>
   <si>
     <t>Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010</t>
   </si>
   <si>
+    <t>Русифікація України — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Руїна — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Рішительні пункти — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Серпневий путч — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Смуга осілості — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Столипінська реформа — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Україна в Першій світовій війні — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Україна у війнах Наполеона — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Хроника первой российской войны в Чечне 2026</t>
   </si>
   <si>
+    <t>Чорносотенці — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1928 ГГ . 2011</t>
   </si>
   <si>
+    <t>Анексія Кримського ханства — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK®. (2023). 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK®. (2023). 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Всесоюзний референдум про збереження СРСР — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Дезінформація під час російсько-української війни — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Друга Малоросійська колегія — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Задунайська Січ — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Запорозька Січ — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
+    <t>Riddle Russia. (2026). Карательная психиатрия в России: назад в СССР?.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Киевский синопсис — Википедия.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Кирило-Мефодіївське товариство — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Київська козаччина — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Конотопські статті — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Крымская война — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Лубенський договір — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Ліквідація автономії Гетьманщини — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Татьяна Таирова-Яковлева. (2007). Мазепа.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Малоросійське генерал-губернаторство — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Малоросійський приказ — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Народний рух України — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Норильское восстание - Википедия.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Переяславська рада — Вікіпедія.</t>
   </si>
   <si>
-    <t>Лариса Якубова. (2023). РАШИЗМ ЗВІР З БЕЗОДНІ.</t>
+    <t>Википедия. (2026). Письмо-протест 139 - Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Поділи Речі Посполитої — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Правління гетьманського уряду — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Лариса Якубова. (2023). Рашизм: Звір з безодні.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Решетилівські статті — Вікіпедія.</t>
   </si>
   <si>
     <t>Мемориал, О.П.Орлов, А.В.Черкасов. (2010). Россия - Чечня - цепь ошибок и преступлений. 1994—1996.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Русифікація України — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Руїна — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Рішительні пункти — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Серпневий путч — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Скасування козацького устрою в Слобідській Україні — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Смуга осілості — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Столипінська реформа — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Україна в Першій світовій війні — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Україна у війнах Наполеона — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Beda Media. (2026). Хроника первой российской войны в Чечне.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Чорносотенці — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Виктор Дённингхаус. (2011). В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1928 ГГ ..</t>
   </si>
   <si>
+    <t>Википедия. (2026). Анексія Кримського ханства — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>https://attack.mitre.org/campaigns/C0028/</t>
+  </si>
+  <si>
+    <t>https://attack.mitre.org/campaigns/C0025/</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B4%25D0%25B5%25D0%25B7%25D1%2596%25D0%25BD%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BF%25D1%2596%25D0%25B4_%25D1%2587%25D0%25B0%25D1%2581_%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2594%25D1%2580%25D1%2583%25D0%25B3%25D0%25B0_%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25B3%25D1%2596%25D1%258F</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25B4%25D1%2583%25D0%25BD%25D0%25B0%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
+  </si>
+  <si>
+    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%B8%D0%B5%D0%B2%D1%81%D0%BA%D0%B8%D0%B9_%D1%81%D0%B8%D0%BD%D0%BE%D0%BF%D1%81%D0%B8%D1%81</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2580%25D0%25B8%25D0%25BB%25D0%25BE-%25D0%259C%25D0%25B5%25D1%2584%25D0%25BE%25D0%25B4%25D1%2596%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D1%2582%25D0%25BE%25D0%25B2%25D0%25B0%25D1%2580%25D0%25B8%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2587%25D1%2587%25D0%25B8%25D0%25BD%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259A%25D0%25BE%25D0%25BD%25D0%25BE%25D1%2582%25D0%25BE%25D0%25BF%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D1%2580%25D1%258B%25D0%25BC%25D1%2581%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2583%25D0%25B1%25D0%25B5%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25B4%25D0%25BE%25D0%25B3%25D0%25BE%25D0%25B2%25D1%2596%25D1%2580</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2580%25D0%25B8%25D0%25BA%25D0%25B0%25D0%25B7</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259D%25D0%25B0%25D1%2580%25D0%25BE%25D0%25B4%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259D%25D0%25BE%25D1%2580%25D0%25B8%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D0%B0_%D1%80%D0%B0%D0%B4%D0%B0</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25B8%25D1%2581%25D1%258C%25D0%25BC%25D0%25BE-%25D0%25BF%25D1%2580%25D0%25BE%25D1%2582%25D0%25B5%25D1%2581%25D1%2582_139</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B4%25D1%2596%25D0%25BB%25D0%25B8_%25D0%25A0%25D0%25B5%25D1%2587%25D1%2596_%25D0%259F%25D0%25BE%25D1%2581%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B8%25D1%2582%25D0%25BE%25D1%2597</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BB%25D1%2596%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B3%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2580%25D1%258F%25D0%25B4%25D1%2583</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25B5%25D1%2588%25D0%25B5%25D1%2582%25D0%25B8%25D0%25BB%25D1%2596%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
     <t>https://web.archive.org/web/20160304195659/http%3A//www.memo.ru/2010/09/27/rch.pdf</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D0%25B8%25D1%2584%25D1%2596%25D0%25BA%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%D0%A0%D1%83%D1%97%D0%BD%D0%B0</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D1%2596%25D1%2588%25D0%25B8%25D1%2582%25D0%25B5%25D0%25BB%25D1%258C%25D0%25BD%25D1%2596_%25D0%25BF%25D1%2583%25D0%25BD%25D0%25BA%25D1%2582%25D0%25B8</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25B5%25D1%2580%25D0%25BF%25D0%25BD%25D0%25B5%25D0%25B2%25D0%25B8%25D0%25B9_%25D0%25BF%25D1%2583%25D1%2582%25D1%2587</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BA%25D0%25B0%25D1%2581%25D1%2583%25D0%25B2%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2583%25D1%2581%25D1%2582%25D1%2580%25D0%25BE%25D1%258E_%25D0%25B2_%25D0%25A1%25D0%25BB%25D0%25BE%25D0%25B1%25D1%2596%25D0%25B4%25D1%2581%25D1%258C%25D0%25BA%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D0%25BC%25D1%2583%25D0%25B3%25D0%25B0_%25D0%25BE%25D1%2581%25D1%2596%25D0%25BB%25D0%25BE%25D1%2581%25D1%2582%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A1%25D1%2582%25D0%25BE%25D0%25BB%25D0%25B8%25D0%25BF%25D1%2596%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2580%25D0%25B5%25D1%2584%25D0%25BE%25D1%2580%25D0%25BC%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D0%25B2_%25D0%259F%25D0%25B5%25D1%2580%25D1%2588%25D1%2596%25D0%25B9_%25D1%2581%25D0%25B2%25D1%2596%25D1%2582%25D0%25BE%25D0%25B2%25D1%2596%25D0%25B9_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B0_%25D1%2583_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0%25D1%2585_%25D0%259D%25D0%25B0%25D0%25BF%25D0%25BE%25D0%25BB%25D0%25B5%25D0%25BE%25D0%25BD%25D0%25B0</t>
+  </si>
+  <si>
     <t>https://beda.media/ru/articles/war-in-chechnya-chronicle-part1-ru</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D1%2580%25D0%25B8%25D0%25BC%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2585%25D0%25B0%25D0%25BD%25D1%2581%25D1%2582%25D0%25B2%25D0%25B0</t>
   </si>
 </sst>
 </file>
@@ -36044,7 +36350,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -36063,7 +36369,10 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>2026</v>
+        <v>2060</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -36071,7 +36380,10 @@
         <v>2017</v>
       </c>
       <c r="B3" t="s">
-        <v>2027</v>
+        <v>2061</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2105</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -36079,10 +36391,10 @@
         <v>2018</v>
       </c>
       <c r="B4" t="s">
-        <v>2028</v>
+        <v>2062</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2036</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -36090,7 +36402,7 @@
         <v>2019</v>
       </c>
       <c r="B5" t="s">
-        <v>2029</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -36098,10 +36410,10 @@
         <v>2020</v>
       </c>
       <c r="B6" t="s">
-        <v>2030</v>
+        <v>2064</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2037</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -36109,7 +36421,10 @@
         <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>2031</v>
+        <v>2065</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2108</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -36117,10 +36432,10 @@
         <v>2022</v>
       </c>
       <c r="B8" t="s">
-        <v>2032</v>
+        <v>2066</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2038</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -36128,10 +36443,10 @@
         <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>2033</v>
+        <v>2067</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2039</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -36139,119 +36454,822 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>2034</v>
+        <v>2068</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2040</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="s">
-        <v>2026</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>2031</v>
+        <v>2070</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>2112</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>2019</v>
+        <v>2027</v>
       </c>
       <c r="B13" t="s">
-        <v>2029</v>
+        <v>2071</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2113</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>2017</v>
+        <v>2028</v>
       </c>
       <c r="B14" t="s">
-        <v>2027</v>
+        <v>2072</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>2022</v>
+        <v>2029</v>
       </c>
       <c r="B15" t="s">
-        <v>2032</v>
+        <v>2073</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2038</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="B16" t="s">
-        <v>2034</v>
+        <v>2074</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2040</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="B17" t="s">
-        <v>2035</v>
+        <v>2075</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2117</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>2018</v>
+        <v>2032</v>
       </c>
       <c r="B18" t="s">
-        <v>2028</v>
+        <v>2076</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2036</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>2020</v>
+        <v>2033</v>
       </c>
       <c r="B19" t="s">
-        <v>2030</v>
+        <v>2077</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2037</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>2023</v>
+        <v>2034</v>
       </c>
       <c r="B20" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>2033</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="B45" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>2039</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>2121</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1"/>
-    <hyperlink ref="C6" r:id="rId2"/>
-    <hyperlink ref="C8" r:id="rId3"/>
-    <hyperlink ref="C9" r:id="rId4"/>
-    <hyperlink ref="C10" r:id="rId5"/>
-    <hyperlink ref="C15" r:id="rId6"/>
-    <hyperlink ref="C16" r:id="rId7"/>
-    <hyperlink ref="C18" r:id="rId8"/>
-    <hyperlink ref="C19" r:id="rId9"/>
-    <hyperlink ref="C20" r:id="rId10"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C6" r:id="rId4"/>
+    <hyperlink ref="C7" r:id="rId5"/>
+    <hyperlink ref="C8" r:id="rId6"/>
+    <hyperlink ref="C9" r:id="rId7"/>
+    <hyperlink ref="C10" r:id="rId8"/>
+    <hyperlink ref="C12" r:id="rId9"/>
+    <hyperlink ref="C13" r:id="rId10"/>
+    <hyperlink ref="C14" r:id="rId11"/>
+    <hyperlink ref="C15" r:id="rId12"/>
+    <hyperlink ref="C16" r:id="rId13"/>
+    <hyperlink ref="C17" r:id="rId14"/>
+    <hyperlink ref="C18" r:id="rId15"/>
+    <hyperlink ref="C19" r:id="rId16"/>
+    <hyperlink ref="C20" r:id="rId17"/>
+    <hyperlink ref="C22" r:id="rId18"/>
+    <hyperlink ref="C23" r:id="rId19"/>
+    <hyperlink ref="C24" r:id="rId20"/>
+    <hyperlink ref="C25" r:id="rId21"/>
+    <hyperlink ref="C26" r:id="rId22"/>
+    <hyperlink ref="C27" r:id="rId23"/>
+    <hyperlink ref="C28" r:id="rId24"/>
+    <hyperlink ref="C29" r:id="rId25"/>
+    <hyperlink ref="C31" r:id="rId26"/>
+    <hyperlink ref="C32" r:id="rId27"/>
+    <hyperlink ref="C33" r:id="rId28"/>
+    <hyperlink ref="C34" r:id="rId29"/>
+    <hyperlink ref="C35" r:id="rId30"/>
+    <hyperlink ref="C36" r:id="rId31"/>
+    <hyperlink ref="C37" r:id="rId32"/>
+    <hyperlink ref="C38" r:id="rId33"/>
+    <hyperlink ref="C39" r:id="rId34"/>
+    <hyperlink ref="C40" r:id="rId35"/>
+    <hyperlink ref="C41" r:id="rId36"/>
+    <hyperlink ref="C42" r:id="rId37"/>
+    <hyperlink ref="C43" r:id="rId38"/>
+    <hyperlink ref="C44" r:id="rId39"/>
+    <hyperlink ref="C45" r:id="rId40"/>
+    <hyperlink ref="C46" r:id="rId41"/>
+    <hyperlink ref="C49" r:id="rId42"/>
+    <hyperlink ref="C50" r:id="rId43"/>
+    <hyperlink ref="C51" r:id="rId44"/>
+    <hyperlink ref="C52" r:id="rId45"/>
+    <hyperlink ref="C53" r:id="rId46"/>
+    <hyperlink ref="C54" r:id="rId47"/>
+    <hyperlink ref="C56" r:id="rId48"/>
+    <hyperlink ref="C58" r:id="rId49"/>
+    <hyperlink ref="C59" r:id="rId50"/>
+    <hyperlink ref="C60" r:id="rId51"/>
+    <hyperlink ref="C61" r:id="rId52"/>
+    <hyperlink ref="C62" r:id="rId53"/>
+    <hyperlink ref="C63" r:id="rId54"/>
+    <hyperlink ref="C64" r:id="rId55"/>
+    <hyperlink ref="C65" r:id="rId56"/>
+    <hyperlink ref="C66" r:id="rId57"/>
+    <hyperlink ref="C67" r:id="rId58"/>
+    <hyperlink ref="C68" r:id="rId59"/>
+    <hyperlink ref="C69" r:id="rId60"/>
+    <hyperlink ref="C70" r:id="rId61"/>
+    <hyperlink ref="C71" r:id="rId62"/>
+    <hyperlink ref="C72" r:id="rId63"/>
+    <hyperlink ref="C73" r:id="rId64"/>
+    <hyperlink ref="C74" r:id="rId65"/>
+    <hyperlink ref="C75" r:id="rId66"/>
+    <hyperlink ref="C76" r:id="rId67"/>
+    <hyperlink ref="C77" r:id="rId68"/>
+    <hyperlink ref="C78" r:id="rId69"/>
+    <hyperlink ref="C79" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9890" uniqueCount="2221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9966" uniqueCount="2286">
   <si>
     <t>ID</t>
   </si>
@@ -368,310 +368,310 @@
     <t>C0076</t>
   </si>
   <si>
-    <t>campaign--84bc21e9-f278-45cd-8acb-817742dcff21</t>
-  </si>
-  <si>
-    <t>campaign--4bf56bd2-d5ca-438b-a3aa-5cbc36381133</t>
-  </si>
-  <si>
-    <t>campaign--3bd127a5-73b3-4aac-8fd7-982a95669434</t>
-  </si>
-  <si>
-    <t>campaign--1b611c93-e848-4ee1-8527-8bbbdf2e62a5</t>
-  </si>
-  <si>
-    <t>campaign--09a157f6-2eda-4e89-85e1-0705374ca9ee</t>
-  </si>
-  <si>
-    <t>campaign--d2e92b25-7923-452d-8885-6245a64315da</t>
-  </si>
-  <si>
-    <t>campaign--20b4d9b6-86c9-414d-b7c2-ba45639bfae6</t>
-  </si>
-  <si>
-    <t>campaign--dbcf8329-be72-43a6-9503-bd3b5f80e167</t>
-  </si>
-  <si>
-    <t>campaign--06e4cf4f-1d7a-4669-bfe2-46cf114cf71f</t>
-  </si>
-  <si>
-    <t>campaign--21b1b148-99e1-447f-863e-5f179ec7aac7</t>
-  </si>
-  <si>
-    <t>campaign--d1a75343-e6bc-456b-af9c-67abfebd8778</t>
-  </si>
-  <si>
-    <t>campaign--a1253a3a-9d62-49e1-acc7-7430a198b8bc</t>
-  </si>
-  <si>
-    <t>campaign--7c61ae27-c860-4b7d-9dbc-12b393680025</t>
-  </si>
-  <si>
-    <t>campaign--0c5ea36b-4e12-47ff-8d99-a4a35e4327b0</t>
-  </si>
-  <si>
-    <t>campaign--8ba7050c-642b-4ab9-9ce1-6ca4a4676ab5</t>
-  </si>
-  <si>
-    <t>campaign--6232bf9b-bb63-402d-b03e-9a0515ee09d8</t>
-  </si>
-  <si>
-    <t>campaign--9f962768-2e42-4c2e-a172-9291db92461b</t>
-  </si>
-  <si>
-    <t>campaign--2e0766ba-2d5c-4bab-a68b-5fe011747831</t>
-  </si>
-  <si>
-    <t>campaign--4a0448c0-0001-4134-acd4-941aa1379172</t>
-  </si>
-  <si>
-    <t>campaign--eedf404e-3e21-4116-be4d-0d7601599b91</t>
-  </si>
-  <si>
-    <t>campaign--e62f4c80-a205-4fe1-91c4-85256ac37f31</t>
-  </si>
-  <si>
-    <t>campaign--6ceef077-03f6-482f-8e76-a98491db2913</t>
-  </si>
-  <si>
-    <t>campaign--2248df9e-ba27-43a8-98d8-9026a6b9de03</t>
-  </si>
-  <si>
-    <t>campaign--05daf063-815a-43c4-bdef-868e86a89149</t>
-  </si>
-  <si>
-    <t>campaign--584843e9-c5e0-4087-a142-c385deeb2bdf</t>
-  </si>
-  <si>
-    <t>campaign--a657f3f9-0df3-4ed7-a7a4-a5412ea7ecb6</t>
-  </si>
-  <si>
-    <t>campaign--8f323bf8-3b9b-4bf4-97ad-3d61fc33fd82</t>
-  </si>
-  <si>
-    <t>campaign--6e5202d1-fbbe-422b-84d5-246cb35c0b2d</t>
-  </si>
-  <si>
-    <t>campaign--8ba3d669-f614-429f-9b77-a9cf527ff71d</t>
-  </si>
-  <si>
-    <t>campaign--7ce1e89d-a9af-4fb3-81ee-15ea23718846</t>
-  </si>
-  <si>
-    <t>campaign--6c24cbbb-4ce2-45a1-981a-cf0fd9c34d97</t>
-  </si>
-  <si>
-    <t>campaign--b9baf1bc-a3fa-4050-8722-e4ac1d29b0aa</t>
-  </si>
-  <si>
-    <t>campaign--eb1f4e4b-b946-449e-8752-60b5a41d8094</t>
-  </si>
-  <si>
-    <t>campaign--fa1c9409-7b35-48bb-8f3f-1de992f2a9fe</t>
-  </si>
-  <si>
-    <t>campaign--485bc4b1-d6a0-4262-b92b-de60846a3cc2</t>
-  </si>
-  <si>
-    <t>campaign--f98d27b7-b9b2-4ee5-968d-2242b9fed57d</t>
-  </si>
-  <si>
-    <t>campaign--d9246b40-5b51-4294-bcd6-dba876074271</t>
-  </si>
-  <si>
-    <t>campaign--c084e1db-0f03-44c2-8697-12757be14ecf</t>
-  </si>
-  <si>
-    <t>campaign--78366146-c147-4bca-adbc-91cf59affa19</t>
-  </si>
-  <si>
-    <t>campaign--c4b1a1bd-5808-4f82-8404-cb671321f0b8</t>
-  </si>
-  <si>
-    <t>campaign--4cb4ba5f-3257-4a64-99a7-89c1c8584ea3</t>
-  </si>
-  <si>
-    <t>campaign--bb5621a4-0317-4a72-9557-a3309369a148</t>
-  </si>
-  <si>
-    <t>campaign--c00efded-d911-444c-8743-89ddb7c2a25b</t>
-  </si>
-  <si>
-    <t>campaign--33e7df73-0ba4-4031-911d-d9a34f23381e</t>
-  </si>
-  <si>
-    <t>campaign--398bbef2-59b4-4eae-b7fb-2ddb4325a3db</t>
-  </si>
-  <si>
-    <t>campaign--5e9e3ee9-0edc-47b8-b51f-27d825c93ba6</t>
-  </si>
-  <si>
-    <t>campaign--a928c5b5-bd92-4716-bd4b-8e2e42e22ee8</t>
-  </si>
-  <si>
-    <t>campaign--13a5e084-1143-4c42-82a1-97c7cc060f9c</t>
-  </si>
-  <si>
-    <t>campaign--2f03ada1-afc9-4e6a-b822-aa65414b1b02</t>
-  </si>
-  <si>
-    <t>campaign--6d1a46e6-ac73-4930-aabd-a8f533a687cf</t>
-  </si>
-  <si>
-    <t>campaign--5f6c1d2e-8b43-49f7-9d3f-f3a0c3ae48b1</t>
-  </si>
-  <si>
-    <t>campaign--2e2bed38-682c-4d2f-ad6c-e2bb4c4cfdd0</t>
-  </si>
-  <si>
-    <t>campaign--fcb45d3f-14e8-4834-8b2c-d18b4c8f5273</t>
-  </si>
-  <si>
-    <t>campaign--c86c2f91-e10d-4e8b-b767-78378e15121e</t>
-  </si>
-  <si>
-    <t>campaign--0ba3a916-5b43-4183-b453-0927882dba85</t>
-  </si>
-  <si>
-    <t>campaign--e0cc83b8-2a5f-42f8-8537-a7a3e72ee650</t>
-  </si>
-  <si>
-    <t>campaign--4fa7d988-4c1c-4971-84cf-ca0467775997</t>
-  </si>
-  <si>
-    <t>campaign--49d099af-a6dc-4afe-8188-c064ef26fde7</t>
-  </si>
-  <si>
-    <t>campaign--007f466b-7682-4d8a-b195-22c21ff3e565</t>
-  </si>
-  <si>
-    <t>campaign--8f1d796b-636c-4cd1-86b4-37c3ece5165a</t>
-  </si>
-  <si>
-    <t>campaign--3d806c36-94c1-487f-b65e-9ff91c2a9abb</t>
-  </si>
-  <si>
-    <t>campaign--f2ebdc18-4134-4740-9f13-2c482064e83a</t>
-  </si>
-  <si>
-    <t>campaign--c4507383-caba-4152-b825-48578038d866</t>
-  </si>
-  <si>
-    <t>campaign--127d73b7-ad29-4bc6-bae2-aec0c43bad66</t>
-  </si>
-  <si>
-    <t>campaign--b67d3570-8e41-417e-8f8e-7d5ecb7e1d31</t>
-  </si>
-  <si>
-    <t>campaign--7b0b746d-42c4-4b10-aa04-8bfec1343821</t>
-  </si>
-  <si>
-    <t>campaign--d00c3e48-4826-4f1e-bfb7-118f00d84861</t>
-  </si>
-  <si>
-    <t>campaign--51b9d6b1-568b-4d68-8f9c-19a0b548272b</t>
-  </si>
-  <si>
-    <t>campaign--ce760399-e985-4e95-bb41-7d3b796dd18b</t>
-  </si>
-  <si>
-    <t>campaign--4e66eed7-56a9-48ac-8a18-99a559927eb6</t>
-  </si>
-  <si>
-    <t>campaign--152cca2d-a341-45fd-a306-6690c012f021</t>
-  </si>
-  <si>
-    <t>campaign--387e09ec-bf7a-447c-a918-bcff0ee9da8b</t>
-  </si>
-  <si>
-    <t>campaign--beeb4667-4ab9-4028-94c4-b6b19eefabeb</t>
-  </si>
-  <si>
-    <t>campaign--40524974-ff86-4741-bc58-ccfb35d10bc7</t>
-  </si>
-  <si>
-    <t>campaign--d5059819-4fb3-4b0e-9e0a-5784b854386c</t>
-  </si>
-  <si>
-    <t>campaign--0dca3871-e3fd-47d7-a07f-e9ea15919c0d</t>
-  </si>
-  <si>
-    <t>campaign--d6da9526-4dd6-4eb9-abfd-44a5e1879d41</t>
-  </si>
-  <si>
-    <t>campaign--b1e8059c-3914-414e-8a6d-0fb74549bec8</t>
-  </si>
-  <si>
-    <t>campaign--2660323c-96cd-4d12-920b-3ca598fbdb74</t>
-  </si>
-  <si>
-    <t>campaign--a51dfeb5-c6ce-44b2-9bc5-c4c6687bd2f0</t>
-  </si>
-  <si>
-    <t>campaign--f3a217be-13bd-488e-b046-33d4a55b2cf3</t>
-  </si>
-  <si>
-    <t>campaign--5424b97c-0790-47c0-bc6a-99fda22a8e9d</t>
-  </si>
-  <si>
-    <t>campaign--6733da7e-2f67-4c13-97a6-00b05a549f10</t>
-  </si>
-  <si>
-    <t>campaign--ce5cc518-cbce-4e92-b8ff-30e504c15c2c</t>
-  </si>
-  <si>
-    <t>campaign--2907649b-fd94-42fa-8784-f18f4584d71a</t>
-  </si>
-  <si>
-    <t>campaign--dddb4201-585e-47c1-95e9-425b0730fb90</t>
-  </si>
-  <si>
-    <t>campaign--cf6632c9-6e3d-4cbc-9dce-724891b573c7</t>
-  </si>
-  <si>
-    <t>campaign--e7ee89b0-2cb6-4b84-948c-7057dd523852</t>
-  </si>
-  <si>
-    <t>campaign--eddd1738-28fd-4da0-b6f4-7c44a32152b7</t>
-  </si>
-  <si>
-    <t>campaign--5fa57ffc-7b8e-49c1-82da-60712fe1a716</t>
-  </si>
-  <si>
-    <t>campaign--466f1dd3-c4d2-4076-b0d7-d52a41e7bc83</t>
-  </si>
-  <si>
-    <t>campaign--11dce568-2d19-4c59-bdfd-64ec6fced3e6</t>
-  </si>
-  <si>
-    <t>campaign--0356e86e-0974-45cf-b41d-6997de20ba10</t>
-  </si>
-  <si>
-    <t>campaign--0956db31-89c5-43f3-aaa6-f6d9b3b7ff12</t>
-  </si>
-  <si>
-    <t>campaign--5177f321-68a6-4d63-a678-c5265f63243b</t>
-  </si>
-  <si>
-    <t>campaign--7402cc4a-618b-4851-8075-cb883379e3c0</t>
-  </si>
-  <si>
-    <t>campaign--b5ce00ca-7682-4ce8-9c4c-8be0c65df490</t>
-  </si>
-  <si>
-    <t>campaign--af98cd78-ddfd-4a73-8ab2-5b920e8221ac</t>
-  </si>
-  <si>
-    <t>campaign--9f187028-927d-4536-ba2f-3f2177c0e164</t>
-  </si>
-  <si>
-    <t>campaign--66970f35-4e71-491e-932e-1fee6b188e71</t>
-  </si>
-  <si>
-    <t>campaign--d419efc6-e0ba-4f5e-83a2-46e1d38cd231</t>
-  </si>
-  <si>
-    <t>campaign--09ffe87c-9f1c-4a9e-9879-3648aa2d3535</t>
+    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
+  </si>
+  <si>
+    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
+  </si>
+  <si>
+    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
+  </si>
+  <si>
+    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
+  </si>
+  <si>
+    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
+  </si>
+  <si>
+    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
+  </si>
+  <si>
+    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
+  </si>
+  <si>
+    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
+  </si>
+  <si>
+    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
+  </si>
+  <si>
+    <t>campaign--5b0cdeff-e761-4c3f-ba0c-feaec1ead563</t>
+  </si>
+  <si>
+    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
+  </si>
+  <si>
+    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
+  </si>
+  <si>
+    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
+  </si>
+  <si>
+    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
+  </si>
+  <si>
+    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
+  </si>
+  <si>
+    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
+  </si>
+  <si>
+    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
+  </si>
+  <si>
+    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
+  </si>
+  <si>
+    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
+  </si>
+  <si>
+    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
+  </si>
+  <si>
+    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
+  </si>
+  <si>
+    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
+  </si>
+  <si>
+    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
+  </si>
+  <si>
+    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
+  </si>
+  <si>
+    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
+  </si>
+  <si>
+    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
+  </si>
+  <si>
+    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
+  </si>
+  <si>
+    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
+  </si>
+  <si>
+    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
+  </si>
+  <si>
+    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
+  </si>
+  <si>
+    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
+  </si>
+  <si>
+    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
+  </si>
+  <si>
+    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
+  </si>
+  <si>
+    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
+  </si>
+  <si>
+    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
+  </si>
+  <si>
+    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
+  </si>
+  <si>
+    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
+  </si>
+  <si>
+    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
+  </si>
+  <si>
+    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
+  </si>
+  <si>
+    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
+  </si>
+  <si>
+    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
+  </si>
+  <si>
+    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
+  </si>
+  <si>
+    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
+  </si>
+  <si>
+    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
+  </si>
+  <si>
+    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
+  </si>
+  <si>
+    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
+  </si>
+  <si>
+    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
+  </si>
+  <si>
+    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
+  </si>
+  <si>
+    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
+  </si>
+  <si>
+    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
+  </si>
+  <si>
+    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
+  </si>
+  <si>
+    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
+  </si>
+  <si>
+    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
+  </si>
+  <si>
+    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
+  </si>
+  <si>
+    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
+  </si>
+  <si>
+    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
+  </si>
+  <si>
+    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
+  </si>
+  <si>
+    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
+  </si>
+  <si>
+    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
+  </si>
+  <si>
+    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
+  </si>
+  <si>
+    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
+  </si>
+  <si>
+    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
+  </si>
+  <si>
+    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
+  </si>
+  <si>
+    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
+  </si>
+  <si>
+    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
+  </si>
+  <si>
+    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
+  </si>
+  <si>
+    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
+  </si>
+  <si>
+    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
+  </si>
+  <si>
+    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
+  </si>
+  <si>
+    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
+  </si>
+  <si>
+    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
+  </si>
+  <si>
+    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
+  </si>
+  <si>
+    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
+  </si>
+  <si>
+    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
+  </si>
+  <si>
+    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
+  </si>
+  <si>
+    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
+  </si>
+  <si>
+    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
+  </si>
+  <si>
+    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
+  </si>
+  <si>
+    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
+  </si>
+  <si>
+    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
+  </si>
+  <si>
+    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
+  </si>
+  <si>
+    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
+  </si>
+  <si>
+    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
+  </si>
+  <si>
+    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
+  </si>
+  <si>
+    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
+  </si>
+  <si>
+    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
+  </si>
+  <si>
+    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
+  </si>
+  <si>
+    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
+  </si>
+  <si>
+    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
+  </si>
+  <si>
+    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
+  </si>
+  <si>
+    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
+  </si>
+  <si>
+    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
+  </si>
+  <si>
+    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
+  </si>
+  <si>
+    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
+  </si>
+  <si>
+    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
+  </si>
+  <si>
+    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
+  </si>
+  <si>
+    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
+  </si>
+  <si>
+    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
+  </si>
+  <si>
+    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
+  </si>
+  <si>
+    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
+  </si>
+  <si>
+    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
+  </si>
+  <si>
+    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
   </si>
   <si>
     <t>«Вечный мир» с Польшей (1686)</t>
@@ -1124,10 +1124,10 @@
     <t>Атака на традиционный уклад украинского села, которое оставалось главным носителем национальной идентичности и экономической независимости. Под лозунгами социалистической модернизации Москва провела насильственное изъятие земли, скота и инвентаря. Крестьян, оказывавших сопротивление (так называемых «куркулів»), массово лишали имущества и депортировали в Сибирь и на Север. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013) (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Тотальная зачистка этнических меньшинств (поляков, немцев, греков, болгар) в рамках Большого террора через целевые национальные приказы НКВД. Параллельно, в 1938 году, Москва официально ликвидирует все без исключения национальные районы и школы для меньшинств, а также вводит постановление об обязательном изучении русского языка во всех школах Украины, возвращаясь к откровенным имперским практикам ассимиляции. (Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1) 1998) (Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1928 ГГ . 2011)</t>
-  </si>
-  <si>
-    <t>Скрытое военное вторжение и оккупация Крымского полуострова, ознаменовавшие начало гибридной вооруженной агрессии РФ против Украины. Операция включала захват административных зданий военными без знаков различия («зелеными человечками»), насильственное назначение подконтрольного премьера и проведение фиктивного референдума. Завершилась официальным юридическим поглощением территории Государственной думой РФ. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
+    <t>Тотальная зачистка этнических меньшинств (поляков, немцев, греков, болгар) в рамках Большого террора через целевые национальные приказы НКВД. Параллельно, в 1938 году, Москва официально ликвидирует все без исключения национальные районы и школы для меньшинств, а также вводит постановление об обязательном изучении русского языка во всех школах Украины, возвращаясь к откровенным имперским практикам ассимиляции. (Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1) 1998) (Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011)</t>
+  </si>
+  <si>
+    <t>Скрытое военное вторжение и оккупация Крымского полуострова, ознаменовавшие начало гибридной вооруженной агрессии РФ против Украины. Операция включала захват административных зданий военными без знаков различия («зелеными человечками»), насильственное назначение подконтрольного премьера и проведение фиктивного референдума. Завершилась официальным юридическим поглощением территории Государственной думой РФ. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>Упразднение традиционной системы местного самоуправления в городах. Это решение перевело суды на русский язык и лишило коренное население возможности использовать родной язык в официальной сфере (Citation: Русифікація України — Вікіпедія 2026).</t>
@@ -1136,7 +1136,7 @@
     <t>Имперская реформа по ликвидации военно-социальной структуры Слобожанщины. Казацкие полки были упразднены, казаки лишены привилегий и переведены в статус государственных крестьян («войсковых обывателей»), а территория превращена в обычную российскую губернию (Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Ответ КГБ на зарождение движения сопротивления среди новой украинской интеллигенции. Включает подавление протестов 1965 года (выступление Стуса, Дзюбы и Черновола на премьере «Теней забытых предков») и давление на подписантов «Письма 139» в 1968 году, в котором видные деятели культуры выступили против незаконных политических судов. Сюда же относится преследование подпольного Украинского национального фронта. (Citation: Письмо-протест 139 - Википедия 2026) (Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) - ХПГ 2026)</t>
+    <t>Ответ КГБ на зарождение движения сопротивления среди новой украинской интеллигенции. Включает подавление протестов 1965 года (выступление Стуса, Дзюбы и Черновола на премьере «Теней забытых предков») и давление на подписантов «Письма 139» в 1968 году, в котором видные деятели культуры выступили против незаконных политических судов. Сюда же относится преследование подпольного Украинского национального фронта. (Citation: Письмо-протест 139 - Википедия 2026) (Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026)</t>
   </si>
   <si>
     <t>Империя массово мобилизует украинцев в качестве пушечного мяса в мировой войне, а в ходе наступления оккупирует Галичину и начинает там политику тотального уничтожения украинских институтов (Citation: Україна в Першій світовій війні — Вікіпедія 2026) (Citation: Історія України — Вікіпедія 2026).</t>
@@ -1190,7 +1190,7 @@
     <t>Первая попытка Советской России (Российской Советской Республики) ликвидировать независимость Украины путем перехвата власти на Всеукраинском съезде советов. Большевистское правительство (СНК) планировало внедрить своих делегатов, искусственно создать большинство и легально проголосовать за передачу власти подконтрольным Советам. Украинское руководство распознало угрозу и мобилизовало своих сторонников, оставив делегатов агрессора в абсолютном меньшинстве и сорвав захват. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013) (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
-    <t>Расширение российской агрессии через захват административных зданий на востоке Украины вооруженными отрядами российских боевиков (группа И. Стрелкова) для создания марионеточных ДНР и ЛНР. Кампания сопровождалась террором против местного населения, сбитием рейса MH17 и массированной дезинформацией. Летом 2014 года РФ ввела регулярные войска, что привело к боям под Иловайском и Дебальцево. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
+    <t>Расширение российской агрессии через захват административных зданий на востоке Украины вооруженными отрядами российских боевиков (группа И. Стрелкова) для создания марионеточных ДНР и ЛНР. Кампания сопровождалась террором против местного населения, сбитием рейса MH17 и массированной дезинформацией. Летом 2014 года РФ ввела регулярные войска, что привело к боям под Иловайском и Дебальцево. (Citation: Война и наказание: Как Россия уничтожала Украину 2023) (Citation: Російсько-українська війна (з 2014) — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>Создание марионеточного правительства (Временного совета ЧР), массовый подкуп элит и снабжение вооруженной оппозиции тяжелой техникой, завершившееся ноябрьским штурмом Грозного с участием кадровых российских военных (Citation: Хроника первой российской войны в Чечне 2026).</t>
@@ -2132,31 +2132,31 @@
     <t>31 January 1924</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696)</t>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696)</t>
   </si>
   <si>
     <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Повстання бузьких козаків (1817)</t>
+    <t>(Citation: Повстання бузьких козаків (1817),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817),(Citation: Задунайська Січ — Вікіпедія 2026),(Citation: Повстання бузьких козаків (1817)</t>
   </si>
   <si>
     <t>,(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -2165,19 +2165,19 @@
     <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Ліквідація Запорозької Січі (1775)</t>
+    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775)</t>
   </si>
   <si>
     <t>(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Перепис населення Російської імперії (1897),(Citation: Перепис населення Російської імперії (1897),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897)</t>
+    <t>(Citation: Перепис населення Російської імперії (1897),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Перепис населення Російської імперії (1897)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
@@ -2189,7 +2189,7 @@
     <t>(Citation: Рашизм: Звір з безодні 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Рашизм: Звір з безодні 2023)</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Киевский синопсис — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026)</t>
@@ -2198,7 +2198,7 @@
     <t>(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
@@ -2213,10 +2213,10 @@
     <t>(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Крымская война — Википедия 2026),(Citation: Київська козаччина — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Крымская война — Википедия 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Крымская война — Википедия 2026),(Citation: Крымская война — Википедия 2026),(Citation: Київська козаччина — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
@@ -2228,7 +2228,7 @@
     <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
+    <t>(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Ліквідація козацтва на Правобережній Україні (1699),(Citation: Ліквідація козацтва на Правобережній Україні (1699)</t>
@@ -2240,7 +2240,7 @@
     <t>(Citation: Московські статті (1665),(Citation: Московські статті (1665),(Citation: Московські статті (1665)</t>
   </si>
   <si>
-    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026)</t>
+    <t>(Citation: Руїна — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
@@ -2255,13 +2255,13 @@
     <t>(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Письмо-протест 139 - Википедия 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987)</t>
   </si>
   <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Переяславська рада — Вікіпедія 2026)</t>
+    <t>(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Переяславські статті (1659),(Citation: Переяславські статті (1659),(Citation: Переяславські статті (1659)</t>
@@ -2273,13 +2273,13 @@
     <t>(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Антикріпосницький рух в Україні (1789-1861)</t>
   </si>
   <si>
-    <t>(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Норильское восстание - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: Рашизм: Звір з безодні 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®),(Citation: Рашизм: Звір з безодні 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK® 2025),(Citation: Campaign C0026 | MITRE ATT&amp;CK® 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Російсько-українська війна (з 2014),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Російсько-українська війна (з 2014),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Campaign C0026 | MITRE ATT&amp;CK® 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK® 2025),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
@@ -2291,13 +2291,13 @@
     <t>(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711)</t>
   </si>
   <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026)</t>
+    <t>(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Російсько-українська війна (з 2014),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
@@ -2315,10 +2315,10 @@
     <t>(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1768—1774)</t>
   </si>
   <si>
-    <t>(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Російсько-турецька війна (1806—1812)</t>
-  </si>
-  <si>
-    <t>(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026)</t>
@@ -2462,43 +2462,43 @@
     <t>Имперские Коллегии</t>
   </si>
   <si>
-    <t>tool--b8bf442f-c688-4983-bc89-7fc0e5a2d70f</t>
-  </si>
-  <si>
-    <t>tool--43db716c-e55e-4798-8810-4606ebb81e52</t>
-  </si>
-  <si>
-    <t>tool--17849785-49e2-4f22-9488-618cbc11cec9</t>
-  </si>
-  <si>
-    <t>tool--03b1e023-5469-49ea-9988-c7118a91b725</t>
-  </si>
-  <si>
-    <t>tool--78806636-7cbc-4a54-9f61-2a5a98a33f13</t>
-  </si>
-  <si>
-    <t>tool--4d2e439d-9619-4447-8a41-1af8960acc55</t>
-  </si>
-  <si>
-    <t>tool--6fd47d4c-bac8-4dcd-b582-e6a42bb51313</t>
-  </si>
-  <si>
-    <t>tool--4a55efd1-b775-4318-8adc-ebb029729960</t>
-  </si>
-  <si>
-    <t>tool--ed0808d4-111e-4057-a345-7d951b669eb5</t>
-  </si>
-  <si>
-    <t>tool--60f65bd4-46b3-4eed-9418-254cf51965fd</t>
-  </si>
-  <si>
-    <t>tool--1652bd4f-c611-4f10-aedc-6581590e2df2</t>
-  </si>
-  <si>
-    <t>tool--b591e96e-6cd5-4b20-9c6f-aa7dc5747255</t>
-  </si>
-  <si>
-    <t>tool--6faacf93-e3f5-43f6-8d94-9d2c7c6382a9</t>
+    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
+  </si>
+  <si>
+    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
+  </si>
+  <si>
+    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
+  </si>
+  <si>
+    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
+  </si>
+  <si>
+    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
+  </si>
+  <si>
+    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
+  </si>
+  <si>
+    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
+  </si>
+  <si>
+    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
+  </si>
+  <si>
+    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
+  </si>
+  <si>
+    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
+  </si>
+  <si>
+    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
+  </si>
+  <si>
+    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
+  </si>
+  <si>
+    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
   </si>
   <si>
     <t>software</t>
@@ -2507,7 +2507,7 @@
     <t>Юридическая фиксация раскола страны на две части с превращением Правобережья в буферную зону: «По условиям Вечного мира Правобережье осталось за Польшей... договорили и постановили, что те места оставатись имеют пусты, так как ныне суть» (Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)(Citation: Мазепа 2007).</t>
   </si>
   <si>
-    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Использование институтов государственного здравоохранения для политически мотивированного диагностирования инакомыслящих (диагноз «вялотекущая шизофрения») и их бессрочной изоляции в психиатрических больницах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Массовые аресты членов Украинской Хельсинкской группы и фабрикация уголовных дел, приведшие к длительной изоляции и гибели видных диссидентов (в том числе Василя Стуса) в лагерях особого режима. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -2852,7 +2852,7 @@
     <t>Вторжение регулярной армии РФ и нанесение массированных ракетно-авиационных ударов по Киеву, Днепру, Харькову и другим украинским городам ранним утром 24 февраля 2022 года. (Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>Систематические кибератаки на энергетические компании и муниципальные теплоснабжающие предприятия в условиях полномасштабной войны для прекращения подачи электроэнергии и тепла украинским гражданским потребителям. (Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®) (Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024). 
+    <t>Систематические кибератаки на энергетические компании и муниципальные теплоснабжающие предприятия в условиях полномасштабной войны для прекращения подачи электроэнергии и тепла украинским гражданским потребителям. (Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024) (Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024). 
 Систематическое нанесение массированных ударов крылатыми ракетами и дронами-камикадзе (Shahed) по объектам генерации (Змиевская ТЭЦ, Харьковская ТЭЦ-5, Трипольская ТЭС, ДнепроГЭС) и трансформаторным подстанциям для создания блэкаутов. (Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026)</t>
   </si>
   <si>
@@ -3054,553 +3054,553 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--889d82e4-c966-46ee-813f-71a4ed883cb3</t>
-  </si>
-  <si>
-    <t>relationship--da414b25-28e7-4ad0-8cca-2cd59cdc48e1</t>
-  </si>
-  <si>
-    <t>relationship--aad22950-d6b3-4fe0-b4b4-caad525e66f9</t>
-  </si>
-  <si>
-    <t>relationship--da141e9b-14f5-475d-99d3-c04fc29be05a</t>
-  </si>
-  <si>
-    <t>relationship--85595de6-5e82-4a7f-b38b-4b435d8cf145</t>
-  </si>
-  <si>
-    <t>relationship--7b26ad80-eb32-4bc4-862c-c1bea3fbb5b8</t>
-  </si>
-  <si>
-    <t>relationship--64c6a3db-95b7-4e80-8617-864066661402</t>
-  </si>
-  <si>
-    <t>relationship--35e874c2-2f0e-465c-84a3-1a52fb3c1b26</t>
-  </si>
-  <si>
-    <t>relationship--dcff66f2-928d-4376-b74d-88e6e8dbf2a5</t>
-  </si>
-  <si>
-    <t>relationship--d7492bb2-0caf-43b4-ae2b-8ee766277e6f</t>
-  </si>
-  <si>
-    <t>relationship--cbae46bb-6a35-426e-b26f-99c4dcfb2180</t>
-  </si>
-  <si>
-    <t>relationship--1708cf7c-b8a3-467b-bfc8-b4377ecd8c38</t>
-  </si>
-  <si>
-    <t>relationship--7574787e-7bb0-4142-9608-d3431597b447</t>
-  </si>
-  <si>
-    <t>relationship--11b3f371-48c5-4e60-aa9e-0916f44736d9</t>
-  </si>
-  <si>
-    <t>relationship--cc273750-9b46-4c99-b177-0a13451fa78b</t>
-  </si>
-  <si>
-    <t>relationship--622624c2-53db-46f8-be5e-d6e076333f46</t>
-  </si>
-  <si>
-    <t>relationship--22bea2fb-f567-4526-920e-59a0897693d6</t>
-  </si>
-  <si>
-    <t>relationship--44443958-236b-4f9d-8dd9-dd2639671b09</t>
-  </si>
-  <si>
-    <t>relationship--0eca743f-f114-4eda-8c60-ec4089510360</t>
-  </si>
-  <si>
-    <t>relationship--78491aa4-2e4c-497b-a148-f18a3699f56b</t>
-  </si>
-  <si>
-    <t>relationship--7b87aecc-4151-47c7-bdb2-52939bf7dbc3</t>
-  </si>
-  <si>
-    <t>relationship--c8b13959-0d01-4ec3-a0f5-48fc07bbf2cb</t>
-  </si>
-  <si>
-    <t>relationship--65a5ac54-0c22-4eb2-aa18-8fdad83e0379</t>
-  </si>
-  <si>
-    <t>relationship--ee484915-af85-415a-aee2-59f72dfabfee</t>
-  </si>
-  <si>
-    <t>relationship--54b740d5-dc2a-488a-9abe-15274e89c834</t>
-  </si>
-  <si>
-    <t>relationship--d4163bd3-d740-44b0-84b8-52453b734603</t>
-  </si>
-  <si>
-    <t>relationship--9f8b72df-9550-4e18-b5b9-5f6d5dbdb913</t>
-  </si>
-  <si>
-    <t>relationship--111463bd-bdd5-4238-b51c-d664db9a7527</t>
-  </si>
-  <si>
-    <t>relationship--e7d51b28-6ac8-4287-8edd-a7a2eebd5b96</t>
-  </si>
-  <si>
-    <t>relationship--c1d642c5-e1bf-4fcb-b15e-f3b758183aeb</t>
-  </si>
-  <si>
-    <t>relationship--644b2b16-6c0b-4193-9307-c7c5138365ad</t>
-  </si>
-  <si>
-    <t>relationship--5f5efdfd-5041-41ef-8ee9-25f9ab012dcf</t>
-  </si>
-  <si>
-    <t>relationship--543ae80c-998e-4a3d-87fc-2a0b9571daf1</t>
-  </si>
-  <si>
-    <t>relationship--5c23f23c-fa2c-42fc-a317-81435663b76b</t>
-  </si>
-  <si>
-    <t>relationship--90480a09-7e26-49ad-a06f-27abea71cd39</t>
-  </si>
-  <si>
-    <t>relationship--fa31a1e8-20be-4e59-acc3-f09fe1e88b70</t>
-  </si>
-  <si>
-    <t>relationship--06d0ed0b-2c51-4206-b60a-a6e4ff14aa9c</t>
-  </si>
-  <si>
-    <t>relationship--82488210-7fea-4709-b86a-ef25cc365ac6</t>
-  </si>
-  <si>
-    <t>relationship--961f7abb-d697-447f-937b-f617667fb890</t>
-  </si>
-  <si>
-    <t>relationship--afe322f3-20c6-4e19-bd5f-d934c0474718</t>
-  </si>
-  <si>
-    <t>relationship--c43b0019-ba2d-48ae-b94b-d9c00bdc7252</t>
-  </si>
-  <si>
-    <t>relationship--08a9e1b2-e85d-4cc5-bff1-39e0b459d38d</t>
-  </si>
-  <si>
-    <t>relationship--9fd32872-fa9b-4d10-a701-c9b9194b1faa</t>
-  </si>
-  <si>
-    <t>relationship--c20acf41-bf5b-459b-9d0e-13fac2907477</t>
-  </si>
-  <si>
-    <t>relationship--6a767d68-cfbb-4a18-8f10-94e866e5b8d7</t>
-  </si>
-  <si>
-    <t>relationship--a3737ab9-45f4-4cc1-b6a0-13c844b88dde</t>
-  </si>
-  <si>
-    <t>relationship--901f30d8-fc0c-4eb8-96f9-32d584a54246</t>
-  </si>
-  <si>
-    <t>relationship--b7663582-1572-4a44-b833-ad625c8cb24e</t>
-  </si>
-  <si>
-    <t>relationship--66e8ebce-a52b-4c43-9394-179226de2659</t>
-  </si>
-  <si>
-    <t>relationship--2fa363d9-3c0c-4552-90c7-8b8da0401f52</t>
-  </si>
-  <si>
-    <t>relationship--9f7e791a-cc20-4d06-9580-dd8ca3b03a4d</t>
-  </si>
-  <si>
-    <t>relationship--80b672fa-e491-44f1-9d66-d0c4886e6662</t>
-  </si>
-  <si>
-    <t>relationship--98d1d772-87b7-4001-b802-5b49faa65cee</t>
-  </si>
-  <si>
-    <t>relationship--213bdb84-51c4-45d0-89ac-99e1ee8522ee</t>
-  </si>
-  <si>
-    <t>relationship--17dea7f1-bad6-4016-b896-5ee021167a3c</t>
-  </si>
-  <si>
-    <t>relationship--7ac430ee-94d3-4633-8163-1e741c370134</t>
-  </si>
-  <si>
-    <t>relationship--422dfbc2-8291-4dc5-aefb-11bd94209cdc</t>
-  </si>
-  <si>
-    <t>relationship--11dc28fb-4450-4809-88bb-0c900fe1c2f3</t>
-  </si>
-  <si>
-    <t>relationship--dbf0b5c8-d27a-43c6-aedc-094feb1c0d90</t>
-  </si>
-  <si>
-    <t>relationship--51500d5f-2f2e-41c6-ad55-109ac321d20e</t>
-  </si>
-  <si>
-    <t>relationship--615b98b1-f463-4b83-b8a3-b570adafa3cc</t>
-  </si>
-  <si>
-    <t>relationship--f3d4e74c-fff3-4f81-b8fa-e219a78584cd</t>
-  </si>
-  <si>
-    <t>relationship--02303830-e777-4696-abd6-79af6cc46785</t>
-  </si>
-  <si>
-    <t>relationship--bd8df92b-4f7e-4fa1-a913-989c9b017938</t>
-  </si>
-  <si>
-    <t>relationship--3c03a0ec-6f48-48ea-b065-211f31f2894e</t>
-  </si>
-  <si>
-    <t>relationship--f8c0eb74-3575-4c55-a2d7-fba3ae802c40</t>
-  </si>
-  <si>
-    <t>relationship--da2da2f9-6084-45e5-a597-036208e9789e</t>
-  </si>
-  <si>
-    <t>relationship--c6ba7b3a-658d-4451-a98d-734322d8c54f</t>
-  </si>
-  <si>
-    <t>relationship--50ddb0a0-2867-44ed-91bc-b4dc901c80a3</t>
-  </si>
-  <si>
-    <t>relationship--88bccc8a-f7a2-49e1-a46f-367f8e27b642</t>
-  </si>
-  <si>
-    <t>relationship--3da1cb1c-cbae-43c0-bda4-07e3c264e71e</t>
-  </si>
-  <si>
-    <t>relationship--4f9574d4-02b8-4eca-9761-bbe5c069b344</t>
-  </si>
-  <si>
-    <t>relationship--9b16c020-b229-44f3-a8a1-c734308acc2a</t>
-  </si>
-  <si>
-    <t>relationship--4ae6a58e-d25b-48f8-ad29-e635c557e4fb</t>
-  </si>
-  <si>
-    <t>relationship--f53a0328-348d-41c6-8135-0ca1de900c44</t>
-  </si>
-  <si>
-    <t>relationship--3f994d91-2c90-41f2-92d8-263b6b544715</t>
-  </si>
-  <si>
-    <t>relationship--8df57727-064b-46cf-b734-615967f897af</t>
-  </si>
-  <si>
-    <t>relationship--0f783440-214a-4e1b-a578-17f990858926</t>
-  </si>
-  <si>
-    <t>relationship--57032a0b-d541-41be-b819-7d0d63f0b5e3</t>
-  </si>
-  <si>
-    <t>relationship--127fbaae-cb89-4739-a530-200a56c7969f</t>
-  </si>
-  <si>
-    <t>relationship--0f43555b-8d92-45d3-ba11-936e6545bc93</t>
-  </si>
-  <si>
-    <t>relationship--eeae3f06-5874-46d3-b082-b8562399910a</t>
-  </si>
-  <si>
-    <t>relationship--08d9608a-ea6a-41f0-af32-d0c899a83e7c</t>
-  </si>
-  <si>
-    <t>relationship--f1861116-7010-481e-8a86-6186461e7dbc</t>
-  </si>
-  <si>
-    <t>relationship--1821da0f-0ff6-4632-aec7-b813e5a83ca2</t>
-  </si>
-  <si>
-    <t>relationship--ae7cce33-6c06-40ca-8b00-7ba834cf1c0d</t>
-  </si>
-  <si>
-    <t>relationship--bb414712-b107-42a6-9d85-b650a2de464b</t>
-  </si>
-  <si>
-    <t>relationship--f6f0c367-67f9-48a0-a597-0ae07851f48a</t>
-  </si>
-  <si>
-    <t>relationship--d950ef63-aa43-40c9-8f83-813083d3d88f</t>
-  </si>
-  <si>
-    <t>relationship--78a7ef97-62b2-4fb4-ac12-997a6aed2ac6</t>
-  </si>
-  <si>
-    <t>relationship--8b727f87-2159-4163-939d-91e1821413e5</t>
-  </si>
-  <si>
-    <t>relationship--a04c3a8d-a32f-4a26-9115-bf067c7473c7</t>
-  </si>
-  <si>
-    <t>relationship--47631dd5-2035-4775-9342-c7a5d57463d2</t>
-  </si>
-  <si>
-    <t>relationship--22eff706-0769-49f0-9f2f-776115e3b86f</t>
-  </si>
-  <si>
-    <t>relationship--96909df7-d822-41ef-bce3-59aeb959f27f</t>
-  </si>
-  <si>
-    <t>relationship--a2be2f18-7418-4bc3-8d13-5a5cc0535a48</t>
-  </si>
-  <si>
-    <t>relationship--30fc98f5-39ab-4f73-9cf8-ecd4f13bad9c</t>
-  </si>
-  <si>
-    <t>relationship--20819672-cfc6-4d90-9978-67392464f9b5</t>
-  </si>
-  <si>
-    <t>relationship--0ea39f20-20c1-4f5a-97d8-19f243edd037</t>
-  </si>
-  <si>
-    <t>relationship--509c7f00-4bc2-49ff-93b0-830f5a811d4a</t>
-  </si>
-  <si>
-    <t>relationship--27307274-6d91-422f-892f-1920ff7f356d</t>
-  </si>
-  <si>
-    <t>relationship--ff40733b-8dae-4471-9e66-760250865fb7</t>
-  </si>
-  <si>
-    <t>relationship--493ade73-abf7-427c-9d87-81defb451d8b</t>
-  </si>
-  <si>
-    <t>relationship--e37eb846-1fc9-44d6-b0a4-05048966e228</t>
-  </si>
-  <si>
-    <t>relationship--a505add1-1a18-4ee5-b1db-fec9c4f48f9c</t>
-  </si>
-  <si>
-    <t>relationship--3b9ac042-c0a7-49ac-857f-05065c54075a</t>
-  </si>
-  <si>
-    <t>relationship--f4f67668-aa63-4766-9725-8f5b0aa8fe4e</t>
-  </si>
-  <si>
-    <t>relationship--1a0ed787-6e98-4d1c-8eaf-ad7622f746b6</t>
-  </si>
-  <si>
-    <t>relationship--51d34cd7-27af-4321-ad3b-c00925ef3bae</t>
-  </si>
-  <si>
-    <t>relationship--38934af6-e0df-4e99-8832-19dfc5aa76fb</t>
-  </si>
-  <si>
-    <t>relationship--8fe1cf5e-353d-49a0-9a18-5c9ce6519107</t>
-  </si>
-  <si>
-    <t>relationship--4b75d83e-aa45-4bdb-9e77-44ab08e9e40b</t>
-  </si>
-  <si>
-    <t>relationship--f06fd8d9-aef2-401f-a307-ca5a0e1285d2</t>
-  </si>
-  <si>
-    <t>relationship--62a5317c-5ba6-408f-9c80-5acfdbd32ee7</t>
-  </si>
-  <si>
-    <t>relationship--77903336-6ba1-40d5-91c7-6ca3ee9c4098</t>
-  </si>
-  <si>
-    <t>relationship--164df4fe-b365-4045-b692-006cc7379eaf</t>
-  </si>
-  <si>
-    <t>relationship--614cfb78-516d-4af0-a676-9f08e44f9179</t>
-  </si>
-  <si>
-    <t>relationship--49632cf4-f231-4539-bbc9-8d6680780a06</t>
-  </si>
-  <si>
-    <t>relationship--a6f31e13-5817-48e2-95f9-24e9d1cbbfc4</t>
-  </si>
-  <si>
-    <t>relationship--f8f236df-0be2-479d-9462-b5d67379bd51</t>
-  </si>
-  <si>
-    <t>relationship--408cd846-38c1-4247-9909-d37fb7b69199</t>
-  </si>
-  <si>
-    <t>relationship--b398d380-4b24-465a-a0a8-9ac8b2f5bd1b</t>
-  </si>
-  <si>
-    <t>relationship--221a7cb6-0e1b-4214-8620-8256aca937f3</t>
-  </si>
-  <si>
-    <t>relationship--b1876f95-fc2c-4f14-8cb5-afdf4ac78fd4</t>
-  </si>
-  <si>
-    <t>relationship--1a627c96-3d45-4503-b6d6-cf1bdac82c8c</t>
-  </si>
-  <si>
-    <t>relationship--abd1d624-9fb5-4369-940c-7d0015306b05</t>
-  </si>
-  <si>
-    <t>relationship--5aeacb37-7169-48d1-b03e-a8ffcf494f58</t>
-  </si>
-  <si>
-    <t>relationship--69546bbe-81ad-44d9-b7f3-7d3c24af479c</t>
-  </si>
-  <si>
-    <t>relationship--009eb8ba-56f4-4694-89af-17ea173d74cb</t>
-  </si>
-  <si>
-    <t>relationship--c0183cdf-818c-444a-9f3b-a2885749f658</t>
-  </si>
-  <si>
-    <t>relationship--07f0e483-8a65-4ad0-8068-b11e520db608</t>
-  </si>
-  <si>
-    <t>relationship--f39563eb-3ce1-408b-ad68-e1d4845500b5</t>
-  </si>
-  <si>
-    <t>relationship--fe28c216-cce3-41e9-b52d-2abf289d47ae</t>
-  </si>
-  <si>
-    <t>relationship--4065ee88-8afa-40c9-ac40-9d26f35b1f67</t>
-  </si>
-  <si>
-    <t>relationship--71f1a72d-7bbc-47d8-8e6c-8ff77ed33ea0</t>
-  </si>
-  <si>
-    <t>relationship--307b1228-84cf-49d8-853a-6af3a53c1627</t>
-  </si>
-  <si>
-    <t>relationship--d775343b-7fcc-4a1c-8e16-9a9cdb64e7a4</t>
-  </si>
-  <si>
-    <t>relationship--923a9d64-ddf0-4008-9bb2-af5d5ee0f230</t>
-  </si>
-  <si>
-    <t>relationship--82bc5611-617c-41ca-be4a-e5b3167d84ed</t>
-  </si>
-  <si>
-    <t>relationship--059aecae-97f4-4744-bcdd-a76d1a2f3f45</t>
-  </si>
-  <si>
-    <t>relationship--d7be5882-6700-4648-ba22-e980a2804072</t>
-  </si>
-  <si>
-    <t>relationship--1fe62db2-8ec1-4e0b-893d-b8c632009d9e</t>
-  </si>
-  <si>
-    <t>relationship--4826c5f8-4a5b-402c-bf84-bc13c03c3fb0</t>
-  </si>
-  <si>
-    <t>relationship--e55c1a27-ff44-4c2d-99a6-6fbd83ff60db</t>
-  </si>
-  <si>
-    <t>relationship--2912252d-746f-449f-9674-63b7caa18c56</t>
-  </si>
-  <si>
-    <t>relationship--61fe7007-0ed2-476c-a796-0d5c78694d88</t>
-  </si>
-  <si>
-    <t>relationship--289c43ba-2986-46ac-a3da-d69eef6f0a59</t>
-  </si>
-  <si>
-    <t>relationship--e2d69ef6-2ea3-4873-86f7-632c7a1fbc1c</t>
-  </si>
-  <si>
-    <t>relationship--b77d1234-dc45-4ad7-baec-4c75b7974d4e</t>
-  </si>
-  <si>
-    <t>relationship--73f6aed0-fefc-4888-8cca-cbe008ddf331</t>
-  </si>
-  <si>
-    <t>relationship--0a95e48e-b6fd-47c4-afed-08529f63fb39</t>
-  </si>
-  <si>
-    <t>relationship--9fbcddc5-9b75-451e-919a-d5e45e700a23</t>
-  </si>
-  <si>
-    <t>relationship--5d80c07d-5436-42ed-9ca4-3270c9c3d146</t>
-  </si>
-  <si>
-    <t>relationship--77cf91d2-6cb7-4ca0-9038-2b87606b5965</t>
-  </si>
-  <si>
-    <t>relationship--95635bce-78b4-4c59-b4d1-03622c8003ab</t>
-  </si>
-  <si>
-    <t>relationship--d12cff3c-fdbf-4fc7-bd6b-f1bb35b7304b</t>
-  </si>
-  <si>
-    <t>relationship--817daffb-a9b8-44e6-a395-6b7bf160e72c</t>
-  </si>
-  <si>
-    <t>relationship--fec74c64-d978-434e-bf80-197e2049f320</t>
-  </si>
-  <si>
-    <t>relationship--e93462ad-6c4e-48bd-a079-9519e3b5a04e</t>
-  </si>
-  <si>
-    <t>relationship--751f13ca-415c-4e84-a953-132107b7697e</t>
-  </si>
-  <si>
-    <t>relationship--da82a7ad-b4d7-4c94-8bea-057e671ae4a4</t>
-  </si>
-  <si>
-    <t>relationship--665cf86c-b8cf-4e87-a5e9-2cfcf18e0941</t>
-  </si>
-  <si>
-    <t>relationship--42757cb1-f4b1-4f96-9ea7-1e8e927da779</t>
-  </si>
-  <si>
-    <t>relationship--ed16aa83-affb-412b-b0e0-ff3c900821b4</t>
-  </si>
-  <si>
-    <t>relationship--abcaca4f-565d-478b-b717-29673f65534e</t>
-  </si>
-  <si>
-    <t>relationship--4254a725-81fd-452f-89f6-fc79843c701d</t>
-  </si>
-  <si>
-    <t>relationship--d05f11fd-62d3-4750-b34c-38d543b2b8c3</t>
-  </si>
-  <si>
-    <t>relationship--b68db160-d755-42d1-a36e-0971d3981d34</t>
-  </si>
-  <si>
-    <t>relationship--2735bc85-a60c-4465-a615-67902a033882</t>
-  </si>
-  <si>
-    <t>relationship--40f72abb-e0ef-4021-8aeb-0386d75fbbc5</t>
-  </si>
-  <si>
-    <t>relationship--f6de26ff-9458-4f70-9b43-8fb687b2d4d5</t>
-  </si>
-  <si>
-    <t>relationship--6dba15dc-fcbd-4e1c-963a-19a14fcaab3d</t>
-  </si>
-  <si>
-    <t>relationship--93ba7432-1e5d-4fe2-9c49-040925e42fcf</t>
-  </si>
-  <si>
-    <t>relationship--083eb465-7bc8-4e16-8155-41bbca4adf9e</t>
-  </si>
-  <si>
-    <t>relationship--bc31acf0-0893-4fc0-a6e1-b5041670f2b7</t>
-  </si>
-  <si>
-    <t>relationship--381d10a2-fd19-4e0e-9c59-0d20082fa5f1</t>
-  </si>
-  <si>
-    <t>relationship--ab67c82d-0704-4805-ad97-5b94f8e8e0dd</t>
-  </si>
-  <si>
-    <t>relationship--bc87995c-9763-461d-a407-c670d6a8772c</t>
-  </si>
-  <si>
-    <t>relationship--f039d33d-c0d7-4b3a-890c-f38e8127745a</t>
-  </si>
-  <si>
-    <t>relationship--5c06f90b-34e7-4af4-9051-814bdb4b2272</t>
-  </si>
-  <si>
-    <t>relationship--8656ea5a-2838-434f-b3e4-e46d58498762</t>
-  </si>
-  <si>
-    <t>relationship--b2de557b-fa55-4519-ac66-528e8af6a3dd</t>
-  </si>
-  <si>
-    <t>relationship--575e47df-7d05-4b63-a760-2fb8af22ca27</t>
+    <t>relationship--5614d86d-6211-45cd-ac6c-26a97c7ed3cf</t>
+  </si>
+  <si>
+    <t>relationship--c00bd06c-4bf5-4ab2-ab25-c5d571553d0c</t>
+  </si>
+  <si>
+    <t>relationship--7201fe1e-0fea-4d3b-97bf-6355ebf82318</t>
+  </si>
+  <si>
+    <t>relationship--d1870805-3ccc-4beb-b2a4-8402f288d864</t>
+  </si>
+  <si>
+    <t>relationship--a1eee09b-bd43-43e9-b586-a6b939c06a11</t>
+  </si>
+  <si>
+    <t>relationship--c274175b-6c03-49c5-a647-607cd5b0e4d2</t>
+  </si>
+  <si>
+    <t>relationship--187b5fcd-6c5c-4c42-8d07-07adbdbecd2d</t>
+  </si>
+  <si>
+    <t>relationship--1006e39a-452b-4831-be5c-fc31a3710a4c</t>
+  </si>
+  <si>
+    <t>relationship--998fc32c-1362-4fe1-badc-2c3295a58dae</t>
+  </si>
+  <si>
+    <t>relationship--b50491d9-1ef9-4e6a-a7d8-ed3bdd53bb26</t>
+  </si>
+  <si>
+    <t>relationship--816bc3db-9456-4de8-a943-e308683f2326</t>
+  </si>
+  <si>
+    <t>relationship--7e5cb007-6d19-46d2-a049-9fb76730abfc</t>
+  </si>
+  <si>
+    <t>relationship--4b7df337-6761-4f4a-8663-ffc85abd9bd7</t>
+  </si>
+  <si>
+    <t>relationship--3e1c35b2-ac79-4f76-b026-a30f8e566a41</t>
+  </si>
+  <si>
+    <t>relationship--a849cb40-97db-4468-a725-2eb757b9285f</t>
+  </si>
+  <si>
+    <t>relationship--47ff22b7-0fad-4eaa-8f49-c7ee57b2bcf5</t>
+  </si>
+  <si>
+    <t>relationship--50db3a6a-bc86-4653-92b1-cc25f4fd3b63</t>
+  </si>
+  <si>
+    <t>relationship--8312e15d-9501-45f6-b5c7-dd40ad215dc7</t>
+  </si>
+  <si>
+    <t>relationship--0cc9ae91-2019-49d4-9ae9-74cf940ab326</t>
+  </si>
+  <si>
+    <t>relationship--62cc7c54-5c61-4755-b62b-11df9f67bc7c</t>
+  </si>
+  <si>
+    <t>relationship--9520ceeb-3ab0-40cd-9976-308b5382c604</t>
+  </si>
+  <si>
+    <t>relationship--df0590aa-456d-4dcd-b3ef-9db58fcdde4d</t>
+  </si>
+  <si>
+    <t>relationship--25875951-42bf-4bd1-8846-1e2b082462c7</t>
+  </si>
+  <si>
+    <t>relationship--363d00f2-89e0-45eb-aeff-56c3eb0b7d1b</t>
+  </si>
+  <si>
+    <t>relationship--ccc50e83-1034-4626-9fad-142e49094870</t>
+  </si>
+  <si>
+    <t>relationship--0e6f9307-ac79-4d43-90f6-e73960d6ec75</t>
+  </si>
+  <si>
+    <t>relationship--24ef7132-be8a-41ec-bacf-c64882a1171d</t>
+  </si>
+  <si>
+    <t>relationship--0cf1df00-44a9-42ec-b61d-3e10fb8c67d6</t>
+  </si>
+  <si>
+    <t>relationship--03e9274c-b7a4-42d6-8f7f-78b71e30af09</t>
+  </si>
+  <si>
+    <t>relationship--5c38fc95-7bc5-4a6a-8681-48be32c65a82</t>
+  </si>
+  <si>
+    <t>relationship--066eb77b-c6df-4d8e-8599-0beb192907e4</t>
+  </si>
+  <si>
+    <t>relationship--541a4d88-df09-4c75-92ae-356afd194692</t>
+  </si>
+  <si>
+    <t>relationship--3af6830d-8cc7-4fed-b927-108a41fd4178</t>
+  </si>
+  <si>
+    <t>relationship--57631293-2a02-4489-8c56-f583e9bc5585</t>
+  </si>
+  <si>
+    <t>relationship--862f0336-33bd-4370-8af3-d29a004f0fc8</t>
+  </si>
+  <si>
+    <t>relationship--9ec2a708-84bf-4339-afb0-0162bb4748ff</t>
+  </si>
+  <si>
+    <t>relationship--4485df60-3f40-40ca-93c4-89378405dc43</t>
+  </si>
+  <si>
+    <t>relationship--722ca219-044e-4221-a0f4-444790a937ba</t>
+  </si>
+  <si>
+    <t>relationship--0819322a-18d8-4e24-b55c-206658d07525</t>
+  </si>
+  <si>
+    <t>relationship--cfa59c71-254e-4a90-903c-fcce14903069</t>
+  </si>
+  <si>
+    <t>relationship--672d610b-b36d-4dd8-b55d-8b986db8b16c</t>
+  </si>
+  <si>
+    <t>relationship--3c9fe144-c86e-42cf-b46f-9fbac0138093</t>
+  </si>
+  <si>
+    <t>relationship--0416c3e3-00bc-44e4-88b4-e2837a311840</t>
+  </si>
+  <si>
+    <t>relationship--0e328b60-be4c-4a17-a480-68f9a95774c9</t>
+  </si>
+  <si>
+    <t>relationship--05358bf0-1b8f-4d3d-9b01-37d1e4f6b814</t>
+  </si>
+  <si>
+    <t>relationship--d8ee9123-00a9-45e8-b9ed-78eaf52fd03c</t>
+  </si>
+  <si>
+    <t>relationship--c99cdf0b-238f-4f4a-bd62-e777028d0888</t>
+  </si>
+  <si>
+    <t>relationship--eb3d94ce-42c1-4f6d-9104-149587001ee8</t>
+  </si>
+  <si>
+    <t>relationship--34fa7ae0-57e6-4802-b731-2a8397e43f5c</t>
+  </si>
+  <si>
+    <t>relationship--658426eb-6159-48b7-834a-d2cba5929840</t>
+  </si>
+  <si>
+    <t>relationship--1b8afd01-f00e-4fb9-8e53-23bf378a5743</t>
+  </si>
+  <si>
+    <t>relationship--c4b84975-0d5b-41da-8dde-a1e4752f8223</t>
+  </si>
+  <si>
+    <t>relationship--3c23657a-af00-4c00-be50-0c2211096383</t>
+  </si>
+  <si>
+    <t>relationship--34f1cc09-99b9-4b55-8a11-a27b71d36a56</t>
+  </si>
+  <si>
+    <t>relationship--2d2d4647-66d2-468f-b5fa-08a23e9f3b52</t>
+  </si>
+  <si>
+    <t>relationship--32fef7ce-3ca8-42d2-9806-8f07130dc59a</t>
+  </si>
+  <si>
+    <t>relationship--45a232f8-5767-419e-9acc-94a2592789a1</t>
+  </si>
+  <si>
+    <t>relationship--8bd14d24-f013-4648-9e45-231c66bee802</t>
+  </si>
+  <si>
+    <t>relationship--e9bd60a6-0325-45da-9bda-fd854a7ce87b</t>
+  </si>
+  <si>
+    <t>relationship--724cc625-5556-40a5-ae14-3d9de64c9a19</t>
+  </si>
+  <si>
+    <t>relationship--00da6316-6f4a-4ee9-84ab-f3bf74b840dc</t>
+  </si>
+  <si>
+    <t>relationship--37a6d563-2564-4062-8967-14950a0a6ff1</t>
+  </si>
+  <si>
+    <t>relationship--5c5eb460-e73e-4c4b-8929-2f3a55616623</t>
+  </si>
+  <si>
+    <t>relationship--41bac798-9a1a-4b92-930c-227474d4cabb</t>
+  </si>
+  <si>
+    <t>relationship--5b9787dc-aaed-4206-acb6-3135336f00dc</t>
+  </si>
+  <si>
+    <t>relationship--92e54ce9-a70b-4436-be5a-e66e682935ec</t>
+  </si>
+  <si>
+    <t>relationship--689c088d-7e07-43c6-a3a3-2059035a0956</t>
+  </si>
+  <si>
+    <t>relationship--1d4bd310-a5da-42a0-896e-ea3ccf0735ef</t>
+  </si>
+  <si>
+    <t>relationship--58b1092a-2708-4e1d-b796-7570f699b314</t>
+  </si>
+  <si>
+    <t>relationship--a700b400-cfb5-4c2d-8ac6-6d3f3a976502</t>
+  </si>
+  <si>
+    <t>relationship--463138d3-daf2-4734-b553-fcc80a9f7245</t>
+  </si>
+  <si>
+    <t>relationship--12c1d59e-77ae-4c17-bd89-4f0d0855db2b</t>
+  </si>
+  <si>
+    <t>relationship--6dd4ef8d-d116-4667-98cd-25d0b4ca2eb2</t>
+  </si>
+  <si>
+    <t>relationship--28bdfc3d-faa4-4c45-8c25-506dc03861d2</t>
+  </si>
+  <si>
+    <t>relationship--2da181d8-efdd-46a5-bc48-a7e761e7700c</t>
+  </si>
+  <si>
+    <t>relationship--30caab21-d762-4082-9483-c4e4b58c8140</t>
+  </si>
+  <si>
+    <t>relationship--edd083ea-aadc-4345-844f-5d40e476e7c8</t>
+  </si>
+  <si>
+    <t>relationship--61c6a3e1-337d-4150-8e33-062db9bf48fb</t>
+  </si>
+  <si>
+    <t>relationship--69593cf2-77f5-4528-95bc-867a7cd474a6</t>
+  </si>
+  <si>
+    <t>relationship--fe839167-b221-48ff-8478-496d40f26604</t>
+  </si>
+  <si>
+    <t>relationship--33cc973e-fa84-415a-a0b3-dc6101374315</t>
+  </si>
+  <si>
+    <t>relationship--0c8a308f-fb09-4df6-9a8b-03dc281625c8</t>
+  </si>
+  <si>
+    <t>relationship--13a0fcb0-b324-4579-a852-51d59b9cfea7</t>
+  </si>
+  <si>
+    <t>relationship--03876e2e-c730-426e-9cf7-5c2d2eacfd12</t>
+  </si>
+  <si>
+    <t>relationship--ac403c59-fdb2-451d-82d5-b227f3fb004e</t>
+  </si>
+  <si>
+    <t>relationship--17501bfb-76d5-452a-a5b7-bb40a2734033</t>
+  </si>
+  <si>
+    <t>relationship--3751fcb4-a779-4bd1-8b91-b4d03da77810</t>
+  </si>
+  <si>
+    <t>relationship--db0bfcda-eb29-4562-aca0-c098711d0d07</t>
+  </si>
+  <si>
+    <t>relationship--092d1143-9f0d-4f94-b49b-b4a78e22aa1f</t>
+  </si>
+  <si>
+    <t>relationship--ff4a5303-2db3-49ae-a53f-7c2dffb9e6ee</t>
+  </si>
+  <si>
+    <t>relationship--2291dd05-1ba6-427c-8f66-f483409905d3</t>
+  </si>
+  <si>
+    <t>relationship--bdf81bef-d89b-49f8-a818-e7348ead0e7d</t>
+  </si>
+  <si>
+    <t>relationship--c0a0ed7b-7375-475c-967c-9635560013b7</t>
+  </si>
+  <si>
+    <t>relationship--35f20b51-ebde-4f96-b4f6-4612f3bceea5</t>
+  </si>
+  <si>
+    <t>relationship--b5c01c41-b1bd-403f-9c86-ee33d9233bb8</t>
+  </si>
+  <si>
+    <t>relationship--9bc2a9d1-da58-403d-98c8-6b56bfd51523</t>
+  </si>
+  <si>
+    <t>relationship--e9b6b440-e6ef-4112-91b7-a10e828f215f</t>
+  </si>
+  <si>
+    <t>relationship--d13278fb-2254-49ef-b205-01e887848910</t>
+  </si>
+  <si>
+    <t>relationship--5efc8b32-1b60-4fad-ae02-e340941487af</t>
+  </si>
+  <si>
+    <t>relationship--2511d69d-6f60-4597-8c57-c435f01cb56c</t>
+  </si>
+  <si>
+    <t>relationship--34272f39-5284-4cd8-aed4-3ac4b7afe9c0</t>
+  </si>
+  <si>
+    <t>relationship--78c44437-c23b-44e3-9b0a-dea9d31afab3</t>
+  </si>
+  <si>
+    <t>relationship--86e8bc77-6840-43e1-9b08-388dd6ce4a71</t>
+  </si>
+  <si>
+    <t>relationship--95a7d566-0538-4e17-b03f-d840ac5a6485</t>
+  </si>
+  <si>
+    <t>relationship--e08df791-6312-4452-a037-50b1c552eae6</t>
+  </si>
+  <si>
+    <t>relationship--ce048198-374c-4f04-8fc5-58aa78334838</t>
+  </si>
+  <si>
+    <t>relationship--ed1b3558-fa7e-4b78-94a6-ede294e5982b</t>
+  </si>
+  <si>
+    <t>relationship--fdb52f1a-9fce-4466-9113-080a43b19d24</t>
+  </si>
+  <si>
+    <t>relationship--a45d91e8-042e-4dde-8bf0-57d321efd381</t>
+  </si>
+  <si>
+    <t>relationship--4c063840-371e-41c6-8f16-15c3bb3b6a07</t>
+  </si>
+  <si>
+    <t>relationship--01302958-accb-41b5-bd1c-cad6bc07a1d6</t>
+  </si>
+  <si>
+    <t>relationship--1e280e04-acc2-4d3a-ad9c-8e779be2623f</t>
+  </si>
+  <si>
+    <t>relationship--68148d92-85e1-47a8-86ad-88953aad0f77</t>
+  </si>
+  <si>
+    <t>relationship--313f6ee5-9364-48f9-839d-edf4e6d25f2a</t>
+  </si>
+  <si>
+    <t>relationship--fb779776-e9f6-45e3-9cb8-c9e509c3e8a7</t>
+  </si>
+  <si>
+    <t>relationship--47e73f6e-a733-46f1-a09b-51f4a0c2574a</t>
+  </si>
+  <si>
+    <t>relationship--d48b2f17-752e-4ef0-85ca-8c5626fe5832</t>
+  </si>
+  <si>
+    <t>relationship--55b721b2-6229-4de6-9655-32647d86e186</t>
+  </si>
+  <si>
+    <t>relationship--e7753b65-5fcf-453a-9139-c1d9028cf696</t>
+  </si>
+  <si>
+    <t>relationship--5f7f0d17-361f-4a98-b1bd-0122c4d69f1d</t>
+  </si>
+  <si>
+    <t>relationship--2e1b7d0a-bc28-4539-92dd-ebfc2bb2a6fc</t>
+  </si>
+  <si>
+    <t>relationship--14628952-a9d9-4da9-a5e2-c807bebc2dbc</t>
+  </si>
+  <si>
+    <t>relationship--9708078b-3306-4693-bf99-43999bd18b3a</t>
+  </si>
+  <si>
+    <t>relationship--ac66737c-9eeb-4d82-a7ef-b0a31bba3e60</t>
+  </si>
+  <si>
+    <t>relationship--e68e8a70-ae5d-4374-9f08-1313f12c0795</t>
+  </si>
+  <si>
+    <t>relationship--f8ea8127-0143-4136-9355-f0672cc93626</t>
+  </si>
+  <si>
+    <t>relationship--9c139044-ce9e-491c-95e2-00ba93a1b5db</t>
+  </si>
+  <si>
+    <t>relationship--a74f7c11-3bc0-48bf-973f-f38cd1531a2e</t>
+  </si>
+  <si>
+    <t>relationship--7d492b91-2741-42d1-a14b-5c68ef16cdde</t>
+  </si>
+  <si>
+    <t>relationship--2e21705c-7535-43ea-971e-ae1c720f97f0</t>
+  </si>
+  <si>
+    <t>relationship--6012c812-46fa-4441-a18e-caca14be105e</t>
+  </si>
+  <si>
+    <t>relationship--7276f7e3-19cc-4f36-b52a-df9b09039d86</t>
+  </si>
+  <si>
+    <t>relationship--38b9b77e-9ac6-4123-ad64-7ee44572da1b</t>
+  </si>
+  <si>
+    <t>relationship--8ab8f626-ae23-4007-bb32-dc128a13c452</t>
+  </si>
+  <si>
+    <t>relationship--a3705dfd-d211-4b6c-b8de-a60b61232ccf</t>
+  </si>
+  <si>
+    <t>relationship--176d7e94-acc7-4510-ab33-fc50ec2eb016</t>
+  </si>
+  <si>
+    <t>relationship--72911605-8706-44a8-9133-cc55f61fbe01</t>
+  </si>
+  <si>
+    <t>relationship--3cecfb1c-8f09-451d-9727-99f8f2060f9a</t>
+  </si>
+  <si>
+    <t>relationship--889bdd3d-7042-4b09-9b8a-2c1063492550</t>
+  </si>
+  <si>
+    <t>relationship--93820292-0d07-4e8a-a732-af6f7fac18f3</t>
+  </si>
+  <si>
+    <t>relationship--d63962bf-f3fd-4159-986d-fb404f8e5c4f</t>
+  </si>
+  <si>
+    <t>relationship--8b4d20df-6e8d-48ed-ad71-b0b73b855a56</t>
+  </si>
+  <si>
+    <t>relationship--9b06ea4e-c75e-41ad-9ba0-b8050f79c4c9</t>
+  </si>
+  <si>
+    <t>relationship--304d883a-85fd-4eb0-8c79-a70babe9fa54</t>
+  </si>
+  <si>
+    <t>relationship--f2124474-a45e-4d8c-b9c3-a4485991a23e</t>
+  </si>
+  <si>
+    <t>relationship--f90a7c85-e4de-457e-b281-b8945307db07</t>
+  </si>
+  <si>
+    <t>relationship--1658c08e-93b2-490d-b21e-2dddf38e2b5c</t>
+  </si>
+  <si>
+    <t>relationship--f3fded44-1a57-418f-b6ae-29b4dbd1bc91</t>
+  </si>
+  <si>
+    <t>relationship--3f971d8b-a5a0-4f8f-b42d-a325cd802149</t>
+  </si>
+  <si>
+    <t>relationship--f45ed62a-12e3-466e-84ea-56ee39b45fe3</t>
+  </si>
+  <si>
+    <t>relationship--acab761b-d19f-4216-a982-e4e9fee04109</t>
+  </si>
+  <si>
+    <t>relationship--bd2a142c-0144-4d20-8e3d-b73ace1abff6</t>
+  </si>
+  <si>
+    <t>relationship--263060ab-6afa-4efa-8121-56ca8c19dea3</t>
+  </si>
+  <si>
+    <t>relationship--18b4ed3f-7d9c-457a-ba75-9b36acdf1b39</t>
+  </si>
+  <si>
+    <t>relationship--4bb0977b-3d05-4362-aeea-cc150865bd4b</t>
+  </si>
+  <si>
+    <t>relationship--9732d9c4-866e-4ec3-acdf-9116f0bd3293</t>
+  </si>
+  <si>
+    <t>relationship--f5e63ee5-77e5-4992-833d-257e32e5ce3e</t>
+  </si>
+  <si>
+    <t>relationship--49d946ff-1e6b-4bf2-a9f1-a9e54213b6ba</t>
+  </si>
+  <si>
+    <t>relationship--3df7af44-b568-4a7c-adf5-95885e794a2f</t>
+  </si>
+  <si>
+    <t>relationship--9e5fe4f7-cd1e-4703-bea2-829fef05d626</t>
+  </si>
+  <si>
+    <t>relationship--14bade66-db15-4761-9e73-2928a3a3891e</t>
+  </si>
+  <si>
+    <t>relationship--2acac976-88b9-4fc7-a0bd-4d03a5f3a9bf</t>
+  </si>
+  <si>
+    <t>relationship--4c3795cc-a1e9-45d1-9a1e-bbf2cde64a15</t>
+  </si>
+  <si>
+    <t>relationship--fe565642-eab5-4ff9-91e1-cea181876211</t>
+  </si>
+  <si>
+    <t>relationship--6278e5d4-ab06-4def-bece-6991bf4b857b</t>
+  </si>
+  <si>
+    <t>relationship--8ae29663-1f05-422d-ba3c-0337760daf4d</t>
+  </si>
+  <si>
+    <t>relationship--7ac36b6b-a053-4b5f-8160-03f2709d8434</t>
+  </si>
+  <si>
+    <t>relationship--33b4f3d5-4d6e-421f-a932-e2ffa44fc7a9</t>
+  </si>
+  <si>
+    <t>relationship--95d794f0-5dc8-4362-b0ff-7ed3dc1eeabd</t>
+  </si>
+  <si>
+    <t>relationship--fbf7379e-6953-413c-8932-a51888aac57e</t>
+  </si>
+  <si>
+    <t>relationship--16390e3a-f86b-4725-907f-991e84d3e0fe</t>
+  </si>
+  <si>
+    <t>relationship--c3d4eae6-f0ec-4700-91e4-270a1b5c6f38</t>
+  </si>
+  <si>
+    <t>relationship--742cbbdd-94d7-4072-9a8b-ecafc56604db</t>
+  </si>
+  <si>
+    <t>relationship--2828cfca-5ceb-4c5a-bb2f-8ffc611954fc</t>
+  </si>
+  <si>
+    <t>relationship--cb6aa417-c3bf-41e3-9e44-209705207413</t>
+  </si>
+  <si>
+    <t>relationship--9f99304a-1059-47a4-bbdf-1f76b23b8ac2</t>
+  </si>
+  <si>
+    <t>relationship--2346dccd-238f-46e8-9aba-6341e3783eda</t>
+  </si>
+  <si>
+    <t>relationship--3138c704-adf0-4cad-8d6a-ad204687d4df</t>
+  </si>
+  <si>
+    <t>relationship--0880242b-9689-482e-9459-4ebd56320f4e</t>
+  </si>
+  <si>
+    <t>relationship--9417f950-d2a7-4417-9c05-6fe57828917e</t>
+  </si>
+  <si>
+    <t>relationship--a2b54231-6b5c-40b3-a417-074b60b3b9e2</t>
+  </si>
+  <si>
+    <t>relationship--23735a53-068a-4d2a-9476-7857dd7e1b74</t>
+  </si>
+  <si>
+    <t>relationship--161fe2ca-c2dc-4d21-a9b0-95935f7d1a52</t>
   </si>
   <si>
     <t>T0030</t>
@@ -4101,253 +4101,253 @@
     <t>Смена алфавита родного языка</t>
   </si>
   <si>
-    <t>attack-pattern--8623a36b-99de-4dfb-ba46-b2b5e9cf0d85</t>
-  </si>
-  <si>
-    <t>attack-pattern--95138ada-459f-440e-a79a-7fcf8874b584</t>
-  </si>
-  <si>
-    <t>attack-pattern--8feebaca-97cf-4478-b1d3-8e0a8ed2edc0</t>
-  </si>
-  <si>
-    <t>attack-pattern--286b8cda-f24d-4dde-a188-c0b140491a96</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8fc16d6-7f03-4404-9d8d-f9782a0d4b3e</t>
-  </si>
-  <si>
-    <t>attack-pattern--60d5bdf7-06c3-4a53-b2d3-36b02a2230e3</t>
-  </si>
-  <si>
-    <t>attack-pattern--880b414d-a823-4193-b270-c0a7de9e6d12</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe23fd12-ed27-416d-a891-53fd0945c418</t>
-  </si>
-  <si>
-    <t>attack-pattern--a92eb244-48f1-4d36-91b8-9ff6404bc66d</t>
-  </si>
-  <si>
-    <t>attack-pattern--08292bee-5177-4f79-bfa6-4f0345a5a446</t>
-  </si>
-  <si>
-    <t>attack-pattern--3a36e7b8-ad04-4cb0-8ffc-9b6502c66d77</t>
-  </si>
-  <si>
-    <t>attack-pattern--c8e73b27-78c5-4634-93ec-287a7cd80529</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5f6323-a749-4b89-a8ae-36633f183b54</t>
-  </si>
-  <si>
-    <t>attack-pattern--37759b81-258f-4d71-9703-9654ac67cab0</t>
-  </si>
-  <si>
-    <t>attack-pattern--60a4cda8-8154-4a3f-9826-f9d39155d257</t>
-  </si>
-  <si>
-    <t>attack-pattern--22e649d9-36b0-4f1f-88e9-e34fd12441c4</t>
-  </si>
-  <si>
-    <t>attack-pattern--2001e1d6-3887-44fe-892d-ce873833b382</t>
-  </si>
-  <si>
-    <t>attack-pattern--dc37deb9-2659-4fc2-b801-127690502a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--bf3afc82-5403-4ae9-9f69-3d9ef357c6c8</t>
-  </si>
-  <si>
-    <t>attack-pattern--563b0db6-14f7-4b63-8256-95de0ef5cf8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--2421e2f6-4b1f-4f1e-8faa-69e9b14cbbe8</t>
-  </si>
-  <si>
-    <t>attack-pattern--7f745905-530b-4294-9eda-f8dafe9f0edd</t>
-  </si>
-  <si>
-    <t>attack-pattern--ca41993a-f62d-477b-802f-e63f4c050380</t>
-  </si>
-  <si>
-    <t>attack-pattern--0ffd53d6-5fd6-43e5-aff6-4e1d50a00743</t>
-  </si>
-  <si>
-    <t>attack-pattern--e49e8037-4bae-447d-86e6-23b275db8d96</t>
-  </si>
-  <si>
-    <t>attack-pattern--1a2eea19-fa56-4b46-b746-af741b0fbe4a</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef93f62-3fe5-4d86-bad7-82607554a597</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe33bd0c-bd06-451b-92ea-b2f65444329b</t>
-  </si>
-  <si>
-    <t>attack-pattern--dac8d747-5bf3-47af-9f54-b010ae92ccea</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4b577cd-5a76-46f7-8c39-b96213fc4263</t>
-  </si>
-  <si>
-    <t>attack-pattern--7be66db5-2484-4f82-9c02-2c658aba5534</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f5deb62-ed66-4518-9b21-c1557815cce5</t>
-  </si>
-  <si>
-    <t>attack-pattern--ac8f6735-f593-4862-b036-039679f6825d</t>
-  </si>
-  <si>
-    <t>attack-pattern--709b796b-4c14-4219-8b7d-848ccf3df33f</t>
-  </si>
-  <si>
-    <t>attack-pattern--229f46aa-5a77-41ce-a34b-4d978b1164ea</t>
-  </si>
-  <si>
-    <t>attack-pattern--91bd2ac0-d39a-4a37-b4ba-3b7d9cc48480</t>
-  </si>
-  <si>
-    <t>attack-pattern--8accb141-a1ff-471e-9a3a-988919bcceb6</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c93037a-c467-4137-81e2-c058a9d90107</t>
-  </si>
-  <si>
-    <t>attack-pattern--595ddc1a-2efe-4154-a6d7-880fb2fe280f</t>
-  </si>
-  <si>
-    <t>attack-pattern--c0c59602-b27b-4b66-b864-82a05ff862db</t>
-  </si>
-  <si>
-    <t>attack-pattern--8fa70d63-cbe1-4ba7-b1a5-2573911cf454</t>
-  </si>
-  <si>
-    <t>attack-pattern--f69b9809-b9e2-4a3e-b8d9-cf3f74af4335</t>
-  </si>
-  <si>
-    <t>attack-pattern--575a4091-4083-4c93-8862-74543ad2f94c</t>
-  </si>
-  <si>
-    <t>attack-pattern--9fb6f979-a54f-46ce-9d0b-ce0c5db37e7a</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd99f80b-0f34-4288-bc79-c0f3cf18e846</t>
-  </si>
-  <si>
-    <t>attack-pattern--aa11cd7e-92e7-43ec-af19-193b81bdb604</t>
-  </si>
-  <si>
-    <t>attack-pattern--0fa8defa-fb0b-4599-9491-7d725883c3fd</t>
-  </si>
-  <si>
-    <t>attack-pattern--37844351-6c24-42d8-99ba-2eb178febd3c</t>
-  </si>
-  <si>
-    <t>attack-pattern--aeca9532-ecda-49fc-9915-fe9b53956bf8</t>
-  </si>
-  <si>
-    <t>attack-pattern--4c4ac28a-0504-4efc-b7bb-a81682cab9ef</t>
-  </si>
-  <si>
-    <t>attack-pattern--0813df13-c30d-4a9c-badc-bf8ff641b717</t>
-  </si>
-  <si>
-    <t>attack-pattern--ae7d996b-f766-44ab-a46b-60abdd2b3ef6</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c8faff-7670-454e-a4f0-3da445f53ac9</t>
-  </si>
-  <si>
-    <t>attack-pattern--b041117e-4c21-419b-a1ad-f357fd63741f</t>
-  </si>
-  <si>
-    <t>attack-pattern--a6684ef1-fa45-4bf7-9ec1-db7ebe4dec10</t>
-  </si>
-  <si>
-    <t>attack-pattern--503486f3-22d3-4ed3-a8fb-f63db2718af0</t>
-  </si>
-  <si>
-    <t>attack-pattern--9f1e418c-f7d0-4526-9824-f880b69b0dc8</t>
-  </si>
-  <si>
-    <t>attack-pattern--019504d9-9143-4762-b36e-729108653789</t>
-  </si>
-  <si>
-    <t>attack-pattern--b8f0d38d-8111-4ef2-87ab-d970fb6f6d04</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d97cbb0-3c4c-4fd3-9b5e-679517b777f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--a8e7461e-9164-42e7-a275-578694585803</t>
-  </si>
-  <si>
-    <t>attack-pattern--cf3d899a-e96c-4063-bf08-65e437c19c7f</t>
-  </si>
-  <si>
-    <t>attack-pattern--73c181fd-e569-4225-9bfb-045b64df9b0c</t>
-  </si>
-  <si>
-    <t>attack-pattern--85208eb7-09ab-4287-a298-87298178d6c7</t>
-  </si>
-  <si>
-    <t>attack-pattern--fd811343-f4f3-4812-ad57-477da21a7e8d</t>
-  </si>
-  <si>
-    <t>attack-pattern--71797db1-dffd-44dd-8bfa-53446c0091df</t>
-  </si>
-  <si>
-    <t>attack-pattern--a08a6f55-9930-4233-8df3-cf86e10008ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--72323e0d-b098-4e42-8cd1-544258dc8973</t>
-  </si>
-  <si>
-    <t>attack-pattern--3b132a9a-ecc8-4b8b-b93c-77771f5dc46c</t>
-  </si>
-  <si>
-    <t>attack-pattern--99619131-579e-49d3-aa32-d9ba015ed29a</t>
-  </si>
-  <si>
-    <t>attack-pattern--242eeb83-aeba-4f79-a3ae-2f62a5bc3706</t>
-  </si>
-  <si>
-    <t>attack-pattern--14d57931-21d5-4fd1-bf37-f26ce432a5ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed09b02f-1bf8-4c07-859e-b28e828825d5</t>
-  </si>
-  <si>
-    <t>attack-pattern--e745fb62-c9c2-41af-affe-cac608952241</t>
-  </si>
-  <si>
-    <t>attack-pattern--062669ed-dadc-446f-992c-3425ac24dd1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--61fccaa6-3ad9-4372-8b42-682b13577269</t>
-  </si>
-  <si>
-    <t>attack-pattern--624b5cee-3da2-4c18-906b-d1f1aca11306</t>
-  </si>
-  <si>
-    <t>attack-pattern--81623f2c-c724-43fa-bbab-429f8575f921</t>
-  </si>
-  <si>
-    <t>attack-pattern--a26ee77d-cf1a-4687-988f-932ccc9542bf</t>
-  </si>
-  <si>
-    <t>attack-pattern--fe1389e1-23dc-4f41-b2e1-15ed665a5840</t>
-  </si>
-  <si>
-    <t>attack-pattern--52c17a9d-8e67-4b7c-bddd-a0111496a6f5</t>
-  </si>
-  <si>
-    <t>attack-pattern--3fff8702-55b8-4c84-a528-2b14b7b980da</t>
-  </si>
-  <si>
-    <t>attack-pattern--b516107a-c248-4465-aa68-d5e20f3bf635</t>
+    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
+  </si>
+  <si>
+    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
+  </si>
+  <si>
+    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
+  </si>
+  <si>
+    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
+  </si>
+  <si>
+    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
+  </si>
+  <si>
+    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
+  </si>
+  <si>
+    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
+  </si>
+  <si>
+    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
+  </si>
+  <si>
+    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
+  </si>
+  <si>
+    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
+  </si>
+  <si>
+    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
+  </si>
+  <si>
+    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
+  </si>
+  <si>
+    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
+  </si>
+  <si>
+    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
+  </si>
+  <si>
+    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
+  </si>
+  <si>
+    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
+  </si>
+  <si>
+    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
+  </si>
+  <si>
+    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
+  </si>
+  <si>
+    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
+  </si>
+  <si>
+    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
+  </si>
+  <si>
+    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
+  </si>
+  <si>
+    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
+  </si>
+  <si>
+    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
+  </si>
+  <si>
+    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
+  </si>
+  <si>
+    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
+  </si>
+  <si>
+    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
+  </si>
+  <si>
+    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
+  </si>
+  <si>
+    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
+  </si>
+  <si>
+    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
+  </si>
+  <si>
+    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
+  </si>
+  <si>
+    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
+  </si>
+  <si>
+    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
+  </si>
+  <si>
+    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
+  </si>
+  <si>
+    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
+  </si>
+  <si>
+    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
+  </si>
+  <si>
+    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
+  </si>
+  <si>
+    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
+  </si>
+  <si>
+    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
+  </si>
+  <si>
+    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
+  </si>
+  <si>
+    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
+  </si>
+  <si>
+    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
+  </si>
+  <si>
+    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
+  </si>
+  <si>
+    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
+  </si>
+  <si>
+    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
+  </si>
+  <si>
+    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
+  </si>
+  <si>
+    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
+  </si>
+  <si>
+    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
+  </si>
+  <si>
+    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
+  </si>
+  <si>
+    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
+  </si>
+  <si>
+    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
+  </si>
+  <si>
+    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
+  </si>
+  <si>
+    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
+  </si>
+  <si>
+    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
+  </si>
+  <si>
+    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
+  </si>
+  <si>
+    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
+  </si>
+  <si>
+    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
+  </si>
+  <si>
+    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
+  </si>
+  <si>
+    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
+  </si>
+  <si>
+    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
+  </si>
+  <si>
+    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
+  </si>
+  <si>
+    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
+  </si>
+  <si>
+    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
+  </si>
+  <si>
+    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
+  </si>
+  <si>
+    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
+  </si>
+  <si>
+    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
+  </si>
+  <si>
+    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
+  </si>
+  <si>
+    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
+  </si>
+  <si>
+    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
   </si>
   <si>
     <t>technique</t>
@@ -4362,7 +4362,7 @@
     <t>Раздел сфер влияния за спиной украинского союзника, сопровождавшийся финансовой сделкой за территорию: Москва официально заплатила за уступку Киева огромную сумму серебром (Citation: Война и наказание: Как Россия уничтожала Украину 2023)(Citation: Мазепа 2007)(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011).</t>
   </si>
   <si>
-    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2026)</t>
+    <t>Применение разрушительных медикаментозных препаратов (нейролептиков) в качестве средства физического и психологического давления на здоровых правозащитников в закрытых стационарах. (Citation: Карательная психиатрия в России: назад в СССР? 2020)</t>
   </si>
   <si>
     <t>Секуляризация и конфискация в имперскую казну земель украинских православных монастырей (1786 год), лишившая локальную церковь экономической базы (Citation: Друга Малоросійська колегія — Вікіпедія 2026).</t>
@@ -4831,1027 +4831,1027 @@
     <t>Изъятие у УССР контроля над внешней политикой, армией, внешней торговлей, транспортом и связью через Конституцию СССР 1924 года с передачей их в ведение союзных наркоматов. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--50904263-2021-46e6-9d4e-b17ef1767a32</t>
-  </si>
-  <si>
-    <t>relationship--9f1ce640-6cd4-41ce-b8e7-30beb441e07b</t>
-  </si>
-  <si>
-    <t>relationship--8dc84f9f-b861-46e6-9192-d6e0be26c243</t>
-  </si>
-  <si>
-    <t>relationship--ee281529-2dfd-403e-9712-983e5fdf4089</t>
-  </si>
-  <si>
-    <t>relationship--19c3ae9a-763c-41e6-93c4-459e7409edc5</t>
-  </si>
-  <si>
-    <t>relationship--7e2dbe56-d4a6-40bc-839b-a06fb70c72b6</t>
-  </si>
-  <si>
-    <t>relationship--bde30250-fec8-4075-9583-34e4d5abb426</t>
-  </si>
-  <si>
-    <t>relationship--92eaf1ec-0b9c-4931-a4a8-98844cba6e89</t>
-  </si>
-  <si>
-    <t>relationship--7b371fd1-75f7-478f-b1c7-00b939d0aece</t>
-  </si>
-  <si>
-    <t>relationship--35ec3b3a-eff2-44fb-aec8-6dd1b1a0cfd8</t>
-  </si>
-  <si>
-    <t>relationship--f090ddba-5fb5-4bf2-bd2e-03a64716ed7b</t>
-  </si>
-  <si>
-    <t>relationship--3125f806-4d48-4e7c-8996-51d6d5e0c75b</t>
-  </si>
-  <si>
-    <t>relationship--a71b6bc7-e18e-4552-a115-69058225ae37</t>
-  </si>
-  <si>
-    <t>relationship--11a39972-abd8-43b4-bb10-03a20a73c08f</t>
-  </si>
-  <si>
-    <t>relationship--8ab321f3-1338-4371-b149-1c668fabf0dd</t>
-  </si>
-  <si>
-    <t>relationship--e294b46c-20b9-4c7f-801f-d357310e305e</t>
-  </si>
-  <si>
-    <t>relationship--8b64c8ae-1518-41b9-a20e-6cf09ca2e48b</t>
-  </si>
-  <si>
-    <t>relationship--089d71fb-07ea-45f2-8da3-a01fe15dce00</t>
-  </si>
-  <si>
-    <t>relationship--491bb5c5-320b-4358-ad14-f8b5d225df94</t>
-  </si>
-  <si>
-    <t>relationship--7d35ca2d-4e05-4cbd-91cb-8a547ac0d139</t>
-  </si>
-  <si>
-    <t>relationship--450083a2-0f16-4351-bbf7-98f58a05acfa</t>
-  </si>
-  <si>
-    <t>relationship--cbcb0245-351e-46ed-b295-16ec259a9bca</t>
-  </si>
-  <si>
-    <t>relationship--8839435d-3403-46a8-864b-e44aa7e5ce64</t>
-  </si>
-  <si>
-    <t>relationship--36bd823d-8d29-4b40-8988-53c9f4147220</t>
-  </si>
-  <si>
-    <t>relationship--d8ae6fde-2c1c-43f4-a634-85ad68c21bf0</t>
-  </si>
-  <si>
-    <t>relationship--8f86c428-0b02-43cc-b405-2ef3507326af</t>
-  </si>
-  <si>
-    <t>relationship--1713ad45-2009-4023-8a34-096b6c63bcf0</t>
-  </si>
-  <si>
-    <t>relationship--fa034e46-b2bb-4c2e-a5e0-52cd498f8a0c</t>
-  </si>
-  <si>
-    <t>relationship--182066db-05cb-40a7-a484-1c8328bfcc10</t>
-  </si>
-  <si>
-    <t>relationship--2f7f4d25-08fb-45f8-93dc-6d79ae865b42</t>
-  </si>
-  <si>
-    <t>relationship--a0fb143f-aaca-45bf-855d-fa1b9d6cf79b</t>
-  </si>
-  <si>
-    <t>relationship--b1b2dcf2-ef8d-41a3-aeb2-f8e80a188c4b</t>
-  </si>
-  <si>
-    <t>relationship--d9494bd7-969c-47c9-ac09-a5458436690d</t>
-  </si>
-  <si>
-    <t>relationship--ca58fdb3-ae70-4904-9241-40e5e2bbfa00</t>
-  </si>
-  <si>
-    <t>relationship--571eb7c7-7df4-4156-9ef3-9ad5a5014462</t>
-  </si>
-  <si>
-    <t>relationship--f48604d5-3465-433f-9d3a-ca75e82895d6</t>
-  </si>
-  <si>
-    <t>relationship--d7110124-cc48-4827-a308-207ac8a3362b</t>
-  </si>
-  <si>
-    <t>relationship--3c04687a-7035-4136-bae0-60e37e3e332e</t>
-  </si>
-  <si>
-    <t>relationship--ade0f069-012a-4140-ad72-72fa3e3efb3b</t>
-  </si>
-  <si>
-    <t>relationship--0d732f10-2516-4f97-8cfb-0c71e4db8ec9</t>
-  </si>
-  <si>
-    <t>relationship--ce0f253a-59cd-4b2c-846e-ac087649efd3</t>
-  </si>
-  <si>
-    <t>relationship--1b8dd273-e71c-4916-8dfc-8e1f3128d50b</t>
-  </si>
-  <si>
-    <t>relationship--ae58917f-a6f0-44ee-a667-55dd75c4bb15</t>
-  </si>
-  <si>
-    <t>relationship--7fc97b2a-0ddb-4660-9de9-3ef19b82455b</t>
-  </si>
-  <si>
-    <t>relationship--93ef4a1f-61bb-4171-9c2f-5f3f4d10f7c4</t>
-  </si>
-  <si>
-    <t>relationship--62d431c1-cfc2-43e9-a9a8-da756690a928</t>
-  </si>
-  <si>
-    <t>relationship--3cf8a689-fc2c-47ac-bb19-79461b0f7161</t>
-  </si>
-  <si>
-    <t>relationship--7613d2e9-5949-43c3-8a05-4b51e5787b59</t>
-  </si>
-  <si>
-    <t>relationship--644f5cae-0211-467a-81f9-59b8421b070c</t>
-  </si>
-  <si>
-    <t>relationship--981a7c37-9588-4112-934e-b22231d066b9</t>
-  </si>
-  <si>
-    <t>relationship--179e4855-e609-484d-becf-994f523e2284</t>
-  </si>
-  <si>
-    <t>relationship--77592244-d658-495b-ad75-fb5f35cab59a</t>
-  </si>
-  <si>
-    <t>relationship--ed2bfd70-bcb7-4ce6-b694-fe610e493952</t>
-  </si>
-  <si>
-    <t>relationship--75a7a305-32b3-4766-8903-3ea13326b47e</t>
-  </si>
-  <si>
-    <t>relationship--88f6af26-efe3-4d98-866a-a87a0560d237</t>
-  </si>
-  <si>
-    <t>relationship--8f9a4b44-b810-4638-8805-1fbddfe84476</t>
-  </si>
-  <si>
-    <t>relationship--c84ba526-27a3-46e4-a8b3-f88d3592421d</t>
-  </si>
-  <si>
-    <t>relationship--6d118374-fffb-47c5-b006-5aacd9caa916</t>
-  </si>
-  <si>
-    <t>relationship--fbff1eb1-f6f7-4f3a-8ae1-5d4785bf9a71</t>
-  </si>
-  <si>
-    <t>relationship--3b656b51-fcc3-4f3e-a463-3cc3793cbf11</t>
-  </si>
-  <si>
-    <t>relationship--f5d4c998-2a74-4260-825f-1f9aac7206d1</t>
-  </si>
-  <si>
-    <t>relationship--9e36db8c-773e-48da-a73d-2660a2f6f69d</t>
-  </si>
-  <si>
-    <t>relationship--749dd6d1-ab34-4211-aaf1-2048a84a5d9d</t>
-  </si>
-  <si>
-    <t>relationship--c4c0d5ab-c6c3-4206-b3bc-1ab4447def2e</t>
-  </si>
-  <si>
-    <t>relationship--8d006552-45fe-4adb-bda4-1604e40e34a4</t>
-  </si>
-  <si>
-    <t>relationship--192a9394-d344-4c10-8fa0-8035a11e0567</t>
-  </si>
-  <si>
-    <t>relationship--4d4c0e29-2c3b-4933-9c72-832928f67ae0</t>
-  </si>
-  <si>
-    <t>relationship--35fe0a4a-1920-4c7a-9cad-039c08f48a5a</t>
-  </si>
-  <si>
-    <t>relationship--f176e5a6-adc5-485a-a206-d829fa767837</t>
-  </si>
-  <si>
-    <t>relationship--88ab7777-3a68-45af-9274-dedf6858fae7</t>
-  </si>
-  <si>
-    <t>relationship--a21d2834-8de3-4afe-9b34-bbb84f32aa9f</t>
-  </si>
-  <si>
-    <t>relationship--c118ef6f-6446-49d0-b220-bd5db2b83f32</t>
-  </si>
-  <si>
-    <t>relationship--07014a19-5d22-43de-8bf7-6f126d5b8949</t>
-  </si>
-  <si>
-    <t>relationship--219ec753-5aff-41db-ae4e-a8b416c3b2d8</t>
-  </si>
-  <si>
-    <t>relationship--a0ef1e81-0c7d-4e28-8d4f-deb30300d49d</t>
-  </si>
-  <si>
-    <t>relationship--3ff2429b-0b1b-43cc-9791-f0e3af03f6c8</t>
-  </si>
-  <si>
-    <t>relationship--2bfb8cc1-b9a1-4f71-a06a-c989eff11075</t>
-  </si>
-  <si>
-    <t>relationship--1fe27c33-d973-481f-b324-807fd5bc64f1</t>
-  </si>
-  <si>
-    <t>relationship--6b8b0038-bcb4-4d64-9d80-2896b6daf4f9</t>
-  </si>
-  <si>
-    <t>relationship--1c93eb84-954e-4d8d-984a-4734aca01dea</t>
-  </si>
-  <si>
-    <t>relationship--bf4cf27b-b1e2-4c4a-94d3-3d68731d7e4c</t>
-  </si>
-  <si>
-    <t>relationship--ad1cb304-d5da-4be7-a022-fa4edf156ff2</t>
-  </si>
-  <si>
-    <t>relationship--c7cc97e4-8f77-4b9b-8499-09d9587eebb9</t>
-  </si>
-  <si>
-    <t>relationship--3f9419ea-2c59-401c-a333-398a8d63f736</t>
-  </si>
-  <si>
-    <t>relationship--40bd6c27-ac79-4a64-ab3e-8392092c6632</t>
-  </si>
-  <si>
-    <t>relationship--288459a0-33bb-44c5-ade8-5a2d8dd53b93</t>
-  </si>
-  <si>
-    <t>relationship--55b061a5-ed77-45c8-a522-42b65265b577</t>
-  </si>
-  <si>
-    <t>relationship--4908d2b4-44d2-4215-911e-11323dc15e21</t>
-  </si>
-  <si>
-    <t>relationship--acc98d57-50f2-412d-938e-40b58cbeffdb</t>
-  </si>
-  <si>
-    <t>relationship--ea5508f4-6427-41da-9bdf-e130b0f06359</t>
-  </si>
-  <si>
-    <t>relationship--08db49f3-64ff-478e-99f5-794ec6f52b08</t>
-  </si>
-  <si>
-    <t>relationship--17ce3a2c-452a-487f-9e37-bf9fbd0e8836</t>
-  </si>
-  <si>
-    <t>relationship--fe79fc9a-d42b-48cb-8fe7-85ce18a3fcd5</t>
-  </si>
-  <si>
-    <t>relationship--5521b7b7-478c-43ff-b22e-803538668b6a</t>
-  </si>
-  <si>
-    <t>relationship--1a41a16f-819f-4a96-b53d-5262ccfd7de5</t>
-  </si>
-  <si>
-    <t>relationship--5fc94f2c-5fec-48b2-a9a2-6d0fd0ec1252</t>
-  </si>
-  <si>
-    <t>relationship--36a6516f-3289-48b3-98f2-ef25e6199d38</t>
-  </si>
-  <si>
-    <t>relationship--c020b2c9-6cf9-40fa-8110-196ec8ba6334</t>
-  </si>
-  <si>
-    <t>relationship--32253f9c-c9a2-45aa-87ed-5bd6634ae620</t>
-  </si>
-  <si>
-    <t>relationship--12776127-015b-4233-b4c2-488e85591bcc</t>
-  </si>
-  <si>
-    <t>relationship--ee751307-f3fb-4fdd-b6a6-dc03760b38cf</t>
-  </si>
-  <si>
-    <t>relationship--d15c000a-4caa-460b-bcae-74ec1a725589</t>
-  </si>
-  <si>
-    <t>relationship--9f379780-e370-4513-a4ad-03c0fcb98ca4</t>
-  </si>
-  <si>
-    <t>relationship--50e32249-8681-463e-bc7b-7e70aa84f004</t>
-  </si>
-  <si>
-    <t>relationship--55df5e32-047c-470f-b683-67a128ebcb89</t>
-  </si>
-  <si>
-    <t>relationship--e7c9b119-3dc1-44a0-ab06-b6ce09def61f</t>
-  </si>
-  <si>
-    <t>relationship--11a2a9c1-594c-4e43-9137-939a3bca12f4</t>
-  </si>
-  <si>
-    <t>relationship--88345c9f-c6b3-49b6-8d2b-d761c8e092f1</t>
-  </si>
-  <si>
-    <t>relationship--c745c745-31df-4393-97c9-82ae9c3e1097</t>
-  </si>
-  <si>
-    <t>relationship--13914f79-1256-4413-8d4c-5cbb3f566bd2</t>
-  </si>
-  <si>
-    <t>relationship--20d9d0de-0994-4387-a2b9-8eef101240d3</t>
-  </si>
-  <si>
-    <t>relationship--14d0858b-f62f-4502-b4ac-26fbc1848f86</t>
-  </si>
-  <si>
-    <t>relationship--188cbcf7-3088-4248-b47e-0fe5a3b9581e</t>
-  </si>
-  <si>
-    <t>relationship--5c3c4292-5fd2-4e61-9aab-759ef4faf510</t>
-  </si>
-  <si>
-    <t>relationship--9a305630-89b9-4bb7-8810-35820d619d09</t>
-  </si>
-  <si>
-    <t>relationship--cfe0d9be-4cb5-4264-9410-d0d30abe64d5</t>
-  </si>
-  <si>
-    <t>relationship--b145f77a-6f6e-4124-9555-898b97ce2a9b</t>
-  </si>
-  <si>
-    <t>relationship--f687f0b5-a326-4dfe-9af7-42aa9820d7ad</t>
-  </si>
-  <si>
-    <t>relationship--e73697a3-d274-45be-8679-5aba06634f98</t>
-  </si>
-  <si>
-    <t>relationship--377519d0-34be-488d-8297-2b75100fca38</t>
-  </si>
-  <si>
-    <t>relationship--013c628a-1353-4397-9f36-a2bb53b09d1e</t>
-  </si>
-  <si>
-    <t>relationship--5a1e51b1-880b-478a-a5f5-d9e4f4044a60</t>
-  </si>
-  <si>
-    <t>relationship--19507a4f-9ae3-4b15-9690-4cd61d81d1fb</t>
-  </si>
-  <si>
-    <t>relationship--e1701364-3ca9-465f-8890-d94d2c9591cd</t>
-  </si>
-  <si>
-    <t>relationship--746f2ff4-e097-4c76-812b-2111d50a0829</t>
-  </si>
-  <si>
-    <t>relationship--440f9065-974b-432b-9405-f703636d44cc</t>
-  </si>
-  <si>
-    <t>relationship--03546cba-397c-4d69-8e76-f411f36348da</t>
-  </si>
-  <si>
-    <t>relationship--9053f9af-f4d9-47d5-b155-8c5db5131c26</t>
-  </si>
-  <si>
-    <t>relationship--a1fe1f7d-5ea2-4318-b7aa-3758f7d2a53a</t>
-  </si>
-  <si>
-    <t>relationship--33028bfb-3e06-489c-b300-0e73eb807216</t>
-  </si>
-  <si>
-    <t>relationship--382fa7ac-8a40-41c1-92df-1b674855253b</t>
-  </si>
-  <si>
-    <t>relationship--23d9bc18-8cfb-4996-b8ab-321d470a48e8</t>
-  </si>
-  <si>
-    <t>relationship--25a90bdb-d410-478c-8b4a-3e8a1e7f7c8e</t>
-  </si>
-  <si>
-    <t>relationship--09e5fdaa-ed64-4f42-acf0-432e489f4914</t>
-  </si>
-  <si>
-    <t>relationship--1aa0f36f-2644-4f85-832d-3c4ed459cfbc</t>
-  </si>
-  <si>
-    <t>relationship--1ed8a4c6-5748-43e7-9aa7-8c86062f6dfa</t>
-  </si>
-  <si>
-    <t>relationship--0faee98e-2979-4e38-bf9d-cad9a019befe</t>
-  </si>
-  <si>
-    <t>relationship--ea93c2c7-5c56-45d6-835c-7b6ad925ec3f</t>
-  </si>
-  <si>
-    <t>relationship--fda1abb1-5109-4da0-a730-df689c03d86d</t>
-  </si>
-  <si>
-    <t>relationship--811de1f9-5922-4769-b7cb-3b7d1b3ed59e</t>
-  </si>
-  <si>
-    <t>relationship--53637650-7396-4d16-95b0-433945a0f293</t>
-  </si>
-  <si>
-    <t>relationship--50f81c9e-7a2d-4a6a-bf8f-0b4c75345cd3</t>
-  </si>
-  <si>
-    <t>relationship--fdbf1246-0803-4855-9f47-11a222d56191</t>
-  </si>
-  <si>
-    <t>relationship--a3fc8ffe-bb50-43c4-b71b-08dd56c21600</t>
-  </si>
-  <si>
-    <t>relationship--1ca267f2-3129-4113-9196-ea31c51c9622</t>
-  </si>
-  <si>
-    <t>relationship--f4f9f954-f273-493c-8f03-fee8f1fbcf3d</t>
-  </si>
-  <si>
-    <t>relationship--5ea6689e-1103-4f37-a94f-29c70fa545d1</t>
-  </si>
-  <si>
-    <t>relationship--cd68ab7b-c88d-487a-8d2a-b46ba7a8927c</t>
-  </si>
-  <si>
-    <t>relationship--77920298-0cb4-4403-af9a-73a7c9d5f133</t>
-  </si>
-  <si>
-    <t>relationship--e795f3b5-5726-46b3-a6bb-7cefad5b49ea</t>
-  </si>
-  <si>
-    <t>relationship--effbe952-fdb9-477c-af6e-ad79c6add145</t>
-  </si>
-  <si>
-    <t>relationship--5ca1671c-ed66-4460-a6a9-371c43c8e530</t>
-  </si>
-  <si>
-    <t>relationship--a347ea58-ade6-405d-9bd2-9444ca45a07a</t>
-  </si>
-  <si>
-    <t>relationship--73e503b1-35ac-46bd-86f6-3b8f66dc8d99</t>
-  </si>
-  <si>
-    <t>relationship--ab474b5b-85c1-49d1-b13c-e82136bf4245</t>
-  </si>
-  <si>
-    <t>relationship--f4b81044-3360-4745-a6a5-604428258690</t>
-  </si>
-  <si>
-    <t>relationship--bfdce7e4-bb7c-461b-b323-fb16d50c7108</t>
-  </si>
-  <si>
-    <t>relationship--a36683a2-f252-481b-85be-91a1ab0e852b</t>
-  </si>
-  <si>
-    <t>relationship--3ba47494-0ae9-437b-951e-eccdc360cb76</t>
-  </si>
-  <si>
-    <t>relationship--b65185f6-a567-4ad9-86a6-35c4aa0cd3c7</t>
-  </si>
-  <si>
-    <t>relationship--cd276be5-897a-4ee9-bf23-3ae952c8366b</t>
-  </si>
-  <si>
-    <t>relationship--31d910d6-aa75-4288-bbc0-5fe603c77c9a</t>
-  </si>
-  <si>
-    <t>relationship--c8c7d773-6860-48e0-a5a2-e8afe0a06e55</t>
-  </si>
-  <si>
-    <t>relationship--3794a50c-3cc8-4b52-8d09-55800ee7b711</t>
-  </si>
-  <si>
-    <t>relationship--7b224d20-3237-4bac-a5c1-837f4bc6a447</t>
-  </si>
-  <si>
-    <t>relationship--dc7d5a0d-96f6-4799-ac74-170996bc71d3</t>
-  </si>
-  <si>
-    <t>relationship--9d37710d-723a-4d98-aa6a-7b7103a92265</t>
-  </si>
-  <si>
-    <t>relationship--adb77168-5386-4c39-93bf-dd9a5287a28b</t>
-  </si>
-  <si>
-    <t>relationship--c625c8d0-aa45-4059-ba32-0cba7ae7fd6d</t>
-  </si>
-  <si>
-    <t>relationship--bb4d4bba-06f4-4059-b64b-a08925a2ba09</t>
-  </si>
-  <si>
-    <t>relationship--a6ac9ff7-c858-42d0-8b78-4f2f15e1e9e8</t>
-  </si>
-  <si>
-    <t>relationship--3e96f0b2-a6e4-4c35-835b-536a56534d61</t>
-  </si>
-  <si>
-    <t>relationship--1d1c8443-4a4c-4b1e-83fb-c573bcdd8609</t>
-  </si>
-  <si>
-    <t>relationship--c2467e24-aa89-4fdb-9aeb-de8cb4d60e92</t>
-  </si>
-  <si>
-    <t>relationship--1e1ef58e-60dc-4cd1-bd5d-9a1b7ffb82f5</t>
-  </si>
-  <si>
-    <t>relationship--8b3bc7f7-8f15-401c-a897-8b4f4c485fab</t>
-  </si>
-  <si>
-    <t>relationship--4ca0c5b1-e701-4ce2-8d12-8c846fbb39a6</t>
-  </si>
-  <si>
-    <t>relationship--6a6a77cb-87b1-40cc-84c6-06538b94c503</t>
-  </si>
-  <si>
-    <t>relationship--029e9bcb-3d83-44fe-856a-792de66e76ce</t>
-  </si>
-  <si>
-    <t>relationship--49d0d7bb-1bd0-411e-a6eb-d7c754d175c3</t>
-  </si>
-  <si>
-    <t>relationship--3b5ac779-c057-45f5-b6e6-bb0d17a3f5e6</t>
-  </si>
-  <si>
-    <t>relationship--d69c2709-1b3e-46b9-b153-dcdf657703cc</t>
-  </si>
-  <si>
-    <t>relationship--ccda6bf7-2d88-4373-9335-2c8437473815</t>
-  </si>
-  <si>
-    <t>relationship--7f4c14d2-03df-480a-aceb-66e6711d2976</t>
-  </si>
-  <si>
-    <t>relationship--1d1b0731-589f-4a1a-b4d7-67f1bd1bf7f0</t>
-  </si>
-  <si>
-    <t>relationship--4df2a787-fce7-4a2d-b0c6-b52205e0ac9b</t>
-  </si>
-  <si>
-    <t>relationship--c60325fe-17d1-4ebc-84c3-1749b59f1ef5</t>
-  </si>
-  <si>
-    <t>relationship--07abd7f2-4b59-4ae8-8872-ba650eb99292</t>
-  </si>
-  <si>
-    <t>relationship--fb304e21-2864-4509-8578-b38764c6aa00</t>
-  </si>
-  <si>
-    <t>relationship--3b47b21f-f45d-4fdd-b93f-7318b2958619</t>
-  </si>
-  <si>
-    <t>relationship--dcb7b4f6-a9b2-4c7b-921a-941109d148b9</t>
-  </si>
-  <si>
-    <t>relationship--bc105e57-f5b4-410b-b4e7-b053d6c8354f</t>
-  </si>
-  <si>
-    <t>relationship--da72f4e7-05a6-4697-a006-ebf7daae88b8</t>
-  </si>
-  <si>
-    <t>relationship--694af659-ddc6-4f95-9f83-e0b0e53d9f12</t>
-  </si>
-  <si>
-    <t>relationship--52b32816-0e96-4bf7-854b-1ea7f0fa5b17</t>
-  </si>
-  <si>
-    <t>relationship--5b472a98-d634-4a30-9980-4d9bcf5de1b1</t>
-  </si>
-  <si>
-    <t>relationship--f10bf7c8-2c1e-477b-947b-a36f9197dd6b</t>
-  </si>
-  <si>
-    <t>relationship--dc644e4c-114e-41da-8dca-70427b6e543c</t>
-  </si>
-  <si>
-    <t>relationship--42757dd2-4dfd-444a-866e-1dd44077393b</t>
-  </si>
-  <si>
-    <t>relationship--bf045a89-5e75-4e7f-bb4e-0106b1ee2ca3</t>
-  </si>
-  <si>
-    <t>relationship--88ec8d99-1d19-4ad9-899e-e0735817f3a3</t>
-  </si>
-  <si>
-    <t>relationship--277e3cf8-150b-4f33-b01d-99e116e67355</t>
-  </si>
-  <si>
-    <t>relationship--9b1d81a0-7dd9-4409-9a67-4fd8dd800d7d</t>
-  </si>
-  <si>
-    <t>relationship--a26b6fb9-1b45-4908-a2d5-cef3d48e1311</t>
-  </si>
-  <si>
-    <t>relationship--e90242f1-fb1b-46ee-ac12-e4ed12000b54</t>
-  </si>
-  <si>
-    <t>relationship--d80eca26-283a-4c92-97b5-c855466844d5</t>
-  </si>
-  <si>
-    <t>relationship--5da9d99c-c93d-4f93-b43d-e5cbab8838d0</t>
-  </si>
-  <si>
-    <t>relationship--7e887476-9de0-4550-9742-271d684ec662</t>
-  </si>
-  <si>
-    <t>relationship--3fa03eb5-e376-42a0-a7e3-bd88627cc549</t>
-  </si>
-  <si>
-    <t>relationship--4968eebd-22fe-4785-b045-ffe11ff5960f</t>
-  </si>
-  <si>
-    <t>relationship--b1342883-0249-4f0c-9295-835e4e344d33</t>
-  </si>
-  <si>
-    <t>relationship--d4f7f80e-0c52-4ead-a877-6952ecbdeb89</t>
-  </si>
-  <si>
-    <t>relationship--c47cf2d8-8ed2-4143-9d9a-1035a6bfd74e</t>
-  </si>
-  <si>
-    <t>relationship--4a44ab9f-4259-48e6-919b-0b309bf7d4a2</t>
-  </si>
-  <si>
-    <t>relationship--e562a8e2-3043-45e9-abd5-5fff979c8098</t>
-  </si>
-  <si>
-    <t>relationship--f7a006d7-a54c-4007-9b41-0e5a19d5f2f1</t>
-  </si>
-  <si>
-    <t>relationship--0df7ee93-4dbc-4556-8c9d-27ab0b7be332</t>
-  </si>
-  <si>
-    <t>relationship--fe6a98c0-3544-4d58-a73f-e7cb95ff7bfd</t>
-  </si>
-  <si>
-    <t>relationship--3b0e4544-935a-44dc-b52f-9e06276ed524</t>
-  </si>
-  <si>
-    <t>relationship--0b300349-3650-4cad-879d-740953d43b27</t>
-  </si>
-  <si>
-    <t>relationship--130b2f16-ed8c-4b38-9496-09070c114e0a</t>
-  </si>
-  <si>
-    <t>relationship--93c3c1a0-6654-4a44-9e51-d41d9b97318c</t>
-  </si>
-  <si>
-    <t>relationship--4a5d7189-7dbc-4839-bf0c-f8333ebcec14</t>
-  </si>
-  <si>
-    <t>relationship--27af09e6-f251-45a9-9e2b-b7bb39ac3ce6</t>
-  </si>
-  <si>
-    <t>relationship--60f58897-14af-4024-9a19-38440f2d8e05</t>
-  </si>
-  <si>
-    <t>relationship--889f3572-fbd5-4c12-90f2-8cf06668b3f4</t>
-  </si>
-  <si>
-    <t>relationship--e2b164ad-12a8-4d18-9a67-0303231353c3</t>
-  </si>
-  <si>
-    <t>relationship--3f0ec1a5-8fcd-41e6-baf4-c82ab31f459e</t>
-  </si>
-  <si>
-    <t>relationship--8c38da6e-a102-4b7e-b660-27757b7cf81f</t>
-  </si>
-  <si>
-    <t>relationship--bdb63612-62f7-4c8c-ab64-42945130d1e8</t>
-  </si>
-  <si>
-    <t>relationship--c9a29469-7d1d-490e-a924-f0a79b0c9416</t>
-  </si>
-  <si>
-    <t>relationship--765d1542-ace9-455e-92d6-2c00612ea1bf</t>
-  </si>
-  <si>
-    <t>relationship--87cf9512-34ab-4409-8f32-b417344f43b3</t>
-  </si>
-  <si>
-    <t>relationship--56197d6f-b102-4489-8901-3c57468fb17f</t>
-  </si>
-  <si>
-    <t>relationship--882bfee5-9b46-483e-87de-818d057e4d0a</t>
-  </si>
-  <si>
-    <t>relationship--e6513013-65fb-4e47-8045-2e30de2a53b0</t>
-  </si>
-  <si>
-    <t>relationship--b4788d80-1953-4277-b97e-3286edcce45b</t>
-  </si>
-  <si>
-    <t>relationship--9dd953ce-eb32-441a-999b-256acde953a0</t>
-  </si>
-  <si>
-    <t>relationship--a60a8032-8a50-496c-8d63-4bce8cd965b3</t>
-  </si>
-  <si>
-    <t>relationship--5430b0d9-9052-4e96-9d8b-b323dbbec3ad</t>
-  </si>
-  <si>
-    <t>relationship--9eca6ea4-bad5-4a91-bd5f-0e0077203913</t>
-  </si>
-  <si>
-    <t>relationship--b4978d4b-2005-4226-b084-f573af7dd0aa</t>
-  </si>
-  <si>
-    <t>relationship--672ee83d-f949-4094-b48b-79f4aaee64a3</t>
-  </si>
-  <si>
-    <t>relationship--861b31f5-218a-40a4-bb92-b7ae6cfca4bd</t>
-  </si>
-  <si>
-    <t>relationship--fd48d9f1-41fb-4690-b252-f36a07c826b9</t>
-  </si>
-  <si>
-    <t>relationship--9496ba54-26ac-4a0f-b1b3-5d5b332df3dc</t>
-  </si>
-  <si>
-    <t>relationship--77817d32-a822-45fc-a549-f2033f8a259f</t>
-  </si>
-  <si>
-    <t>relationship--689b5082-1860-4af9-94b5-a1a864174caf</t>
-  </si>
-  <si>
-    <t>relationship--bfb72f7a-7820-4ae8-91f9-c841cedcaf50</t>
-  </si>
-  <si>
-    <t>relationship--ce9ae2d9-1561-49d8-9b27-47b9ffae90aa</t>
-  </si>
-  <si>
-    <t>relationship--6c37e1ac-42c5-4dc5-9fdd-9c1db2985f02</t>
-  </si>
-  <si>
-    <t>relationship--e203f843-7152-43aa-ac53-6bc383abbde0</t>
-  </si>
-  <si>
-    <t>relationship--79f9fb53-369c-485a-b1e8-a648a4672881</t>
-  </si>
-  <si>
-    <t>relationship--cc3fa8c9-6563-4d07-8366-e3d1e9742f44</t>
-  </si>
-  <si>
-    <t>relationship--8114f1d6-a671-4ab9-8a15-12da06ce2b4c</t>
-  </si>
-  <si>
-    <t>relationship--6530ce2a-a597-4103-9004-5bf3279bf9af</t>
-  </si>
-  <si>
-    <t>relationship--b006bf6e-7885-4e63-b21c-a8b5c2c9b270</t>
-  </si>
-  <si>
-    <t>relationship--e7c40b8a-8910-4717-8d47-2f33af618e1a</t>
-  </si>
-  <si>
-    <t>relationship--0b71308c-d561-47c0-bd1f-c8d9c5b2e67a</t>
-  </si>
-  <si>
-    <t>relationship--e7e6017b-62a3-4bcc-ac91-78ab4d791032</t>
-  </si>
-  <si>
-    <t>relationship--b756d8cf-b208-4b09-9558-252a094aa457</t>
-  </si>
-  <si>
-    <t>relationship--6a00cbbd-b00f-4f22-ad9b-7b4702738962</t>
-  </si>
-  <si>
-    <t>relationship--5c440561-e38a-466e-9555-8b43b92f7d37</t>
-  </si>
-  <si>
-    <t>relationship--03745cba-1552-4c2e-b9b0-446989ce4c92</t>
-  </si>
-  <si>
-    <t>relationship--c4a26a4b-04e1-4bc0-8a52-827b3fd16d04</t>
-  </si>
-  <si>
-    <t>relationship--151837c8-e2b9-40af-90a4-90777bfeb569</t>
-  </si>
-  <si>
-    <t>relationship--562a719b-244f-4576-b3a1-e8f63570719b</t>
-  </si>
-  <si>
-    <t>relationship--61d06baa-1be9-4f29-b0d6-648689348347</t>
-  </si>
-  <si>
-    <t>relationship--3f91fa7d-fd5e-428b-b9e5-52b77c66a44b</t>
-  </si>
-  <si>
-    <t>relationship--35a1f702-f3d0-437f-b192-ab4eaf7072ec</t>
-  </si>
-  <si>
-    <t>relationship--88154d87-ee53-4f2a-bcae-443294dfd3d7</t>
-  </si>
-  <si>
-    <t>relationship--8fa6133e-2409-4086-a38e-295b3331fe1e</t>
-  </si>
-  <si>
-    <t>relationship--dae48123-e72c-457a-9b89-1d53a5ab26ed</t>
-  </si>
-  <si>
-    <t>relationship--8d9c2c90-1695-4a03-af4c-f001e9b734dc</t>
-  </si>
-  <si>
-    <t>relationship--c699b6c0-4b41-4e2f-80d6-0a19fe50ff6c</t>
-  </si>
-  <si>
-    <t>relationship--fd8bc4ef-5c0a-440b-8e4b-f7346743911c</t>
-  </si>
-  <si>
-    <t>relationship--4c184424-80e2-487f-b185-f868db6c80d4</t>
-  </si>
-  <si>
-    <t>relationship--885c19f5-029d-44f6-be78-e1d23c3d4cdf</t>
-  </si>
-  <si>
-    <t>relationship--c21abbed-ad81-4c81-b37b-3b569185c93c</t>
-  </si>
-  <si>
-    <t>relationship--7bbae35d-f3e3-4e5a-bab2-e26f88b03ff9</t>
-  </si>
-  <si>
-    <t>relationship--5be04712-bd35-4322-8a64-0f7b815bec52</t>
-  </si>
-  <si>
-    <t>relationship--1d2aa0bf-db07-411f-b63e-f4357e28ee36</t>
-  </si>
-  <si>
-    <t>relationship--393e4ecb-c528-42b2-bc46-1f4b495e97c8</t>
-  </si>
-  <si>
-    <t>relationship--ed647326-a799-42e4-bf59-60f96b1941ed</t>
-  </si>
-  <si>
-    <t>relationship--d7035e41-3d39-40bb-b1f8-1d0f1e9181fe</t>
-  </si>
-  <si>
-    <t>relationship--6419b1f9-067a-4614-9778-dbfc46da687f</t>
-  </si>
-  <si>
-    <t>relationship--380f7b6b-5d65-4348-b727-aa82d27815d0</t>
-  </si>
-  <si>
-    <t>relationship--a19e1e6c-f404-4fe1-8182-cc1e87b204f3</t>
-  </si>
-  <si>
-    <t>relationship--61dd9227-ed0e-4372-be64-8140025b5eff</t>
-  </si>
-  <si>
-    <t>relationship--d1ac60e1-3cc3-4f08-bc33-5f6bbb2c6b54</t>
-  </si>
-  <si>
-    <t>relationship--dfd93469-9cce-4692-8651-fb115933f1aa</t>
-  </si>
-  <si>
-    <t>relationship--e49ae246-29e6-4178-9470-b6c6ab526928</t>
-  </si>
-  <si>
-    <t>relationship--eec22026-5df2-4710-b6db-43ac5324d334</t>
-  </si>
-  <si>
-    <t>relationship--68dd4196-3255-4dfe-8d66-9305b96089db</t>
-  </si>
-  <si>
-    <t>relationship--05ead870-071e-40ef-b68c-11666edb81bc</t>
-  </si>
-  <si>
-    <t>relationship--b34fb22d-d5b5-4bd3-bb63-4c3523b53595</t>
-  </si>
-  <si>
-    <t>relationship--507c6601-beca-4d52-bff7-f2e48a7b5139</t>
-  </si>
-  <si>
-    <t>relationship--0379ec2f-c532-44b6-bdf4-dfbae108e651</t>
-  </si>
-  <si>
-    <t>relationship--ca06c89a-39cf-4797-8528-1e9ac6c1796f</t>
-  </si>
-  <si>
-    <t>relationship--3f35ff73-38cf-4dc3-9b71-eb659acb342a</t>
-  </si>
-  <si>
-    <t>relationship--a608d4e0-d88e-4f2c-a1a4-6ef8f4bf5513</t>
-  </si>
-  <si>
-    <t>relationship--1d5d36d4-748e-4f8c-8de5-a8e22c24bb90</t>
-  </si>
-  <si>
-    <t>relationship--0156d84c-3ab8-4de7-a67d-ac6ccef18ef4</t>
-  </si>
-  <si>
-    <t>relationship--9ad2fceb-6f19-4477-91f5-2d53ab52b824</t>
-  </si>
-  <si>
-    <t>relationship--a0d8191f-c0b7-4d30-a5a3-5a226b9e291a</t>
-  </si>
-  <si>
-    <t>relationship--123ad057-53b4-4cd7-9ec7-8b9dc58028bb</t>
-  </si>
-  <si>
-    <t>relationship--287f0a0f-8848-4412-8971-edf616559cfc</t>
-  </si>
-  <si>
-    <t>relationship--dc93ced9-0e46-44b9-9550-df5bcc710137</t>
-  </si>
-  <si>
-    <t>relationship--07485167-d7da-4a8d-afee-edd9f71e86d9</t>
-  </si>
-  <si>
-    <t>relationship--b989c0cc-da64-4a88-980e-0487c3a391df</t>
-  </si>
-  <si>
-    <t>relationship--a422e1fa-dd68-4964-8441-8a26f4c77060</t>
-  </si>
-  <si>
-    <t>relationship--76c4b983-5919-4770-ac1c-b65d6f62748e</t>
-  </si>
-  <si>
-    <t>relationship--47c69cc8-89e5-46ff-9c97-e6bf5b7365b4</t>
-  </si>
-  <si>
-    <t>relationship--c6a21ce8-0384-47ee-890f-9441d8daae83</t>
-  </si>
-  <si>
-    <t>relationship--88b11cdf-20d4-4fac-a308-42dd3855b3fe</t>
-  </si>
-  <si>
-    <t>relationship--5369f320-2551-45a0-a468-aaed1fb67b25</t>
-  </si>
-  <si>
-    <t>relationship--fb564629-2361-46f5-8b83-41c234332297</t>
-  </si>
-  <si>
-    <t>relationship--57a6fc91-0d56-4664-bf0b-8d1b8692a22c</t>
-  </si>
-  <si>
-    <t>relationship--b194d6aa-b386-40ca-86dd-6ec6931e7a2d</t>
-  </si>
-  <si>
-    <t>relationship--2c8600a4-63cd-4680-9ca0-e101928991ec</t>
-  </si>
-  <si>
-    <t>relationship--b44b10fc-fb7c-4238-b850-052f43c6b4c2</t>
-  </si>
-  <si>
-    <t>relationship--55673426-60b0-4c14-9204-e73188165b28</t>
-  </si>
-  <si>
-    <t>relationship--a5ba58a7-9082-4753-a72d-2869505f670d</t>
-  </si>
-  <si>
-    <t>relationship--f646bf62-a55d-4616-ad99-d9df181bc16f</t>
-  </si>
-  <si>
-    <t>relationship--2149d320-d5d2-451b-9346-7fa9d858dd84</t>
-  </si>
-  <si>
-    <t>relationship--4f2f8d74-770f-4250-b5bd-ae9f6eceeb2e</t>
-  </si>
-  <si>
-    <t>relationship--cf446416-e9a7-4ef6-bfdc-15a9a031360e</t>
-  </si>
-  <si>
-    <t>relationship--1441e698-9f62-4527-9ad6-097ce4f68bf8</t>
-  </si>
-  <si>
-    <t>relationship--6f50775d-cd46-48ba-a26f-31a5f857374b</t>
-  </si>
-  <si>
-    <t>relationship--eefc035c-2ad6-404e-a485-c28de920b885</t>
-  </si>
-  <si>
-    <t>relationship--2a0646ed-67da-4291-8d77-30b27297ef6c</t>
-  </si>
-  <si>
-    <t>relationship--5309f230-016e-4963-9f0a-4647f087f1ca</t>
-  </si>
-  <si>
-    <t>relationship--b4464e86-d4a4-4b0c-ba8e-b0091c28d837</t>
-  </si>
-  <si>
-    <t>relationship--46d06255-f976-4949-96ae-8dc191c08be3</t>
-  </si>
-  <si>
-    <t>relationship--abf6e3d0-332a-44a3-bb04-0037e7d6fa14</t>
-  </si>
-  <si>
-    <t>relationship--04e93ba0-d7c3-4074-a120-e6869ac24d90</t>
-  </si>
-  <si>
-    <t>relationship--cb08dc61-c06d-43e9-93d8-a52bd4bd9ce9</t>
-  </si>
-  <si>
-    <t>relationship--77d698f4-b4bb-4511-af0f-77911c182127</t>
-  </si>
-  <si>
-    <t>relationship--06f24406-847d-4dfc-b2f3-3a2584a74d78</t>
-  </si>
-  <si>
-    <t>relationship--23a96e08-7357-4834-8dfc-9f9465900cdc</t>
-  </si>
-  <si>
-    <t>relationship--072b2c8e-eea0-4fc0-8a26-3e534a134562</t>
+    <t>relationship--2e3ad4d6-4817-44d6-a810-1f698a978be1</t>
+  </si>
+  <si>
+    <t>relationship--15f996d2-eaeb-4d08-a6d3-775e6a2f8fbc</t>
+  </si>
+  <si>
+    <t>relationship--04fb06f2-36c2-42da-ba70-c29842d9f3a8</t>
+  </si>
+  <si>
+    <t>relationship--d36f4e6e-728d-4a94-bf5f-9656edeea1da</t>
+  </si>
+  <si>
+    <t>relationship--d15c118c-55a7-4935-aeef-0806723fc244</t>
+  </si>
+  <si>
+    <t>relationship--1fd62ded-faf1-40f6-9a80-8936866af763</t>
+  </si>
+  <si>
+    <t>relationship--2d8b27f2-c98c-4b39-88f4-5b574cb9b16e</t>
+  </si>
+  <si>
+    <t>relationship--c5079e4d-1e54-477a-8e87-858564de885c</t>
+  </si>
+  <si>
+    <t>relationship--0b7931ad-13c9-4e31-bb22-89a1b3b5c3d8</t>
+  </si>
+  <si>
+    <t>relationship--3e43cceb-804e-4e9f-9eb9-980ceea91b04</t>
+  </si>
+  <si>
+    <t>relationship--ba91c710-f339-4c01-a363-be7e7bbf27f3</t>
+  </si>
+  <si>
+    <t>relationship--aac5ca0c-b5f4-4d56-afe6-efa851eef9d5</t>
+  </si>
+  <si>
+    <t>relationship--3237f077-a7a4-4db3-bcc0-8dd58cdf8f28</t>
+  </si>
+  <si>
+    <t>relationship--0612d69c-356a-433b-b2be-0041a7ea6311</t>
+  </si>
+  <si>
+    <t>relationship--736d6234-a45a-4b13-8d65-9d78531f8c15</t>
+  </si>
+  <si>
+    <t>relationship--4a4c98b5-4eb3-4f7b-9472-10828dfa027a</t>
+  </si>
+  <si>
+    <t>relationship--e89ed10a-5ac2-4324-a479-c757c443c9f2</t>
+  </si>
+  <si>
+    <t>relationship--a1ce28ab-391c-4839-864d-65981ace7e50</t>
+  </si>
+  <si>
+    <t>relationship--81f9f1de-ff42-4716-b8ae-58db05eb14e9</t>
+  </si>
+  <si>
+    <t>relationship--5a4845b2-82b0-4319-a7df-3ec49cd4caa1</t>
+  </si>
+  <si>
+    <t>relationship--aba5c12c-37dd-4141-988c-c40248ab20e4</t>
+  </si>
+  <si>
+    <t>relationship--9532b2f2-fe57-4003-81c0-ced8230649a0</t>
+  </si>
+  <si>
+    <t>relationship--9e2bd625-9c8a-491b-88af-fa56bef0cb01</t>
+  </si>
+  <si>
+    <t>relationship--a9e9f64b-4279-4970-b5a6-a888ab472781</t>
+  </si>
+  <si>
+    <t>relationship--7ef9f9d7-6b11-4527-931d-4be1859b8455</t>
+  </si>
+  <si>
+    <t>relationship--95e3cb37-74b2-4501-9ea7-56692dc24879</t>
+  </si>
+  <si>
+    <t>relationship--ac49cbf5-277a-474b-8b5a-db00c63fa9e2</t>
+  </si>
+  <si>
+    <t>relationship--248c0613-5d29-4b5a-b780-9d3faba8e10b</t>
+  </si>
+  <si>
+    <t>relationship--9a059b65-1ded-4470-b2f6-42747e77ba68</t>
+  </si>
+  <si>
+    <t>relationship--b3c79ef3-3d27-463c-9284-93bdb89ba863</t>
+  </si>
+  <si>
+    <t>relationship--dda52d9b-48f7-437a-bf7f-8d1431a370bf</t>
+  </si>
+  <si>
+    <t>relationship--ab8b6530-fe93-49bc-abaf-b6f11504f098</t>
+  </si>
+  <si>
+    <t>relationship--c53182a4-e78b-4543-affd-b08ddd57606a</t>
+  </si>
+  <si>
+    <t>relationship--1adbac6f-5b26-41e7-8629-024177c49d43</t>
+  </si>
+  <si>
+    <t>relationship--5bbd8003-05ff-4bff-bdb6-f3e7069a9d56</t>
+  </si>
+  <si>
+    <t>relationship--1860e0ed-660b-4853-9ff9-acf4008a1c60</t>
+  </si>
+  <si>
+    <t>relationship--0f626ab6-b22c-43cc-a529-427f27d4cd4a</t>
+  </si>
+  <si>
+    <t>relationship--b121753a-fe68-4d5c-a739-da48fca417e4</t>
+  </si>
+  <si>
+    <t>relationship--7ce06181-38d2-41b8-a75f-79d0e7ec6bae</t>
+  </si>
+  <si>
+    <t>relationship--783a6d7a-1c0e-4d55-84fe-375b495a73ef</t>
+  </si>
+  <si>
+    <t>relationship--91896033-1306-4164-ad3c-f7c9af44a58b</t>
+  </si>
+  <si>
+    <t>relationship--5e4917f1-5bd5-4bfc-a170-040e70d2f3c1</t>
+  </si>
+  <si>
+    <t>relationship--7990f3bc-8d0a-42cd-acaf-0bb0cb647a90</t>
+  </si>
+  <si>
+    <t>relationship--bfc9348a-9983-430a-8931-b7e35613d7b2</t>
+  </si>
+  <si>
+    <t>relationship--b9f40bc8-8e9f-473f-9d66-672b653721f9</t>
+  </si>
+  <si>
+    <t>relationship--0848b07e-1b83-4ee0-82e2-d8f1e17ee99a</t>
+  </si>
+  <si>
+    <t>relationship--d7eafec2-7c5e-4a6e-ad62-d713cc14b414</t>
+  </si>
+  <si>
+    <t>relationship--84602b4a-38d6-48e6-9d35-7e4275415071</t>
+  </si>
+  <si>
+    <t>relationship--617026e5-fd9d-49ea-a9d1-a84d87f652f0</t>
+  </si>
+  <si>
+    <t>relationship--69b45d78-b769-4614-b1e1-58942289ffe1</t>
+  </si>
+  <si>
+    <t>relationship--beecf6d7-36fe-43f7-a1da-7315c042bd10</t>
+  </si>
+  <si>
+    <t>relationship--74af7e90-dd63-418a-b257-84f0e3aee0dc</t>
+  </si>
+  <si>
+    <t>relationship--41dbbfbb-bb93-4e80-9a3d-4f84a36e5826</t>
+  </si>
+  <si>
+    <t>relationship--4962e2ed-68d1-4488-86de-3a303a238a2b</t>
+  </si>
+  <si>
+    <t>relationship--6647a361-ee08-4d1c-9707-c5313ef988a8</t>
+  </si>
+  <si>
+    <t>relationship--afaad920-53d7-45fe-b133-cb0ed1b0d297</t>
+  </si>
+  <si>
+    <t>relationship--733568b7-95ed-47e0-a741-ccf995cdf001</t>
+  </si>
+  <si>
+    <t>relationship--ac8da5f2-078f-4051-a6ab-82ef4221043a</t>
+  </si>
+  <si>
+    <t>relationship--52a05cca-efba-4875-8158-74fc9db94cbc</t>
+  </si>
+  <si>
+    <t>relationship--a62fe462-c0fd-45ea-bd02-b7ae576b0a77</t>
+  </si>
+  <si>
+    <t>relationship--71253b77-8675-46fb-b8d7-4fbbf8f381ab</t>
+  </si>
+  <si>
+    <t>relationship--e2bbc820-11de-4385-9f33-39aed660e08e</t>
+  </si>
+  <si>
+    <t>relationship--de9f3fc1-16dd-424d-98e0-7ce81ed92ce3</t>
+  </si>
+  <si>
+    <t>relationship--c554de6a-4ca1-4258-9c30-de58c01f848e</t>
+  </si>
+  <si>
+    <t>relationship--88bb3243-d057-4c18-902e-4135bf1045fc</t>
+  </si>
+  <si>
+    <t>relationship--d55af97a-39e5-47a7-8f40-7c20c61e8654</t>
+  </si>
+  <si>
+    <t>relationship--62b71848-b849-4080-911f-aba18b3b6a1c</t>
+  </si>
+  <si>
+    <t>relationship--8410eca9-cfe9-4cb2-bc0b-34794e3a1dc1</t>
+  </si>
+  <si>
+    <t>relationship--15401ffc-3093-40be-9f11-825cc9e3484e</t>
+  </si>
+  <si>
+    <t>relationship--2a84694e-0961-4bb8-b770-22dd2420c4af</t>
+  </si>
+  <si>
+    <t>relationship--2cfb2ee2-2574-453e-bb71-d1330a8c310f</t>
+  </si>
+  <si>
+    <t>relationship--09190a94-3902-4948-94cf-f1859831afec</t>
+  </si>
+  <si>
+    <t>relationship--265d1479-d38b-4859-b41b-d3240b6ab7aa</t>
+  </si>
+  <si>
+    <t>relationship--ff33a5bc-6d82-452d-937b-ec9c08cdc50b</t>
+  </si>
+  <si>
+    <t>relationship--803e9bbf-161a-4e5e-9731-a3dea5f24369</t>
+  </si>
+  <si>
+    <t>relationship--e4d6e73a-af5a-4d83-b335-2e083045ce97</t>
+  </si>
+  <si>
+    <t>relationship--1d17f76d-5b3d-4615-adab-9aba717c3f50</t>
+  </si>
+  <si>
+    <t>relationship--5d161d88-7f5e-4e40-9601-7425c8fad16d</t>
+  </si>
+  <si>
+    <t>relationship--8debb06e-d43e-4e19-bf07-4a870ec0fb66</t>
+  </si>
+  <si>
+    <t>relationship--ad8449b4-ef75-4f64-a179-6c16292e769a</t>
+  </si>
+  <si>
+    <t>relationship--4a10a6c1-b091-4a62-b86d-39236c9798a0</t>
+  </si>
+  <si>
+    <t>relationship--35b3910e-ed22-4888-bfc5-f349e0bb22c1</t>
+  </si>
+  <si>
+    <t>relationship--09310efa-0ebb-4cef-be5c-0c04372cbab4</t>
+  </si>
+  <si>
+    <t>relationship--a0cab5c2-6d75-4c7e-a1d1-9104e6f4d382</t>
+  </si>
+  <si>
+    <t>relationship--c67f914b-7aee-4b52-80be-14ff0de19509</t>
+  </si>
+  <si>
+    <t>relationship--2c7ea63d-f8ce-4f79-a51b-aee5da46d382</t>
+  </si>
+  <si>
+    <t>relationship--9ba73000-425c-4eef-8d23-0eddd5fbe5b8</t>
+  </si>
+  <si>
+    <t>relationship--b97c6c8f-4556-4f0c-b727-b7c1ee3bbc29</t>
+  </si>
+  <si>
+    <t>relationship--f7bb10ae-1dd7-4d5d-9c54-78bf99b976d6</t>
+  </si>
+  <si>
+    <t>relationship--5552c579-ca7a-4a01-b8b3-3ca980cba14b</t>
+  </si>
+  <si>
+    <t>relationship--156e8d02-57d9-4d23-b134-3a2ca6eadf60</t>
+  </si>
+  <si>
+    <t>relationship--d96da0bc-fbf6-411f-8bc3-2ca02f16725c</t>
+  </si>
+  <si>
+    <t>relationship--bed818e0-76ce-4506-bc5f-a8a1ec1a295d</t>
+  </si>
+  <si>
+    <t>relationship--3f5df155-5aae-44da-9af9-1a226d03e6ab</t>
+  </si>
+  <si>
+    <t>relationship--e5728e9c-6648-4dc0-b6ec-78774623accc</t>
+  </si>
+  <si>
+    <t>relationship--4ab76bec-c8cf-4c6e-a539-0ada2cfeb687</t>
+  </si>
+  <si>
+    <t>relationship--5d8f1aa8-f58f-4286-b678-6fe780d8ef89</t>
+  </si>
+  <si>
+    <t>relationship--37225940-e78f-463d-aae7-9c295d1690a5</t>
+  </si>
+  <si>
+    <t>relationship--c232b6ce-e4e3-492a-8ae7-cc0cfe0ae42b</t>
+  </si>
+  <si>
+    <t>relationship--0fdcd987-9d89-452a-bf7f-845555e8c2b8</t>
+  </si>
+  <si>
+    <t>relationship--46189e0b-5bb5-4884-a2a2-6252bd84b2ca</t>
+  </si>
+  <si>
+    <t>relationship--986f87b8-7ad8-489a-9938-b1068257ebe0</t>
+  </si>
+  <si>
+    <t>relationship--03375ddd-96af-4bf3-a288-92a3be6af9b4</t>
+  </si>
+  <si>
+    <t>relationship--d2d2421b-0ea8-427e-9d70-f0506dc0c64d</t>
+  </si>
+  <si>
+    <t>relationship--a0226ea2-b120-4749-b341-18b2a3de7dd0</t>
+  </si>
+  <si>
+    <t>relationship--84ab087d-7457-42f3-898d-5fee54bd0483</t>
+  </si>
+  <si>
+    <t>relationship--c7c9485c-39ed-4fba-a7ad-beb89b7cf56f</t>
+  </si>
+  <si>
+    <t>relationship--239d7608-34a5-4835-b7f7-c02ac2a9a6af</t>
+  </si>
+  <si>
+    <t>relationship--f287ba30-6aed-42b3-b3bc-5bee0294e476</t>
+  </si>
+  <si>
+    <t>relationship--fb3b5767-aec3-481e-95b4-b71c2ef6de96</t>
+  </si>
+  <si>
+    <t>relationship--501812d7-1650-4734-a274-3ef98476cd55</t>
+  </si>
+  <si>
+    <t>relationship--b0444f41-3c81-4a1a-b481-3f49ec4a4e31</t>
+  </si>
+  <si>
+    <t>relationship--b80cabe7-6934-4b3a-9b89-02bef7d6c618</t>
+  </si>
+  <si>
+    <t>relationship--f5dc9fa0-9614-4a88-9e07-f45255c10932</t>
+  </si>
+  <si>
+    <t>relationship--0c1ef22b-d183-4824-b170-bffcec8a57ee</t>
+  </si>
+  <si>
+    <t>relationship--45203285-e86a-4b6b-bb9e-7405a51a3c34</t>
+  </si>
+  <si>
+    <t>relationship--c02c8bfd-f9a6-4d25-b9bc-fee664d7846d</t>
+  </si>
+  <si>
+    <t>relationship--526d32f2-6608-473d-96a9-0128fd8c4d65</t>
+  </si>
+  <si>
+    <t>relationship--707b76d4-6b45-4def-a530-fba1a7697323</t>
+  </si>
+  <si>
+    <t>relationship--af67535f-654c-476d-933a-70b357f7ad7d</t>
+  </si>
+  <si>
+    <t>relationship--70c92e60-aa83-4abd-9f0f-9a07452090a8</t>
+  </si>
+  <si>
+    <t>relationship--34b4188e-a222-419b-a8a7-87dc5979b184</t>
+  </si>
+  <si>
+    <t>relationship--ba6bcb7f-a2c3-4a1e-a231-847c8c3c25af</t>
+  </si>
+  <si>
+    <t>relationship--ec5aefef-ed6b-4569-9562-52bc2218958f</t>
+  </si>
+  <si>
+    <t>relationship--8333d52c-373c-4705-8b6a-fc8f60f4acb9</t>
+  </si>
+  <si>
+    <t>relationship--2b10ba2c-3e5c-4493-90a9-6a4969709943</t>
+  </si>
+  <si>
+    <t>relationship--d6588f70-b2c0-4f7b-a7de-4234a7d3d393</t>
+  </si>
+  <si>
+    <t>relationship--c8608ea5-5c2e-4d1f-af4e-a403e58a1ddc</t>
+  </si>
+  <si>
+    <t>relationship--3362b6b6-9539-44fb-bbb1-77ca62463972</t>
+  </si>
+  <si>
+    <t>relationship--86f9b1d0-343f-4d2a-b067-baeaa1a5e2ae</t>
+  </si>
+  <si>
+    <t>relationship--ee4218f6-1ce4-4b3d-8d0f-c35d633fa5fd</t>
+  </si>
+  <si>
+    <t>relationship--5e65b072-02c9-4fd1-927e-fe73a3b9c3cc</t>
+  </si>
+  <si>
+    <t>relationship--43f4cbac-131e-477f-ba40-a48a4f09bae7</t>
+  </si>
+  <si>
+    <t>relationship--1703c07c-db59-4561-9aef-0e98c02b9770</t>
+  </si>
+  <si>
+    <t>relationship--d4963880-dd41-4212-afa4-2fdd2806447b</t>
+  </si>
+  <si>
+    <t>relationship--ff8a2389-f5dc-4ca6-ab72-fa4f2934be66</t>
+  </si>
+  <si>
+    <t>relationship--b289c407-48a4-4c20-acde-4fc18f0793aa</t>
+  </si>
+  <si>
+    <t>relationship--8e516f24-9475-40a8-bf4d-e32d3ab3b0f8</t>
+  </si>
+  <si>
+    <t>relationship--a783f428-93f7-4d30-8b8c-3cea3af59dbd</t>
+  </si>
+  <si>
+    <t>relationship--510e5f0c-f40b-4613-b116-7905ed679254</t>
+  </si>
+  <si>
+    <t>relationship--5ee050bb-caa5-4027-8c86-d89457143b70</t>
+  </si>
+  <si>
+    <t>relationship--570688c9-d884-4a11-8a88-dce68ac57c6d</t>
+  </si>
+  <si>
+    <t>relationship--038d1bfe-28b7-44c2-a6a0-ee5e025aedc0</t>
+  </si>
+  <si>
+    <t>relationship--ef099864-160b-40b4-a485-abae77993da8</t>
+  </si>
+  <si>
+    <t>relationship--8d18a790-bb6d-4123-b992-bff8839edc74</t>
+  </si>
+  <si>
+    <t>relationship--dcd721b8-0e41-47d5-b197-ced965eef40c</t>
+  </si>
+  <si>
+    <t>relationship--a467f8b9-78d7-4bad-acfb-978800a868c6</t>
+  </si>
+  <si>
+    <t>relationship--1cce5d0a-384f-407f-8829-0a81968155ce</t>
+  </si>
+  <si>
+    <t>relationship--f1d13d8d-c7fb-43ea-a060-1a5a1a177c2f</t>
+  </si>
+  <si>
+    <t>relationship--ea2ebc72-d18a-448b-9b13-7823bf2b0020</t>
+  </si>
+  <si>
+    <t>relationship--4324d530-438a-4a08-a4a5-450f34b19740</t>
+  </si>
+  <si>
+    <t>relationship--d7aa4588-8ac3-4532-af96-1a85eb79795f</t>
+  </si>
+  <si>
+    <t>relationship--790bc734-b044-4365-ae92-81e0d489b7f1</t>
+  </si>
+  <si>
+    <t>relationship--88c49f62-bbc9-4dbb-b171-f40ca7468289</t>
+  </si>
+  <si>
+    <t>relationship--1d0432ae-0659-41ba-a845-4d858ffe37e2</t>
+  </si>
+  <si>
+    <t>relationship--05dd34a2-9957-4e86-9534-e400d6dcf24a</t>
+  </si>
+  <si>
+    <t>relationship--676bcf81-589f-48d4-852f-44a7687fd5bb</t>
+  </si>
+  <si>
+    <t>relationship--ad47e557-908d-4ff3-b767-9809667070b2</t>
+  </si>
+  <si>
+    <t>relationship--c7f696be-a1d0-434e-8c6e-45c6cb26d255</t>
+  </si>
+  <si>
+    <t>relationship--29e04dd7-5a43-408b-a8ff-8c8b3516666e</t>
+  </si>
+  <si>
+    <t>relationship--53885f25-29da-4650-a3ab-c780b8b681ed</t>
+  </si>
+  <si>
+    <t>relationship--5522fb34-89d3-4d94-8943-19a95cfd80a8</t>
+  </si>
+  <si>
+    <t>relationship--00054969-0bcd-410a-a089-d1c4f48f4ced</t>
+  </si>
+  <si>
+    <t>relationship--fa66eb5a-75ee-432c-b536-d6b2f38b929b</t>
+  </si>
+  <si>
+    <t>relationship--fac1d288-ae4a-4c88-833f-854bed4c2fff</t>
+  </si>
+  <si>
+    <t>relationship--44d2840b-fe2f-45d6-b326-c73f8e8f0f1c</t>
+  </si>
+  <si>
+    <t>relationship--2daf3b19-b9bf-4d3b-87cb-a316e35f4e23</t>
+  </si>
+  <si>
+    <t>relationship--445ef799-5441-4780-858a-d669d25d61a5</t>
+  </si>
+  <si>
+    <t>relationship--cc8ed1d5-ac37-4c4c-8144-10b4803716d5</t>
+  </si>
+  <si>
+    <t>relationship--3a8fd0f8-288e-4644-9df2-8b8fa0a7d324</t>
+  </si>
+  <si>
+    <t>relationship--e2f78c0c-cfd5-43b5-9b1d-61dfe130674d</t>
+  </si>
+  <si>
+    <t>relationship--c38ab01c-8556-430e-8eb6-9fbcf10e0dd9</t>
+  </si>
+  <si>
+    <t>relationship--6494ae06-a2ca-46ef-9b80-3595bbb7393c</t>
+  </si>
+  <si>
+    <t>relationship--aa3904df-e13b-43ea-a06e-d284ba324f6e</t>
+  </si>
+  <si>
+    <t>relationship--424767de-ec68-4018-91b1-880c745a3d5a</t>
+  </si>
+  <si>
+    <t>relationship--cfbd9282-fdc2-4d1c-8035-fac2e924d447</t>
+  </si>
+  <si>
+    <t>relationship--cb07b69c-2cc8-4e90-9658-3995beba2394</t>
+  </si>
+  <si>
+    <t>relationship--48b3fccb-7a56-44f2-a4b3-45eb812e2726</t>
+  </si>
+  <si>
+    <t>relationship--2094783b-721a-411d-a142-06bfb458e71a</t>
+  </si>
+  <si>
+    <t>relationship--6f26e46d-aea8-4f6a-8a13-b598f88d16d9</t>
+  </si>
+  <si>
+    <t>relationship--ec759562-bbd9-4b75-a7b6-79108da59569</t>
+  </si>
+  <si>
+    <t>relationship--d3d29946-55b5-4e56-bb77-4817111ed284</t>
+  </si>
+  <si>
+    <t>relationship--823dadbb-4af3-46e8-af9d-b39b17ca84d5</t>
+  </si>
+  <si>
+    <t>relationship--88e28cf4-e804-47bd-99b3-ddcb8497b4a4</t>
+  </si>
+  <si>
+    <t>relationship--876f4555-3d08-4bfd-8a9d-73479599d3d6</t>
+  </si>
+  <si>
+    <t>relationship--a7ec7934-e4f4-4026-b71f-7990ecb296b7</t>
+  </si>
+  <si>
+    <t>relationship--487de349-615b-48ad-80d7-b95236eecc02</t>
+  </si>
+  <si>
+    <t>relationship--13995ae8-f441-41b5-9724-aab410eaa87f</t>
+  </si>
+  <si>
+    <t>relationship--afd12d83-7475-4510-8c3f-72e983b88113</t>
+  </si>
+  <si>
+    <t>relationship--11a8a1e0-ece3-43f9-8821-02e803bda225</t>
+  </si>
+  <si>
+    <t>relationship--55a46f0e-5aae-462d-80a2-1fee0880dcef</t>
+  </si>
+  <si>
+    <t>relationship--ea520e3e-d699-477c-8969-2c6d6e3d36d4</t>
+  </si>
+  <si>
+    <t>relationship--9b9aae58-6a65-4e11-a5ec-e9510321fea1</t>
+  </si>
+  <si>
+    <t>relationship--b063931d-c06e-4f16-9cfc-b0dddb3e3c43</t>
+  </si>
+  <si>
+    <t>relationship--db2c8d09-3e56-4685-ab16-f063526b19b2</t>
+  </si>
+  <si>
+    <t>relationship--a8e4b3d5-dc03-4f52-8f65-1ee2fa2f0162</t>
+  </si>
+  <si>
+    <t>relationship--707512ad-77bd-4472-ba56-13352a5d0859</t>
+  </si>
+  <si>
+    <t>relationship--85a3d8fe-68d5-41cf-86ae-d20bab16132b</t>
+  </si>
+  <si>
+    <t>relationship--6cff1afe-2cb8-4db9-840b-01edf39d52bc</t>
+  </si>
+  <si>
+    <t>relationship--db76e378-fc70-4c63-97ca-2aabe1818f45</t>
+  </si>
+  <si>
+    <t>relationship--f3f1dcd0-5834-4149-9583-df73aabde910</t>
+  </si>
+  <si>
+    <t>relationship--3c5f7264-7249-466b-b2ff-1aab1cfcf7a8</t>
+  </si>
+  <si>
+    <t>relationship--10b8424a-5a18-48f7-8460-9b56f02c64a9</t>
+  </si>
+  <si>
+    <t>relationship--420bac05-ec0c-457e-b10d-05709ed00508</t>
+  </si>
+  <si>
+    <t>relationship--e4a1859d-56db-473f-8f3a-01d1ecff9865</t>
+  </si>
+  <si>
+    <t>relationship--6f10115c-4687-4bb1-ad80-a8286e8d7ea1</t>
+  </si>
+  <si>
+    <t>relationship--af89ecff-ebd0-48b1-a999-cf7e090359f5</t>
+  </si>
+  <si>
+    <t>relationship--900f0776-6af6-4e52-9d40-407a14a1b10b</t>
+  </si>
+  <si>
+    <t>relationship--ad5911ae-9931-4303-917c-8bf0af554ba2</t>
+  </si>
+  <si>
+    <t>relationship--27fe1e23-9e8e-4e9a-867c-e971f5b27938</t>
+  </si>
+  <si>
+    <t>relationship--cbb50fab-7e8e-4d6c-86d5-832106d6b535</t>
+  </si>
+  <si>
+    <t>relationship--67460a1f-ba46-4ccd-b625-bd6f2659da8a</t>
+  </si>
+  <si>
+    <t>relationship--c79370be-6bfa-4f46-b747-87900992f20c</t>
+  </si>
+  <si>
+    <t>relationship--66de0818-b1aa-4fdf-8b59-41657de9a959</t>
+  </si>
+  <si>
+    <t>relationship--6c62bd91-cec9-43e4-96c0-7de19a976626</t>
+  </si>
+  <si>
+    <t>relationship--10b316d6-a09c-4d60-988f-646e42467869</t>
+  </si>
+  <si>
+    <t>relationship--6e328eb1-08b5-4e49-975c-94c709bd409b</t>
+  </si>
+  <si>
+    <t>relationship--3406d69f-e0ac-4f8e-87a4-6dff7e804f99</t>
+  </si>
+  <si>
+    <t>relationship--269c07e7-e785-4fbe-9b44-37915c651501</t>
+  </si>
+  <si>
+    <t>relationship--f6705a7b-13a9-46b0-bcdb-4e1d69b9d930</t>
+  </si>
+  <si>
+    <t>relationship--232b88a1-d90d-4d5e-8167-da7b7c35c1e3</t>
+  </si>
+  <si>
+    <t>relationship--2cb4cae9-3ff4-4d54-8779-eabc3825c303</t>
+  </si>
+  <si>
+    <t>relationship--2a8ee6fa-55f4-4ad6-9954-df7b9cd95e87</t>
+  </si>
+  <si>
+    <t>relationship--c6724897-4f7a-486a-9976-c1e916d1539d</t>
+  </si>
+  <si>
+    <t>relationship--9eec828d-aff9-4828-856a-ad89e8adc4be</t>
+  </si>
+  <si>
+    <t>relationship--0679e913-f222-4d1f-9a96-6fd772a674ba</t>
+  </si>
+  <si>
+    <t>relationship--c51a31a2-b9e1-4b98-bc26-f590dad3dd7e</t>
+  </si>
+  <si>
+    <t>relationship--0be151f9-7e48-4fd1-b215-5c05f2729c36</t>
+  </si>
+  <si>
+    <t>relationship--61a209ed-7f03-488e-ad53-53aefd2e9ebb</t>
+  </si>
+  <si>
+    <t>relationship--ead62c20-6c77-4fd3-949e-c9a6954be6e7</t>
+  </si>
+  <si>
+    <t>relationship--3dcb1927-c157-4cc5-a204-237cc422e526</t>
+  </si>
+  <si>
+    <t>relationship--f5e5f729-f586-4c58-a2ac-9121ffe6abda</t>
+  </si>
+  <si>
+    <t>relationship--dbe7fab1-5ef3-491d-a1e7-a8c0a701c0aa</t>
+  </si>
+  <si>
+    <t>relationship--e73af7f5-6e5f-49a9-8ed3-d13e0868880d</t>
+  </si>
+  <si>
+    <t>relationship--e20bd310-d4bc-4df3-bfb3-a9836ddfb310</t>
+  </si>
+  <si>
+    <t>relationship--10158e66-8cd1-4b8c-86b9-f88759d46427</t>
+  </si>
+  <si>
+    <t>relationship--d1cb891e-1cad-4db4-8bc7-f62fdabf433e</t>
+  </si>
+  <si>
+    <t>relationship--baf7aa9e-6e05-43a1-b972-90441df19a3e</t>
+  </si>
+  <si>
+    <t>relationship--ec58d906-6864-4068-89bb-bebe7ae99785</t>
+  </si>
+  <si>
+    <t>relationship--d298e28d-250f-4cd0-a856-b89e5ce7b88d</t>
+  </si>
+  <si>
+    <t>relationship--c269fe15-c5be-4823-a518-f9fc55959bc6</t>
+  </si>
+  <si>
+    <t>relationship--50050696-12a8-4fa3-a415-53b8b82dea85</t>
+  </si>
+  <si>
+    <t>relationship--874d162e-2c50-4199-b6a4-39079e1afd2c</t>
+  </si>
+  <si>
+    <t>relationship--f4a5485f-8491-422f-8796-eb43f662ef04</t>
+  </si>
+  <si>
+    <t>relationship--70afaa59-d579-4c48-a4f7-e5f655976d8e</t>
+  </si>
+  <si>
+    <t>relationship--a423a829-7a8d-45da-b736-9a04cf98b61a</t>
+  </si>
+  <si>
+    <t>relationship--70bbeb57-4b3c-4fab-adc1-1dc6198e13b4</t>
+  </si>
+  <si>
+    <t>relationship--0a67dac3-b381-434b-abb7-ef513e09f6cf</t>
+  </si>
+  <si>
+    <t>relationship--4f678204-fcd8-4267-9153-9a4371987f30</t>
+  </si>
+  <si>
+    <t>relationship--ef486430-74c7-4fe2-b673-5fc558d8a341</t>
+  </si>
+  <si>
+    <t>relationship--33b362c3-ef66-4952-a0ed-0dedcc6fb7ff</t>
+  </si>
+  <si>
+    <t>relationship--b792f9e3-9b9c-4536-a89f-174effa04791</t>
+  </si>
+  <si>
+    <t>relationship--8f35ece3-fb19-421a-9f69-555f1050e821</t>
+  </si>
+  <si>
+    <t>relationship--f7a42814-cfdc-4ee8-b3aa-f621d054d2bd</t>
+  </si>
+  <si>
+    <t>relationship--6d5ec928-0460-4088-bf4d-a84766632043</t>
+  </si>
+  <si>
+    <t>relationship--2577f486-51c5-4c4f-bc31-c358edfae31d</t>
+  </si>
+  <si>
+    <t>relationship--957dac06-84ad-428b-95bf-66a508e5d916</t>
+  </si>
+  <si>
+    <t>relationship--6533395a-88f1-4ea2-b736-36c326d771a9</t>
+  </si>
+  <si>
+    <t>relationship--57f29431-847a-43e0-b7e6-1a431a2058e8</t>
+  </si>
+  <si>
+    <t>relationship--e4a98f6c-89c4-440c-b379-ab19a0b17e01</t>
+  </si>
+  <si>
+    <t>relationship--00ab4613-70a8-4939-9c07-372c0bc9860c</t>
+  </si>
+  <si>
+    <t>relationship--cc04b3b3-67ae-44e0-9436-7ff30af33bf7</t>
+  </si>
+  <si>
+    <t>relationship--c1eaee30-f633-4217-bd44-8d15f9d8c065</t>
+  </si>
+  <si>
+    <t>relationship--077a5af9-f296-4f30-967a-ab5cd4faf152</t>
+  </si>
+  <si>
+    <t>relationship--7e59d2ea-b884-41f7-92fd-edc063f147c8</t>
+  </si>
+  <si>
+    <t>relationship--ed7fbb91-8764-4af0-8a62-052e4e6d95d4</t>
+  </si>
+  <si>
+    <t>relationship--cb1bd2c3-a763-4fd2-8c8d-29ca5b1c6ff7</t>
+  </si>
+  <si>
+    <t>relationship--383f4b08-21e5-4e95-a92a-190a74bec975</t>
+  </si>
+  <si>
+    <t>relationship--b8487f86-404d-4580-bb96-4bf795ba066b</t>
+  </si>
+  <si>
+    <t>relationship--52d1bb56-b482-4ba3-8323-d423f21a8c6e</t>
+  </si>
+  <si>
+    <t>relationship--55236e8d-545e-4952-a518-32d267b79248</t>
+  </si>
+  <si>
+    <t>relationship--630137a1-fab5-4996-b489-94b760c08587</t>
+  </si>
+  <si>
+    <t>relationship--8c718d39-0585-4e91-a06f-d9366b81648b</t>
+  </si>
+  <si>
+    <t>relationship--7d415e7b-01a9-478e-9e71-65687ae5091a</t>
+  </si>
+  <si>
+    <t>relationship--aac45e98-80d3-4f9b-bee1-28f0397d63c5</t>
+  </si>
+  <si>
+    <t>relationship--2435cd1e-cd99-425b-832c-7d629f6ee15a</t>
+  </si>
+  <si>
+    <t>relationship--dd956bb0-b061-4a33-8b45-ce09ae518653</t>
+  </si>
+  <si>
+    <t>relationship--b9968c17-292b-4890-aac2-73f7458b4efc</t>
+  </si>
+  <si>
+    <t>relationship--d8c5dfde-2fa6-4075-a4ee-14afcf5356db</t>
+  </si>
+  <si>
+    <t>relationship--ee02a592-fd90-451d-90d5-d2c8d4467ecc</t>
+  </si>
+  <si>
+    <t>relationship--8e295d63-6597-43da-9840-66b7e6ca81b7</t>
+  </si>
+  <si>
+    <t>relationship--92a21bbe-ad5f-4baf-91b0-734d79c01d80</t>
+  </si>
+  <si>
+    <t>relationship--46b0d5ce-0d5c-45b9-9803-2ae4190d0c4c</t>
+  </si>
+  <si>
+    <t>relationship--805a683c-6989-4638-a65d-bcbc3764742a</t>
+  </si>
+  <si>
+    <t>relationship--7e36c1c8-aeb0-4f4f-84ea-86db8d462300</t>
+  </si>
+  <si>
+    <t>relationship--160f57d0-2863-43a6-bfa1-267076ca1d6a</t>
+  </si>
+  <si>
+    <t>relationship--367f3fa8-0c9c-4a10-94a5-5d72b06f96b7</t>
+  </si>
+  <si>
+    <t>relationship--0ec2c2c7-802b-40c0-8428-c963a8e4f90c</t>
+  </si>
+  <si>
+    <t>relationship--e71cbf0d-3d7b-4dbd-ac52-cc1a5866aad4</t>
+  </si>
+  <si>
+    <t>relationship--d852a84f-3c45-4ef2-8fd1-13a3c224137f</t>
+  </si>
+  <si>
+    <t>relationship--878c28e1-7169-459c-91a4-3ed447223d70</t>
+  </si>
+  <si>
+    <t>relationship--81b6bc77-c102-4a05-a579-5e89bd13cc12</t>
+  </si>
+  <si>
+    <t>relationship--77ffef49-fa37-4d05-b1a4-1d7751f79ee4</t>
+  </si>
+  <si>
+    <t>relationship--577e0dbe-1ef5-4fd2-a187-44324ce4a72e</t>
+  </si>
+  <si>
+    <t>relationship--b500e8e8-9847-4766-8f94-34b72b6689c8</t>
+  </si>
+  <si>
+    <t>relationship--29b1511e-eca2-451c-90c5-d4a2b3b608e7</t>
+  </si>
+  <si>
+    <t>relationship--c7fbd8ed-a720-4bec-bd85-41cbe4cdc22f</t>
+  </si>
+  <si>
+    <t>relationship--c74ac39e-968c-46f0-9d68-0c89efe7d6d7</t>
+  </si>
+  <si>
+    <t>relationship--ed809171-4923-43da-a9ad-138283fb7eaf</t>
+  </si>
+  <si>
+    <t>relationship--d6a739e6-c1dd-4cd3-a692-753d5edfcafa</t>
+  </si>
+  <si>
+    <t>relationship--89dd3e0e-2239-4e0c-8cb6-8861b76e0d3c</t>
+  </si>
+  <si>
+    <t>relationship--70f3bbdf-9325-4013-8c73-4f02cb19a47f</t>
+  </si>
+  <si>
+    <t>relationship--0d3ee557-dd08-4c96-baa0-b81cb941cf3e</t>
+  </si>
+  <si>
+    <t>relationship--9591863f-3471-44ae-8a35-1bc56d3a62c1</t>
+  </si>
+  <si>
+    <t>relationship--6f169388-5ee6-4848-805b-165b3fa47dff</t>
+  </si>
+  <si>
+    <t>relationship--33b65c8d-6b41-4163-b2d3-1666c37a9032</t>
+  </si>
+  <si>
+    <t>relationship--f4df1e00-8a91-4b71-b675-25d60bad6a98</t>
+  </si>
+  <si>
+    <t>relationship--24d503a3-8f4f-4244-ad19-1b222b59e7ef</t>
+  </si>
+  <si>
+    <t>relationship--2b63bdcf-a516-4ee3-b148-08bdd7a7cb9d</t>
+  </si>
+  <si>
+    <t>relationship--c0d66f67-d5fc-4718-87b7-13907602bba3</t>
+  </si>
+  <si>
+    <t>relationship--e67e91a0-480a-4ef4-8eeb-81989eadf823</t>
+  </si>
+  <si>
+    <t>relationship--cf7e2563-1bd6-49b2-b95d-70e7b2d5ef86</t>
+  </si>
+  <si>
+    <t>relationship--3519f430-e040-4aee-951d-4527c6545b36</t>
+  </si>
+  <si>
+    <t>relationship--76186630-c101-4f9d-a1ff-6aec5709b600</t>
+  </si>
+  <si>
+    <t>relationship--85357ec1-3dc2-4f90-854e-433509aab018</t>
+  </si>
+  <si>
+    <t>relationship--20780665-a60b-4f7f-971f-5184a072cefc</t>
+  </si>
+  <si>
+    <t>relationship--8b9d3fc3-1e2e-4ca0-ac96-0153a479d186</t>
+  </si>
+  <si>
+    <t>relationship--a74f2cd1-670a-4c86-9add-59a4fda87cbf</t>
+  </si>
+  <si>
+    <t>relationship--295d93e4-0fd4-401e-9b07-610d743be347</t>
+  </si>
+  <si>
+    <t>relationship--8770ccbf-0457-469f-b0eb-bf0fc740dd31</t>
+  </si>
+  <si>
+    <t>relationship--6780bd12-6e75-4185-b1a9-6ea68e82f9a5</t>
+  </si>
+  <si>
+    <t>relationship--363dd54a-6b6c-4d29-b12b-7633f127ae4f</t>
+  </si>
+  <si>
+    <t>relationship--c6fae978-de61-436a-b541-b9ccb8b8ddea</t>
+  </si>
+  <si>
+    <t>relationship--87e4a348-08b9-4ba3-aeed-4e125c080132</t>
+  </si>
+  <si>
+    <t>relationship--515541a7-6128-4a36-bad8-b4a99b8d1f25</t>
+  </si>
+  <si>
+    <t>relationship--627f7ec5-e07a-4a9e-a179-f56072219e23</t>
+  </si>
+  <si>
+    <t>relationship--9950a4bf-9fc5-48aa-8149-a7cc237741b6</t>
+  </si>
+  <si>
+    <t>relationship--47d76080-8a63-4b2b-a690-ecdd1ac8a447</t>
+  </si>
+  <si>
+    <t>relationship--52320481-114d-4984-ae7c-159c0ade1951</t>
+  </si>
+  <si>
+    <t>relationship--b962befb-5ce9-4090-a7ae-d21e5213b24e</t>
+  </si>
+  <si>
+    <t>relationship--98d9c5dd-04c8-41f6-b66b-72031418daa8</t>
+  </si>
+  <si>
+    <t>relationship--b3145501-4aef-4bd4-a84b-56abc85bf491</t>
+  </si>
+  <si>
+    <t>relationship--94c95dc2-8858-4f49-8ece-3ec79609c4c4</t>
+  </si>
+  <si>
+    <t>relationship--75e0cd78-c4ab-4ad1-b1b1-dfad9c2d7b41</t>
+  </si>
+  <si>
+    <t>relationship--1e3e92b7-4def-4664-b9c7-3fab81304d41</t>
+  </si>
+  <si>
+    <t>relationship--a69c6c2e-b12f-47cc-8e0e-db22bccf842d</t>
+  </si>
+  <si>
+    <t>relationship--cf5f23ba-6c2b-402c-9fe3-ae75fa116ee2</t>
+  </si>
+  <si>
+    <t>relationship--f90aefa2-2a8d-4e22-b012-96035822427f</t>
+  </si>
+  <si>
+    <t>relationship--7b93a63c-7ddb-46ed-b1f5-689c84b6dd44</t>
+  </si>
+  <si>
+    <t>relationship--3ab348ce-8d96-4260-bf68-9c2abbeb728e</t>
+  </si>
+  <si>
+    <t>relationship--13bce4b8-606b-4b06-b217-1513ec54251a</t>
   </si>
   <si>
     <t>attributed-to</t>
@@ -5893,22 +5893,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--080fc39f-be32-4bdf-aa6b-d86e3dcd4f81</t>
-  </si>
-  <si>
-    <t>intrusion-set--1e2aa43d-a27c-407c-b94a-405123ec52f9</t>
-  </si>
-  <si>
-    <t>intrusion-set--6fcf2657-4840-4754-a318-5cee4b91d670</t>
-  </si>
-  <si>
-    <t>intrusion-set--4f0187aa-3964-42bb-8185-827fd9232dcb</t>
-  </si>
-  <si>
-    <t>intrusion-set--6bb397ce-d257-45ef-9a68-fd682239dc91</t>
-  </si>
-  <si>
-    <t>intrusion-set--701ece7a-3998-432c-ab53-b4496887b072</t>
+    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
+  </si>
+  <si>
+    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
+  </si>
+  <si>
+    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
+  </si>
+  <si>
+    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
+  </si>
+  <si>
+    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
+  </si>
+  <si>
+    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
   </si>
   <si>
     <t>group</t>
@@ -5917,313 +5917,313 @@
     <t>Вторжение войск генерала Деникина под лозунгом восстановления «единой и неделимой России» и вооруженное вытеснение украинских частей из освобожденного ими Киева 31 августа 1919 года («Киевская катастрофа»), приведшее к развалу фронта. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--12bc8904-99bc-4a55-a768-c6d397e1a829</t>
-  </si>
-  <si>
-    <t>relationship--f69b368a-adad-48c6-8f60-0c29f400c102</t>
-  </si>
-  <si>
-    <t>relationship--18c6088c-8841-4ec9-aac2-46a007ebcc21</t>
-  </si>
-  <si>
-    <t>relationship--a963ff2b-070c-4db6-a06d-e5e88f4f3325</t>
-  </si>
-  <si>
-    <t>relationship--797f6d6f-ef9f-4e5e-ae50-0adf72381d8d</t>
-  </si>
-  <si>
-    <t>relationship--aac285db-9b35-40f3-850d-3879630f39b0</t>
-  </si>
-  <si>
-    <t>relationship--01b73e42-a773-4c1d-ae11-0261602aa1d5</t>
-  </si>
-  <si>
-    <t>relationship--fd3683f7-5961-46fb-a76a-82b65e3a5b73</t>
-  </si>
-  <si>
-    <t>relationship--70eb29ba-2799-438a-823e-c446df6bb1c3</t>
-  </si>
-  <si>
-    <t>relationship--3034bb38-cc9e-4fe3-9842-ae672d1b5536</t>
-  </si>
-  <si>
-    <t>relationship--386bf42f-4150-4986-9814-edbe336dfe55</t>
-  </si>
-  <si>
-    <t>relationship--284bb962-aeb3-442f-b754-228c2dd8867e</t>
-  </si>
-  <si>
-    <t>relationship--d05d0b21-357b-4498-bc88-e7c4cc4f9f9f</t>
-  </si>
-  <si>
-    <t>relationship--d2022ffe-3862-4f2c-9b89-19cb8f674ff3</t>
-  </si>
-  <si>
-    <t>relationship--44935fe7-597d-4305-8969-7d4193d4937e</t>
-  </si>
-  <si>
-    <t>relationship--b237bf26-ef58-44ce-884b-12d24cef4ebc</t>
-  </si>
-  <si>
-    <t>relationship--78f059a7-2d33-49be-9c65-b63c987a69e8</t>
-  </si>
-  <si>
-    <t>relationship--6cd0cf96-c86f-49ec-8146-9ffbe9e15ab1</t>
-  </si>
-  <si>
-    <t>relationship--eb81fea3-4753-4b73-893f-16fd43321646</t>
-  </si>
-  <si>
-    <t>relationship--170c807a-1fe8-4130-977a-13bd8e119f56</t>
-  </si>
-  <si>
-    <t>relationship--cdf4555b-3027-4c26-8582-bdb5ea5f869a</t>
-  </si>
-  <si>
-    <t>relationship--53131930-c0c4-4d4b-9c82-ee16de54ce19</t>
-  </si>
-  <si>
-    <t>relationship--4821fa4d-5f4d-4bfb-8bd6-4a0299575b5b</t>
-  </si>
-  <si>
-    <t>relationship--37cfc5df-0284-43b0-8c9f-621300de40cb</t>
-  </si>
-  <si>
-    <t>relationship--31c52698-3b14-4ed3-b949-6f20a9f44ea9</t>
-  </si>
-  <si>
-    <t>relationship--b392a5a2-6f29-4155-b30e-c35d6e81164a</t>
-  </si>
-  <si>
-    <t>relationship--10b967cf-5d22-49ba-9593-7586cfb25d57</t>
-  </si>
-  <si>
-    <t>relationship--9a4cfe1d-243b-4da7-8f85-a5a234c0de46</t>
-  </si>
-  <si>
-    <t>relationship--229bc6e3-bd6e-4f00-920a-bf0b75aeb3ce</t>
-  </si>
-  <si>
-    <t>relationship--3b64a530-ee75-43af-ad56-3f7be087f2b6</t>
-  </si>
-  <si>
-    <t>relationship--24417c43-3986-4157-a47b-138ce21c1586</t>
-  </si>
-  <si>
-    <t>relationship--d2f3847c-ea68-485c-9b5c-5489b3c02399</t>
-  </si>
-  <si>
-    <t>relationship--243e8e41-8775-4d04-8cf5-4270b8f00b87</t>
-  </si>
-  <si>
-    <t>relationship--1e9db859-18a1-4b08-bbd4-9c8cb097729b</t>
-  </si>
-  <si>
-    <t>relationship--05eb80d0-303e-4b3d-8974-3be40c5a6cdc</t>
-  </si>
-  <si>
-    <t>relationship--c1b7dbad-95fa-4b86-aa0b-f4847943206f</t>
-  </si>
-  <si>
-    <t>relationship--712355d5-0423-4efa-910b-56b77ad545fa</t>
-  </si>
-  <si>
-    <t>relationship--5fbfc696-714c-42dc-a387-89d2a7bb4132</t>
-  </si>
-  <si>
-    <t>relationship--9179dcc8-fd36-43e7-8ebc-45c9b2d0c555</t>
-  </si>
-  <si>
-    <t>relationship--e179b84d-4d95-4dce-a854-38c32b638bc9</t>
-  </si>
-  <si>
-    <t>relationship--d019a938-c6f0-42a3-b4c7-00fc1eac691c</t>
-  </si>
-  <si>
-    <t>relationship--fc05427b-b7ed-4a94-b62c-2bb9ef30d7ad</t>
-  </si>
-  <si>
-    <t>relationship--c5355ea4-9dd7-41b9-a281-58dfe58bacd2</t>
-  </si>
-  <si>
-    <t>relationship--e322551c-b3c2-40e8-9efa-d9fe5c984aab</t>
-  </si>
-  <si>
-    <t>relationship--6fabfad7-778f-461e-9d87-7d2f8192ddc4</t>
-  </si>
-  <si>
-    <t>relationship--1cada7a0-7e70-4c74-85aa-54969bd99f6d</t>
-  </si>
-  <si>
-    <t>relationship--464ccc93-dc4f-4050-bb8b-07a28cef790e</t>
-  </si>
-  <si>
-    <t>relationship--b6b6b49c-9491-4e42-a665-09884c32fa52</t>
-  </si>
-  <si>
-    <t>relationship--0e9d2f82-e202-4317-94cf-8932067cdd33</t>
-  </si>
-  <si>
-    <t>relationship--5b7b09b3-9a51-4d65-a86c-4befe3ab7fbc</t>
-  </si>
-  <si>
-    <t>relationship--f30be867-5cae-40b0-8c91-06f5c306ff2b</t>
-  </si>
-  <si>
-    <t>relationship--ca78e3f5-edc4-46ff-86f6-89fb3c35288e</t>
-  </si>
-  <si>
-    <t>relationship--7752b90a-82a7-4e9c-b827-c26959415840</t>
-  </si>
-  <si>
-    <t>relationship--ffa36b52-804f-4e4a-a467-aff1ccaeb8b2</t>
-  </si>
-  <si>
-    <t>relationship--b1dd4bc9-7ef5-4050-b0f8-f5fb9c2019e0</t>
-  </si>
-  <si>
-    <t>relationship--2ee3efa5-74c8-4255-94b2-ce1b5ff81142</t>
-  </si>
-  <si>
-    <t>relationship--fe6278dd-37ff-4ae0-aaa2-15e5deec1bad</t>
-  </si>
-  <si>
-    <t>relationship--e6bf0e77-c31d-42b9-8cd6-f52b8fb3d2db</t>
-  </si>
-  <si>
-    <t>relationship--5e841f9c-b382-44fc-b069-31d7ed86d613</t>
-  </si>
-  <si>
-    <t>relationship--26b24ed3-bab4-48b5-af20-473d37df73a1</t>
-  </si>
-  <si>
-    <t>relationship--5dc7f800-2702-41e3-a999-ec18d12bdb0b</t>
-  </si>
-  <si>
-    <t>relationship--bb205bd8-3105-49e8-a966-8a5a4b80ce4b</t>
-  </si>
-  <si>
-    <t>relationship--066eb730-edbb-4eb7-be95-30ee7a67bbad</t>
-  </si>
-  <si>
-    <t>relationship--997ffb23-24f9-4bf6-ae61-1773c568c2d6</t>
-  </si>
-  <si>
-    <t>relationship--90927691-a826-45b1-aa61-4b0253556a02</t>
-  </si>
-  <si>
-    <t>relationship--da285461-ab09-48e4-bac7-6e4b7f5c2e1d</t>
-  </si>
-  <si>
-    <t>relationship--ae5ce0c4-d70d-40a0-891a-6472f31c7fa3</t>
-  </si>
-  <si>
-    <t>relationship--a16aa153-ab2d-49f9-96bf-61989c058b71</t>
-  </si>
-  <si>
-    <t>relationship--64487f17-db95-46e3-adff-3d3d2629772b</t>
-  </si>
-  <si>
-    <t>relationship--5c1bd692-3e7e-43aa-907a-435464271bc7</t>
-  </si>
-  <si>
-    <t>relationship--c2595a81-92d7-404b-ad9f-1b290af8866b</t>
-  </si>
-  <si>
-    <t>relationship--bd9c2824-ba1b-4fc6-b7be-815d4341d76c</t>
-  </si>
-  <si>
-    <t>relationship--13d8371a-bd47-4e2d-9833-64256ea7236e</t>
-  </si>
-  <si>
-    <t>relationship--d4f3bacb-f6e3-44e1-948e-fb11cc9afcdb</t>
-  </si>
-  <si>
-    <t>relationship--c561afa2-ce06-447a-8c4c-be71f21480c7</t>
-  </si>
-  <si>
-    <t>relationship--28cf8d5f-6d6f-453c-a201-317c04dee34d</t>
-  </si>
-  <si>
-    <t>relationship--769341f9-ee3b-42c3-b2ab-3398313428ec</t>
-  </si>
-  <si>
-    <t>relationship--2d753309-a85e-415c-a222-0301ec963f66</t>
-  </si>
-  <si>
-    <t>relationship--cc65d3dc-fb26-4e54-b54f-9d2c812c7cff</t>
-  </si>
-  <si>
-    <t>relationship--1eb1a282-23cc-43ab-b857-0d11d636e2a5</t>
-  </si>
-  <si>
-    <t>relationship--2bbbd285-77d1-4fd6-91c9-5d028c72f098</t>
-  </si>
-  <si>
-    <t>relationship--a1492f55-f3d8-429c-8ec4-384c57f58821</t>
-  </si>
-  <si>
-    <t>relationship--c63d2783-b3b7-47a3-9be9-d1677fa6945c</t>
-  </si>
-  <si>
-    <t>relationship--0b4d5b99-7039-4ab0-a99d-094ceaa1cd91</t>
-  </si>
-  <si>
-    <t>relationship--c3b294ff-66a0-4e31-a6b4-12d7a648a472</t>
-  </si>
-  <si>
-    <t>relationship--4eef5b22-d5ab-478f-8fcc-018f34f58e25</t>
-  </si>
-  <si>
-    <t>relationship--40042475-a205-4c1b-97e7-7c76c7865cbb</t>
-  </si>
-  <si>
-    <t>relationship--c67c90d0-effd-43e6-84de-05d750e98fe0</t>
-  </si>
-  <si>
-    <t>relationship--b12bd32f-d8c0-47c2-a1f0-cfddf25000c1</t>
-  </si>
-  <si>
-    <t>relationship--ba3fd383-b77d-4c48-9eb4-506a4833f1f2</t>
-  </si>
-  <si>
-    <t>relationship--15c27931-d7a9-4b5c-9058-bf081b37a8a3</t>
-  </si>
-  <si>
-    <t>relationship--1ad4791e-261a-4512-8123-89fc26e12b25</t>
-  </si>
-  <si>
-    <t>relationship--17997574-a161-4f2d-81d7-a8ffc9343dcf</t>
-  </si>
-  <si>
-    <t>relationship--39edf99e-7601-4a47-ad39-8e3d080fba7d</t>
-  </si>
-  <si>
-    <t>relationship--5173a2ce-e76a-4bb7-8685-3d30657cf7bb</t>
-  </si>
-  <si>
-    <t>relationship--36eb1714-2670-44e7-b9cb-96d0eb426b72</t>
-  </si>
-  <si>
-    <t>relationship--3d4c10fe-6943-48fd-b897-e90c3158744f</t>
-  </si>
-  <si>
-    <t>relationship--78c6f40f-c64c-4681-9061-63acf50a4bd6</t>
-  </si>
-  <si>
-    <t>relationship--b24d5aea-09e9-41bc-85a0-240a7b69a591</t>
-  </si>
-  <si>
-    <t>relationship--2bb139e8-1edc-4db2-b8c1-482176975ad4</t>
-  </si>
-  <si>
-    <t>relationship--ca8c42ef-8ef1-4ccb-8237-f9206f58f733</t>
-  </si>
-  <si>
-    <t>relationship--fd974d03-b680-4744-85c5-8e1ac2ce7c31</t>
-  </si>
-  <si>
-    <t>relationship--d88929a7-dc71-49ce-b9a1-bfedc801e8a8</t>
+    <t>relationship--579007f9-28a0-48e4-9185-c1e2d0b17ae3</t>
+  </si>
+  <si>
+    <t>relationship--cbe422cd-9fe9-4132-84f1-96be195ac993</t>
+  </si>
+  <si>
+    <t>relationship--5667cd4d-ca36-46d4-a17a-9d54006f1f5b</t>
+  </si>
+  <si>
+    <t>relationship--f281ae66-2d30-4085-b524-194af26c8459</t>
+  </si>
+  <si>
+    <t>relationship--36dcc214-651c-4657-acdf-5a62bef3ec0f</t>
+  </si>
+  <si>
+    <t>relationship--13a0e8d5-cd26-41ad-989a-1ffb8a550016</t>
+  </si>
+  <si>
+    <t>relationship--2bf4f3c6-637c-41b5-b365-73fd8f1340fa</t>
+  </si>
+  <si>
+    <t>relationship--bc31601d-18b2-4aed-90e3-208e5d49b78a</t>
+  </si>
+  <si>
+    <t>relationship--9807e38f-6ad6-447a-ae60-a64f9f343370</t>
+  </si>
+  <si>
+    <t>relationship--8a514380-8a2d-4c81-9db0-93a248171fba</t>
+  </si>
+  <si>
+    <t>relationship--b2f79bb7-979e-4ea3-86ef-eebc886aaa6b</t>
+  </si>
+  <si>
+    <t>relationship--545039f1-fa7a-4f32-9e79-7584f9399a5a</t>
+  </si>
+  <si>
+    <t>relationship--bb7c01ba-b6d1-40f6-a6d0-3e4b0cdddbef</t>
+  </si>
+  <si>
+    <t>relationship--974dffe7-2fe4-45f0-bf21-5df9f49100d0</t>
+  </si>
+  <si>
+    <t>relationship--590d5394-a905-4b57-8ea4-38e941c36875</t>
+  </si>
+  <si>
+    <t>relationship--c76b1d3c-c2e5-45d1-a417-d580c9825105</t>
+  </si>
+  <si>
+    <t>relationship--3037be7e-2186-4f85-beb4-bfc477eef251</t>
+  </si>
+  <si>
+    <t>relationship--ceeb598f-298b-4fdd-aa06-06c66f75cb93</t>
+  </si>
+  <si>
+    <t>relationship--6e2eee1c-1d01-4aa2-b34b-1ce62806dae9</t>
+  </si>
+  <si>
+    <t>relationship--c347dbcd-3768-45bb-85b5-ee75069b5731</t>
+  </si>
+  <si>
+    <t>relationship--eacab9fe-e01f-49fc-a53a-bdbdacec0a5d</t>
+  </si>
+  <si>
+    <t>relationship--0a00c5e3-fc83-48cd-8ddb-09ef4bbedfe0</t>
+  </si>
+  <si>
+    <t>relationship--0ee2ab17-a17d-488c-a01f-4cc29fa47acc</t>
+  </si>
+  <si>
+    <t>relationship--72e5cce2-bbff-48a2-b689-589ad7bde2fb</t>
+  </si>
+  <si>
+    <t>relationship--d3b4874f-ecb2-4381-9b8d-7927f05858d0</t>
+  </si>
+  <si>
+    <t>relationship--ca5afe22-bac2-4077-b67b-337995a60f43</t>
+  </si>
+  <si>
+    <t>relationship--77b67bf7-363d-4a9d-9f8b-9742086db6c6</t>
+  </si>
+  <si>
+    <t>relationship--63fe6e4d-581d-431b-8116-9e090e8a745c</t>
+  </si>
+  <si>
+    <t>relationship--94908fc4-bb5b-4683-805a-dbd8dc5e4999</t>
+  </si>
+  <si>
+    <t>relationship--d9fe5d2b-3357-4241-901b-39166dd33941</t>
+  </si>
+  <si>
+    <t>relationship--035ae41a-01e9-4155-9738-28abee46fa01</t>
+  </si>
+  <si>
+    <t>relationship--22ee9109-c21a-4017-a011-8847cb95d8af</t>
+  </si>
+  <si>
+    <t>relationship--de151bf0-ed08-4e2c-924e-d1e4fcd66047</t>
+  </si>
+  <si>
+    <t>relationship--1b8dfcb3-509e-4b06-a3eb-15219d4b259f</t>
+  </si>
+  <si>
+    <t>relationship--d9c1c0f7-5386-45dd-90f5-cdcf145f2c40</t>
+  </si>
+  <si>
+    <t>relationship--a7369f3d-8b80-46e3-bb86-52408e4d0a70</t>
+  </si>
+  <si>
+    <t>relationship--924eeef7-4ac6-4094-a9d7-36befeac2c17</t>
+  </si>
+  <si>
+    <t>relationship--4135c852-a440-4feb-a662-d639156221ad</t>
+  </si>
+  <si>
+    <t>relationship--b50f9c63-ba9d-4a49-a4f7-45d9b53d8ef0</t>
+  </si>
+  <si>
+    <t>relationship--02f7b89f-53fa-478f-a1b5-7b61d8dcbff2</t>
+  </si>
+  <si>
+    <t>relationship--64360548-9a83-41f8-90e4-d73d3eb2c33a</t>
+  </si>
+  <si>
+    <t>relationship--8283b0e0-32c7-4708-9057-d42e6598176b</t>
+  </si>
+  <si>
+    <t>relationship--c1c921d9-699e-4928-8506-67dcd2061170</t>
+  </si>
+  <si>
+    <t>relationship--f2726f56-5487-4b4f-af8a-7031b19d1d76</t>
+  </si>
+  <si>
+    <t>relationship--d84105e6-4a04-4cf4-8a2c-c4a12e5dea08</t>
+  </si>
+  <si>
+    <t>relationship--3b452af0-3666-4c28-974e-a4fb53bbf295</t>
+  </si>
+  <si>
+    <t>relationship--f8ab7e5a-e300-48c9-b77c-8e67a4d7df27</t>
+  </si>
+  <si>
+    <t>relationship--40666857-41f2-4d46-bf70-47aa0c34dcc7</t>
+  </si>
+  <si>
+    <t>relationship--771548ba-7416-4cde-95d1-c788b08aaa71</t>
+  </si>
+  <si>
+    <t>relationship--779d583e-d222-4b26-956a-1e19ac4b77e2</t>
+  </si>
+  <si>
+    <t>relationship--d82e2525-0fdd-49cb-b3f1-1f2efa99ee08</t>
+  </si>
+  <si>
+    <t>relationship--31777070-381d-45d3-b313-00646e092c07</t>
+  </si>
+  <si>
+    <t>relationship--0f4de468-fd2f-4285-9db2-740ef8555069</t>
+  </si>
+  <si>
+    <t>relationship--24ad6afb-6426-413a-a29f-38668ad6ff90</t>
+  </si>
+  <si>
+    <t>relationship--946d5ae9-8056-4e22-9cd4-417de7f38d82</t>
+  </si>
+  <si>
+    <t>relationship--2a1f9d54-b16b-46ad-a923-604adfe79e1e</t>
+  </si>
+  <si>
+    <t>relationship--9a57978d-fe99-4297-8eb2-9746f0966990</t>
+  </si>
+  <si>
+    <t>relationship--366127f5-ecfd-431d-8baa-60078e576cef</t>
+  </si>
+  <si>
+    <t>relationship--835e8e03-39f2-4a00-a970-4f85d13ecae3</t>
+  </si>
+  <si>
+    <t>relationship--8a4a0c57-9338-42e3-8d0f-f04cc7e4970f</t>
+  </si>
+  <si>
+    <t>relationship--13eee957-a48f-466d-833c-b05db7b68537</t>
+  </si>
+  <si>
+    <t>relationship--5c8531a1-d41b-4b0b-8a4e-dfae8afcfa13</t>
+  </si>
+  <si>
+    <t>relationship--823a5587-50a0-40bc-9bde-70e3c2182300</t>
+  </si>
+  <si>
+    <t>relationship--293ad61a-8091-43f2-9fdc-e1adb4c75bc9</t>
+  </si>
+  <si>
+    <t>relationship--08e3ea95-b7f8-4937-b29c-4a1672614f9c</t>
+  </si>
+  <si>
+    <t>relationship--49edb497-7c42-44fc-bb53-870ca69c42d0</t>
+  </si>
+  <si>
+    <t>relationship--2051eeb2-4f36-497b-b503-5da4e20d78a0</t>
+  </si>
+  <si>
+    <t>relationship--30d0c38d-f5e6-4c94-a312-bb0202c53235</t>
+  </si>
+  <si>
+    <t>relationship--a372bff6-e803-4af7-ba39-d0996ef7de00</t>
+  </si>
+  <si>
+    <t>relationship--16bf97f2-e1ac-451b-93db-61a5ca25cfa5</t>
+  </si>
+  <si>
+    <t>relationship--b4456713-6f1a-423c-9417-3fd9318794b5</t>
+  </si>
+  <si>
+    <t>relationship--7368aac6-f55d-45e8-bcd2-0150164725c0</t>
+  </si>
+  <si>
+    <t>relationship--8fa92939-0395-495a-a2cc-25920befafd6</t>
+  </si>
+  <si>
+    <t>relationship--7f8c1d68-a431-4053-a40c-08397553d9f8</t>
+  </si>
+  <si>
+    <t>relationship--fe830b39-4d93-4844-92e9-630d112bb1cc</t>
+  </si>
+  <si>
+    <t>relationship--ba30d8c0-0a8a-43e3-884e-9ebc68c8b18b</t>
+  </si>
+  <si>
+    <t>relationship--a9ada7e1-57e6-4aba-95c7-33f97a61382d</t>
+  </si>
+  <si>
+    <t>relationship--4e5af6b1-7d02-4647-843f-917014cbfee5</t>
+  </si>
+  <si>
+    <t>relationship--a41e87ab-e2f0-472e-8b8b-b96ee2a8dbfb</t>
+  </si>
+  <si>
+    <t>relationship--7a731bc9-9092-4523-8921-dd7a3d94426f</t>
+  </si>
+  <si>
+    <t>relationship--b2beb81b-3b22-4e86-9770-beb7bcb9e418</t>
+  </si>
+  <si>
+    <t>relationship--eba89ba0-a62f-4d7a-aac2-58639ab713f8</t>
+  </si>
+  <si>
+    <t>relationship--cd2cd507-1be3-4d9a-b9fc-fcbddeac37be</t>
+  </si>
+  <si>
+    <t>relationship--0cfbf64b-f9a8-4961-bdcc-328c9364a656</t>
+  </si>
+  <si>
+    <t>relationship--3db40fe1-6e0d-4323-8da9-f0359cfa8be7</t>
+  </si>
+  <si>
+    <t>relationship--077d87d9-6da7-4b46-9cfc-4c84e7f788af</t>
+  </si>
+  <si>
+    <t>relationship--86e9c863-5ae5-46bf-b0e4-b02eaa185bd7</t>
+  </si>
+  <si>
+    <t>relationship--434ffa6e-8e3f-42bf-8887-3b685da7afe2</t>
+  </si>
+  <si>
+    <t>relationship--61560840-331e-4982-ab6f-90edf192c51f</t>
+  </si>
+  <si>
+    <t>relationship--5ed32bcc-ffac-41fb-ade7-6baf29882120</t>
+  </si>
+  <si>
+    <t>relationship--abce58d8-6877-4dcb-a877-9e213452f4b6</t>
+  </si>
+  <si>
+    <t>relationship--0b3c0a27-bbc5-4005-ac5d-bb05a255a1fd</t>
+  </si>
+  <si>
+    <t>relationship--9f3989ee-e8dd-48ba-a582-6a1fb2c277cf</t>
+  </si>
+  <si>
+    <t>relationship--5f947b73-c283-438a-b661-e922ef128815</t>
+  </si>
+  <si>
+    <t>relationship--f2028f92-96ba-481d-a719-e43200be30eb</t>
+  </si>
+  <si>
+    <t>relationship--9b0772cb-acd9-4f8a-82b1-c429efd3c3fc</t>
+  </si>
+  <si>
+    <t>relationship--cf2a8f50-c042-4978-8ac9-040f681a0902</t>
+  </si>
+  <si>
+    <t>relationship--dd0249b1-41cf-49f2-8b39-909edba54fbb</t>
+  </si>
+  <si>
+    <t>relationship--0863f965-e8ec-4d07-86db-37554adca29b</t>
+  </si>
+  <si>
+    <t>relationship--e86d43ec-a735-4d99-ad60-b0135dbfb42f</t>
+  </si>
+  <si>
+    <t>relationship--fc6c0597-d0d4-4933-8519-4d7a7c7297f6</t>
+  </si>
+  <si>
+    <t>relationship--27d3b66b-60c5-4691-884a-af621f775026</t>
+  </si>
+  <si>
+    <t>relationship--653d9b5d-056b-4633-8ccb-46dd884fe269</t>
   </si>
   <si>
     <t>reference</t>
@@ -6238,6 +6238,9 @@
     <t>2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023</t>
   </si>
   <si>
+    <t>2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024</t>
+  </si>
+  <si>
     <t>APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK® 2025</t>
   </si>
   <si>
@@ -6253,9 +6256,18 @@
     <t>Історія України — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Андрусовское перемирие - Википедия 2026</t>
+  </si>
+  <si>
     <t>Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Батуринська трагедія — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011</t>
+  </si>
+  <si>
     <t>Война и наказание: Как Россия уничтожала Украину 2023</t>
   </si>
   <si>
@@ -6280,6 +6292,9 @@
     <t>ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011</t>
   </si>
   <si>
+    <t>Карательная психиатрия в России: назад в СССР? 2020</t>
+  </si>
+  <si>
     <t>Кенгирское восстание заключённых - Википедия 2026</t>
   </si>
   <si>
@@ -6307,6 +6322,9 @@
     <t>Мазепа 2007</t>
   </si>
   <si>
+    <t>Мазепа, Иван Степанович — Википедия 2026</t>
+  </si>
+  <si>
     <t>Малоросійське генерал-губернаторство — Вікіпедія 2026</t>
   </si>
   <si>
@@ -6379,13 +6397,61 @@
     <t>Чорносотенці — Вікіпедія 2026</t>
   </si>
   <si>
-    <t>Карательная психиатрия в России: назад в СССР? 2020</t>
+    <t>Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013</t>
+  </si>
+  <si>
+    <t>Україна й українці в постімперську добу (1917—1939) 2021</t>
+  </si>
+  <si>
+    <t>Російсько-українська війна (з 2014) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Московсько-українська війна (1658—1659) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Антикріпосницький рух в Україні (1789-1861) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Русско-турецкая война (1877—1878) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1) 1998</t>
+  </si>
+  <si>
+    <t>Русско-турецкая война (1768—1774) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Перепис населення Російської імперії (1897) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Ліквідація Запорозької Січі (1775) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Московські статті (1665) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Листопадове повстання (1830—1831) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Польское восстание (1863—1864) — Википедия 2026</t>
   </si>
   <si>
     <t>Анексія Кримського ханства — Вікіпедія 2026</t>
   </si>
   <si>
-    <t>В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1928 ГГ . 2011</t>
+    <t>Переяславські статті (1659) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026</t>
+  </si>
+  <si>
+    <t>Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Аннексия Бессарабии Российской империей (1812) — Википедия 2026</t>
   </si>
   <si>
     <t>MITRE ATT&amp;CK®. (2023). 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
@@ -6394,6 +6460,9 @@
     <t>MITRE ATT&amp;CK®. (2023). 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
+    <t>MITRE ATT&amp;CK®. (2024). 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
+  </si>
+  <si>
     <t>MITRE ATT&amp;CK®. (2025). APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
@@ -6409,9 +6478,18 @@
     <t>Вікіпедія. (2026). Історія України — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Андрусовское перемирие - Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Анексія Київської митрополії Московським патріархатом — Вікіпедія.</t>
   </si>
   <si>
+    <t>Вікіпедія. (2026). Батуринська трагедія — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Виктор Дённингхаус. (2011). В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ ..</t>
+  </si>
+  <si>
     <t>Михаил Зыгарь. (2023). Война и наказание: Как Россия уничтожала Украину.</t>
   </si>
   <si>
@@ -6436,6 +6514,9 @@
     <t>Татьяна Таирова-Яковлева. (2011). ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА».</t>
   </si>
   <si>
+    <t>Riddle Russia. (2020). Карательная психиатрия в России: назад в СССР?.</t>
+  </si>
+  <si>
     <t>Википедия. (2026). Кенгирское восстание заключённых - Википедия.</t>
   </si>
   <si>
@@ -6463,6 +6544,9 @@
     <t>Татьяна Таирова-Яковлева. (2007). Мазепа.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Мазепа, Иван Степанович — Википедия.</t>
+  </si>
+  <si>
     <t>Вікіпедія. (2026). Малоросійське генерал-губернаторство — Вікіпедія.</t>
   </si>
   <si>
@@ -6535,13 +6619,61 @@
     <t>Википедия. (2026). Чорносотенці — Вікіпедія.</t>
   </si>
   <si>
-    <t>Riddle Russia. (2020). Карательная психиатрия в России: назад в СССР?.</t>
+    <t>Лариса Якубова, большая команда. (2013). Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.).</t>
+  </si>
+  <si>
+    <t>Єфіменко Г. Г., Кульчицький С. В., Пиріг Р. Я., Скальський В. В., Якубова Л. Д.. (2021). Україна й українці в постімперську добу (1917—1939).</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Російсько-українська війна (з 2014) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Московсько-українська війна (1658—1659) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Антикріпосницький рух в Україні (1789-1861) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Русско-турецкая война (1877—1878) — Википедия.</t>
+  </si>
+  <si>
+    <t>Лариса Якубова. (1998). Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1).</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Русско-турецкая война (1768—1774) — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Перепис населення Російської імперії (1897) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Ліквідація Запорозької Січі (1775) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Московські статті (1665) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Листопадове повстання (1830—1831) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Польское восстание (1863—1864) — Википедия.</t>
   </si>
   <si>
     <t>Википедия. (2026). Анексія Кримського ханства — Вікіпедія.</t>
   </si>
   <si>
-    <t>Виктор Дённингхаус. (2011). В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1928 ГГ ..</t>
+    <t>Википедия. (2026). Переяславські статті (1659) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Евгений Захаров, Харьковская правозащитная группа. (2026). ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987).</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Аннексия Бессарабии Российской империей (1812) — Википедия.</t>
   </si>
   <si>
     <t>https://attack.mitre.org/campaigns/C0028/</t>
@@ -6550,6 +6682,9 @@
     <t>https://attack.mitre.org/campaigns/C0025/</t>
   </si>
   <si>
+    <t>https://attack.mitre.org/campaigns/C0034/</t>
+  </si>
+  <si>
     <t>https://attack.mitre.org/campaigns/C0051/</t>
   </si>
   <si>
@@ -6565,9 +6700,15 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2586%25D1%2581%25D1%2582%25D0%25BE%25D1%2580%25D1%2596%25D1%258F_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B4%25D1%2580%25D1%2583%25D1%2581%25D0%25BE%25D0%25B2%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BC%25D0%25B8%25D1%2580%25D0%25B8%25D0%25B5</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D0%25B8%25D1%2597%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25BC%25D0%25B8%25D1%2582%25D1%2580%25D0%25BE%25D0%25BF%25D0%25BE%25D0%25BB%25D1%2596%25D1%2597_%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D0%25B8%25D0%25BC_%25D0%25BF%25D0%25B0%25D1%2582%25D1%2580%25D1%2596%25D0%25B0%25D1%2580%25D1%2585%25D0%25B0%25D1%2582%25D0%25BE%25D0%25BC</t>
   </si>
   <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2591%25D0%25B0%25D1%2582%25D1%2583%25D1%2580%25D0%25B8%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D1%2582%25D1%2580%25D0%25B0%25D0%25B3%25D0%25B5%25D0%25B4%25D1%2596%25D1%258F</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2592%25D1%2581%25D0%25B5%25D1%2581%25D0%25BE%25D1%258E%25D0%25B7%25D0%25BD%25D0%25B8%25D0%25B9_%25D1%2580%25D0%25B5%25D1%2584%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BD%25D0%25B4%25D1%2583%25D0%25BC_%25D0%25BF%25D1%2580%25D0%25BE_%25D0%25B7%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A1%25D0%25A0%25D0%25A1%25D0%25A0</t>
   </si>
   <si>
@@ -6586,6 +6727,9 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25A1%25D1%2596%25D1%2587</t>
   </si>
   <si>
+    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+  </si>
+  <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%259A%25D0%25B5%25D0%25BD%25D0%25B3%25D0%25B8%25D1%2580%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%25D0%25B7%25D0%25B0%25D0%25BA%25D0%25BB%25D1%258E%25D1%2587%25D1%2591%25D0%25BD%25D0%25BD%25D1%258B%25D1%2585</t>
   </si>
   <si>
@@ -6610,6 +6754,9 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25B0%25D0%25B2%25D1%2582%25D0%25BE%25D0%25BD%25D0%25BE%25D0%25BC%25D1%2596%25D1%2597_%25D0%2593%25D0%25B5%25D1%2582%25D1%258C%25D0%25BC%25D0%25B0%25D0%25BD%25D1%2589%25D0%25B8%25D0%25BD%25D0%25B8</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25B7%25D0%25B5%25D0%25BF%25D0%25B0%2C_%25D0%2598%25D0%25B2%25D0%25B0%25D0%25BD_%25D0%25A1%25D1%2582%25D0%25B5%25D0%25BF%25D0%25B0%25D0%25BD%25D0%25BE%25D0%25B2%25D0%25B8%25D1%2587</t>
+  </si>
+  <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25B0%25D0%25BB%25D0%25BE%25D1%2580%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25B5_%25D0%25B3%25D0%25B5%25D0%25BD%25D0%25B5%25D1%2580%25D0%25B0%25D0%25BB-%25D0%25B3%25D1%2583%25D0%25B1%25D0%25B5%25D1%2580%25D0%25BD%25D0%25B0%25D1%2582%25D0%25BE%25D1%2580%25D1%2581%25D1%2582%25D0%25B2%25D0%25BE</t>
   </si>
   <si>
@@ -6679,10 +6826,58 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
   </si>
   <si>
-    <t>https://ridl.io/ru/karatelnaja-psihiatrija-v-rossii-nazad-v-sssr/</t>
+    <t>http://resource.history.org.ua/item/0016476</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%28%25D0%25B7_2014%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%281658%E2%80%941659%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D1%2582%25D0%25B8%25D0%25BA%25D1%2580%25D1%2596%25D0%25BF%25D0%25BE%25D1%2581%25D0%25BD%25D0%25B8%25D1%2586%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25B2_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281789-1861%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281877%25E2%2580%25941878%29</t>
+  </si>
+  <si>
+    <t>http://resource.history.org.ua/publ/journal_1998_6_22</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281768%25E2%2580%25941774%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BF%25D0%25B8%25D1%2581_%25D0%25BD%25D0%25B0%25D1%2581%25D0%25B5%25D0%25BB%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D1%2596%25D1%2597_%281897%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25A1%25D1%2596%25D1%2587%25D1%2596_%281775%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596_%281665%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D0%25B8%25D1%2581%25D1%2582%25D0%25BE%25D0%25BF%25D0%25B0%25D0%25B4%25D0%25BE%25D0%25B2%25D0%25B5_%25D0%25BF%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%281830%25E2%2580%25941831%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%281863%25E2%2580%25941864%29</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D1%2580%25D0%25B8%25D0%25BC%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2585%25D0%25B0%25D0%25BD%25D1%2581%25D1%2582%25D0%25B2%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96_%281659%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%2582%25D0%25B2%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281699%29</t>
+  </si>
+  <si>
+    <t>https://museum.khpg.org/ru/1628664422</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D1%2585%25D1%2596%25D0%25B4_%25D0%259F%25D0%25B8%25D0%25BB%25D0%25B8%25D0%25BF%25D0%25B0_%25D0%259E%25D1%2580%25D0%25BB%25D0%25B8%25D0%25BA%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2583_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2583_%281711%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D0%25B8%25D1%258F_%25D0%2591%25D0%25B5%25D1%2581%25D1%2581%25D0%25B0%25D1%2580%25D0%25B0%25D0%25B1%25D0%25B8%25D0%25B8_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D0%25B8%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B8%25D0%25B5%25D0%25B9_%281812%29</t>
   </si>
 </sst>
 </file>
@@ -37533,7 +37728,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -37552,10 +37747,10 @@
         <v>2070</v>
       </c>
       <c r="B2" t="s">
-        <v>2122</v>
+        <v>2144</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2174</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -37563,10 +37758,10 @@
         <v>2071</v>
       </c>
       <c r="B3" t="s">
-        <v>2123</v>
+        <v>2145</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2175</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -37574,10 +37769,10 @@
         <v>2072</v>
       </c>
       <c r="B4" t="s">
-        <v>2124</v>
+        <v>2146</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2176</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -37585,10 +37780,10 @@
         <v>2073</v>
       </c>
       <c r="B5" t="s">
-        <v>2125</v>
+        <v>2147</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2177</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -37596,10 +37791,10 @@
         <v>2074</v>
       </c>
       <c r="B6" t="s">
-        <v>2126</v>
+        <v>2148</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2178</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -37607,10 +37802,10 @@
         <v>2075</v>
       </c>
       <c r="B7" t="s">
-        <v>2127</v>
+        <v>2149</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2179</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -37618,10 +37813,10 @@
         <v>2076</v>
       </c>
       <c r="B8" t="s">
-        <v>2128</v>
+        <v>2150</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2180</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -37629,10 +37824,10 @@
         <v>2077</v>
       </c>
       <c r="B9" t="s">
-        <v>2129</v>
+        <v>2151</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2181</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -37640,7 +37835,10 @@
         <v>2078</v>
       </c>
       <c r="B10" t="s">
-        <v>2130</v>
+        <v>2152</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2226</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -37648,10 +37846,10 @@
         <v>2079</v>
       </c>
       <c r="B11" t="s">
-        <v>2131</v>
+        <v>2153</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2182</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -37659,10 +37857,10 @@
         <v>2080</v>
       </c>
       <c r="B12" t="s">
-        <v>2132</v>
+        <v>2154</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2183</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -37670,10 +37868,7 @@
         <v>2081</v>
       </c>
       <c r="B13" t="s">
-        <v>2133</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>2184</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -37681,10 +37876,7 @@
         <v>2082</v>
       </c>
       <c r="B14" t="s">
-        <v>2134</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2185</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -37692,10 +37884,10 @@
         <v>2083</v>
       </c>
       <c r="B15" t="s">
-        <v>2135</v>
+        <v>2157</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2186</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -37703,10 +37895,10 @@
         <v>2084</v>
       </c>
       <c r="B16" t="s">
-        <v>2136</v>
+        <v>2158</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2187</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -37714,7 +37906,10 @@
         <v>2085</v>
       </c>
       <c r="B17" t="s">
-        <v>2137</v>
+        <v>2159</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2231</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -37722,10 +37917,10 @@
         <v>2086</v>
       </c>
       <c r="B18" t="s">
-        <v>2138</v>
+        <v>2160</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2188</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -37733,10 +37928,10 @@
         <v>2087</v>
       </c>
       <c r="B19" t="s">
-        <v>2139</v>
+        <v>2161</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2189</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -37744,10 +37939,10 @@
         <v>2088</v>
       </c>
       <c r="B20" t="s">
-        <v>2140</v>
+        <v>2162</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2190</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -37755,10 +37950,7 @@
         <v>2089</v>
       </c>
       <c r="B21" t="s">
-        <v>2141</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2191</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -37766,10 +37958,10 @@
         <v>2090</v>
       </c>
       <c r="B22" t="s">
-        <v>2142</v>
+        <v>2164</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2192</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -37777,10 +37969,10 @@
         <v>2091</v>
       </c>
       <c r="B23" t="s">
-        <v>2143</v>
+        <v>2165</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2193</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -37788,10 +37980,10 @@
         <v>2092</v>
       </c>
       <c r="B24" t="s">
-        <v>2144</v>
+        <v>2166</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2194</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -37799,10 +37991,10 @@
         <v>2093</v>
       </c>
       <c r="B25" t="s">
-        <v>2145</v>
+        <v>2167</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2195</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -37810,7 +38002,10 @@
         <v>2094</v>
       </c>
       <c r="B26" t="s">
-        <v>2146</v>
+        <v>2168</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2239</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -37818,10 +38013,10 @@
         <v>2095</v>
       </c>
       <c r="B27" t="s">
-        <v>2147</v>
+        <v>2169</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2196</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -37829,10 +38024,10 @@
         <v>2096</v>
       </c>
       <c r="B28" t="s">
-        <v>2148</v>
+        <v>2170</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2197</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -37840,10 +38035,10 @@
         <v>2097</v>
       </c>
       <c r="B29" t="s">
-        <v>2149</v>
+        <v>2171</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2198</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -37851,10 +38046,10 @@
         <v>2098</v>
       </c>
       <c r="B30" t="s">
-        <v>2150</v>
+        <v>2172</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2199</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -37862,10 +38057,7 @@
         <v>2099</v>
       </c>
       <c r="B31" t="s">
-        <v>2151</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>2200</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -37873,10 +38065,10 @@
         <v>2100</v>
       </c>
       <c r="B32" t="s">
-        <v>2152</v>
+        <v>2174</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2201</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -37884,10 +38076,10 @@
         <v>2101</v>
       </c>
       <c r="B33" t="s">
-        <v>2153</v>
+        <v>2175</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2202</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -37895,10 +38087,10 @@
         <v>2102</v>
       </c>
       <c r="B34" t="s">
-        <v>2154</v>
+        <v>2176</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2203</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -37906,7 +38098,10 @@
         <v>2103</v>
       </c>
       <c r="B35" t="s">
-        <v>2155</v>
+        <v>2177</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2247</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -37914,10 +38109,10 @@
         <v>2104</v>
       </c>
       <c r="B36" t="s">
-        <v>2156</v>
+        <v>2178</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2204</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -37925,10 +38120,10 @@
         <v>2105</v>
       </c>
       <c r="B37" t="s">
-        <v>2157</v>
+        <v>2179</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2205</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -37936,10 +38131,10 @@
         <v>2106</v>
       </c>
       <c r="B38" t="s">
-        <v>2158</v>
+        <v>2180</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2206</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -37947,10 +38142,10 @@
         <v>2107</v>
       </c>
       <c r="B39" t="s">
-        <v>2159</v>
+        <v>2181</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2207</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -37958,10 +38153,10 @@
         <v>2108</v>
       </c>
       <c r="B40" t="s">
-        <v>2160</v>
+        <v>2182</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2208</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -37969,10 +38164,7 @@
         <v>2109</v>
       </c>
       <c r="B41" t="s">
-        <v>2161</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>2209</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -37980,10 +38172,10 @@
         <v>2110</v>
       </c>
       <c r="B42" t="s">
-        <v>2162</v>
+        <v>2184</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2210</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -37991,10 +38183,10 @@
         <v>2111</v>
       </c>
       <c r="B43" t="s">
-        <v>2163</v>
+        <v>2185</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2211</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -38002,10 +38194,10 @@
         <v>2112</v>
       </c>
       <c r="B44" t="s">
-        <v>2164</v>
+        <v>2186</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2212</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -38013,10 +38205,10 @@
         <v>2113</v>
       </c>
       <c r="B45" t="s">
-        <v>2165</v>
+        <v>2187</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2213</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -38024,10 +38216,10 @@
         <v>2114</v>
       </c>
       <c r="B46" t="s">
-        <v>2166</v>
+        <v>2188</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2214</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -38035,10 +38227,10 @@
         <v>2115</v>
       </c>
       <c r="B47" t="s">
-        <v>2167</v>
+        <v>2189</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2215</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -38046,10 +38238,10 @@
         <v>2116</v>
       </c>
       <c r="B48" t="s">
-        <v>2168</v>
+        <v>2190</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2216</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -38057,10 +38249,10 @@
         <v>2117</v>
       </c>
       <c r="B49" t="s">
-        <v>2169</v>
+        <v>2191</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2217</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -38068,295 +38260,295 @@
         <v>2118</v>
       </c>
       <c r="B50" t="s">
-        <v>2170</v>
+        <v>2192</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2218</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>2085</v>
+        <v>2119</v>
       </c>
       <c r="B51" t="s">
-        <v>2137</v>
+        <v>2193</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2262</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>2078</v>
+        <v>2120</v>
       </c>
       <c r="B52" t="s">
-        <v>2130</v>
+        <v>2194</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2263</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>2076</v>
+        <v>2121</v>
       </c>
       <c r="B53" t="s">
-        <v>2128</v>
+        <v>2195</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2180</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>2111</v>
+        <v>2122</v>
       </c>
       <c r="B54" t="s">
-        <v>2163</v>
+        <v>2196</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2211</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>2088</v>
+        <v>2123</v>
       </c>
       <c r="B55" t="s">
-        <v>2140</v>
+        <v>2197</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2190</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>2113</v>
+        <v>2124</v>
       </c>
       <c r="B56" t="s">
-        <v>2165</v>
+        <v>2198</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2213</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>2107</v>
+        <v>2125</v>
       </c>
       <c r="B57" t="s">
-        <v>2159</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>2109</v>
+        <v>2082</v>
       </c>
       <c r="B58" t="s">
-        <v>2161</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>2209</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>2103</v>
+        <v>2123</v>
       </c>
       <c r="B59" t="s">
-        <v>2155</v>
+        <v>2197</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2266</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>2094</v>
+        <v>2112</v>
       </c>
       <c r="B60" t="s">
-        <v>2146</v>
+        <v>2186</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2255</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>2106</v>
+        <v>2077</v>
       </c>
       <c r="B61" t="s">
-        <v>2158</v>
+        <v>2151</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>2206</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>2108</v>
+        <v>2126</v>
       </c>
       <c r="B62" t="s">
-        <v>2160</v>
+        <v>2200</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>2208</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>2115</v>
+        <v>2089</v>
       </c>
       <c r="B63" t="s">
-        <v>2167</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>2215</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>2080</v>
+        <v>2088</v>
       </c>
       <c r="B64" t="s">
-        <v>2132</v>
+        <v>2162</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>2183</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>2104</v>
+        <v>2113</v>
       </c>
       <c r="B65" t="s">
-        <v>2156</v>
+        <v>2187</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>2204</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2117</v>
+        <v>2109</v>
       </c>
       <c r="B66" t="s">
-        <v>2169</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>2217</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>2119</v>
+        <v>2093</v>
       </c>
       <c r="B67" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>2219</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>2084</v>
+        <v>2124</v>
       </c>
       <c r="B68" t="s">
-        <v>2136</v>
+        <v>2198</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>2187</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>2096</v>
+        <v>2107</v>
       </c>
       <c r="B69" t="s">
-        <v>2148</v>
+        <v>2181</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>2197</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>2112</v>
+        <v>2127</v>
       </c>
       <c r="B70" t="s">
-        <v>2164</v>
+        <v>2201</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>2212</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>2118</v>
+        <v>2098</v>
       </c>
       <c r="B71" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>2218</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B72" t="s">
-        <v>2139</v>
+        <v>2160</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>2189</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>2091</v>
+        <v>2084</v>
       </c>
       <c r="B73" t="s">
-        <v>2143</v>
+        <v>2158</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>2193</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>2089</v>
+        <v>2114</v>
       </c>
       <c r="B74" t="s">
-        <v>2141</v>
+        <v>2188</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>2191</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>2077</v>
+        <v>2128</v>
       </c>
       <c r="B75" t="s">
-        <v>2129</v>
+        <v>2202</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>2181</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>2093</v>
+        <v>2122</v>
       </c>
       <c r="B76" t="s">
-        <v>2145</v>
+        <v>2196</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>2195</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="B77" t="s">
-        <v>2134</v>
+        <v>2153</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>2185</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -38364,128 +38556,411 @@
         <v>2099</v>
       </c>
       <c r="B78" t="s">
-        <v>2151</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>2200</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>2098</v>
+        <v>2129</v>
       </c>
       <c r="B79" t="s">
-        <v>2150</v>
+        <v>2203</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>2199</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>2086</v>
+        <v>2100</v>
       </c>
       <c r="B80" t="s">
-        <v>2138</v>
+        <v>2174</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>2188</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>2101</v>
+        <v>2130</v>
       </c>
       <c r="B81" t="s">
-        <v>2153</v>
+        <v>2204</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>2202</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>2102</v>
+        <v>2131</v>
       </c>
       <c r="B82" t="s">
-        <v>2154</v>
+        <v>2205</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>2203</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>2092</v>
+        <v>2081</v>
       </c>
       <c r="B83" t="s">
-        <v>2144</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>2194</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>2095</v>
+        <v>2078</v>
       </c>
       <c r="B84" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>2196</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>2120</v>
+        <v>2092</v>
       </c>
       <c r="B85" t="s">
-        <v>2172</v>
+        <v>2166</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>2220</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>2116</v>
+        <v>2090</v>
       </c>
       <c r="B86" t="s">
-        <v>2168</v>
+        <v>2164</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>2216</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>2090</v>
+        <v>2117</v>
       </c>
       <c r="B87" t="s">
-        <v>2142</v>
+        <v>2191</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>2192</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>2100</v>
+        <v>2132</v>
       </c>
       <c r="B88" t="s">
-        <v>2152</v>
+        <v>2206</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>2201</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B97" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B102" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
         <v>2121</v>
       </c>
-      <c r="B89" t="s">
-        <v>2173</v>
+      <c r="B104" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B108" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>2285</v>
       </c>
     </row>
   </sheetData>
@@ -38498,77 +38973,101 @@
     <hyperlink ref="C7" r:id="rId6"/>
     <hyperlink ref="C8" r:id="rId7"/>
     <hyperlink ref="C9" r:id="rId8"/>
-    <hyperlink ref="C11" r:id="rId9"/>
-    <hyperlink ref="C12" r:id="rId10"/>
-    <hyperlink ref="C13" r:id="rId11"/>
-    <hyperlink ref="C14" r:id="rId12"/>
-    <hyperlink ref="C15" r:id="rId13"/>
-    <hyperlink ref="C16" r:id="rId14"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C15" r:id="rId12"/>
+    <hyperlink ref="C16" r:id="rId13"/>
+    <hyperlink ref="C17" r:id="rId14"/>
     <hyperlink ref="C18" r:id="rId15"/>
     <hyperlink ref="C19" r:id="rId16"/>
     <hyperlink ref="C20" r:id="rId17"/>
-    <hyperlink ref="C21" r:id="rId18"/>
-    <hyperlink ref="C22" r:id="rId19"/>
-    <hyperlink ref="C23" r:id="rId20"/>
-    <hyperlink ref="C24" r:id="rId21"/>
-    <hyperlink ref="C25" r:id="rId22"/>
+    <hyperlink ref="C22" r:id="rId18"/>
+    <hyperlink ref="C23" r:id="rId19"/>
+    <hyperlink ref="C24" r:id="rId20"/>
+    <hyperlink ref="C25" r:id="rId21"/>
+    <hyperlink ref="C26" r:id="rId22"/>
     <hyperlink ref="C27" r:id="rId23"/>
     <hyperlink ref="C28" r:id="rId24"/>
     <hyperlink ref="C29" r:id="rId25"/>
     <hyperlink ref="C30" r:id="rId26"/>
-    <hyperlink ref="C31" r:id="rId27"/>
-    <hyperlink ref="C32" r:id="rId28"/>
-    <hyperlink ref="C33" r:id="rId29"/>
-    <hyperlink ref="C34" r:id="rId30"/>
+    <hyperlink ref="C32" r:id="rId27"/>
+    <hyperlink ref="C33" r:id="rId28"/>
+    <hyperlink ref="C34" r:id="rId29"/>
+    <hyperlink ref="C35" r:id="rId30"/>
     <hyperlink ref="C36" r:id="rId31"/>
     <hyperlink ref="C37" r:id="rId32"/>
     <hyperlink ref="C38" r:id="rId33"/>
     <hyperlink ref="C39" r:id="rId34"/>
     <hyperlink ref="C40" r:id="rId35"/>
-    <hyperlink ref="C41" r:id="rId36"/>
-    <hyperlink ref="C42" r:id="rId37"/>
-    <hyperlink ref="C43" r:id="rId38"/>
-    <hyperlink ref="C44" r:id="rId39"/>
-    <hyperlink ref="C45" r:id="rId40"/>
-    <hyperlink ref="C46" r:id="rId41"/>
-    <hyperlink ref="C47" r:id="rId42"/>
-    <hyperlink ref="C48" r:id="rId43"/>
-    <hyperlink ref="C49" r:id="rId44"/>
-    <hyperlink ref="C50" r:id="rId45"/>
-    <hyperlink ref="C53" r:id="rId46"/>
-    <hyperlink ref="C54" r:id="rId47"/>
-    <hyperlink ref="C55" r:id="rId48"/>
-    <hyperlink ref="C56" r:id="rId49"/>
-    <hyperlink ref="C57" r:id="rId50"/>
-    <hyperlink ref="C58" r:id="rId51"/>
-    <hyperlink ref="C61" r:id="rId52"/>
-    <hyperlink ref="C62" r:id="rId53"/>
-    <hyperlink ref="C63" r:id="rId54"/>
+    <hyperlink ref="C42" r:id="rId36"/>
+    <hyperlink ref="C43" r:id="rId37"/>
+    <hyperlink ref="C44" r:id="rId38"/>
+    <hyperlink ref="C45" r:id="rId39"/>
+    <hyperlink ref="C46" r:id="rId40"/>
+    <hyperlink ref="C47" r:id="rId41"/>
+    <hyperlink ref="C48" r:id="rId42"/>
+    <hyperlink ref="C49" r:id="rId43"/>
+    <hyperlink ref="C50" r:id="rId44"/>
+    <hyperlink ref="C51" r:id="rId45"/>
+    <hyperlink ref="C52" r:id="rId46"/>
+    <hyperlink ref="C53" r:id="rId47"/>
+    <hyperlink ref="C54" r:id="rId48"/>
+    <hyperlink ref="C55" r:id="rId49"/>
+    <hyperlink ref="C56" r:id="rId50"/>
+    <hyperlink ref="C59" r:id="rId51"/>
+    <hyperlink ref="C60" r:id="rId52"/>
+    <hyperlink ref="C61" r:id="rId53"/>
+    <hyperlink ref="C62" r:id="rId54"/>
     <hyperlink ref="C64" r:id="rId55"/>
     <hyperlink ref="C65" r:id="rId56"/>
-    <hyperlink ref="C66" r:id="rId57"/>
-    <hyperlink ref="C67" r:id="rId58"/>
-    <hyperlink ref="C68" r:id="rId59"/>
-    <hyperlink ref="C69" r:id="rId60"/>
-    <hyperlink ref="C70" r:id="rId61"/>
-    <hyperlink ref="C71" r:id="rId62"/>
-    <hyperlink ref="C72" r:id="rId63"/>
-    <hyperlink ref="C73" r:id="rId64"/>
-    <hyperlink ref="C74" r:id="rId65"/>
-    <hyperlink ref="C75" r:id="rId66"/>
-    <hyperlink ref="C76" r:id="rId67"/>
-    <hyperlink ref="C77" r:id="rId68"/>
-    <hyperlink ref="C78" r:id="rId69"/>
-    <hyperlink ref="C79" r:id="rId70"/>
-    <hyperlink ref="C80" r:id="rId71"/>
-    <hyperlink ref="C81" r:id="rId72"/>
-    <hyperlink ref="C82" r:id="rId73"/>
-    <hyperlink ref="C83" r:id="rId74"/>
-    <hyperlink ref="C84" r:id="rId75"/>
-    <hyperlink ref="C85" r:id="rId76"/>
-    <hyperlink ref="C86" r:id="rId77"/>
-    <hyperlink ref="C87" r:id="rId78"/>
-    <hyperlink ref="C88" r:id="rId79"/>
+    <hyperlink ref="C67" r:id="rId57"/>
+    <hyperlink ref="C68" r:id="rId58"/>
+    <hyperlink ref="C69" r:id="rId59"/>
+    <hyperlink ref="C70" r:id="rId60"/>
+    <hyperlink ref="C71" r:id="rId61"/>
+    <hyperlink ref="C72" r:id="rId62"/>
+    <hyperlink ref="C73" r:id="rId63"/>
+    <hyperlink ref="C74" r:id="rId64"/>
+    <hyperlink ref="C75" r:id="rId65"/>
+    <hyperlink ref="C76" r:id="rId66"/>
+    <hyperlink ref="C77" r:id="rId67"/>
+    <hyperlink ref="C79" r:id="rId68"/>
+    <hyperlink ref="C80" r:id="rId69"/>
+    <hyperlink ref="C81" r:id="rId70"/>
+    <hyperlink ref="C82" r:id="rId71"/>
+    <hyperlink ref="C84" r:id="rId72"/>
+    <hyperlink ref="C85" r:id="rId73"/>
+    <hyperlink ref="C86" r:id="rId74"/>
+    <hyperlink ref="C87" r:id="rId75"/>
+    <hyperlink ref="C88" r:id="rId76"/>
+    <hyperlink ref="C89" r:id="rId77"/>
+    <hyperlink ref="C90" r:id="rId78"/>
+    <hyperlink ref="C91" r:id="rId79"/>
+    <hyperlink ref="C92" r:id="rId80"/>
+    <hyperlink ref="C93" r:id="rId81"/>
+    <hyperlink ref="C94" r:id="rId82"/>
+    <hyperlink ref="C95" r:id="rId83"/>
+    <hyperlink ref="C96" r:id="rId84"/>
+    <hyperlink ref="C97" r:id="rId85"/>
+    <hyperlink ref="C98" r:id="rId86"/>
+    <hyperlink ref="C99" r:id="rId87"/>
+    <hyperlink ref="C100" r:id="rId88"/>
+    <hyperlink ref="C101" r:id="rId89"/>
+    <hyperlink ref="C102" r:id="rId90"/>
+    <hyperlink ref="C103" r:id="rId91"/>
+    <hyperlink ref="C104" r:id="rId92"/>
+    <hyperlink ref="C105" r:id="rId93"/>
+    <hyperlink ref="C106" r:id="rId94"/>
+    <hyperlink ref="C107" r:id="rId95"/>
+    <hyperlink ref="C108" r:id="rId96"/>
+    <hyperlink ref="C109" r:id="rId97"/>
+    <hyperlink ref="C110" r:id="rId98"/>
+    <hyperlink ref="C111" r:id="rId99"/>
+    <hyperlink ref="C112" r:id="rId100"/>
+    <hyperlink ref="C113" r:id="rId101"/>
+    <hyperlink ref="C114" r:id="rId102"/>
+    <hyperlink ref="C115" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-campaigns.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9966" uniqueCount="2286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9972" uniqueCount="2289">
   <si>
     <t>ID</t>
   </si>
@@ -368,310 +368,310 @@
     <t>C0076</t>
   </si>
   <si>
-    <t>campaign--d5d3608b-1e2e-4e8e-9e3e-172b7ae8783f</t>
-  </si>
-  <si>
-    <t>campaign--da1bd8ae-397a-4c07-81d5-4ee62243c68b</t>
-  </si>
-  <si>
-    <t>campaign--6ba841e9-a6e2-4de1-ae16-ca96739e35ed</t>
-  </si>
-  <si>
-    <t>campaign--d25e87a6-7133-4e11-8e93-259d4f2bd994</t>
-  </si>
-  <si>
-    <t>campaign--327371af-9be7-44c2-8b57-7e51eea988c4</t>
-  </si>
-  <si>
-    <t>campaign--e31b1ed6-33c7-4d93-a2c6-a9b1dac0ac8c</t>
-  </si>
-  <si>
-    <t>campaign--000c635b-27f2-43b1-b98d-ff81a4105054</t>
-  </si>
-  <si>
-    <t>campaign--13625203-0aca-405b-9409-d6bb04dedcc2</t>
-  </si>
-  <si>
-    <t>campaign--c89888d0-b5d3-4947-b33d-d1d066710b8d</t>
-  </si>
-  <si>
-    <t>campaign--5b0cdeff-e761-4c3f-ba0c-feaec1ead563</t>
-  </si>
-  <si>
-    <t>campaign--cbda1a24-f09e-414b-ab6c-1177afcf6579</t>
-  </si>
-  <si>
-    <t>campaign--477d33b8-e868-4f14-994c-3ff87914d154</t>
-  </si>
-  <si>
-    <t>campaign--d07a6a51-42fd-4fca-9e60-9f47a2f3d55b</t>
-  </si>
-  <si>
-    <t>campaign--6dc22dba-186d-44f2-b8e5-932b3d3ae163</t>
-  </si>
-  <si>
-    <t>campaign--30e8ed62-d3e8-4143-9e5e-632bd7aa23cc</t>
-  </si>
-  <si>
-    <t>campaign--5a248622-bb69-496e-b7a9-6563aebba048</t>
-  </si>
-  <si>
-    <t>campaign--35ebb683-a8d6-4486-b3b2-f449826b17ce</t>
-  </si>
-  <si>
-    <t>campaign--9d8a0b71-9771-4b85-a072-eb7f2ebaaa79</t>
-  </si>
-  <si>
-    <t>campaign--04b69ccd-9489-447b-99a2-77765d33a863</t>
-  </si>
-  <si>
-    <t>campaign--e29a7c8b-78d8-4200-a28e-b29c47fd3db4</t>
-  </si>
-  <si>
-    <t>campaign--bee06f63-5b9a-40ee-8ded-3807e18b2794</t>
-  </si>
-  <si>
-    <t>campaign--12a31509-f6b1-4af2-ba71-d0d3f1a7e55c</t>
-  </si>
-  <si>
-    <t>campaign--cfd8e869-e600-4d3e-ab87-ab274a92891e</t>
-  </si>
-  <si>
-    <t>campaign--6569f13e-42ba-41d7-a075-7940b2fa7c53</t>
-  </si>
-  <si>
-    <t>campaign--b375cce2-197a-4d61-84e5-bc95c4f061aa</t>
-  </si>
-  <si>
-    <t>campaign--d1be4871-85b3-4161-b768-fcbdd3f3d268</t>
-  </si>
-  <si>
-    <t>campaign--b4a7dd59-002b-4a93-b13c-ab142a60073b</t>
-  </si>
-  <si>
-    <t>campaign--a06fac12-cd5a-4e5a-b61a-efbc0cd5c005</t>
-  </si>
-  <si>
-    <t>campaign--380516f0-c58a-4738-90e3-693af3883357</t>
-  </si>
-  <si>
-    <t>campaign--20b012fa-ab52-4e32-8992-ea76da37110f</t>
-  </si>
-  <si>
-    <t>campaign--d726fa7f-7c1c-4924-88a6-74444222bd9f</t>
-  </si>
-  <si>
-    <t>campaign--0a86d435-8e69-4f3a-bc96-b3ac668c82bc</t>
-  </si>
-  <si>
-    <t>campaign--fa5a41c0-90cb-4caf-860d-a3428108338f</t>
-  </si>
-  <si>
-    <t>campaign--93b9db3d-54e0-4cd1-a73d-8da9102e4009</t>
-  </si>
-  <si>
-    <t>campaign--2e5633ce-2d35-42b6-9ef4-0bf9c8b1bf35</t>
-  </si>
-  <si>
-    <t>campaign--cb207683-dcc4-4b73-ac2f-0be500edc74f</t>
-  </si>
-  <si>
-    <t>campaign--afb7bd59-6c2a-440a-a21d-5961efba5eff</t>
-  </si>
-  <si>
-    <t>campaign--43bcd15c-cf4f-4445-acbd-65ae81877442</t>
-  </si>
-  <si>
-    <t>campaign--d81de34f-47cd-428a-a41a-09a6f56a9da7</t>
-  </si>
-  <si>
-    <t>campaign--034fab01-25ca-406a-af72-18424cd8865e</t>
-  </si>
-  <si>
-    <t>campaign--65f10cf2-b7b9-4bba-99bd-850bd647691e</t>
-  </si>
-  <si>
-    <t>campaign--5a7b9428-869c-4411-836b-ac68418c3e88</t>
-  </si>
-  <si>
-    <t>campaign--993b7232-af60-4415-a814-7856a5aac9b0</t>
-  </si>
-  <si>
-    <t>campaign--adcbb713-6625-4bb2-bbdb-ca95dce75216</t>
-  </si>
-  <si>
-    <t>campaign--fc8f6110-efac-4b90-b548-1454dac7a19b</t>
-  </si>
-  <si>
-    <t>campaign--5c62e27c-a9a5-4f3d-8c9b-c9e0b90a244b</t>
-  </si>
-  <si>
-    <t>campaign--4ef7374d-4184-4e74-8a4d-61459b26d02f</t>
-  </si>
-  <si>
-    <t>campaign--cfee05cb-c034-4971-a531-902e845ccef3</t>
-  </si>
-  <si>
-    <t>campaign--34f93fca-7d2a-4e55-bc81-7f5697e97ef5</t>
-  </si>
-  <si>
-    <t>campaign--6664b694-3b86-465b-9e27-aea2b4bb1daa</t>
-  </si>
-  <si>
-    <t>campaign--3f943474-7a02-49f9-95d4-6284c13fcf28</t>
-  </si>
-  <si>
-    <t>campaign--8260bb29-de17-4c6d-8152-bcfe4b2b99ab</t>
-  </si>
-  <si>
-    <t>campaign--249316b5-9848-4974-bb96-36f491ad2ff3</t>
-  </si>
-  <si>
-    <t>campaign--51f52048-db4e-4bb3-a9d3-9c3ef5a7efdf</t>
-  </si>
-  <si>
-    <t>campaign--62d59075-a1be-4fc3-bb73-dfbba3d9890f</t>
-  </si>
-  <si>
-    <t>campaign--620a3478-b534-42fe-ae16-eef44729927d</t>
-  </si>
-  <si>
-    <t>campaign--33d73442-ef8e-4272-9b52-8409285e64d4</t>
-  </si>
-  <si>
-    <t>campaign--dde6e95d-8a5e-4d08-9cec-a7ff943a6316</t>
-  </si>
-  <si>
-    <t>campaign--451c6e51-6fd7-493b-82dd-f5b2d321469c</t>
-  </si>
-  <si>
-    <t>campaign--999f0ed3-c7f6-4cbe-b1a2-d7d8d6eedf7b</t>
-  </si>
-  <si>
-    <t>campaign--324dfd0b-8bb9-4e73-b770-c4878fa141b3</t>
-  </si>
-  <si>
-    <t>campaign--e48baa05-e5ad-4906-b269-18674c9abe58</t>
-  </si>
-  <si>
-    <t>campaign--5ac2c3e0-9d38-426d-81e5-09cf5a941ae2</t>
-  </si>
-  <si>
-    <t>campaign--b98a9b9a-6b83-45f6-b65e-38d9bffe4df7</t>
-  </si>
-  <si>
-    <t>campaign--71c8fe9d-7933-4793-8688-8ab211e64903</t>
-  </si>
-  <si>
-    <t>campaign--f8715c92-b16d-427b-8db4-e3a8d3c8f294</t>
-  </si>
-  <si>
-    <t>campaign--4d0ec18b-c72b-4515-9f5d-4246894f9414</t>
-  </si>
-  <si>
-    <t>campaign--d55f729d-5ef5-4b86-a509-1a176d91bbf5</t>
-  </si>
-  <si>
-    <t>campaign--5f5df72e-1fe1-43dd-82d6-8d828a183ff5</t>
-  </si>
-  <si>
-    <t>campaign--6c70c6bf-d458-4a42-a588-2d462edf232e</t>
-  </si>
-  <si>
-    <t>campaign--3e59ca2e-eae8-41fa-b2ec-cb039c9b4210</t>
-  </si>
-  <si>
-    <t>campaign--89ab3728-120a-41b6-b6f8-eee58aa5bf75</t>
-  </si>
-  <si>
-    <t>campaign--15dd6c2c-0e8f-4497-8d49-119a63052355</t>
-  </si>
-  <si>
-    <t>campaign--f5969a82-f450-48d2-a83f-31c2c2fcfc5a</t>
-  </si>
-  <si>
-    <t>campaign--8df71303-011a-488a-a3d5-cfabdf43a3bc</t>
-  </si>
-  <si>
-    <t>campaign--d59baa17-740d-4701-ac73-c8a740a1902e</t>
-  </si>
-  <si>
-    <t>campaign--bb2e0c40-4185-4a26-9a4a-843f0f42fb91</t>
-  </si>
-  <si>
-    <t>campaign--1c942e99-7fdf-43c2-a1c7-0c036960d550</t>
-  </si>
-  <si>
-    <t>campaign--2587cdb8-4685-4f49-ad80-4cf1673de499</t>
-  </si>
-  <si>
-    <t>campaign--4850b46c-5052-41fe-8b42-439a1d32be7b</t>
-  </si>
-  <si>
-    <t>campaign--160fbc62-8a4d-4576-86c8-bb6e8212b355</t>
-  </si>
-  <si>
-    <t>campaign--f726e55f-ac4b-4710-9b09-6b1bd5d7aca3</t>
-  </si>
-  <si>
-    <t>campaign--b12ec413-1bd9-46dd-b084-f775d59555ce</t>
-  </si>
-  <si>
-    <t>campaign--4b166b15-a737-4bfc-a873-ce378b04442b</t>
-  </si>
-  <si>
-    <t>campaign--7f39ffcb-c876-4ac1-97c7-77225d687cf7</t>
-  </si>
-  <si>
-    <t>campaign--c6287a90-fda2-414b-9536-7e8d7b333225</t>
-  </si>
-  <si>
-    <t>campaign--bfff8349-9b26-4bec-993e-4d3fb7792a21</t>
-  </si>
-  <si>
-    <t>campaign--a88279c6-8e3a-4610-98b4-61afdf9b1b00</t>
-  </si>
-  <si>
-    <t>campaign--a7923c48-f560-4ecf-99f5-9b6a59a4c658</t>
-  </si>
-  <si>
-    <t>campaign--bf2d7f34-0a40-4a70-8642-f68ef8dae022</t>
-  </si>
-  <si>
-    <t>campaign--86b88822-1271-4a0b-b652-bac9d6c1e4e8</t>
-  </si>
-  <si>
-    <t>campaign--ab434fb0-c7d3-4c1c-bcbd-c4c4498cf657</t>
-  </si>
-  <si>
-    <t>campaign--a156a043-c7da-45b0-aa0a-5299ead941bb</t>
-  </si>
-  <si>
-    <t>campaign--0cfea08d-0a35-4a62-a6b8-66a75b949383</t>
-  </si>
-  <si>
-    <t>campaign--8a97f881-3742-4d79-9bf1-0d2b3f8bacfe</t>
-  </si>
-  <si>
-    <t>campaign--b12ceb44-a32c-43df-82b7-e817321bdc3c</t>
-  </si>
-  <si>
-    <t>campaign--9c6d7b3b-bfe7-43c5-9b32-9928bf384cb3</t>
-  </si>
-  <si>
-    <t>campaign--2df6168b-6e9d-456f-a84a-30638a365400</t>
-  </si>
-  <si>
-    <t>campaign--d10ef172-c6c8-4f61-9f6c-4be1a77043ec</t>
-  </si>
-  <si>
-    <t>campaign--eecb9861-e70e-403d-bf70-88d38775c3b5</t>
-  </si>
-  <si>
-    <t>campaign--9a356b3e-0022-416c-bda6-336376c7b0f7</t>
-  </si>
-  <si>
-    <t>campaign--3b1dfe61-fc96-495a-92c1-e9617744d5b3</t>
+    <t>campaign--97185b62-b756-44d3-b841-c26ff2caa435</t>
+  </si>
+  <si>
+    <t>campaign--28368dc3-bac3-40ca-9be2-53cd5b18ae5a</t>
+  </si>
+  <si>
+    <t>campaign--3e7aca06-438d-4972-b481-5eef5dddab91</t>
+  </si>
+  <si>
+    <t>campaign--42c2db2c-bca8-4f4c-90a1-feed7ccb5499</t>
+  </si>
+  <si>
+    <t>campaign--0e489ab4-57c8-4ea9-b1c1-35a091e8dcf5</t>
+  </si>
+  <si>
+    <t>campaign--3951c130-926c-4354-b30a-d9b845e20711</t>
+  </si>
+  <si>
+    <t>campaign--5df5ab6d-110b-41b0-914c-d68a42814b3f</t>
+  </si>
+  <si>
+    <t>campaign--332047f3-d991-48d5-a8d0-d626d70b1520</t>
+  </si>
+  <si>
+    <t>campaign--35760d2a-4bf9-493b-ab94-fa67c4ff8fcd</t>
+  </si>
+  <si>
+    <t>campaign--780db662-7237-47c6-9d76-e0a9c213b1ca</t>
+  </si>
+  <si>
+    <t>campaign--d38fee72-8a5f-42cd-a0e6-08b3642e49e2</t>
+  </si>
+  <si>
+    <t>campaign--ae71667a-64b0-4a35-bd4b-2212af26d6f2</t>
+  </si>
+  <si>
+    <t>campaign--1063f60a-3894-4344-97eb-1a62a8d09e50</t>
+  </si>
+  <si>
+    <t>campaign--1f2bd0e1-55a3-4605-9910-a28c81b3aba4</t>
+  </si>
+  <si>
+    <t>campaign--21ac6d95-7b1e-4b4a-a039-c789d4ded516</t>
+  </si>
+  <si>
+    <t>campaign--7fc58166-effa-406a-8ca4-a7e4fb477a96</t>
+  </si>
+  <si>
+    <t>campaign--374ff3ac-7e13-4ceb-870a-1c25a5e81f45</t>
+  </si>
+  <si>
+    <t>campaign--2514ee85-51a9-477d-893a-bb45313d0bd5</t>
+  </si>
+  <si>
+    <t>campaign--89014d54-7b08-4fba-83ac-c8722773fad8</t>
+  </si>
+  <si>
+    <t>campaign--ba097673-a412-4203-bb06-447f860a51d3</t>
+  </si>
+  <si>
+    <t>campaign--a55ffc4f-129f-4d38-8324-fdd1ebbb5a4b</t>
+  </si>
+  <si>
+    <t>campaign--01e2f625-82e2-488e-8622-00ebde701e23</t>
+  </si>
+  <si>
+    <t>campaign--fd958d24-a4bf-4243-ae08-e860c13ea805</t>
+  </si>
+  <si>
+    <t>campaign--a6face44-139d-466a-a5ff-e8c3ff709ace</t>
+  </si>
+  <si>
+    <t>campaign--a413d1f2-8330-4668-b8bd-fd8086250234</t>
+  </si>
+  <si>
+    <t>campaign--48e3bbbf-203d-40a1-bc6d-aa8b18e5598e</t>
+  </si>
+  <si>
+    <t>campaign--08d1bb96-2342-4cdb-b6b9-55a161a88419</t>
+  </si>
+  <si>
+    <t>campaign--76935537-cdec-406c-9f4a-a4cbc121cc00</t>
+  </si>
+  <si>
+    <t>campaign--f4466bbc-027a-4e44-935a-035f903ef19e</t>
+  </si>
+  <si>
+    <t>campaign--c7e7bcde-9c6c-437b-ad59-5e5bd2d5c514</t>
+  </si>
+  <si>
+    <t>campaign--236b5c9a-15f6-43ce-9667-200af4732480</t>
+  </si>
+  <si>
+    <t>campaign--b8c59485-94d3-40a6-b0fc-23d338986d1f</t>
+  </si>
+  <si>
+    <t>campaign--167376d8-aab7-4cbb-b314-230969e6a7a3</t>
+  </si>
+  <si>
+    <t>campaign--b2510237-29ac-4193-8722-444a86b52190</t>
+  </si>
+  <si>
+    <t>campaign--c8bcfd3d-d39b-4d28-9b5c-c5f3e8e0728f</t>
+  </si>
+  <si>
+    <t>campaign--8432f3de-ec66-4e20-88e9-54ed4587df9b</t>
+  </si>
+  <si>
+    <t>campaign--5bf5d20e-3e8f-4b7f-beb9-1a3189e2cadf</t>
+  </si>
+  <si>
+    <t>campaign--5f5766b1-030a-4e87-b165-48a1f821e9a6</t>
+  </si>
+  <si>
+    <t>campaign--ac432357-fb30-4c0f-9123-ff894b2784de</t>
+  </si>
+  <si>
+    <t>campaign--4bc43f67-3dc2-4c2b-9539-a42ff3e48f8f</t>
+  </si>
+  <si>
+    <t>campaign--a89eb731-49da-49ec-94fd-10f7ec7e3212</t>
+  </si>
+  <si>
+    <t>campaign--db4a09bc-80d8-443b-8be6-9a04e643eab5</t>
+  </si>
+  <si>
+    <t>campaign--0c92bef0-ae48-4178-a4e8-2845fe5e43ba</t>
+  </si>
+  <si>
+    <t>campaign--1a54b369-cecd-4acf-aeeb-addc0eee2b65</t>
+  </si>
+  <si>
+    <t>campaign--fc415691-46e4-4d5b-88ef-568d20e2f82a</t>
+  </si>
+  <si>
+    <t>campaign--30bc8d41-e4ff-476d-a84a-d5435273ad2e</t>
+  </si>
+  <si>
+    <t>campaign--37aea0f8-0538-4f63-994d-621cd042cbe7</t>
+  </si>
+  <si>
+    <t>campaign--b9035652-ec19-498f-ad70-c1e7c3af8809</t>
+  </si>
+  <si>
+    <t>campaign--25c5110f-77ed-4932-b111-1dfc5e875a95</t>
+  </si>
+  <si>
+    <t>campaign--84ee7058-67a7-46ba-b6ee-a9087bb87634</t>
+  </si>
+  <si>
+    <t>campaign--75cf364b-6744-4d5a-bb26-0abd1753609f</t>
+  </si>
+  <si>
+    <t>campaign--192a1e9c-2e3d-43d2-b6a6-175a55e941b5</t>
+  </si>
+  <si>
+    <t>campaign--071a2be9-c5af-4201-9e25-71e6c6dc63cf</t>
+  </si>
+  <si>
+    <t>campaign--ed10ebb7-caaa-481f-8655-7cc6acbade91</t>
+  </si>
+  <si>
+    <t>campaign--dc27daac-0791-47f7-aaee-d0e5c7a16918</t>
+  </si>
+  <si>
+    <t>campaign--7c31c341-4948-4d76-bc9a-d602657f0db3</t>
+  </si>
+  <si>
+    <t>campaign--f136d4ca-d08c-4b0b-9e1d-368e30dbfa5b</t>
+  </si>
+  <si>
+    <t>campaign--3f35fe1f-00d3-4e41-98a9-2e406c219312</t>
+  </si>
+  <si>
+    <t>campaign--31aacef3-25a8-4fba-ac95-bae1bb0592fb</t>
+  </si>
+  <si>
+    <t>campaign--491b0716-9561-4ea6-a89b-4ba9e0953e3c</t>
+  </si>
+  <si>
+    <t>campaign--a4455377-a120-45a5-9089-99fb95fdb59a</t>
+  </si>
+  <si>
+    <t>campaign--ea61a171-fa35-4ed1-9287-41e3ca667409</t>
+  </si>
+  <si>
+    <t>campaign--7771ca5f-0b5b-4fbb-9f0b-f37801347fca</t>
+  </si>
+  <si>
+    <t>campaign--0b3c9ce1-a0be-4440-b0f0-c762880ed332</t>
+  </si>
+  <si>
+    <t>campaign--96ec7087-d1b0-4076-a568-5f8a779eef00</t>
+  </si>
+  <si>
+    <t>campaign--46077bfe-ce3a-4542-8b5c-b8b6d8d6fdef</t>
+  </si>
+  <si>
+    <t>campaign--1e47c887-315a-4c3d-bea5-d9632702b517</t>
+  </si>
+  <si>
+    <t>campaign--61012452-31df-4e70-80b3-74be0914a200</t>
+  </si>
+  <si>
+    <t>campaign--bf409339-c5e5-4ab8-8b1a-246071ed19b5</t>
+  </si>
+  <si>
+    <t>campaign--d0eb71bc-3823-42d6-b3e5-427e2a915763</t>
+  </si>
+  <si>
+    <t>campaign--9a0c9c17-48be-4239-ae4b-ba408248d9ba</t>
+  </si>
+  <si>
+    <t>campaign--6a3d44b3-9d73-4774-a015-293e5ff7c59f</t>
+  </si>
+  <si>
+    <t>campaign--6058b9a2-6422-4498-bc1f-466e8f5404d0</t>
+  </si>
+  <si>
+    <t>campaign--a3e43158-57aa-48a2-8b22-c4338061ebe6</t>
+  </si>
+  <si>
+    <t>campaign--556f85fe-e335-4694-aa72-2e4da45a572d</t>
+  </si>
+  <si>
+    <t>campaign--3fc52fc0-1fc8-40f8-99fe-daee0cafc351</t>
+  </si>
+  <si>
+    <t>campaign--dee519da-cbc0-4a3f-8f64-811927f8fa8a</t>
+  </si>
+  <si>
+    <t>campaign--fcb5345d-ae74-4a0d-8859-00654996201a</t>
+  </si>
+  <si>
+    <t>campaign--ca069712-0be3-42d8-a175-c8e568760aba</t>
+  </si>
+  <si>
+    <t>campaign--9fd8c082-9e7d-4657-b402-c6b5164ebb7c</t>
+  </si>
+  <si>
+    <t>campaign--62313c07-9360-40f3-9a67-f106b3a9901f</t>
+  </si>
+  <si>
+    <t>campaign--a92151c2-5f7d-4c2e-a659-7a10e298595d</t>
+  </si>
+  <si>
+    <t>campaign--e2dc6026-4b3e-4088-8687-ee5e8efc0fcc</t>
+  </si>
+  <si>
+    <t>campaign--b8913d57-e3f2-43cc-989e-b5dc2cd92219</t>
+  </si>
+  <si>
+    <t>campaign--771a290d-43a0-43fb-89a5-2aaf271da029</t>
+  </si>
+  <si>
+    <t>campaign--c29e446f-6d4f-4920-91d5-fc54dedf1f5f</t>
+  </si>
+  <si>
+    <t>campaign--0bd21e62-2023-485d-9c17-c2684d1bebdb</t>
+  </si>
+  <si>
+    <t>campaign--7c688b14-67e6-476e-8096-a44c3fb95db9</t>
+  </si>
+  <si>
+    <t>campaign--567e3204-7775-46bb-b5f9-874bfeaf0c6f</t>
+  </si>
+  <si>
+    <t>campaign--dbde897a-31a7-4684-a98d-5805601ba4c2</t>
+  </si>
+  <si>
+    <t>campaign--906ac28e-dbce-42ff-9e99-9b6cc4aaa5e3</t>
+  </si>
+  <si>
+    <t>campaign--ce2366df-0b95-4d79-8f46-07ffa76c4215</t>
+  </si>
+  <si>
+    <t>campaign--efaaf655-e666-48b6-b47f-c6778bee3360</t>
+  </si>
+  <si>
+    <t>campaign--00f784da-4f20-4b91-acbe-8f9b76ff9596</t>
+  </si>
+  <si>
+    <t>campaign--59c82e4e-f119-41db-98a0-42312fac19cb</t>
+  </si>
+  <si>
+    <t>campaign--5478a268-e577-4b91-8abc-920e07341e66</t>
+  </si>
+  <si>
+    <t>campaign--b7c7a3d4-e14e-4089-805e-0d6bd5d494c2</t>
+  </si>
+  <si>
+    <t>campaign--acd8df7a-c420-435e-a7c2-1b8fd5170fab</t>
+  </si>
+  <si>
+    <t>campaign--d36ba52b-faba-4013-81c1-bc5462725fe9</t>
+  </si>
+  <si>
+    <t>campaign--cec91334-cad3-439c-9fd6-a172aa9d1c68</t>
+  </si>
+  <si>
+    <t>campaign--487d3e61-633a-4a79-8421-e58f556d93e1</t>
+  </si>
+  <si>
+    <t>campaign--dffc0208-5ef6-47c3-99a3-57d880da041e</t>
   </si>
   <si>
     <t>«Вечный мир» с Польшей (1686)</t>
@@ -1004,7 +1004,7 @@
     <t>Государственная кампания по уничтожению украинского языка и культуры. Включала закрытие воскресных школ, запрет национальной прессы, официальное отрицание существования языка (Валуевский циркуляр), вывоз исторических архивов в Москву и прямые денежные доплаты чиновникам за русификацию местного населения (Citation: Русифікація України — Вікіпедія 2026).</t>
   </si>
   <si>
-    <t>Кампания по превращению свободного населения в бесправных военных рабов, спровоцировавшая подавленное восстание бугских казаков в 1817 году. Позднее, в 1828 году, завершилась переманиванием атамана Гладкого и ликвидацией последней Задунайской Сечи турками (Citation: Повстання бузьких козаків (1817) — Вікіпедія 2026, Задунайська Січ — Вікіпедія 2026).</t>
+    <t>Кампания по превращению свободного населения в бесправных военных рабов, спровоцировавшая подавленное восстание бугских казаков в 1817 году. Позднее, в 1828 году, завершилась переманиванием атамана Гладкого и ликвидацией последней Задунайской Сечи турками (Citation: Повстання бузьких козаків (1817) — Вікіпедія 2026) (Citation: Задунайська Січ — Вікіпедія 2026).</t>
   </si>
   <si>
     <t>Сепаратные мирные переговоры между Москвой и Речью Посполитой об окончании войны и разделе сфер влияния, прошедшие в полной изоляции украинской стороны: «Это настоящая драма для украинцев: по настоянию польской стороны украинцев к переговорам не допускают» (Citation: Война и наказание: Как Россия уничтожала Украину 2023).</t>
@@ -2132,7 +2132,7 @@
     <t>31 January 1924</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007)</t>
   </si>
   <si>
     <t>(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Карательная психиатрия в России: назад в СССР? 2020),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
@@ -2141,16 +2141,16 @@
     <t>(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026),(Citation: Друга Малоросійська колегія — Вікіпедія 2026),(Citation: Ліквідація автономії Гетьманщини — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Азовські походи (1695—1696),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
+  </si>
+  <si>
+    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Андрусовское перемирие - Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007)</t>
+  </si>
+  <si>
+    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Анексія Київської митрополії Московським патріархатом — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
@@ -2165,22 +2165,22 @@
     <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
+    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
   </si>
   <si>
-    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775)</t>
+    <t>(Citation: Ліквідація Запорозької Січі (1775),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Ліквідація Запорозької Січі (1775),(Citation: Ліквідація Запорозької Січі (1775)</t>
   </si>
   <si>
     <t>(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026),(Citation: Україна у війнах Наполеона — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Перепис населення Російської імперії (1897),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897),(Citation: Перепис населення Російської імперії (1897)</t>
-  </si>
-  <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Перепис населення Російської імперії (1897),(Citation: Перепис населення Російської імперії (1897),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Перепис населення Російської імперії (1897)</t>
+  </si>
+  <si>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026),(Citation: Поділи Речі Посполитої — Вікіпедія 2026)</t>
@@ -2192,19 +2192,19 @@
     <t>(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
-    <t>(Citation: Киевский синопсис — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026)</t>
+    <t>(Citation: Киевский синопсис — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Киевский синопсис — Википедия 2026),(Citation: Киевский синопсис — Википедия 2026)</t>
   </si>
   <si>
     <t>(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010),(Citation: Россия - Чечня - цепь ошибок и преступлений. 1994—1996 2010)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Іван Мазепа — Вікіпедія 2026)</t>
+    <t>(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026),(Citation: Двойное преступление СССР: как советы скрывали Чернобыльскую катастрофу 2026)</t>
   </si>
   <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
@@ -2213,16 +2213,16 @@
     <t>(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026),(Citation: Конотопські статті — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Крымская война — Википедия 2026),(Citation: Крымская война — Википедия 2026),(Citation: Київська козаччина — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
+    <t>(Citation: Крымская война — Википедия 2026),(Citation: Київська козаччина — Вікіпедія 2026),(Citation: Крымская война — Википедия 2026),(Citation: Крымская война — Википедия 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
     <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Запорозька Січ — Вікіпедія 2026)</t>
+    <t>(Citation: Північна війна (1700—1721),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Запорозька Січ — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026)</t>
@@ -2240,13 +2240,13 @@
     <t>(Citation: Московські статті (1665),(Citation: Московські статті (1665),(Citation: Московські статті (1665)</t>
   </si>
   <si>
-    <t>(Citation: Руїна — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026)</t>
+    <t>(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Московсько-українська війна (1658—1659),(Citation: Руїна — Вікіпедія 2026),(Citation: Руїна — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.)</t>
   </si>
   <si>
-    <t>(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011)</t>
+    <t>(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011),(Citation: В ТЕНИ «БОЛЬШОГО БРАТА» ЗАПАДНЫЕ НАЦИОНАЛЬНЫЕ МЕНЬШИНСТВА В СССР 1917-1938 ГГ . 2011)</t>
   </si>
   <si>
     <t>(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026),(Citation: Скасування козацького устрою в Слобідській Україні — Вікіпедія 2026)</t>
@@ -2255,10 +2255,10 @@
     <t>(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987),(Citation: Письмо-протест 139 - Википедия 2026),(Citation: ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987)</t>
   </si>
   <si>
-    <t>(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026)</t>
+    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Історія України — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026),(Citation: Україна в Першій світовій війні — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Мазепа 2007),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Іван Мазепа — Вікіпедія 2026),(Citation: Мазепа, Иван Степанович — Википедия 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Мазепа 2007),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Батуринська трагедія — Вікіпедія 2026),(Citation: Мазепа 2007)</t>
   </si>
   <si>
     <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Переяславська рада — Вікіпедія 2026)</t>
@@ -2273,16 +2273,16 @@
     <t>(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Антикріпосницький рух в Україні (1789-1861),(Citation: Антикріпосницький рух в Україні (1789-1861)</t>
   </si>
   <si>
-    <t>(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Історія України — Вікіпедія 2026),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Польское восстание (1863—1864),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026),(Citation: Норильское восстание - Википедия 2026),(Citation: Кенгирское восстание заключённых - Википедия 2026)</t>
   </si>
   <si>
-    <t>(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Російсько-українська війна (з 2014),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Російсько-українська війна (з 2014),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Campaign C0026 | MITRE ATT&amp;CK® 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK® 2025),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
-  </si>
-  <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
+    <t>(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Російсько-українська війна (з 2014),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: FrostyGoop Incident | MITRE ATT&amp;CK® 2024),(Citation: Російсько-українська війна (з 2014),(Citation: Рашизм: Звір з безодні 2023),(Citation: Российские удары по украинской энергосистеме — Википедия 2026),(Citation: APT28 Nearest Neighbor Campaign | MITRE ATT&amp;CK® 2025),(Citation: Удари по об'єктах критичної інфраструктури України під час російсько-української війни — Вікіпедія 2026),(Citation: 2022 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2024),(Citation: Campaign C0026 | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+  </si>
+  <si>
+    <t>(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Північна війна (1700—1721),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026),(Citation: Серпневий путч — Вікіпедія 2026)</t>
@@ -2291,13 +2291,13 @@
     <t>(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711),(Citation: Похід Пилипа Орлика на Правобережну Україну (1711)</t>
   </si>
   <si>
-    <t>(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026)</t>
-  </si>
-  <si>
-    <t>(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
-  </si>
-  <si>
-    <t>(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Російсько-українська війна (з 2014),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Рашизм: Звір з безодні 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Російсько-українська війна (з 2014),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026),(Citation: Лубенський договір — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Правління гетьманського уряду — Вікіпедія 2026)</t>
+  </si>
+  <si>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
+  </si>
+  <si>
+    <t>(Citation: Російсько-українська війна (з 2014),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Російсько-українська війна (з 2014),(Citation: Рашизм: Звір з безодні 2023),(Citation: Дезінформація під час російсько-української війни — Вікіпедія 2026),(Citation: 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: 2016 Ukraine Electric Power Attack | MITRE ATT&amp;CK® 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026),(Citation: Хроника первой российской войны в Чечне 2026)</t>
@@ -2306,7 +2306,7 @@
     <t>(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026),(Citation: Кирило-Мефодіївське товариство — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026)</t>
+    <t>(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011),(Citation: Решетилівські статті — Вікіпедія 2026),(Citation: ИВАН МАЗЕПА И РОССИЙСКАЯ ИМПЕРИЯ ИСТОРИЯ «ПРЕДАТЕЛЬСТВА» 2011)</t>
   </si>
   <si>
     <t>(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026),(Citation: Рішительні пункти — Вікіпедія 2026)</t>
@@ -2315,10 +2315,10 @@
     <t>(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1768—1774),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1768—1774)</t>
   </si>
   <si>
-    <t>(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812)</t>
-  </si>
-  <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
+    <t>(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Аннексия Бессарабии Российской империей (1812),(Citation: Російсько-турецька війна (1806—1812),(Citation: Російсько-турецька війна (1806—1812)</t>
+  </si>
+  <si>
+    <t>(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русско-турецкая война (1877—1878),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Война и наказание: Как Россия уничтожала Украину 2023)</t>
   </si>
   <si>
     <t>(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026),(Citation: Малоросійське генерал-губернаторство — Вікіпедія 2026)</t>
@@ -2327,10 +2327,10 @@
     <t>(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026),(Citation: Малоросійський приказ — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
-  </si>
-  <si>
-    <t>(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
+  </si>
+  <si>
+    <t>(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Война и наказание: Как Россия уничтожала Украину 2023),(Citation: Русифікація України — Вікіпедія 2026),(Citation: Русифікація України — Вікіпедія 2026)</t>
   </si>
   <si>
     <t>(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026),(Citation: Столипінська реформа — Вікіпедія 2026)</t>
@@ -2345,7 +2345,7 @@
     <t>(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026),(Citation: Чорносотенці — Вікіпедія 2026)</t>
   </si>
   <si>
-    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
+    <t>(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Україна й українці в постімперську добу (1917—1939),(Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.),(Citation: Україна й українці в постімперську добу (1917—1939)</t>
   </si>
   <si>
     <t>source ID</t>
@@ -2462,43 +2462,43 @@
     <t>Имперские Коллегии</t>
   </si>
   <si>
-    <t>tool--2de74860-9286-45c7-b350-d41ae6685351</t>
-  </si>
-  <si>
-    <t>tool--e5929876-f3ec-466c-90a8-ec4a16cd8ac7</t>
-  </si>
-  <si>
-    <t>tool--ff0e5cd8-b850-4df9-845a-ab14c6ba2104</t>
-  </si>
-  <si>
-    <t>tool--af3c7286-be13-4569-ac9d-c96ebbac6a34</t>
-  </si>
-  <si>
-    <t>tool--5ceff728-9a89-463d-b71b-79b952d31693</t>
-  </si>
-  <si>
-    <t>tool--d57519cc-1898-4106-8e8b-4798bf53d3b4</t>
-  </si>
-  <si>
-    <t>tool--b4c0d62c-b3f5-4069-a07d-c7e9a48427e5</t>
-  </si>
-  <si>
-    <t>tool--4ba8494b-f590-4308-868c-37a12508f6a3</t>
-  </si>
-  <si>
-    <t>tool--413178e7-81d2-4bdd-ab53-c632febad570</t>
-  </si>
-  <si>
-    <t>tool--4ebdeb25-4eb2-43cd-a70b-e019e1a4ef6c</t>
-  </si>
-  <si>
-    <t>tool--5dcf4786-4e1a-44f2-8aa0-e4b5fdf1f93f</t>
-  </si>
-  <si>
-    <t>tool--fd9d33aa-46ee-48a8-b37c-b5813b8dd7cb</t>
-  </si>
-  <si>
-    <t>tool--5c43501c-aa32-48a4-a151-6c6897e3b0dd</t>
+    <t>tool--e07eeae6-c3e5-45f1-b8f1-c3e50a179665</t>
+  </si>
+  <si>
+    <t>tool--df0ba05b-fd65-4437-9c8f-5fbbf4498f51</t>
+  </si>
+  <si>
+    <t>tool--d0e502ca-3ba5-4364-b2ab-30d53b87c681</t>
+  </si>
+  <si>
+    <t>tool--4d016c34-bb94-4b61-88bc-7e9cacc2185b</t>
+  </si>
+  <si>
+    <t>tool--66dcf02c-a2aa-4a17-9e43-2e456ebdee31</t>
+  </si>
+  <si>
+    <t>tool--06c48a32-5cf5-4cef-8992-72c541bfdfac</t>
+  </si>
+  <si>
+    <t>tool--24a04dcd-846a-4c5b-bfcd-47828e9ddd57</t>
+  </si>
+  <si>
+    <t>tool--e8d0468c-8a92-4294-baa2-a91bcd6f19e4</t>
+  </si>
+  <si>
+    <t>tool--2bf94bf0-b6e0-4e29-bef7-8745173179cb</t>
+  </si>
+  <si>
+    <t>tool--82bcdaea-f53f-45de-8281-b671db596090</t>
+  </si>
+  <si>
+    <t>tool--634cf340-6e8c-49d7-b45f-c9fb4f722daa</t>
+  </si>
+  <si>
+    <t>tool--88d6ef27-a088-40e6-b97f-8a49b8c508e1</t>
+  </si>
+  <si>
+    <t>tool--fb5d65db-23c3-4502-8fd9-7b40965d2ed8</t>
   </si>
   <si>
     <t>software</t>
@@ -3054,553 +3054,553 @@
     <t>Использование Договора об образовании СССР (декабрь 1922 г.) для формального декларирования союза равноправных республик, маскирующего окончательную централизацию власти в Москве. (Citation: Україна й українці в постімперську добу (1917—1939) 2021)</t>
   </si>
   <si>
-    <t>relationship--5614d86d-6211-45cd-ac6c-26a97c7ed3cf</t>
-  </si>
-  <si>
-    <t>relationship--c00bd06c-4bf5-4ab2-ab25-c5d571553d0c</t>
-  </si>
-  <si>
-    <t>relationship--7201fe1e-0fea-4d3b-97bf-6355ebf82318</t>
-  </si>
-  <si>
-    <t>relationship--d1870805-3ccc-4beb-b2a4-8402f288d864</t>
-  </si>
-  <si>
-    <t>relationship--a1eee09b-bd43-43e9-b586-a6b939c06a11</t>
-  </si>
-  <si>
-    <t>relationship--c274175b-6c03-49c5-a647-607cd5b0e4d2</t>
-  </si>
-  <si>
-    <t>relationship--187b5fcd-6c5c-4c42-8d07-07adbdbecd2d</t>
-  </si>
-  <si>
-    <t>relationship--1006e39a-452b-4831-be5c-fc31a3710a4c</t>
-  </si>
-  <si>
-    <t>relationship--998fc32c-1362-4fe1-badc-2c3295a58dae</t>
-  </si>
-  <si>
-    <t>relationship--b50491d9-1ef9-4e6a-a7d8-ed3bdd53bb26</t>
-  </si>
-  <si>
-    <t>relationship--816bc3db-9456-4de8-a943-e308683f2326</t>
-  </si>
-  <si>
-    <t>relationship--7e5cb007-6d19-46d2-a049-9fb76730abfc</t>
-  </si>
-  <si>
-    <t>relationship--4b7df337-6761-4f4a-8663-ffc85abd9bd7</t>
-  </si>
-  <si>
-    <t>relationship--3e1c35b2-ac79-4f76-b026-a30f8e566a41</t>
-  </si>
-  <si>
-    <t>relationship--a849cb40-97db-4468-a725-2eb757b9285f</t>
-  </si>
-  <si>
-    <t>relationship--47ff22b7-0fad-4eaa-8f49-c7ee57b2bcf5</t>
-  </si>
-  <si>
-    <t>relationship--50db3a6a-bc86-4653-92b1-cc25f4fd3b63</t>
-  </si>
-  <si>
-    <t>relationship--8312e15d-9501-45f6-b5c7-dd40ad215dc7</t>
-  </si>
-  <si>
-    <t>relationship--0cc9ae91-2019-49d4-9ae9-74cf940ab326</t>
-  </si>
-  <si>
-    <t>relationship--62cc7c54-5c61-4755-b62b-11df9f67bc7c</t>
-  </si>
-  <si>
-    <t>relationship--9520ceeb-3ab0-40cd-9976-308b5382c604</t>
-  </si>
-  <si>
-    <t>relationship--df0590aa-456d-4dcd-b3ef-9db58fcdde4d</t>
-  </si>
-  <si>
-    <t>relationship--25875951-42bf-4bd1-8846-1e2b082462c7</t>
-  </si>
-  <si>
-    <t>relationship--363d00f2-89e0-45eb-aeff-56c3eb0b7d1b</t>
-  </si>
-  <si>
-    <t>relationship--ccc50e83-1034-4626-9fad-142e49094870</t>
-  </si>
-  <si>
-    <t>relationship--0e6f9307-ac79-4d43-90f6-e73960d6ec75</t>
-  </si>
-  <si>
-    <t>relationship--24ef7132-be8a-41ec-bacf-c64882a1171d</t>
-  </si>
-  <si>
-    <t>relationship--0cf1df00-44a9-42ec-b61d-3e10fb8c67d6</t>
-  </si>
-  <si>
-    <t>relationship--03e9274c-b7a4-42d6-8f7f-78b71e30af09</t>
-  </si>
-  <si>
-    <t>relationship--5c38fc95-7bc5-4a6a-8681-48be32c65a82</t>
-  </si>
-  <si>
-    <t>relationship--066eb77b-c6df-4d8e-8599-0beb192907e4</t>
-  </si>
-  <si>
-    <t>relationship--541a4d88-df09-4c75-92ae-356afd194692</t>
-  </si>
-  <si>
-    <t>relationship--3af6830d-8cc7-4fed-b927-108a41fd4178</t>
-  </si>
-  <si>
-    <t>relationship--57631293-2a02-4489-8c56-f583e9bc5585</t>
-  </si>
-  <si>
-    <t>relationship--862f0336-33bd-4370-8af3-d29a004f0fc8</t>
-  </si>
-  <si>
-    <t>relationship--9ec2a708-84bf-4339-afb0-0162bb4748ff</t>
-  </si>
-  <si>
-    <t>relationship--4485df60-3f40-40ca-93c4-89378405dc43</t>
-  </si>
-  <si>
-    <t>relationship--722ca219-044e-4221-a0f4-444790a937ba</t>
-  </si>
-  <si>
-    <t>relationship--0819322a-18d8-4e24-b55c-206658d07525</t>
-  </si>
-  <si>
-    <t>relationship--cfa59c71-254e-4a90-903c-fcce14903069</t>
-  </si>
-  <si>
-    <t>relationship--672d610b-b36d-4dd8-b55d-8b986db8b16c</t>
-  </si>
-  <si>
-    <t>relationship--3c9fe144-c86e-42cf-b46f-9fbac0138093</t>
-  </si>
-  <si>
-    <t>relationship--0416c3e3-00bc-44e4-88b4-e2837a311840</t>
-  </si>
-  <si>
-    <t>relationship--0e328b60-be4c-4a17-a480-68f9a95774c9</t>
-  </si>
-  <si>
-    <t>relationship--05358bf0-1b8f-4d3d-9b01-37d1e4f6b814</t>
-  </si>
-  <si>
-    <t>relationship--d8ee9123-00a9-45e8-b9ed-78eaf52fd03c</t>
-  </si>
-  <si>
-    <t>relationship--c99cdf0b-238f-4f4a-bd62-e777028d0888</t>
-  </si>
-  <si>
-    <t>relationship--eb3d94ce-42c1-4f6d-9104-149587001ee8</t>
-  </si>
-  <si>
-    <t>relationship--34fa7ae0-57e6-4802-b731-2a8397e43f5c</t>
-  </si>
-  <si>
-    <t>relationship--658426eb-6159-48b7-834a-d2cba5929840</t>
-  </si>
-  <si>
-    <t>relationship--1b8afd01-f00e-4fb9-8e53-23bf378a5743</t>
-  </si>
-  <si>
-    <t>relationship--c4b84975-0d5b-41da-8dde-a1e4752f8223</t>
-  </si>
-  <si>
-    <t>relationship--3c23657a-af00-4c00-be50-0c2211096383</t>
-  </si>
-  <si>
-    <t>relationship--34f1cc09-99b9-4b55-8a11-a27b71d36a56</t>
-  </si>
-  <si>
-    <t>relationship--2d2d4647-66d2-468f-b5fa-08a23e9f3b52</t>
-  </si>
-  <si>
-    <t>relationship--32fef7ce-3ca8-42d2-9806-8f07130dc59a</t>
-  </si>
-  <si>
-    <t>relationship--45a232f8-5767-419e-9acc-94a2592789a1</t>
-  </si>
-  <si>
-    <t>relationship--8bd14d24-f013-4648-9e45-231c66bee802</t>
-  </si>
-  <si>
-    <t>relationship--e9bd60a6-0325-45da-9bda-fd854a7ce87b</t>
-  </si>
-  <si>
-    <t>relationship--724cc625-5556-40a5-ae14-3d9de64c9a19</t>
-  </si>
-  <si>
-    <t>relationship--00da6316-6f4a-4ee9-84ab-f3bf74b840dc</t>
-  </si>
-  <si>
-    <t>relationship--37a6d563-2564-4062-8967-14950a0a6ff1</t>
-  </si>
-  <si>
-    <t>relationship--5c5eb460-e73e-4c4b-8929-2f3a55616623</t>
-  </si>
-  <si>
-    <t>relationship--41bac798-9a1a-4b92-930c-227474d4cabb</t>
-  </si>
-  <si>
-    <t>relationship--5b9787dc-aaed-4206-acb6-3135336f00dc</t>
-  </si>
-  <si>
-    <t>relationship--92e54ce9-a70b-4436-be5a-e66e682935ec</t>
-  </si>
-  <si>
-    <t>relationship--689c088d-7e07-43c6-a3a3-2059035a0956</t>
-  </si>
-  <si>
-    <t>relationship--1d4bd310-a5da-42a0-896e-ea3ccf0735ef</t>
-  </si>
-  <si>
-    <t>relationship--58b1092a-2708-4e1d-b796-7570f699b314</t>
-  </si>
-  <si>
-    <t>relationship--a700b400-cfb5-4c2d-8ac6-6d3f3a976502</t>
-  </si>
-  <si>
-    <t>relationship--463138d3-daf2-4734-b553-fcc80a9f7245</t>
-  </si>
-  <si>
-    <t>relationship--12c1d59e-77ae-4c17-bd89-4f0d0855db2b</t>
-  </si>
-  <si>
-    <t>relationship--6dd4ef8d-d116-4667-98cd-25d0b4ca2eb2</t>
-  </si>
-  <si>
-    <t>relationship--28bdfc3d-faa4-4c45-8c25-506dc03861d2</t>
-  </si>
-  <si>
-    <t>relationship--2da181d8-efdd-46a5-bc48-a7e761e7700c</t>
-  </si>
-  <si>
-    <t>relationship--30caab21-d762-4082-9483-c4e4b58c8140</t>
-  </si>
-  <si>
-    <t>relationship--edd083ea-aadc-4345-844f-5d40e476e7c8</t>
-  </si>
-  <si>
-    <t>relationship--61c6a3e1-337d-4150-8e33-062db9bf48fb</t>
-  </si>
-  <si>
-    <t>relationship--69593cf2-77f5-4528-95bc-867a7cd474a6</t>
-  </si>
-  <si>
-    <t>relationship--fe839167-b221-48ff-8478-496d40f26604</t>
-  </si>
-  <si>
-    <t>relationship--33cc973e-fa84-415a-a0b3-dc6101374315</t>
-  </si>
-  <si>
-    <t>relationship--0c8a308f-fb09-4df6-9a8b-03dc281625c8</t>
-  </si>
-  <si>
-    <t>relationship--13a0fcb0-b324-4579-a852-51d59b9cfea7</t>
-  </si>
-  <si>
-    <t>relationship--03876e2e-c730-426e-9cf7-5c2d2eacfd12</t>
-  </si>
-  <si>
-    <t>relationship--ac403c59-fdb2-451d-82d5-b227f3fb004e</t>
-  </si>
-  <si>
-    <t>relationship--17501bfb-76d5-452a-a5b7-bb40a2734033</t>
-  </si>
-  <si>
-    <t>relationship--3751fcb4-a779-4bd1-8b91-b4d03da77810</t>
-  </si>
-  <si>
-    <t>relationship--db0bfcda-eb29-4562-aca0-c098711d0d07</t>
-  </si>
-  <si>
-    <t>relationship--092d1143-9f0d-4f94-b49b-b4a78e22aa1f</t>
-  </si>
-  <si>
-    <t>relationship--ff4a5303-2db3-49ae-a53f-7c2dffb9e6ee</t>
-  </si>
-  <si>
-    <t>relationship--2291dd05-1ba6-427c-8f66-f483409905d3</t>
-  </si>
-  <si>
-    <t>relationship--bdf81bef-d89b-49f8-a818-e7348ead0e7d</t>
-  </si>
-  <si>
-    <t>relationship--c0a0ed7b-7375-475c-967c-9635560013b7</t>
-  </si>
-  <si>
-    <t>relationship--35f20b51-ebde-4f96-b4f6-4612f3bceea5</t>
-  </si>
-  <si>
-    <t>relationship--b5c01c41-b1bd-403f-9c86-ee33d9233bb8</t>
-  </si>
-  <si>
-    <t>relationship--9bc2a9d1-da58-403d-98c8-6b56bfd51523</t>
-  </si>
-  <si>
-    <t>relationship--e9b6b440-e6ef-4112-91b7-a10e828f215f</t>
-  </si>
-  <si>
-    <t>relationship--d13278fb-2254-49ef-b205-01e887848910</t>
-  </si>
-  <si>
-    <t>relationship--5efc8b32-1b60-4fad-ae02-e340941487af</t>
-  </si>
-  <si>
-    <t>relationship--2511d69d-6f60-4597-8c57-c435f01cb56c</t>
-  </si>
-  <si>
-    <t>relationship--34272f39-5284-4cd8-aed4-3ac4b7afe9c0</t>
-  </si>
-  <si>
-    <t>relationship--78c44437-c23b-44e3-9b0a-dea9d31afab3</t>
-  </si>
-  <si>
-    <t>relationship--86e8bc77-6840-43e1-9b08-388dd6ce4a71</t>
-  </si>
-  <si>
-    <t>relationship--95a7d566-0538-4e17-b03f-d840ac5a6485</t>
-  </si>
-  <si>
-    <t>relationship--e08df791-6312-4452-a037-50b1c552eae6</t>
-  </si>
-  <si>
-    <t>relationship--ce048198-374c-4f04-8fc5-58aa78334838</t>
-  </si>
-  <si>
-    <t>relationship--ed1b3558-fa7e-4b78-94a6-ede294e5982b</t>
-  </si>
-  <si>
-    <t>relationship--fdb52f1a-9fce-4466-9113-080a43b19d24</t>
-  </si>
-  <si>
-    <t>relationship--a45d91e8-042e-4dde-8bf0-57d321efd381</t>
-  </si>
-  <si>
-    <t>relationship--4c063840-371e-41c6-8f16-15c3bb3b6a07</t>
-  </si>
-  <si>
-    <t>relationship--01302958-accb-41b5-bd1c-cad6bc07a1d6</t>
-  </si>
-  <si>
-    <t>relationship--1e280e04-acc2-4d3a-ad9c-8e779be2623f</t>
-  </si>
-  <si>
-    <t>relationship--68148d92-85e1-47a8-86ad-88953aad0f77</t>
-  </si>
-  <si>
-    <t>relationship--313f6ee5-9364-48f9-839d-edf4e6d25f2a</t>
-  </si>
-  <si>
-    <t>relationship--fb779776-e9f6-45e3-9cb8-c9e509c3e8a7</t>
-  </si>
-  <si>
-    <t>relationship--47e73f6e-a733-46f1-a09b-51f4a0c2574a</t>
-  </si>
-  <si>
-    <t>relationship--d48b2f17-752e-4ef0-85ca-8c5626fe5832</t>
-  </si>
-  <si>
-    <t>relationship--55b721b2-6229-4de6-9655-32647d86e186</t>
-  </si>
-  <si>
-    <t>relationship--e7753b65-5fcf-453a-9139-c1d9028cf696</t>
-  </si>
-  <si>
-    <t>relationship--5f7f0d17-361f-4a98-b1bd-0122c4d69f1d</t>
-  </si>
-  <si>
-    <t>relationship--2e1b7d0a-bc28-4539-92dd-ebfc2bb2a6fc</t>
-  </si>
-  <si>
-    <t>relationship--14628952-a9d9-4da9-a5e2-c807bebc2dbc</t>
-  </si>
-  <si>
-    <t>relationship--9708078b-3306-4693-bf99-43999bd18b3a</t>
-  </si>
-  <si>
-    <t>relationship--ac66737c-9eeb-4d82-a7ef-b0a31bba3e60</t>
-  </si>
-  <si>
-    <t>relationship--e68e8a70-ae5d-4374-9f08-1313f12c0795</t>
-  </si>
-  <si>
-    <t>relationship--f8ea8127-0143-4136-9355-f0672cc93626</t>
-  </si>
-  <si>
-    <t>relationship--9c139044-ce9e-491c-95e2-00ba93a1b5db</t>
-  </si>
-  <si>
-    <t>relationship--a74f7c11-3bc0-48bf-973f-f38cd1531a2e</t>
-  </si>
-  <si>
-    <t>relationship--7d492b91-2741-42d1-a14b-5c68ef16cdde</t>
-  </si>
-  <si>
-    <t>relationship--2e21705c-7535-43ea-971e-ae1c720f97f0</t>
-  </si>
-  <si>
-    <t>relationship--6012c812-46fa-4441-a18e-caca14be105e</t>
-  </si>
-  <si>
-    <t>relationship--7276f7e3-19cc-4f36-b52a-df9b09039d86</t>
-  </si>
-  <si>
-    <t>relationship--38b9b77e-9ac6-4123-ad64-7ee44572da1b</t>
-  </si>
-  <si>
-    <t>relationship--8ab8f626-ae23-4007-bb32-dc128a13c452</t>
-  </si>
-  <si>
-    <t>relationship--a3705dfd-d211-4b6c-b8de-a60b61232ccf</t>
-  </si>
-  <si>
-    <t>relationship--176d7e94-acc7-4510-ab33-fc50ec2eb016</t>
-  </si>
-  <si>
-    <t>relationship--72911605-8706-44a8-9133-cc55f61fbe01</t>
-  </si>
-  <si>
-    <t>relationship--3cecfb1c-8f09-451d-9727-99f8f2060f9a</t>
-  </si>
-  <si>
-    <t>relationship--889bdd3d-7042-4b09-9b8a-2c1063492550</t>
-  </si>
-  <si>
-    <t>relationship--93820292-0d07-4e8a-a732-af6f7fac18f3</t>
-  </si>
-  <si>
-    <t>relationship--d63962bf-f3fd-4159-986d-fb404f8e5c4f</t>
-  </si>
-  <si>
-    <t>relationship--8b4d20df-6e8d-48ed-ad71-b0b73b855a56</t>
-  </si>
-  <si>
-    <t>relationship--9b06ea4e-c75e-41ad-9ba0-b8050f79c4c9</t>
-  </si>
-  <si>
-    <t>relationship--304d883a-85fd-4eb0-8c79-a70babe9fa54</t>
-  </si>
-  <si>
-    <t>relationship--f2124474-a45e-4d8c-b9c3-a4485991a23e</t>
-  </si>
-  <si>
-    <t>relationship--f90a7c85-e4de-457e-b281-b8945307db07</t>
-  </si>
-  <si>
-    <t>relationship--1658c08e-93b2-490d-b21e-2dddf38e2b5c</t>
-  </si>
-  <si>
-    <t>relationship--f3fded44-1a57-418f-b6ae-29b4dbd1bc91</t>
-  </si>
-  <si>
-    <t>relationship--3f971d8b-a5a0-4f8f-b42d-a325cd802149</t>
-  </si>
-  <si>
-    <t>relationship--f45ed62a-12e3-466e-84ea-56ee39b45fe3</t>
-  </si>
-  <si>
-    <t>relationship--acab761b-d19f-4216-a982-e4e9fee04109</t>
-  </si>
-  <si>
-    <t>relationship--bd2a142c-0144-4d20-8e3d-b73ace1abff6</t>
-  </si>
-  <si>
-    <t>relationship--263060ab-6afa-4efa-8121-56ca8c19dea3</t>
-  </si>
-  <si>
-    <t>relationship--18b4ed3f-7d9c-457a-ba75-9b36acdf1b39</t>
-  </si>
-  <si>
-    <t>relationship--4bb0977b-3d05-4362-aeea-cc150865bd4b</t>
-  </si>
-  <si>
-    <t>relationship--9732d9c4-866e-4ec3-acdf-9116f0bd3293</t>
-  </si>
-  <si>
-    <t>relationship--f5e63ee5-77e5-4992-833d-257e32e5ce3e</t>
-  </si>
-  <si>
-    <t>relationship--49d946ff-1e6b-4bf2-a9f1-a9e54213b6ba</t>
-  </si>
-  <si>
-    <t>relationship--3df7af44-b568-4a7c-adf5-95885e794a2f</t>
-  </si>
-  <si>
-    <t>relationship--9e5fe4f7-cd1e-4703-bea2-829fef05d626</t>
-  </si>
-  <si>
-    <t>relationship--14bade66-db15-4761-9e73-2928a3a3891e</t>
-  </si>
-  <si>
-    <t>relationship--2acac976-88b9-4fc7-a0bd-4d03a5f3a9bf</t>
-  </si>
-  <si>
-    <t>relationship--4c3795cc-a1e9-45d1-9a1e-bbf2cde64a15</t>
-  </si>
-  <si>
-    <t>relationship--fe565642-eab5-4ff9-91e1-cea181876211</t>
-  </si>
-  <si>
-    <t>relationship--6278e5d4-ab06-4def-bece-6991bf4b857b</t>
-  </si>
-  <si>
-    <t>relationship--8ae29663-1f05-422d-ba3c-0337760daf4d</t>
-  </si>
-  <si>
-    <t>relationship--7ac36b6b-a053-4b5f-8160-03f2709d8434</t>
-  </si>
-  <si>
-    <t>relationship--33b4f3d5-4d6e-421f-a932-e2ffa44fc7a9</t>
-  </si>
-  <si>
-    <t>relationship--95d794f0-5dc8-4362-b0ff-7ed3dc1eeabd</t>
-  </si>
-  <si>
-    <t>relationship--fbf7379e-6953-413c-8932-a51888aac57e</t>
-  </si>
-  <si>
-    <t>relationship--16390e3a-f86b-4725-907f-991e84d3e0fe</t>
-  </si>
-  <si>
-    <t>relationship--c3d4eae6-f0ec-4700-91e4-270a1b5c6f38</t>
-  </si>
-  <si>
-    <t>relationship--742cbbdd-94d7-4072-9a8b-ecafc56604db</t>
-  </si>
-  <si>
-    <t>relationship--2828cfca-5ceb-4c5a-bb2f-8ffc611954fc</t>
-  </si>
-  <si>
-    <t>relationship--cb6aa417-c3bf-41e3-9e44-209705207413</t>
-  </si>
-  <si>
-    <t>relationship--9f99304a-1059-47a4-bbdf-1f76b23b8ac2</t>
-  </si>
-  <si>
-    <t>relationship--2346dccd-238f-46e8-9aba-6341e3783eda</t>
-  </si>
-  <si>
-    <t>relationship--3138c704-adf0-4cad-8d6a-ad204687d4df</t>
-  </si>
-  <si>
-    <t>relationship--0880242b-9689-482e-9459-4ebd56320f4e</t>
-  </si>
-  <si>
-    <t>relationship--9417f950-d2a7-4417-9c05-6fe57828917e</t>
-  </si>
-  <si>
-    <t>relationship--a2b54231-6b5c-40b3-a417-074b60b3b9e2</t>
-  </si>
-  <si>
-    <t>relationship--23735a53-068a-4d2a-9476-7857dd7e1b74</t>
-  </si>
-  <si>
-    <t>relationship--161fe2ca-c2dc-4d21-a9b0-95935f7d1a52</t>
+    <t>relationship--16144da2-91f9-49e6-917d-a71bbff07b37</t>
+  </si>
+  <si>
+    <t>relationship--9697c005-6797-4bf7-a837-4f028c927ee6</t>
+  </si>
+  <si>
+    <t>relationship--6e404788-5d9d-414b-a956-d54684562ead</t>
+  </si>
+  <si>
+    <t>relationship--2c434e02-6e26-4156-ae31-6b299dae7863</t>
+  </si>
+  <si>
+    <t>relationship--37a22f39-51a3-4b42-8cbf-4682cb984c5f</t>
+  </si>
+  <si>
+    <t>relationship--de3e18c5-8e55-4213-b7a5-016f634f52d6</t>
+  </si>
+  <si>
+    <t>relationship--b294a298-4572-45ba-83cd-6febe20eb9c8</t>
+  </si>
+  <si>
+    <t>relationship--2a87fd2a-b184-456a-9ff3-5287906fb03f</t>
+  </si>
+  <si>
+    <t>relationship--2984ab74-0098-40b3-910a-a4468d5b1140</t>
+  </si>
+  <si>
+    <t>relationship--f455f2ef-5c5e-4c45-ad3f-b7e6496eb027</t>
+  </si>
+  <si>
+    <t>relationship--4bc8e783-3567-4fb8-867d-b2b0591c3676</t>
+  </si>
+  <si>
+    <t>relationship--ae99f88c-b34e-48a8-b884-8751b57831c3</t>
+  </si>
+  <si>
+    <t>relationship--913af001-f7cb-4207-8322-14ef2f4f006b</t>
+  </si>
+  <si>
+    <t>relationship--fcb25d74-cfa2-45a2-af99-29eb0ad4b064</t>
+  </si>
+  <si>
+    <t>relationship--ba3d5ece-0df2-4f39-a0e6-2ab151c4f803</t>
+  </si>
+  <si>
+    <t>relationship--98d13a8f-5671-46ab-98bf-dcee471a7416</t>
+  </si>
+  <si>
+    <t>relationship--6dd55282-c047-46db-b47d-ffef75634f32</t>
+  </si>
+  <si>
+    <t>relationship--6576dbf2-9887-46d4-b7c0-077b0aa6d520</t>
+  </si>
+  <si>
+    <t>relationship--82e78eaa-a5b5-4328-a73f-d51422047701</t>
+  </si>
+  <si>
+    <t>relationship--c407b553-608e-42df-8f20-99867374029b</t>
+  </si>
+  <si>
+    <t>relationship--58cbd296-f428-4f07-9627-ef721bca5e24</t>
+  </si>
+  <si>
+    <t>relationship--4e4c1786-5c5a-49fc-bd5f-4f98209e04a8</t>
+  </si>
+  <si>
+    <t>relationship--3fd82cd0-8553-4535-9d88-2432d8d6c588</t>
+  </si>
+  <si>
+    <t>relationship--1dbbc37e-23d4-44c4-acdc-e3cac17cc385</t>
+  </si>
+  <si>
+    <t>relationship--fbde6f1d-be2f-4e5f-92a5-c9e21f6b00e6</t>
+  </si>
+  <si>
+    <t>relationship--44b541d4-16cd-4697-91ed-8959150b93ea</t>
+  </si>
+  <si>
+    <t>relationship--bc00c803-905b-483d-a214-b756ab179b45</t>
+  </si>
+  <si>
+    <t>relationship--930512ae-f088-4597-bae8-dcc756d386d6</t>
+  </si>
+  <si>
+    <t>relationship--1e3bdd39-f6fd-459b-953c-ddafac2af3ee</t>
+  </si>
+  <si>
+    <t>relationship--6cda8772-c59c-40f6-951e-7203c973239e</t>
+  </si>
+  <si>
+    <t>relationship--26435369-1682-4a9f-a340-a6ff3307ec65</t>
+  </si>
+  <si>
+    <t>relationship--46ba6b14-29ac-4278-b078-f34ba26b1be5</t>
+  </si>
+  <si>
+    <t>relationship--b0380dea-279d-4897-9888-5307871a3acb</t>
+  </si>
+  <si>
+    <t>relationship--ade84795-f059-4866-a09e-37e6ac5adf40</t>
+  </si>
+  <si>
+    <t>relationship--62bee3ce-caad-42e9-b7bd-9c2262a342cc</t>
+  </si>
+  <si>
+    <t>relationship--d7952f2c-eaf9-43a6-a7b0-b46555772b73</t>
+  </si>
+  <si>
+    <t>relationship--3d23f2db-b299-4698-8767-c4d5bc249f9c</t>
+  </si>
+  <si>
+    <t>relationship--51baad2a-4458-43c3-a534-392226563e3e</t>
+  </si>
+  <si>
+    <t>relationship--f125e8d8-5e5f-4821-9e91-21780cd1efd6</t>
+  </si>
+  <si>
+    <t>relationship--c9d89fd2-934d-49d0-bcc6-892b5bc54c05</t>
+  </si>
+  <si>
+    <t>relationship--ce4f2eda-e514-4c3d-8877-f503c4fcee9d</t>
+  </si>
+  <si>
+    <t>relationship--6c0df7e5-7d02-4aeb-961c-dc80d2bb33b6</t>
+  </si>
+  <si>
+    <t>relationship--7dc82937-c2c7-4121-b82f-1b15049d4567</t>
+  </si>
+  <si>
+    <t>relationship--1438c8ef-dd0f-46a1-a329-7a84094089a7</t>
+  </si>
+  <si>
+    <t>relationship--10b591e9-7eed-4d3f-9cb3-261d8bdf56f5</t>
+  </si>
+  <si>
+    <t>relationship--6320ca25-0dec-426b-a89f-1901840d4a9b</t>
+  </si>
+  <si>
+    <t>relationship--cc37dc30-86e3-4e5b-826c-87bc71b2f98b</t>
+  </si>
+  <si>
+    <t>relationship--434be38d-f7c2-4833-98af-4f52da9cc033</t>
+  </si>
+  <si>
+    <t>relationship--58c8f148-2f0b-40dd-9946-4e4b08b5a9e1</t>
+  </si>
+  <si>
+    <t>relationship--6e559c18-f8de-46cc-8a2c-903c7173ba23</t>
+  </si>
+  <si>
+    <t>relationship--7bccdde2-9194-47a0-a92f-44b4e77a8a1b</t>
+  </si>
+  <si>
+    <t>relationship--8cae63fe-5d4f-407d-bbdd-3ffbdacaa5f7</t>
+  </si>
+  <si>
+    <t>relationship--e15f196e-7079-436f-80ff-106dfbfcb050</t>
+  </si>
+  <si>
+    <t>relationship--5818dc97-498b-4db4-821f-eabf92cc0147</t>
+  </si>
+  <si>
+    <t>relationship--a31d3284-f6df-4832-8e81-ca077371c7a0</t>
+  </si>
+  <si>
+    <t>relationship--07d341f1-5e24-4da9-96ed-ceaeec948632</t>
+  </si>
+  <si>
+    <t>relationship--36acbe6c-f5be-48c5-8910-6f4d6a84c5b2</t>
+  </si>
+  <si>
+    <t>relationship--b079861e-56d8-44f5-9e8c-a969b05fd089</t>
+  </si>
+  <si>
+    <t>relationship--878b41f7-4aa2-4254-bda7-45809fbcf30e</t>
+  </si>
+  <si>
+    <t>relationship--05cc6a6d-7c0c-4ec8-babb-4f489f107014</t>
+  </si>
+  <si>
+    <t>relationship--8e01371e-9a5c-4f4e-b109-a7f005b94faa</t>
+  </si>
+  <si>
+    <t>relationship--5081685d-0e81-4e84-b914-876e5723e0b1</t>
+  </si>
+  <si>
+    <t>relationship--9a11a133-cf32-4216-bd62-e8d351e98517</t>
+  </si>
+  <si>
+    <t>relationship--b33a6108-0645-4a98-8bdc-2cfe83bfbd05</t>
+  </si>
+  <si>
+    <t>relationship--bf3b16c7-2687-4e50-b058-2b9980d05443</t>
+  </si>
+  <si>
+    <t>relationship--c67ab420-a3b8-4617-b942-fa34e0df8c81</t>
+  </si>
+  <si>
+    <t>relationship--c8bc29c2-0d05-4b84-b82e-576a60d9ca1b</t>
+  </si>
+  <si>
+    <t>relationship--818b14a7-3bf9-4917-974c-7283e66d21fc</t>
+  </si>
+  <si>
+    <t>relationship--d99f39d0-fb23-460a-a041-4d9557b9b445</t>
+  </si>
+  <si>
+    <t>relationship--f3c6f5e7-4e68-4633-b7d9-e2b35b32bd0d</t>
+  </si>
+  <si>
+    <t>relationship--d28c162f-cc0d-45ef-926b-5ecc38320d78</t>
+  </si>
+  <si>
+    <t>relationship--bf09b1a3-7528-424a-ad44-13d32054a3aa</t>
+  </si>
+  <si>
+    <t>relationship--2f3cdf54-d10f-43ea-8e57-ec386e7a5a04</t>
+  </si>
+  <si>
+    <t>relationship--736363d3-ad9d-49b8-8469-50f98e2ffcc6</t>
+  </si>
+  <si>
+    <t>relationship--7d80956f-0e1d-4804-83c2-3fb5e44342e0</t>
+  </si>
+  <si>
+    <t>relationship--8ed5c2d1-de73-46aa-a16a-aaed5f37518e</t>
+  </si>
+  <si>
+    <t>relationship--332abc6c-519c-49ea-8fdf-4c2ad58c5d30</t>
+  </si>
+  <si>
+    <t>relationship--65ee3d9c-ae09-4e8d-987d-6cc1d219e01f</t>
+  </si>
+  <si>
+    <t>relationship--1bee2722-fd00-4414-b078-719bb1bc13fc</t>
+  </si>
+  <si>
+    <t>relationship--e13a70ac-3b25-4075-bb54-0d44ba465878</t>
+  </si>
+  <si>
+    <t>relationship--29a3ce2b-6be4-44fb-8fae-beef5f0296a1</t>
+  </si>
+  <si>
+    <t>relationship--9c61218c-a3e3-4688-8723-8a681f5d4799</t>
+  </si>
+  <si>
+    <t>relationship--9b31e25d-8cbe-455c-954b-206d112c4a0a</t>
+  </si>
+  <si>
+    <t>relationship--da89423c-a636-491c-b7a6-20300d79e176</t>
+  </si>
+  <si>
+    <t>relationship--65d9dcda-82e0-4983-98d9-09100bf11f69</t>
+  </si>
+  <si>
+    <t>relationship--a66e5426-deea-479c-9b33-48831ef1f74f</t>
+  </si>
+  <si>
+    <t>relationship--8a7f492f-6d0f-48ef-8475-cf6d9343beae</t>
+  </si>
+  <si>
+    <t>relationship--d7cba973-52a5-4ffa-8792-fad9de0f4ff5</t>
+  </si>
+  <si>
+    <t>relationship--66c41619-1a71-4cdf-959c-b20e132a9feb</t>
+  </si>
+  <si>
+    <t>relationship--1c5a2877-55d2-47f0-852c-41cffd9ea9cd</t>
+  </si>
+  <si>
+    <t>relationship--338d5a11-cbad-444b-b042-b4aaae1152ef</t>
+  </si>
+  <si>
+    <t>relationship--15a7a091-9597-443c-9546-c8c0b6f7015e</t>
+  </si>
+  <si>
+    <t>relationship--b397365a-1c8a-4bf6-9323-b3fa37ec8120</t>
+  </si>
+  <si>
+    <t>relationship--0944d14f-213e-42c6-9227-990789faa016</t>
+  </si>
+  <si>
+    <t>relationship--93c54f83-b658-4267-9ebd-1d808cf45f79</t>
+  </si>
+  <si>
+    <t>relationship--83510ac8-d535-4650-8d81-ebdbe8b636d3</t>
+  </si>
+  <si>
+    <t>relationship--834f449c-b379-41ab-8593-fdc8a6f7da85</t>
+  </si>
+  <si>
+    <t>relationship--25bfdfd7-c584-4eee-badb-e362294f2728</t>
+  </si>
+  <si>
+    <t>relationship--6540b8e2-98fe-49f7-8a99-50d9dd1b8a11</t>
+  </si>
+  <si>
+    <t>relationship--ea9fe07e-1615-4dcf-a3bd-33abcf4ffd14</t>
+  </si>
+  <si>
+    <t>relationship--95761fd2-eff3-4bbd-a79a-d47e24029c7f</t>
+  </si>
+  <si>
+    <t>relationship--9ac65c10-b5e4-4ae1-ac04-e2577a4aff40</t>
+  </si>
+  <si>
+    <t>relationship--b8c173ac-8a9e-4765-bb1c-39b1ee53caac</t>
+  </si>
+  <si>
+    <t>relationship--117354e0-cd7d-484e-8756-87c5bb5fcd00</t>
+  </si>
+  <si>
+    <t>relationship--d435d200-8dbb-4172-80cb-ec869208eca5</t>
+  </si>
+  <si>
+    <t>relationship--eff1e690-9246-4cf9-b550-79f17cb29b68</t>
+  </si>
+  <si>
+    <t>relationship--9bae57d2-f5dc-42a0-836b-0f349e4cdc25</t>
+  </si>
+  <si>
+    <t>relationship--0156d507-7b40-45ec-8289-0f4fa5ba6163</t>
+  </si>
+  <si>
+    <t>relationship--33ab6ec3-19cf-4b49-8724-2b4af682af04</t>
+  </si>
+  <si>
+    <t>relationship--e1842498-5a34-4609-8db6-b2f82df3b197</t>
+  </si>
+  <si>
+    <t>relationship--719527aa-6dc8-4a61-a342-91d03a5c2d21</t>
+  </si>
+  <si>
+    <t>relationship--ba2437e9-e819-46a7-bab0-0878dbf9846d</t>
+  </si>
+  <si>
+    <t>relationship--818f6226-9afb-4912-b6a3-b69725ad0e2a</t>
+  </si>
+  <si>
+    <t>relationship--3a49096f-d797-4844-a514-37aadfb14943</t>
+  </si>
+  <si>
+    <t>relationship--a210a033-712a-4265-af86-ce866ebe8502</t>
+  </si>
+  <si>
+    <t>relationship--0e65dd55-8151-4a51-9adb-ad2b722c7b11</t>
+  </si>
+  <si>
+    <t>relationship--36958ad9-6617-44a9-ad62-03aa55bac03a</t>
+  </si>
+  <si>
+    <t>relationship--ace3997d-4e21-4b81-b6d6-147e08c0b0c2</t>
+  </si>
+  <si>
+    <t>relationship--65dfe9e2-f92b-41f5-a8d7-4d0cb775fd3c</t>
+  </si>
+  <si>
+    <t>relationship--57e70d24-0604-4783-99d1-8efa72bc229d</t>
+  </si>
+  <si>
+    <t>relationship--040c9390-eb5e-49cb-b5bf-d96b81a19376</t>
+  </si>
+  <si>
+    <t>relationship--d1bd4886-86ef-4466-a263-446fe6e1866f</t>
+  </si>
+  <si>
+    <t>relationship--f0b97568-130b-464d-8b32-c4d044aab10d</t>
+  </si>
+  <si>
+    <t>relationship--3dc31397-38e8-4bc1-bd09-06e562e88e3e</t>
+  </si>
+  <si>
+    <t>relationship--938ee97f-1383-42f4-a3fb-f79e9c820e3e</t>
+  </si>
+  <si>
+    <t>relationship--76049fb7-5bc2-4c9e-ba0e-297af2a4ef6b</t>
+  </si>
+  <si>
+    <t>relationship--ff825748-c271-4e23-981a-ace5d89e2f0d</t>
+  </si>
+  <si>
+    <t>relationship--c82e0390-57e7-451d-a05b-56a4cc08989b</t>
+  </si>
+  <si>
+    <t>relationship--777a2696-e49b-4777-9f59-3361cf2d959b</t>
+  </si>
+  <si>
+    <t>relationship--8bdae4af-4576-4585-9cc5-e67149a7a200</t>
+  </si>
+  <si>
+    <t>relationship--399137a2-b686-429b-a19e-996acc7a7bdb</t>
+  </si>
+  <si>
+    <t>relationship--78f7ba38-124d-49f4-aed3-9d01c6378d20</t>
+  </si>
+  <si>
+    <t>relationship--8e2c490b-78d0-4915-85f2-227774d6bb35</t>
+  </si>
+  <si>
+    <t>relationship--7d6fed15-cb67-4aeb-ba7e-4a5ac7f66e2e</t>
+  </si>
+  <si>
+    <t>relationship--93000c5d-435d-4b59-9bd9-6d18f4e88428</t>
+  </si>
+  <si>
+    <t>relationship--78cbaae0-d659-4816-9359-5700b0606cdf</t>
+  </si>
+  <si>
+    <t>relationship--ab8e5783-d185-4c0f-a17a-74ad9e6a2395</t>
+  </si>
+  <si>
+    <t>relationship--b2df047b-98d1-45d7-b379-53985bddf1c4</t>
+  </si>
+  <si>
+    <t>relationship--093ff580-0911-4ef5-aaae-92411c9b6597</t>
+  </si>
+  <si>
+    <t>relationship--16ee1bba-6e3c-440b-ba1f-56293093ae00</t>
+  </si>
+  <si>
+    <t>relationship--b884c378-1ffb-4f35-9e95-278a0657ecb7</t>
+  </si>
+  <si>
+    <t>relationship--f45365a5-32b0-417c-95f2-19c2f90abf3f</t>
+  </si>
+  <si>
+    <t>relationship--fbc3460b-ad11-409e-8859-f19a4ebe8d2e</t>
+  </si>
+  <si>
+    <t>relationship--d0393c1a-f522-4c8a-b58c-a9946069de19</t>
+  </si>
+  <si>
+    <t>relationship--155f9979-73ec-4eba-8808-38de97758784</t>
+  </si>
+  <si>
+    <t>relationship--f85f0758-4c57-4e59-a2b0-dd5977a28769</t>
+  </si>
+  <si>
+    <t>relationship--cc9b386b-845a-4409-a53c-e88fe3165ca7</t>
+  </si>
+  <si>
+    <t>relationship--c02574e7-28f8-4149-9e60-de548f2b2739</t>
+  </si>
+  <si>
+    <t>relationship--c70d52db-bc94-4b2e-af45-20f3874bfedd</t>
+  </si>
+  <si>
+    <t>relationship--e4d5e664-a09e-41aa-8901-163d02b7287b</t>
+  </si>
+  <si>
+    <t>relationship--3b3277ba-6e98-4c8e-8b72-d65d2c00ae61</t>
+  </si>
+  <si>
+    <t>relationship--190fb4f5-b465-4775-9528-46d207d120b2</t>
+  </si>
+  <si>
+    <t>relationship--12db5486-053c-48ed-bb49-48b1e4b11391</t>
+  </si>
+  <si>
+    <t>relationship--fc4c3558-5f44-4a25-898a-91cd7a53e0c4</t>
+  </si>
+  <si>
+    <t>relationship--32fbbc5a-d409-4e61-9a20-e1c8ef9a9f42</t>
+  </si>
+  <si>
+    <t>relationship--443f6959-879a-43a2-ae33-c42f99cf5108</t>
+  </si>
+  <si>
+    <t>relationship--63d649b8-b431-413e-b07d-eca5e0019b2a</t>
+  </si>
+  <si>
+    <t>relationship--8302cd38-5016-42ed-accb-70cdb1d2996e</t>
+  </si>
+  <si>
+    <t>relationship--461e13fb-702e-42e7-91b5-f27c6db3ea70</t>
+  </si>
+  <si>
+    <t>relationship--b85d0c7b-f276-4a67-a101-da016bce172a</t>
+  </si>
+  <si>
+    <t>relationship--b0d665a3-7b3c-4aa3-9687-a3a5368ac34e</t>
+  </si>
+  <si>
+    <t>relationship--3101592e-1242-464d-adcb-9c68c43f6ac1</t>
+  </si>
+  <si>
+    <t>relationship--6e72e46e-9f47-43db-9851-59d899089853</t>
+  </si>
+  <si>
+    <t>relationship--d872ba7d-f1bd-4e7d-83cb-4237e5a6ccae</t>
+  </si>
+  <si>
+    <t>relationship--205a45c2-7248-43c9-8fbc-b25eb7af9d3e</t>
+  </si>
+  <si>
+    <t>relationship--4b2a8dc7-2b7b-42ab-90c2-c202d6c481e9</t>
+  </si>
+  <si>
+    <t>relationship--bc9a8aa8-b287-4ec4-bb2d-5f64eadcc530</t>
+  </si>
+  <si>
+    <t>relationship--fa65970c-ac67-4d39-aaf4-cd3c7bbbadcd</t>
+  </si>
+  <si>
+    <t>relationship--b781b174-17d4-41fa-879e-962fa3c6472e</t>
+  </si>
+  <si>
+    <t>relationship--ec58069d-2af0-4181-bac9-4dddda88c28c</t>
+  </si>
+  <si>
+    <t>relationship--f8ae12cf-66ec-4c01-a250-46bb97f99c7d</t>
+  </si>
+  <si>
+    <t>relationship--6e8f3632-6158-4971-bf6c-f6b75abaa66d</t>
+  </si>
+  <si>
+    <t>relationship--3d819923-9d97-4a8b-a67c-30fde21645b9</t>
+  </si>
+  <si>
+    <t>relationship--f3e7964d-4204-43d9-95ba-a61a39073b86</t>
+  </si>
+  <si>
+    <t>relationship--a9a82add-18b6-4428-b7d4-a07995c91849</t>
+  </si>
+  <si>
+    <t>relationship--8df00cdb-e745-4f6f-b241-b40ee4cad23c</t>
+  </si>
+  <si>
+    <t>relationship--4f13473b-9a37-4531-b782-850ced97e89d</t>
+  </si>
+  <si>
+    <t>relationship--8b6fa31a-3839-49f7-9e18-677cc43b927d</t>
+  </si>
+  <si>
+    <t>relationship--2fb417b5-205b-4b9f-98fc-c9db2c7172b3</t>
+  </si>
+  <si>
+    <t>relationship--24a70091-a353-470d-81e3-cf75b2979c7c</t>
+  </si>
+  <si>
+    <t>relationship--63722a18-6f07-4a93-8e38-135c8fbcbb56</t>
+  </si>
+  <si>
+    <t>relationship--d43afa20-2d6c-47c9-abbb-fba45f539dc7</t>
+  </si>
+  <si>
+    <t>relationship--e513611f-dbb7-41ad-8e96-eeab94495952</t>
   </si>
   <si>
     <t>T0030</t>
@@ -4101,253 +4101,253 @@
     <t>Смена алфавита родного языка</t>
   </si>
   <si>
-    <t>attack-pattern--22337eab-4ab5-4577-a766-4a514a636fe2</t>
-  </si>
-  <si>
-    <t>attack-pattern--d71852a6-d08a-4937-b2b1-ccf143798754</t>
-  </si>
-  <si>
-    <t>attack-pattern--67fd1251-9ad0-415e-94db-14c6fcda7c8c</t>
-  </si>
-  <si>
-    <t>attack-pattern--c55f58f1-faf2-498e-84f2-59993e1ecbcc</t>
-  </si>
-  <si>
-    <t>attack-pattern--1f8e90a1-2fa1-4e0c-9de7-2a6b61fc3412</t>
-  </si>
-  <si>
-    <t>attack-pattern--5e67abdd-9625-497c-8eed-591b2d0091a8</t>
-  </si>
-  <si>
-    <t>attack-pattern--8861e444-81bb-468e-9fc5-8b7e401e8898</t>
-  </si>
-  <si>
-    <t>attack-pattern--71b8603d-1b4a-45dd-bdc5-58df6fe6a1cb</t>
-  </si>
-  <si>
-    <t>attack-pattern--07605117-d49e-4edb-b205-a42d341fbafe</t>
-  </si>
-  <si>
-    <t>attack-pattern--0de3e487-7362-4416-91f8-3c71cc10d76d</t>
-  </si>
-  <si>
-    <t>attack-pattern--36fadd8e-e035-4c50-be0d-258be309a516</t>
-  </si>
-  <si>
-    <t>attack-pattern--9596e8a1-16fa-466f-b16e-b567018e83c6</t>
-  </si>
-  <si>
-    <t>attack-pattern--137a55c1-3751-4f3e-b038-0a8a31ae7b53</t>
-  </si>
-  <si>
-    <t>attack-pattern--ef5c8e81-c4de-408e-a0bb-eeba03e4ef41</t>
-  </si>
-  <si>
-    <t>attack-pattern--f62f4a3e-70ad-4d66-978f-70460748790e</t>
-  </si>
-  <si>
-    <t>attack-pattern--d4d22a9d-86be-4ed6-bb79-7792aad443f3</t>
-  </si>
-  <si>
-    <t>attack-pattern--4a811ffb-e200-4e7b-a48d-5dbb2e05d21b</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b4499c1-7976-4838-ac5f-1b2503e91894</t>
-  </si>
-  <si>
-    <t>attack-pattern--2bb142f3-19c9-4d2d-ab6b-e91a6d1eb45d</t>
-  </si>
-  <si>
-    <t>attack-pattern--f60c3210-890a-4015-a4a9-e1966101ed5d</t>
-  </si>
-  <si>
-    <t>attack-pattern--6a388bfd-b3f8-4136-a3d0-3b6c92b62616</t>
-  </si>
-  <si>
-    <t>attack-pattern--3953a646-ca74-4d27-bb4b-801773351821</t>
-  </si>
-  <si>
-    <t>attack-pattern--c985b114-66f8-43e8-a9d5-09f7dcce76d2</t>
-  </si>
-  <si>
-    <t>attack-pattern--9861afc3-113a-4f8e-ba90-12d851653a4c</t>
-  </si>
-  <si>
-    <t>attack-pattern--6819df95-06a3-4c71-874f-8daea090f07e</t>
-  </si>
-  <si>
-    <t>attack-pattern--c671af96-e92c-44ff-820d-00bdb7de4fca</t>
-  </si>
-  <si>
-    <t>attack-pattern--d984185b-2502-414b-969d-f165cdeedc31</t>
-  </si>
-  <si>
-    <t>attack-pattern--03024756-3f6a-42b3-b93e-2d31c7ce6b6b</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a5da3da-67cf-4659-bb91-0b28685766a1</t>
-  </si>
-  <si>
-    <t>attack-pattern--b3a3b655-dacd-4ee5-bae1-68801c3d15dc</t>
-  </si>
-  <si>
-    <t>attack-pattern--2f0e072e-5d5e-458e-a5c3-8efbaef46084</t>
-  </si>
-  <si>
-    <t>attack-pattern--8a804fba-621a-4868-b128-51cebf0ad2b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--3eff3cd8-fbaf-4e5d-b38e-c72604acb3ce</t>
-  </si>
-  <si>
-    <t>attack-pattern--cbff6b3a-8340-4986-9183-3c02b87fd1b2</t>
-  </si>
-  <si>
-    <t>attack-pattern--c93829ec-d90f-41a9-9191-466a6365de51</t>
-  </si>
-  <si>
-    <t>attack-pattern--9facc2a5-8243-49aa-96cb-a94ef85b25c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--9d3f3422-f494-42ab-9385-bc4e8ef727ca</t>
-  </si>
-  <si>
-    <t>attack-pattern--c7ccd834-4f08-4829-96ae-45e58d47945f</t>
-  </si>
-  <si>
-    <t>attack-pattern--b0851c83-e4d2-41c1-b5de-9115df406339</t>
-  </si>
-  <si>
-    <t>attack-pattern--0b6448a8-18a4-4d48-bfcf-172a74724542</t>
-  </si>
-  <si>
-    <t>attack-pattern--76b6c6fb-ce17-427d-b717-16011ae54b6e</t>
-  </si>
-  <si>
-    <t>attack-pattern--40f36bf9-2850-4992-b47f-4abe909a0e93</t>
-  </si>
-  <si>
-    <t>attack-pattern--02964caf-d52a-4d68-abcc-cdd1ef5fa69d</t>
-  </si>
-  <si>
-    <t>attack-pattern--cc782e40-0ae3-4f6d-94cb-2828cb2d5005</t>
-  </si>
-  <si>
-    <t>attack-pattern--09c9ca23-10d8-4f0f-a7dd-e99bb022299a</t>
-  </si>
-  <si>
-    <t>attack-pattern--9162f78a-1b72-4adc-9f8b-0a6b6410a3a7</t>
-  </si>
-  <si>
-    <t>attack-pattern--9e90f9e3-ced7-476d-acac-467e8c865ca0</t>
-  </si>
-  <si>
-    <t>attack-pattern--7ee9829e-072b-48f0-b801-b5b627c8bf1a</t>
-  </si>
-  <si>
-    <t>attack-pattern--ea9a2533-0faa-4b9d-bb0e-237ca902e1d7</t>
-  </si>
-  <si>
-    <t>attack-pattern--da48c22f-a5e2-41e7-97e4-07bfc4156350</t>
-  </si>
-  <si>
-    <t>attack-pattern--6e962dbe-f818-407b-b5a6-3eec9fbe9ec2</t>
-  </si>
-  <si>
-    <t>attack-pattern--6f08f0ef-8704-4d0e-90f5-ad421918d899</t>
-  </si>
-  <si>
-    <t>attack-pattern--09059676-291f-4053-a7b5-17d93eb87d30</t>
-  </si>
-  <si>
-    <t>attack-pattern--4b8920a8-f486-4065-aff8-4e7b6ee8b829</t>
-  </si>
-  <si>
-    <t>attack-pattern--3d1653fe-5ea0-4eb0-8c78-f849ecc43e11</t>
-  </si>
-  <si>
-    <t>attack-pattern--41699f0f-f822-4dbc-b201-dca7ac3eddce</t>
-  </si>
-  <si>
-    <t>attack-pattern--b34ebb98-d962-4987-8399-890eef9c69fe</t>
-  </si>
-  <si>
-    <t>attack-pattern--738e1811-a9a5-4407-be43-b726fd7e7589</t>
-  </si>
-  <si>
-    <t>attack-pattern--86f1c7c0-561e-4b45-97c0-faad41484e38</t>
-  </si>
-  <si>
-    <t>attack-pattern--d5f24756-885a-43f1-a9f0-b0088651bbc3</t>
-  </si>
-  <si>
-    <t>attack-pattern--c6da22a5-ceb4-4f40-a3bc-bcd6e655d591</t>
-  </si>
-  <si>
-    <t>attack-pattern--d38398cd-b820-4626-9510-465d56ba906c</t>
-  </si>
-  <si>
-    <t>attack-pattern--36e1d7c1-2f0e-41c6-8aee-177df4bdbc61</t>
-  </si>
-  <si>
-    <t>attack-pattern--0d6e1a1e-2c33-4280-86f2-8a1d0049b089</t>
-  </si>
-  <si>
-    <t>attack-pattern--a882288f-98fe-4c75-859a-17d669c08376</t>
-  </si>
-  <si>
-    <t>attack-pattern--5df092aa-9e0d-440d-8aa0-5f9988432ae3</t>
-  </si>
-  <si>
-    <t>attack-pattern--edd49cde-2190-45a8-9277-0fafcda1502c</t>
-  </si>
-  <si>
-    <t>attack-pattern--a87aa45d-2118-4e87-af92-e75e367453c9</t>
-  </si>
-  <si>
-    <t>attack-pattern--5f90feb8-5507-456c-9d1d-0e0e3cce55de</t>
-  </si>
-  <si>
-    <t>attack-pattern--d051e585-aa48-4964-b54e-2e08adc472f9</t>
-  </si>
-  <si>
-    <t>attack-pattern--edcb13e5-fbb1-4396-9e8c-1e3fe9dde52c</t>
-  </si>
-  <si>
-    <t>attack-pattern--2d723928-4bb8-45b5-86d4-a6f2398ca02f</t>
-  </si>
-  <si>
-    <t>attack-pattern--3c5f8bcd-ee2b-4396-9e79-3c99fcc96d81</t>
-  </si>
-  <si>
-    <t>attack-pattern--12023694-fdfd-480d-990d-fefa0cc12655</t>
-  </si>
-  <si>
-    <t>attack-pattern--ed457228-1fd9-4a65-ac85-388ba6460f94</t>
-  </si>
-  <si>
-    <t>attack-pattern--b2df162e-6cd7-4286-8841-dbeff90a7e20</t>
-  </si>
-  <si>
-    <t>attack-pattern--63335f7f-c1d8-42d3-bab5-4055c59e6a1e</t>
-  </si>
-  <si>
-    <t>attack-pattern--f2e939fc-283e-4bea-9fbf-f17acac31435</t>
-  </si>
-  <si>
-    <t>attack-pattern--8f3de97b-1ed5-4594-9889-41cd32d8adf5</t>
-  </si>
-  <si>
-    <t>attack-pattern--e1c78d1f-6f07-4f4b-9220-6d455354bc64</t>
-  </si>
-  <si>
-    <t>attack-pattern--02c5997b-a7da-48ac-96da-c4daa1aafc35</t>
-  </si>
-  <si>
-    <t>attack-pattern--fef3fc3b-399c-41e0-8c76-a6eb1d014ada</t>
-  </si>
-  <si>
-    <t>attack-pattern--77c6e8eb-0074-49c8-90cd-9c830db4859f</t>
+    <t>attack-pattern--d67e92a1-567a-4443-b196-42eee7df7df9</t>
+  </si>
+  <si>
+    <t>attack-pattern--f87361eb-4cc0-472a-9d20-d8814c3dcb83</t>
+  </si>
+  <si>
+    <t>attack-pattern--11df0e1b-fb0b-495a-8517-fe9629386cc7</t>
+  </si>
+  <si>
+    <t>attack-pattern--69b5ecb8-ed59-476a-a8d0-692d61060065</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1616020-3221-457d-9111-770be3da803f</t>
+  </si>
+  <si>
+    <t>attack-pattern--23537b01-052d-4788-a1c5-ac64ea3a5440</t>
+  </si>
+  <si>
+    <t>attack-pattern--b1ae5e87-2d91-4460-ab24-a874f71d0aa3</t>
+  </si>
+  <si>
+    <t>attack-pattern--14ddac56-e61c-489c-9f2a-0ead47acab72</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfe0ba66-044c-4fae-899d-2776ecd25970</t>
+  </si>
+  <si>
+    <t>attack-pattern--7302168b-1756-4aa2-9831-57b042e5e79c</t>
+  </si>
+  <si>
+    <t>attack-pattern--0e9f8dfa-7044-47a4-99c4-b8108e0c3531</t>
+  </si>
+  <si>
+    <t>attack-pattern--541f9c2f-5e7e-40bd-8807-e27b27bf27f9</t>
+  </si>
+  <si>
+    <t>attack-pattern--d1450cbb-9ca9-4637-a3d4-415897d678b3</t>
+  </si>
+  <si>
+    <t>attack-pattern--f8863479-abf3-40aa-909f-422ff587ef75</t>
+  </si>
+  <si>
+    <t>attack-pattern--1c3cc896-6014-4a38-bb84-f755661f9f8a</t>
+  </si>
+  <si>
+    <t>attack-pattern--3d477757-3882-43e5-b3b5-5c453472af4e</t>
+  </si>
+  <si>
+    <t>attack-pattern--0a36cf96-d155-4205-badf-fce21153e3d3</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f543b48-8526-45f6-9f4c-c0aabf08b950</t>
+  </si>
+  <si>
+    <t>attack-pattern--f7a7642e-6431-4d94-8930-784669743a6e</t>
+  </si>
+  <si>
+    <t>attack-pattern--d8fec2ab-fe86-4530-9801-bbbe5c3baf44</t>
+  </si>
+  <si>
+    <t>attack-pattern--77f583b6-9202-4712-9a61-f28cba87bf1b</t>
+  </si>
+  <si>
+    <t>attack-pattern--ca19f909-8e73-4014-ab69-a521482caa77</t>
+  </si>
+  <si>
+    <t>attack-pattern--e06e27d3-c18f-4bac-9bb6-17121de4850b</t>
+  </si>
+  <si>
+    <t>attack-pattern--0f207f69-c49f-4bd9-a2c8-81d5903af798</t>
+  </si>
+  <si>
+    <t>attack-pattern--d039ccb5-695e-4e9c-903d-4a25d80a5e91</t>
+  </si>
+  <si>
+    <t>attack-pattern--281cf3bf-8184-4148-8d26-8ae24ac5facd</t>
+  </si>
+  <si>
+    <t>attack-pattern--20e9f442-a9aa-49d2-86e7-10b3677d2b71</t>
+  </si>
+  <si>
+    <t>attack-pattern--7b5e8502-6625-4bfb-becf-4701773fc345</t>
+  </si>
+  <si>
+    <t>attack-pattern--01cef48e-e90c-42c2-b99f-c6ce6b48b026</t>
+  </si>
+  <si>
+    <t>attack-pattern--954103ab-7172-4bc3-80d2-6eda761140c7</t>
+  </si>
+  <si>
+    <t>attack-pattern--47a73afc-602e-4840-98f7-559a0583a02f</t>
+  </si>
+  <si>
+    <t>attack-pattern--ce173a13-3838-4451-bcde-529c8c9cbf4d</t>
+  </si>
+  <si>
+    <t>attack-pattern--0c6b2071-1b00-4c4e-ad42-c086fe85e44d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3b7ebd5a-2989-4a5f-8187-7dcbb6319ecd</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c2787d0-9bb3-4445-baf7-affe99ffc75d</t>
+  </si>
+  <si>
+    <t>attack-pattern--255d85ab-8ae5-4855-9d4d-398d57bfb428</t>
+  </si>
+  <si>
+    <t>attack-pattern--ab6eb169-9d35-462e-8540-e600dcfcc755</t>
+  </si>
+  <si>
+    <t>attack-pattern--a67dba4e-5c9c-4a96-8564-cc1477847aa2</t>
+  </si>
+  <si>
+    <t>attack-pattern--2665c1bf-c793-4ff8-81e1-8cdfb042a050</t>
+  </si>
+  <si>
+    <t>attack-pattern--01660591-eff8-4002-8b86-edbc8ddcff75</t>
+  </si>
+  <si>
+    <t>attack-pattern--df7b78e3-6709-4b71-ae0c-08ed1a47de6b</t>
+  </si>
+  <si>
+    <t>attack-pattern--31403032-89b6-4a29-af26-bdb2c907f869</t>
+  </si>
+  <si>
+    <t>attack-pattern--e1500254-a805-457b-9c9f-eaa7ed4441c2</t>
+  </si>
+  <si>
+    <t>attack-pattern--15b42e50-034b-48ec-a530-08f4da421ced</t>
+  </si>
+  <si>
+    <t>attack-pattern--2eccd110-1bf6-4854-a82c-0a45775e907f</t>
+  </si>
+  <si>
+    <t>attack-pattern--bbbea8cd-eb4e-4314-abc8-2293225ab5e6</t>
+  </si>
+  <si>
+    <t>attack-pattern--ba18aeed-1fa0-4221-b5c3-2951c695226d</t>
+  </si>
+  <si>
+    <t>attack-pattern--58aadf94-c0fc-45fe-b84d-86af05ac2a41</t>
+  </si>
+  <si>
+    <t>attack-pattern--f409ed58-993e-4cd3-816b-35cb16df5f13</t>
+  </si>
+  <si>
+    <t>attack-pattern--3408f6b9-9851-47a8-8c46-591cab11c267</t>
+  </si>
+  <si>
+    <t>attack-pattern--661bd189-a8b3-42ff-bf5b-33de03ae6136</t>
+  </si>
+  <si>
+    <t>attack-pattern--7ef5f9c4-8044-44bc-88a6-9395e47e160a</t>
+  </si>
+  <si>
+    <t>attack-pattern--d2982864-148c-45ed-9a9d-73124e552f59</t>
+  </si>
+  <si>
+    <t>attack-pattern--60789ba9-9b1e-4a2d-804d-b16342fe5f3d</t>
+  </si>
+  <si>
+    <t>attack-pattern--63e9746b-4223-4c4d-bb27-a4c2f724f832</t>
+  </si>
+  <si>
+    <t>attack-pattern--b6ab653b-b93b-46b8-9fc3-d24ccf9a86a1</t>
+  </si>
+  <si>
+    <t>attack-pattern--59e9ef1f-3d12-4523-a3ac-0b4c11c35573</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c3ab581-f839-4439-bf70-a00298d8cbb7</t>
+  </si>
+  <si>
+    <t>attack-pattern--b7f8cff2-87c7-48c1-aeb7-5cf9187b1090</t>
+  </si>
+  <si>
+    <t>attack-pattern--40ddc318-d9d7-4035-80a9-21f5de23c666</t>
+  </si>
+  <si>
+    <t>attack-pattern--9a46e5ee-7093-4048-9d7e-501463c0424d</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c78bc06-b7d9-4d72-87cc-3896a83a79c1</t>
+  </si>
+  <si>
+    <t>attack-pattern--3ec89812-91d7-48b1-aa07-b78e44175f91</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a21e55e-d799-41ce-a799-461e1995bd5a</t>
+  </si>
+  <si>
+    <t>attack-pattern--5ba903c1-2421-4964-8ca4-f56dcc96a1c3</t>
+  </si>
+  <si>
+    <t>attack-pattern--f6f80852-da09-4571-bd87-ab371a289296</t>
+  </si>
+  <si>
+    <t>attack-pattern--1337b0db-4d5f-447f-83d1-3682c83da1be</t>
+  </si>
+  <si>
+    <t>attack-pattern--50e11ffa-fd63-4200-af97-d723ceb03f87</t>
+  </si>
+  <si>
+    <t>attack-pattern--3c07dbf7-3e3e-47d9-b439-53989a64f430</t>
+  </si>
+  <si>
+    <t>attack-pattern--948886a4-efe9-40cc-8153-3370afff323e</t>
+  </si>
+  <si>
+    <t>attack-pattern--c21a61e0-99df-4c01-abf2-5e46d8345613</t>
+  </si>
+  <si>
+    <t>attack-pattern--d4ba7ff5-0107-437e-853c-b8c4d37ea441</t>
+  </si>
+  <si>
+    <t>attack-pattern--c69305fb-035a-4c61-8929-2e22cea42d61</t>
+  </si>
+  <si>
+    <t>attack-pattern--39c46a2f-f777-48c7-b903-20ce80bca89b</t>
+  </si>
+  <si>
+    <t>attack-pattern--9f4aa723-88b2-42d4-b7f0-58bfc3f42435</t>
+  </si>
+  <si>
+    <t>attack-pattern--9b1b420b-4d1a-4108-a086-73ba81138b1a</t>
+  </si>
+  <si>
+    <t>attack-pattern--cfd09f3f-20c2-4148-a51e-c7533a4f6866</t>
+  </si>
+  <si>
+    <t>attack-pattern--5da8aa0b-7c9c-4638-bc17-9ed6bf1aafa6</t>
+  </si>
+  <si>
+    <t>attack-pattern--2685f739-43ca-4258-8e7f-0cf545de3477</t>
+  </si>
+  <si>
+    <t>attack-pattern--b9b7420d-58cf-49d6-9884-18e4d72f0a38</t>
+  </si>
+  <si>
+    <t>attack-pattern--1a522e5a-e65b-443f-8aae-2bc39534e85e</t>
+  </si>
+  <si>
+    <t>attack-pattern--f2121d22-b6ab-4c8d-b1a6-a65df30bd836</t>
+  </si>
+  <si>
+    <t>attack-pattern--faf29c5e-51f3-4afd-9b72-70769986b561</t>
   </si>
   <si>
     <t>technique</t>
@@ -4831,1027 +4831,1027 @@
     <t>Изъятие у УССР контроля над внешней политикой, армией, внешней торговлей, транспортом и связью через Конституцию СССР 1924 года с передачей их в ведение союзных наркоматов. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--2e3ad4d6-4817-44d6-a810-1f698a978be1</t>
-  </si>
-  <si>
-    <t>relationship--15f996d2-eaeb-4d08-a6d3-775e6a2f8fbc</t>
-  </si>
-  <si>
-    <t>relationship--04fb06f2-36c2-42da-ba70-c29842d9f3a8</t>
-  </si>
-  <si>
-    <t>relationship--d36f4e6e-728d-4a94-bf5f-9656edeea1da</t>
-  </si>
-  <si>
-    <t>relationship--d15c118c-55a7-4935-aeef-0806723fc244</t>
-  </si>
-  <si>
-    <t>relationship--1fd62ded-faf1-40f6-9a80-8936866af763</t>
-  </si>
-  <si>
-    <t>relationship--2d8b27f2-c98c-4b39-88f4-5b574cb9b16e</t>
-  </si>
-  <si>
-    <t>relationship--c5079e4d-1e54-477a-8e87-858564de885c</t>
-  </si>
-  <si>
-    <t>relationship--0b7931ad-13c9-4e31-bb22-89a1b3b5c3d8</t>
-  </si>
-  <si>
-    <t>relationship--3e43cceb-804e-4e9f-9eb9-980ceea91b04</t>
-  </si>
-  <si>
-    <t>relationship--ba91c710-f339-4c01-a363-be7e7bbf27f3</t>
-  </si>
-  <si>
-    <t>relationship--aac5ca0c-b5f4-4d56-afe6-efa851eef9d5</t>
-  </si>
-  <si>
-    <t>relationship--3237f077-a7a4-4db3-bcc0-8dd58cdf8f28</t>
-  </si>
-  <si>
-    <t>relationship--0612d69c-356a-433b-b2be-0041a7ea6311</t>
-  </si>
-  <si>
-    <t>relationship--736d6234-a45a-4b13-8d65-9d78531f8c15</t>
-  </si>
-  <si>
-    <t>relationship--4a4c98b5-4eb3-4f7b-9472-10828dfa027a</t>
-  </si>
-  <si>
-    <t>relationship--e89ed10a-5ac2-4324-a479-c757c443c9f2</t>
-  </si>
-  <si>
-    <t>relationship--a1ce28ab-391c-4839-864d-65981ace7e50</t>
-  </si>
-  <si>
-    <t>relationship--81f9f1de-ff42-4716-b8ae-58db05eb14e9</t>
-  </si>
-  <si>
-    <t>relationship--5a4845b2-82b0-4319-a7df-3ec49cd4caa1</t>
-  </si>
-  <si>
-    <t>relationship--aba5c12c-37dd-4141-988c-c40248ab20e4</t>
-  </si>
-  <si>
-    <t>relationship--9532b2f2-fe57-4003-81c0-ced8230649a0</t>
-  </si>
-  <si>
-    <t>relationship--9e2bd625-9c8a-491b-88af-fa56bef0cb01</t>
-  </si>
-  <si>
-    <t>relationship--a9e9f64b-4279-4970-b5a6-a888ab472781</t>
-  </si>
-  <si>
-    <t>relationship--7ef9f9d7-6b11-4527-931d-4be1859b8455</t>
-  </si>
-  <si>
-    <t>relationship--95e3cb37-74b2-4501-9ea7-56692dc24879</t>
-  </si>
-  <si>
-    <t>relationship--ac49cbf5-277a-474b-8b5a-db00c63fa9e2</t>
-  </si>
-  <si>
-    <t>relationship--248c0613-5d29-4b5a-b780-9d3faba8e10b</t>
-  </si>
-  <si>
-    <t>relationship--9a059b65-1ded-4470-b2f6-42747e77ba68</t>
-  </si>
-  <si>
-    <t>relationship--b3c79ef3-3d27-463c-9284-93bdb89ba863</t>
-  </si>
-  <si>
-    <t>relationship--dda52d9b-48f7-437a-bf7f-8d1431a370bf</t>
-  </si>
-  <si>
-    <t>relationship--ab8b6530-fe93-49bc-abaf-b6f11504f098</t>
-  </si>
-  <si>
-    <t>relationship--c53182a4-e78b-4543-affd-b08ddd57606a</t>
-  </si>
-  <si>
-    <t>relationship--1adbac6f-5b26-41e7-8629-024177c49d43</t>
-  </si>
-  <si>
-    <t>relationship--5bbd8003-05ff-4bff-bdb6-f3e7069a9d56</t>
-  </si>
-  <si>
-    <t>relationship--1860e0ed-660b-4853-9ff9-acf4008a1c60</t>
-  </si>
-  <si>
-    <t>relationship--0f626ab6-b22c-43cc-a529-427f27d4cd4a</t>
-  </si>
-  <si>
-    <t>relationship--b121753a-fe68-4d5c-a739-da48fca417e4</t>
-  </si>
-  <si>
-    <t>relationship--7ce06181-38d2-41b8-a75f-79d0e7ec6bae</t>
-  </si>
-  <si>
-    <t>relationship--783a6d7a-1c0e-4d55-84fe-375b495a73ef</t>
-  </si>
-  <si>
-    <t>relationship--91896033-1306-4164-ad3c-f7c9af44a58b</t>
-  </si>
-  <si>
-    <t>relationship--5e4917f1-5bd5-4bfc-a170-040e70d2f3c1</t>
-  </si>
-  <si>
-    <t>relationship--7990f3bc-8d0a-42cd-acaf-0bb0cb647a90</t>
-  </si>
-  <si>
-    <t>relationship--bfc9348a-9983-430a-8931-b7e35613d7b2</t>
-  </si>
-  <si>
-    <t>relationship--b9f40bc8-8e9f-473f-9d66-672b653721f9</t>
-  </si>
-  <si>
-    <t>relationship--0848b07e-1b83-4ee0-82e2-d8f1e17ee99a</t>
-  </si>
-  <si>
-    <t>relationship--d7eafec2-7c5e-4a6e-ad62-d713cc14b414</t>
-  </si>
-  <si>
-    <t>relationship--84602b4a-38d6-48e6-9d35-7e4275415071</t>
-  </si>
-  <si>
-    <t>relationship--617026e5-fd9d-49ea-a9d1-a84d87f652f0</t>
-  </si>
-  <si>
-    <t>relationship--69b45d78-b769-4614-b1e1-58942289ffe1</t>
-  </si>
-  <si>
-    <t>relationship--beecf6d7-36fe-43f7-a1da-7315c042bd10</t>
-  </si>
-  <si>
-    <t>relationship--74af7e90-dd63-418a-b257-84f0e3aee0dc</t>
-  </si>
-  <si>
-    <t>relationship--41dbbfbb-bb93-4e80-9a3d-4f84a36e5826</t>
-  </si>
-  <si>
-    <t>relationship--4962e2ed-68d1-4488-86de-3a303a238a2b</t>
-  </si>
-  <si>
-    <t>relationship--6647a361-ee08-4d1c-9707-c5313ef988a8</t>
-  </si>
-  <si>
-    <t>relationship--afaad920-53d7-45fe-b133-cb0ed1b0d297</t>
-  </si>
-  <si>
-    <t>relationship--733568b7-95ed-47e0-a741-ccf995cdf001</t>
-  </si>
-  <si>
-    <t>relationship--ac8da5f2-078f-4051-a6ab-82ef4221043a</t>
-  </si>
-  <si>
-    <t>relationship--52a05cca-efba-4875-8158-74fc9db94cbc</t>
-  </si>
-  <si>
-    <t>relationship--a62fe462-c0fd-45ea-bd02-b7ae576b0a77</t>
-  </si>
-  <si>
-    <t>relationship--71253b77-8675-46fb-b8d7-4fbbf8f381ab</t>
-  </si>
-  <si>
-    <t>relationship--e2bbc820-11de-4385-9f33-39aed660e08e</t>
-  </si>
-  <si>
-    <t>relationship--de9f3fc1-16dd-424d-98e0-7ce81ed92ce3</t>
-  </si>
-  <si>
-    <t>relationship--c554de6a-4ca1-4258-9c30-de58c01f848e</t>
-  </si>
-  <si>
-    <t>relationship--88bb3243-d057-4c18-902e-4135bf1045fc</t>
-  </si>
-  <si>
-    <t>relationship--d55af97a-39e5-47a7-8f40-7c20c61e8654</t>
-  </si>
-  <si>
-    <t>relationship--62b71848-b849-4080-911f-aba18b3b6a1c</t>
-  </si>
-  <si>
-    <t>relationship--8410eca9-cfe9-4cb2-bc0b-34794e3a1dc1</t>
-  </si>
-  <si>
-    <t>relationship--15401ffc-3093-40be-9f11-825cc9e3484e</t>
-  </si>
-  <si>
-    <t>relationship--2a84694e-0961-4bb8-b770-22dd2420c4af</t>
-  </si>
-  <si>
-    <t>relationship--2cfb2ee2-2574-453e-bb71-d1330a8c310f</t>
-  </si>
-  <si>
-    <t>relationship--09190a94-3902-4948-94cf-f1859831afec</t>
-  </si>
-  <si>
-    <t>relationship--265d1479-d38b-4859-b41b-d3240b6ab7aa</t>
-  </si>
-  <si>
-    <t>relationship--ff33a5bc-6d82-452d-937b-ec9c08cdc50b</t>
-  </si>
-  <si>
-    <t>relationship--803e9bbf-161a-4e5e-9731-a3dea5f24369</t>
-  </si>
-  <si>
-    <t>relationship--e4d6e73a-af5a-4d83-b335-2e083045ce97</t>
-  </si>
-  <si>
-    <t>relationship--1d17f76d-5b3d-4615-adab-9aba717c3f50</t>
-  </si>
-  <si>
-    <t>relationship--5d161d88-7f5e-4e40-9601-7425c8fad16d</t>
-  </si>
-  <si>
-    <t>relationship--8debb06e-d43e-4e19-bf07-4a870ec0fb66</t>
-  </si>
-  <si>
-    <t>relationship--ad8449b4-ef75-4f64-a179-6c16292e769a</t>
-  </si>
-  <si>
-    <t>relationship--4a10a6c1-b091-4a62-b86d-39236c9798a0</t>
-  </si>
-  <si>
-    <t>relationship--35b3910e-ed22-4888-bfc5-f349e0bb22c1</t>
-  </si>
-  <si>
-    <t>relationship--09310efa-0ebb-4cef-be5c-0c04372cbab4</t>
-  </si>
-  <si>
-    <t>relationship--a0cab5c2-6d75-4c7e-a1d1-9104e6f4d382</t>
-  </si>
-  <si>
-    <t>relationship--c67f914b-7aee-4b52-80be-14ff0de19509</t>
-  </si>
-  <si>
-    <t>relationship--2c7ea63d-f8ce-4f79-a51b-aee5da46d382</t>
-  </si>
-  <si>
-    <t>relationship--9ba73000-425c-4eef-8d23-0eddd5fbe5b8</t>
-  </si>
-  <si>
-    <t>relationship--b97c6c8f-4556-4f0c-b727-b7c1ee3bbc29</t>
-  </si>
-  <si>
-    <t>relationship--f7bb10ae-1dd7-4d5d-9c54-78bf99b976d6</t>
-  </si>
-  <si>
-    <t>relationship--5552c579-ca7a-4a01-b8b3-3ca980cba14b</t>
-  </si>
-  <si>
-    <t>relationship--156e8d02-57d9-4d23-b134-3a2ca6eadf60</t>
-  </si>
-  <si>
-    <t>relationship--d96da0bc-fbf6-411f-8bc3-2ca02f16725c</t>
-  </si>
-  <si>
-    <t>relationship--bed818e0-76ce-4506-bc5f-a8a1ec1a295d</t>
-  </si>
-  <si>
-    <t>relationship--3f5df155-5aae-44da-9af9-1a226d03e6ab</t>
-  </si>
-  <si>
-    <t>relationship--e5728e9c-6648-4dc0-b6ec-78774623accc</t>
-  </si>
-  <si>
-    <t>relationship--4ab76bec-c8cf-4c6e-a539-0ada2cfeb687</t>
-  </si>
-  <si>
-    <t>relationship--5d8f1aa8-f58f-4286-b678-6fe780d8ef89</t>
-  </si>
-  <si>
-    <t>relationship--37225940-e78f-463d-aae7-9c295d1690a5</t>
-  </si>
-  <si>
-    <t>relationship--c232b6ce-e4e3-492a-8ae7-cc0cfe0ae42b</t>
-  </si>
-  <si>
-    <t>relationship--0fdcd987-9d89-452a-bf7f-845555e8c2b8</t>
-  </si>
-  <si>
-    <t>relationship--46189e0b-5bb5-4884-a2a2-6252bd84b2ca</t>
-  </si>
-  <si>
-    <t>relationship--986f87b8-7ad8-489a-9938-b1068257ebe0</t>
-  </si>
-  <si>
-    <t>relationship--03375ddd-96af-4bf3-a288-92a3be6af9b4</t>
-  </si>
-  <si>
-    <t>relationship--d2d2421b-0ea8-427e-9d70-f0506dc0c64d</t>
-  </si>
-  <si>
-    <t>relationship--a0226ea2-b120-4749-b341-18b2a3de7dd0</t>
-  </si>
-  <si>
-    <t>relationship--84ab087d-7457-42f3-898d-5fee54bd0483</t>
-  </si>
-  <si>
-    <t>relationship--c7c9485c-39ed-4fba-a7ad-beb89b7cf56f</t>
-  </si>
-  <si>
-    <t>relationship--239d7608-34a5-4835-b7f7-c02ac2a9a6af</t>
-  </si>
-  <si>
-    <t>relationship--f287ba30-6aed-42b3-b3bc-5bee0294e476</t>
-  </si>
-  <si>
-    <t>relationship--fb3b5767-aec3-481e-95b4-b71c2ef6de96</t>
-  </si>
-  <si>
-    <t>relationship--501812d7-1650-4734-a274-3ef98476cd55</t>
-  </si>
-  <si>
-    <t>relationship--b0444f41-3c81-4a1a-b481-3f49ec4a4e31</t>
-  </si>
-  <si>
-    <t>relationship--b80cabe7-6934-4b3a-9b89-02bef7d6c618</t>
-  </si>
-  <si>
-    <t>relationship--f5dc9fa0-9614-4a88-9e07-f45255c10932</t>
-  </si>
-  <si>
-    <t>relationship--0c1ef22b-d183-4824-b170-bffcec8a57ee</t>
-  </si>
-  <si>
-    <t>relationship--45203285-e86a-4b6b-bb9e-7405a51a3c34</t>
-  </si>
-  <si>
-    <t>relationship--c02c8bfd-f9a6-4d25-b9bc-fee664d7846d</t>
-  </si>
-  <si>
-    <t>relationship--526d32f2-6608-473d-96a9-0128fd8c4d65</t>
-  </si>
-  <si>
-    <t>relationship--707b76d4-6b45-4def-a530-fba1a7697323</t>
-  </si>
-  <si>
-    <t>relationship--af67535f-654c-476d-933a-70b357f7ad7d</t>
-  </si>
-  <si>
-    <t>relationship--70c92e60-aa83-4abd-9f0f-9a07452090a8</t>
-  </si>
-  <si>
-    <t>relationship--34b4188e-a222-419b-a8a7-87dc5979b184</t>
-  </si>
-  <si>
-    <t>relationship--ba6bcb7f-a2c3-4a1e-a231-847c8c3c25af</t>
-  </si>
-  <si>
-    <t>relationship--ec5aefef-ed6b-4569-9562-52bc2218958f</t>
-  </si>
-  <si>
-    <t>relationship--8333d52c-373c-4705-8b6a-fc8f60f4acb9</t>
-  </si>
-  <si>
-    <t>relationship--2b10ba2c-3e5c-4493-90a9-6a4969709943</t>
-  </si>
-  <si>
-    <t>relationship--d6588f70-b2c0-4f7b-a7de-4234a7d3d393</t>
-  </si>
-  <si>
-    <t>relationship--c8608ea5-5c2e-4d1f-af4e-a403e58a1ddc</t>
-  </si>
-  <si>
-    <t>relationship--3362b6b6-9539-44fb-bbb1-77ca62463972</t>
-  </si>
-  <si>
-    <t>relationship--86f9b1d0-343f-4d2a-b067-baeaa1a5e2ae</t>
-  </si>
-  <si>
-    <t>relationship--ee4218f6-1ce4-4b3d-8d0f-c35d633fa5fd</t>
-  </si>
-  <si>
-    <t>relationship--5e65b072-02c9-4fd1-927e-fe73a3b9c3cc</t>
-  </si>
-  <si>
-    <t>relationship--43f4cbac-131e-477f-ba40-a48a4f09bae7</t>
-  </si>
-  <si>
-    <t>relationship--1703c07c-db59-4561-9aef-0e98c02b9770</t>
-  </si>
-  <si>
-    <t>relationship--d4963880-dd41-4212-afa4-2fdd2806447b</t>
-  </si>
-  <si>
-    <t>relationship--ff8a2389-f5dc-4ca6-ab72-fa4f2934be66</t>
-  </si>
-  <si>
-    <t>relationship--b289c407-48a4-4c20-acde-4fc18f0793aa</t>
-  </si>
-  <si>
-    <t>relationship--8e516f24-9475-40a8-bf4d-e32d3ab3b0f8</t>
-  </si>
-  <si>
-    <t>relationship--a783f428-93f7-4d30-8b8c-3cea3af59dbd</t>
-  </si>
-  <si>
-    <t>relationship--510e5f0c-f40b-4613-b116-7905ed679254</t>
-  </si>
-  <si>
-    <t>relationship--5ee050bb-caa5-4027-8c86-d89457143b70</t>
-  </si>
-  <si>
-    <t>relationship--570688c9-d884-4a11-8a88-dce68ac57c6d</t>
-  </si>
-  <si>
-    <t>relationship--038d1bfe-28b7-44c2-a6a0-ee5e025aedc0</t>
-  </si>
-  <si>
-    <t>relationship--ef099864-160b-40b4-a485-abae77993da8</t>
-  </si>
-  <si>
-    <t>relationship--8d18a790-bb6d-4123-b992-bff8839edc74</t>
-  </si>
-  <si>
-    <t>relationship--dcd721b8-0e41-47d5-b197-ced965eef40c</t>
-  </si>
-  <si>
-    <t>relationship--a467f8b9-78d7-4bad-acfb-978800a868c6</t>
-  </si>
-  <si>
-    <t>relationship--1cce5d0a-384f-407f-8829-0a81968155ce</t>
-  </si>
-  <si>
-    <t>relationship--f1d13d8d-c7fb-43ea-a060-1a5a1a177c2f</t>
-  </si>
-  <si>
-    <t>relationship--ea2ebc72-d18a-448b-9b13-7823bf2b0020</t>
-  </si>
-  <si>
-    <t>relationship--4324d530-438a-4a08-a4a5-450f34b19740</t>
-  </si>
-  <si>
-    <t>relationship--d7aa4588-8ac3-4532-af96-1a85eb79795f</t>
-  </si>
-  <si>
-    <t>relationship--790bc734-b044-4365-ae92-81e0d489b7f1</t>
-  </si>
-  <si>
-    <t>relationship--88c49f62-bbc9-4dbb-b171-f40ca7468289</t>
-  </si>
-  <si>
-    <t>relationship--1d0432ae-0659-41ba-a845-4d858ffe37e2</t>
-  </si>
-  <si>
-    <t>relationship--05dd34a2-9957-4e86-9534-e400d6dcf24a</t>
-  </si>
-  <si>
-    <t>relationship--676bcf81-589f-48d4-852f-44a7687fd5bb</t>
-  </si>
-  <si>
-    <t>relationship--ad47e557-908d-4ff3-b767-9809667070b2</t>
-  </si>
-  <si>
-    <t>relationship--c7f696be-a1d0-434e-8c6e-45c6cb26d255</t>
-  </si>
-  <si>
-    <t>relationship--29e04dd7-5a43-408b-a8ff-8c8b3516666e</t>
-  </si>
-  <si>
-    <t>relationship--53885f25-29da-4650-a3ab-c780b8b681ed</t>
-  </si>
-  <si>
-    <t>relationship--5522fb34-89d3-4d94-8943-19a95cfd80a8</t>
-  </si>
-  <si>
-    <t>relationship--00054969-0bcd-410a-a089-d1c4f48f4ced</t>
-  </si>
-  <si>
-    <t>relationship--fa66eb5a-75ee-432c-b536-d6b2f38b929b</t>
-  </si>
-  <si>
-    <t>relationship--fac1d288-ae4a-4c88-833f-854bed4c2fff</t>
-  </si>
-  <si>
-    <t>relationship--44d2840b-fe2f-45d6-b326-c73f8e8f0f1c</t>
-  </si>
-  <si>
-    <t>relationship--2daf3b19-b9bf-4d3b-87cb-a316e35f4e23</t>
-  </si>
-  <si>
-    <t>relationship--445ef799-5441-4780-858a-d669d25d61a5</t>
-  </si>
-  <si>
-    <t>relationship--cc8ed1d5-ac37-4c4c-8144-10b4803716d5</t>
-  </si>
-  <si>
-    <t>relationship--3a8fd0f8-288e-4644-9df2-8b8fa0a7d324</t>
-  </si>
-  <si>
-    <t>relationship--e2f78c0c-cfd5-43b5-9b1d-61dfe130674d</t>
-  </si>
-  <si>
-    <t>relationship--c38ab01c-8556-430e-8eb6-9fbcf10e0dd9</t>
-  </si>
-  <si>
-    <t>relationship--6494ae06-a2ca-46ef-9b80-3595bbb7393c</t>
-  </si>
-  <si>
-    <t>relationship--aa3904df-e13b-43ea-a06e-d284ba324f6e</t>
-  </si>
-  <si>
-    <t>relationship--424767de-ec68-4018-91b1-880c745a3d5a</t>
-  </si>
-  <si>
-    <t>relationship--cfbd9282-fdc2-4d1c-8035-fac2e924d447</t>
-  </si>
-  <si>
-    <t>relationship--cb07b69c-2cc8-4e90-9658-3995beba2394</t>
-  </si>
-  <si>
-    <t>relationship--48b3fccb-7a56-44f2-a4b3-45eb812e2726</t>
-  </si>
-  <si>
-    <t>relationship--2094783b-721a-411d-a142-06bfb458e71a</t>
-  </si>
-  <si>
-    <t>relationship--6f26e46d-aea8-4f6a-8a13-b598f88d16d9</t>
-  </si>
-  <si>
-    <t>relationship--ec759562-bbd9-4b75-a7b6-79108da59569</t>
-  </si>
-  <si>
-    <t>relationship--d3d29946-55b5-4e56-bb77-4817111ed284</t>
-  </si>
-  <si>
-    <t>relationship--823dadbb-4af3-46e8-af9d-b39b17ca84d5</t>
-  </si>
-  <si>
-    <t>relationship--88e28cf4-e804-47bd-99b3-ddcb8497b4a4</t>
-  </si>
-  <si>
-    <t>relationship--876f4555-3d08-4bfd-8a9d-73479599d3d6</t>
-  </si>
-  <si>
-    <t>relationship--a7ec7934-e4f4-4026-b71f-7990ecb296b7</t>
-  </si>
-  <si>
-    <t>relationship--487de349-615b-48ad-80d7-b95236eecc02</t>
-  </si>
-  <si>
-    <t>relationship--13995ae8-f441-41b5-9724-aab410eaa87f</t>
-  </si>
-  <si>
-    <t>relationship--afd12d83-7475-4510-8c3f-72e983b88113</t>
-  </si>
-  <si>
-    <t>relationship--11a8a1e0-ece3-43f9-8821-02e803bda225</t>
-  </si>
-  <si>
-    <t>relationship--55a46f0e-5aae-462d-80a2-1fee0880dcef</t>
-  </si>
-  <si>
-    <t>relationship--ea520e3e-d699-477c-8969-2c6d6e3d36d4</t>
-  </si>
-  <si>
-    <t>relationship--9b9aae58-6a65-4e11-a5ec-e9510321fea1</t>
-  </si>
-  <si>
-    <t>relationship--b063931d-c06e-4f16-9cfc-b0dddb3e3c43</t>
-  </si>
-  <si>
-    <t>relationship--db2c8d09-3e56-4685-ab16-f063526b19b2</t>
-  </si>
-  <si>
-    <t>relationship--a8e4b3d5-dc03-4f52-8f65-1ee2fa2f0162</t>
-  </si>
-  <si>
-    <t>relationship--707512ad-77bd-4472-ba56-13352a5d0859</t>
-  </si>
-  <si>
-    <t>relationship--85a3d8fe-68d5-41cf-86ae-d20bab16132b</t>
-  </si>
-  <si>
-    <t>relationship--6cff1afe-2cb8-4db9-840b-01edf39d52bc</t>
-  </si>
-  <si>
-    <t>relationship--db76e378-fc70-4c63-97ca-2aabe1818f45</t>
-  </si>
-  <si>
-    <t>relationship--f3f1dcd0-5834-4149-9583-df73aabde910</t>
-  </si>
-  <si>
-    <t>relationship--3c5f7264-7249-466b-b2ff-1aab1cfcf7a8</t>
-  </si>
-  <si>
-    <t>relationship--10b8424a-5a18-48f7-8460-9b56f02c64a9</t>
-  </si>
-  <si>
-    <t>relationship--420bac05-ec0c-457e-b10d-05709ed00508</t>
-  </si>
-  <si>
-    <t>relationship--e4a1859d-56db-473f-8f3a-01d1ecff9865</t>
-  </si>
-  <si>
-    <t>relationship--6f10115c-4687-4bb1-ad80-a8286e8d7ea1</t>
-  </si>
-  <si>
-    <t>relationship--af89ecff-ebd0-48b1-a999-cf7e090359f5</t>
-  </si>
-  <si>
-    <t>relationship--900f0776-6af6-4e52-9d40-407a14a1b10b</t>
-  </si>
-  <si>
-    <t>relationship--ad5911ae-9931-4303-917c-8bf0af554ba2</t>
-  </si>
-  <si>
-    <t>relationship--27fe1e23-9e8e-4e9a-867c-e971f5b27938</t>
-  </si>
-  <si>
-    <t>relationship--cbb50fab-7e8e-4d6c-86d5-832106d6b535</t>
-  </si>
-  <si>
-    <t>relationship--67460a1f-ba46-4ccd-b625-bd6f2659da8a</t>
-  </si>
-  <si>
-    <t>relationship--c79370be-6bfa-4f46-b747-87900992f20c</t>
-  </si>
-  <si>
-    <t>relationship--66de0818-b1aa-4fdf-8b59-41657de9a959</t>
-  </si>
-  <si>
-    <t>relationship--6c62bd91-cec9-43e4-96c0-7de19a976626</t>
-  </si>
-  <si>
-    <t>relationship--10b316d6-a09c-4d60-988f-646e42467869</t>
-  </si>
-  <si>
-    <t>relationship--6e328eb1-08b5-4e49-975c-94c709bd409b</t>
-  </si>
-  <si>
-    <t>relationship--3406d69f-e0ac-4f8e-87a4-6dff7e804f99</t>
-  </si>
-  <si>
-    <t>relationship--269c07e7-e785-4fbe-9b44-37915c651501</t>
-  </si>
-  <si>
-    <t>relationship--f6705a7b-13a9-46b0-bcdb-4e1d69b9d930</t>
-  </si>
-  <si>
-    <t>relationship--232b88a1-d90d-4d5e-8167-da7b7c35c1e3</t>
-  </si>
-  <si>
-    <t>relationship--2cb4cae9-3ff4-4d54-8779-eabc3825c303</t>
-  </si>
-  <si>
-    <t>relationship--2a8ee6fa-55f4-4ad6-9954-df7b9cd95e87</t>
-  </si>
-  <si>
-    <t>relationship--c6724897-4f7a-486a-9976-c1e916d1539d</t>
-  </si>
-  <si>
-    <t>relationship--9eec828d-aff9-4828-856a-ad89e8adc4be</t>
-  </si>
-  <si>
-    <t>relationship--0679e913-f222-4d1f-9a96-6fd772a674ba</t>
-  </si>
-  <si>
-    <t>relationship--c51a31a2-b9e1-4b98-bc26-f590dad3dd7e</t>
-  </si>
-  <si>
-    <t>relationship--0be151f9-7e48-4fd1-b215-5c05f2729c36</t>
-  </si>
-  <si>
-    <t>relationship--61a209ed-7f03-488e-ad53-53aefd2e9ebb</t>
-  </si>
-  <si>
-    <t>relationship--ead62c20-6c77-4fd3-949e-c9a6954be6e7</t>
-  </si>
-  <si>
-    <t>relationship--3dcb1927-c157-4cc5-a204-237cc422e526</t>
-  </si>
-  <si>
-    <t>relationship--f5e5f729-f586-4c58-a2ac-9121ffe6abda</t>
-  </si>
-  <si>
-    <t>relationship--dbe7fab1-5ef3-491d-a1e7-a8c0a701c0aa</t>
-  </si>
-  <si>
-    <t>relationship--e73af7f5-6e5f-49a9-8ed3-d13e0868880d</t>
-  </si>
-  <si>
-    <t>relationship--e20bd310-d4bc-4df3-bfb3-a9836ddfb310</t>
-  </si>
-  <si>
-    <t>relationship--10158e66-8cd1-4b8c-86b9-f88759d46427</t>
-  </si>
-  <si>
-    <t>relationship--d1cb891e-1cad-4db4-8bc7-f62fdabf433e</t>
-  </si>
-  <si>
-    <t>relationship--baf7aa9e-6e05-43a1-b972-90441df19a3e</t>
-  </si>
-  <si>
-    <t>relationship--ec58d906-6864-4068-89bb-bebe7ae99785</t>
-  </si>
-  <si>
-    <t>relationship--d298e28d-250f-4cd0-a856-b89e5ce7b88d</t>
-  </si>
-  <si>
-    <t>relationship--c269fe15-c5be-4823-a518-f9fc55959bc6</t>
-  </si>
-  <si>
-    <t>relationship--50050696-12a8-4fa3-a415-53b8b82dea85</t>
-  </si>
-  <si>
-    <t>relationship--874d162e-2c50-4199-b6a4-39079e1afd2c</t>
-  </si>
-  <si>
-    <t>relationship--f4a5485f-8491-422f-8796-eb43f662ef04</t>
-  </si>
-  <si>
-    <t>relationship--70afaa59-d579-4c48-a4f7-e5f655976d8e</t>
-  </si>
-  <si>
-    <t>relationship--a423a829-7a8d-45da-b736-9a04cf98b61a</t>
-  </si>
-  <si>
-    <t>relationship--70bbeb57-4b3c-4fab-adc1-1dc6198e13b4</t>
-  </si>
-  <si>
-    <t>relationship--0a67dac3-b381-434b-abb7-ef513e09f6cf</t>
-  </si>
-  <si>
-    <t>relationship--4f678204-fcd8-4267-9153-9a4371987f30</t>
-  </si>
-  <si>
-    <t>relationship--ef486430-74c7-4fe2-b673-5fc558d8a341</t>
-  </si>
-  <si>
-    <t>relationship--33b362c3-ef66-4952-a0ed-0dedcc6fb7ff</t>
-  </si>
-  <si>
-    <t>relationship--b792f9e3-9b9c-4536-a89f-174effa04791</t>
-  </si>
-  <si>
-    <t>relationship--8f35ece3-fb19-421a-9f69-555f1050e821</t>
-  </si>
-  <si>
-    <t>relationship--f7a42814-cfdc-4ee8-b3aa-f621d054d2bd</t>
-  </si>
-  <si>
-    <t>relationship--6d5ec928-0460-4088-bf4d-a84766632043</t>
-  </si>
-  <si>
-    <t>relationship--2577f486-51c5-4c4f-bc31-c358edfae31d</t>
-  </si>
-  <si>
-    <t>relationship--957dac06-84ad-428b-95bf-66a508e5d916</t>
-  </si>
-  <si>
-    <t>relationship--6533395a-88f1-4ea2-b736-36c326d771a9</t>
-  </si>
-  <si>
-    <t>relationship--57f29431-847a-43e0-b7e6-1a431a2058e8</t>
-  </si>
-  <si>
-    <t>relationship--e4a98f6c-89c4-440c-b379-ab19a0b17e01</t>
-  </si>
-  <si>
-    <t>relationship--00ab4613-70a8-4939-9c07-372c0bc9860c</t>
-  </si>
-  <si>
-    <t>relationship--cc04b3b3-67ae-44e0-9436-7ff30af33bf7</t>
-  </si>
-  <si>
-    <t>relationship--c1eaee30-f633-4217-bd44-8d15f9d8c065</t>
-  </si>
-  <si>
-    <t>relationship--077a5af9-f296-4f30-967a-ab5cd4faf152</t>
-  </si>
-  <si>
-    <t>relationship--7e59d2ea-b884-41f7-92fd-edc063f147c8</t>
-  </si>
-  <si>
-    <t>relationship--ed7fbb91-8764-4af0-8a62-052e4e6d95d4</t>
-  </si>
-  <si>
-    <t>relationship--cb1bd2c3-a763-4fd2-8c8d-29ca5b1c6ff7</t>
-  </si>
-  <si>
-    <t>relationship--383f4b08-21e5-4e95-a92a-190a74bec975</t>
-  </si>
-  <si>
-    <t>relationship--b8487f86-404d-4580-bb96-4bf795ba066b</t>
-  </si>
-  <si>
-    <t>relationship--52d1bb56-b482-4ba3-8323-d423f21a8c6e</t>
-  </si>
-  <si>
-    <t>relationship--55236e8d-545e-4952-a518-32d267b79248</t>
-  </si>
-  <si>
-    <t>relationship--630137a1-fab5-4996-b489-94b760c08587</t>
-  </si>
-  <si>
-    <t>relationship--8c718d39-0585-4e91-a06f-d9366b81648b</t>
-  </si>
-  <si>
-    <t>relationship--7d415e7b-01a9-478e-9e71-65687ae5091a</t>
-  </si>
-  <si>
-    <t>relationship--aac45e98-80d3-4f9b-bee1-28f0397d63c5</t>
-  </si>
-  <si>
-    <t>relationship--2435cd1e-cd99-425b-832c-7d629f6ee15a</t>
-  </si>
-  <si>
-    <t>relationship--dd956bb0-b061-4a33-8b45-ce09ae518653</t>
-  </si>
-  <si>
-    <t>relationship--b9968c17-292b-4890-aac2-73f7458b4efc</t>
-  </si>
-  <si>
-    <t>relationship--d8c5dfde-2fa6-4075-a4ee-14afcf5356db</t>
-  </si>
-  <si>
-    <t>relationship--ee02a592-fd90-451d-90d5-d2c8d4467ecc</t>
-  </si>
-  <si>
-    <t>relationship--8e295d63-6597-43da-9840-66b7e6ca81b7</t>
-  </si>
-  <si>
-    <t>relationship--92a21bbe-ad5f-4baf-91b0-734d79c01d80</t>
-  </si>
-  <si>
-    <t>relationship--46b0d5ce-0d5c-45b9-9803-2ae4190d0c4c</t>
-  </si>
-  <si>
-    <t>relationship--805a683c-6989-4638-a65d-bcbc3764742a</t>
-  </si>
-  <si>
-    <t>relationship--7e36c1c8-aeb0-4f4f-84ea-86db8d462300</t>
-  </si>
-  <si>
-    <t>relationship--160f57d0-2863-43a6-bfa1-267076ca1d6a</t>
-  </si>
-  <si>
-    <t>relationship--367f3fa8-0c9c-4a10-94a5-5d72b06f96b7</t>
-  </si>
-  <si>
-    <t>relationship--0ec2c2c7-802b-40c0-8428-c963a8e4f90c</t>
-  </si>
-  <si>
-    <t>relationship--e71cbf0d-3d7b-4dbd-ac52-cc1a5866aad4</t>
-  </si>
-  <si>
-    <t>relationship--d852a84f-3c45-4ef2-8fd1-13a3c224137f</t>
-  </si>
-  <si>
-    <t>relationship--878c28e1-7169-459c-91a4-3ed447223d70</t>
-  </si>
-  <si>
-    <t>relationship--81b6bc77-c102-4a05-a579-5e89bd13cc12</t>
-  </si>
-  <si>
-    <t>relationship--77ffef49-fa37-4d05-b1a4-1d7751f79ee4</t>
-  </si>
-  <si>
-    <t>relationship--577e0dbe-1ef5-4fd2-a187-44324ce4a72e</t>
-  </si>
-  <si>
-    <t>relationship--b500e8e8-9847-4766-8f94-34b72b6689c8</t>
-  </si>
-  <si>
-    <t>relationship--29b1511e-eca2-451c-90c5-d4a2b3b608e7</t>
-  </si>
-  <si>
-    <t>relationship--c7fbd8ed-a720-4bec-bd85-41cbe4cdc22f</t>
-  </si>
-  <si>
-    <t>relationship--c74ac39e-968c-46f0-9d68-0c89efe7d6d7</t>
-  </si>
-  <si>
-    <t>relationship--ed809171-4923-43da-a9ad-138283fb7eaf</t>
-  </si>
-  <si>
-    <t>relationship--d6a739e6-c1dd-4cd3-a692-753d5edfcafa</t>
-  </si>
-  <si>
-    <t>relationship--89dd3e0e-2239-4e0c-8cb6-8861b76e0d3c</t>
-  </si>
-  <si>
-    <t>relationship--70f3bbdf-9325-4013-8c73-4f02cb19a47f</t>
-  </si>
-  <si>
-    <t>relationship--0d3ee557-dd08-4c96-baa0-b81cb941cf3e</t>
-  </si>
-  <si>
-    <t>relationship--9591863f-3471-44ae-8a35-1bc56d3a62c1</t>
-  </si>
-  <si>
-    <t>relationship--6f169388-5ee6-4848-805b-165b3fa47dff</t>
-  </si>
-  <si>
-    <t>relationship--33b65c8d-6b41-4163-b2d3-1666c37a9032</t>
-  </si>
-  <si>
-    <t>relationship--f4df1e00-8a91-4b71-b675-25d60bad6a98</t>
-  </si>
-  <si>
-    <t>relationship--24d503a3-8f4f-4244-ad19-1b222b59e7ef</t>
-  </si>
-  <si>
-    <t>relationship--2b63bdcf-a516-4ee3-b148-08bdd7a7cb9d</t>
-  </si>
-  <si>
-    <t>relationship--c0d66f67-d5fc-4718-87b7-13907602bba3</t>
-  </si>
-  <si>
-    <t>relationship--e67e91a0-480a-4ef4-8eeb-81989eadf823</t>
-  </si>
-  <si>
-    <t>relationship--cf7e2563-1bd6-49b2-b95d-70e7b2d5ef86</t>
-  </si>
-  <si>
-    <t>relationship--3519f430-e040-4aee-951d-4527c6545b36</t>
-  </si>
-  <si>
-    <t>relationship--76186630-c101-4f9d-a1ff-6aec5709b600</t>
-  </si>
-  <si>
-    <t>relationship--85357ec1-3dc2-4f90-854e-433509aab018</t>
-  </si>
-  <si>
-    <t>relationship--20780665-a60b-4f7f-971f-5184a072cefc</t>
-  </si>
-  <si>
-    <t>relationship--8b9d3fc3-1e2e-4ca0-ac96-0153a479d186</t>
-  </si>
-  <si>
-    <t>relationship--a74f2cd1-670a-4c86-9add-59a4fda87cbf</t>
-  </si>
-  <si>
-    <t>relationship--295d93e4-0fd4-401e-9b07-610d743be347</t>
-  </si>
-  <si>
-    <t>relationship--8770ccbf-0457-469f-b0eb-bf0fc740dd31</t>
-  </si>
-  <si>
-    <t>relationship--6780bd12-6e75-4185-b1a9-6ea68e82f9a5</t>
-  </si>
-  <si>
-    <t>relationship--363dd54a-6b6c-4d29-b12b-7633f127ae4f</t>
-  </si>
-  <si>
-    <t>relationship--c6fae978-de61-436a-b541-b9ccb8b8ddea</t>
-  </si>
-  <si>
-    <t>relationship--87e4a348-08b9-4ba3-aeed-4e125c080132</t>
-  </si>
-  <si>
-    <t>relationship--515541a7-6128-4a36-bad8-b4a99b8d1f25</t>
-  </si>
-  <si>
-    <t>relationship--627f7ec5-e07a-4a9e-a179-f56072219e23</t>
-  </si>
-  <si>
-    <t>relationship--9950a4bf-9fc5-48aa-8149-a7cc237741b6</t>
-  </si>
-  <si>
-    <t>relationship--47d76080-8a63-4b2b-a690-ecdd1ac8a447</t>
-  </si>
-  <si>
-    <t>relationship--52320481-114d-4984-ae7c-159c0ade1951</t>
-  </si>
-  <si>
-    <t>relationship--b962befb-5ce9-4090-a7ae-d21e5213b24e</t>
-  </si>
-  <si>
-    <t>relationship--98d9c5dd-04c8-41f6-b66b-72031418daa8</t>
-  </si>
-  <si>
-    <t>relationship--b3145501-4aef-4bd4-a84b-56abc85bf491</t>
-  </si>
-  <si>
-    <t>relationship--94c95dc2-8858-4f49-8ece-3ec79609c4c4</t>
-  </si>
-  <si>
-    <t>relationship--75e0cd78-c4ab-4ad1-b1b1-dfad9c2d7b41</t>
-  </si>
-  <si>
-    <t>relationship--1e3e92b7-4def-4664-b9c7-3fab81304d41</t>
-  </si>
-  <si>
-    <t>relationship--a69c6c2e-b12f-47cc-8e0e-db22bccf842d</t>
-  </si>
-  <si>
-    <t>relationship--cf5f23ba-6c2b-402c-9fe3-ae75fa116ee2</t>
-  </si>
-  <si>
-    <t>relationship--f90aefa2-2a8d-4e22-b012-96035822427f</t>
-  </si>
-  <si>
-    <t>relationship--7b93a63c-7ddb-46ed-b1f5-689c84b6dd44</t>
-  </si>
-  <si>
-    <t>relationship--3ab348ce-8d96-4260-bf68-9c2abbeb728e</t>
-  </si>
-  <si>
-    <t>relationship--13bce4b8-606b-4b06-b217-1513ec54251a</t>
+    <t>relationship--4138b4da-9b4a-4810-8234-01f088b2ef84</t>
+  </si>
+  <si>
+    <t>relationship--187d585c-3c8c-452b-af29-a98dd6d0c790</t>
+  </si>
+  <si>
+    <t>relationship--a2a277a8-d68f-4890-b6ad-2f062fe5eb52</t>
+  </si>
+  <si>
+    <t>relationship--49bfcdee-0811-4e07-99d3-ea60966de109</t>
+  </si>
+  <si>
+    <t>relationship--f05621c7-ad01-4355-901d-20c3bed12c54</t>
+  </si>
+  <si>
+    <t>relationship--609ed9e0-8e20-4cf4-84b5-53571e3e2f02</t>
+  </si>
+  <si>
+    <t>relationship--8f712af0-daec-4fec-ac07-e716982da013</t>
+  </si>
+  <si>
+    <t>relationship--530d8452-141f-4f05-b35d-3196f6474b62</t>
+  </si>
+  <si>
+    <t>relationship--b53961b4-1ae8-4160-ae4d-42264492598d</t>
+  </si>
+  <si>
+    <t>relationship--a07a243a-5196-4d10-bd4c-6710b8b351e0</t>
+  </si>
+  <si>
+    <t>relationship--1bfa5390-07ec-418e-adf0-d1bb78d429e5</t>
+  </si>
+  <si>
+    <t>relationship--5f1bded5-3de0-4e81-8e96-b51d5bc64368</t>
+  </si>
+  <si>
+    <t>relationship--1bdc7cd5-2ee1-42f6-b684-ff7531fa9e4a</t>
+  </si>
+  <si>
+    <t>relationship--0ac78c44-7b00-4a46-8c4e-8fc97e87a671</t>
+  </si>
+  <si>
+    <t>relationship--4f149647-7dda-40a9-97d4-a0172656a6a2</t>
+  </si>
+  <si>
+    <t>relationship--9f70a209-0fce-4de7-8560-bd747b68f230</t>
+  </si>
+  <si>
+    <t>relationship--bd191415-4590-49eb-8995-1518efd9a587</t>
+  </si>
+  <si>
+    <t>relationship--d54dea5c-d6ff-4830-8a7e-5761b68f462d</t>
+  </si>
+  <si>
+    <t>relationship--2b77291f-cb53-4bb2-a480-2d675534486a</t>
+  </si>
+  <si>
+    <t>relationship--31992d27-7e29-464c-bfb4-5e6ec101ae9a</t>
+  </si>
+  <si>
+    <t>relationship--7f3df424-3f0a-4e8b-ad21-e2bb30e03b70</t>
+  </si>
+  <si>
+    <t>relationship--b210e0a4-77b8-45b4-8302-acc843eee7c9</t>
+  </si>
+  <si>
+    <t>relationship--d85132e9-70aa-46bf-b3b0-68deb7dccc03</t>
+  </si>
+  <si>
+    <t>relationship--ed82f8c0-0118-4b29-adbb-3ff2283b3758</t>
+  </si>
+  <si>
+    <t>relationship--75b01daa-79c8-41b0-aa84-e6776c9bfe7e</t>
+  </si>
+  <si>
+    <t>relationship--1ac1f0cb-ea14-4307-b3f4-c7e8c78acbb9</t>
+  </si>
+  <si>
+    <t>relationship--ce23341a-f769-4548-b480-775518d22c72</t>
+  </si>
+  <si>
+    <t>relationship--a3623915-8451-4484-a638-9cc79759edf8</t>
+  </si>
+  <si>
+    <t>relationship--f2f5d0fd-c627-4148-becf-ed7bf72046fd</t>
+  </si>
+  <si>
+    <t>relationship--da796365-b316-430f-ba32-e083db19acdd</t>
+  </si>
+  <si>
+    <t>relationship--819e7857-7f0e-42ce-89d3-ca6cf925d01c</t>
+  </si>
+  <si>
+    <t>relationship--a834fafe-2e75-43d6-9bdb-a572809b116d</t>
+  </si>
+  <si>
+    <t>relationship--f3b88869-903a-4db6-a5b4-fb5d2acd997d</t>
+  </si>
+  <si>
+    <t>relationship--683c17cc-8a59-4e91-b473-27b0791ae0ce</t>
+  </si>
+  <si>
+    <t>relationship--097b2e9c-ebb0-42ff-8f3f-663a11d77b7c</t>
+  </si>
+  <si>
+    <t>relationship--6c7003f5-9e62-45fc-a64d-fcbe0339eace</t>
+  </si>
+  <si>
+    <t>relationship--60cef4be-fc20-4e92-9dc0-b7ae246d89d8</t>
+  </si>
+  <si>
+    <t>relationship--5c73d2f3-61e2-46fb-bcd2-b62142a5d7e7</t>
+  </si>
+  <si>
+    <t>relationship--2b65c9dd-0df7-4429-8fb5-25b10f196fa3</t>
+  </si>
+  <si>
+    <t>relationship--be680fd1-cdf9-48f9-b32b-af03edcd5f49</t>
+  </si>
+  <si>
+    <t>relationship--24cd3805-31bf-4d10-bc4e-689fad4be8a7</t>
+  </si>
+  <si>
+    <t>relationship--a10a418b-47c7-4162-85f3-bfa1eace9d91</t>
+  </si>
+  <si>
+    <t>relationship--3b355b20-d54d-486f-8971-0cfe0534cd4a</t>
+  </si>
+  <si>
+    <t>relationship--82d16f2f-0a2c-4561-a6e8-4b9e36ac6e6d</t>
+  </si>
+  <si>
+    <t>relationship--dcecb634-8324-42b1-b91b-9dc407202d5c</t>
+  </si>
+  <si>
+    <t>relationship--2dedb174-ce09-4791-ac10-81a064e97e43</t>
+  </si>
+  <si>
+    <t>relationship--d06f3699-71e9-4994-aed3-fc6c1d4c103d</t>
+  </si>
+  <si>
+    <t>relationship--991acbe3-46b4-4ece-8191-6ca86a63cedd</t>
+  </si>
+  <si>
+    <t>relationship--5bff5a94-791a-438c-a7c4-898a49eda6a4</t>
+  </si>
+  <si>
+    <t>relationship--9d4c8082-15fb-49c3-a058-1e6f230473bc</t>
+  </si>
+  <si>
+    <t>relationship--9e8bd416-a9a5-4207-9acc-46f25aacbdb1</t>
+  </si>
+  <si>
+    <t>relationship--f1ba875e-abe4-43d3-bdca-9f5b299753f2</t>
+  </si>
+  <si>
+    <t>relationship--9583c8de-f3ff-4a8b-8163-dab5fb1e24ad</t>
+  </si>
+  <si>
+    <t>relationship--8d884304-83d9-4af2-a3e8-94c2e27ed308</t>
+  </si>
+  <si>
+    <t>relationship--40d7fbe3-8fbb-455c-9220-93e4002ef10d</t>
+  </si>
+  <si>
+    <t>relationship--6a628742-c864-4748-abd9-da2f3f180740</t>
+  </si>
+  <si>
+    <t>relationship--74b6a8d6-621f-4e0d-a039-7f3d7fb5cb26</t>
+  </si>
+  <si>
+    <t>relationship--e04e78cc-5f18-41d9-9898-c4c59b651beb</t>
+  </si>
+  <si>
+    <t>relationship--49cea33e-bc3f-4c27-a018-bd25a3cb90b8</t>
+  </si>
+  <si>
+    <t>relationship--075a9738-f9f7-4364-89d0-a7c6d1483457</t>
+  </si>
+  <si>
+    <t>relationship--1e5802f2-2fa3-4929-826c-8dc3240ca1f4</t>
+  </si>
+  <si>
+    <t>relationship--3cdc29c6-4557-4e25-a305-457aa88441ae</t>
+  </si>
+  <si>
+    <t>relationship--9b2d4f54-0818-4e04-bf2c-7464ff329b22</t>
+  </si>
+  <si>
+    <t>relationship--980e5e48-abdb-47df-be26-10b127e090d3</t>
+  </si>
+  <si>
+    <t>relationship--39aeec91-4b13-4530-bc9c-810361e46cb7</t>
+  </si>
+  <si>
+    <t>relationship--a4cad2fb-a5c1-498c-b6ca-2517937adb79</t>
+  </si>
+  <si>
+    <t>relationship--95e387fa-0515-4a56-a500-3fb7c415a376</t>
+  </si>
+  <si>
+    <t>relationship--c2b2e394-676e-4412-8781-3cc9d8f9621e</t>
+  </si>
+  <si>
+    <t>relationship--7b958cef-f8f4-49cf-a5b1-af13644c3252</t>
+  </si>
+  <si>
+    <t>relationship--cc4f6fe7-9aea-43a3-ba9a-e77eaa3b8d77</t>
+  </si>
+  <si>
+    <t>relationship--f93a4c95-eed0-426e-be95-9c603951319b</t>
+  </si>
+  <si>
+    <t>relationship--af47548c-8ed8-455d-a2db-0bc93f4030b3</t>
+  </si>
+  <si>
+    <t>relationship--c1745f80-3290-4984-9dd6-ee4299f490b1</t>
+  </si>
+  <si>
+    <t>relationship--d4e6d433-b83a-4fec-b78c-6470cedbed0e</t>
+  </si>
+  <si>
+    <t>relationship--baba5c19-c8f3-4534-ad1a-864f3e9c8af6</t>
+  </si>
+  <si>
+    <t>relationship--cf4ec701-fa7a-4fba-bd7a-851429b88cc0</t>
+  </si>
+  <si>
+    <t>relationship--6dae93ac-f5ef-4b59-82f3-78dcabd8e94e</t>
+  </si>
+  <si>
+    <t>relationship--0b279b18-ce31-4fa5-8f87-6a4a394eb886</t>
+  </si>
+  <si>
+    <t>relationship--0a58485f-695b-4ea9-808d-ab4d235463e3</t>
+  </si>
+  <si>
+    <t>relationship--848bdfbe-75d2-472f-9331-3d956b9d7322</t>
+  </si>
+  <si>
+    <t>relationship--2c5c1c46-398a-40aa-9914-2449ea6edf94</t>
+  </si>
+  <si>
+    <t>relationship--21a7018b-055f-4605-8b79-32213036025a</t>
+  </si>
+  <si>
+    <t>relationship--ad35db0d-4857-4207-a772-86ae1524bc73</t>
+  </si>
+  <si>
+    <t>relationship--c054d111-0cab-4194-b81b-602738e62f1e</t>
+  </si>
+  <si>
+    <t>relationship--335c70ce-5be3-43b9-a53f-6ccf0002bf1c</t>
+  </si>
+  <si>
+    <t>relationship--6ea1a5d4-7467-4b7d-948f-21a358049e4d</t>
+  </si>
+  <si>
+    <t>relationship--e6bad643-553c-4ba0-bc40-264d85592851</t>
+  </si>
+  <si>
+    <t>relationship--7a9d0203-aef0-41b5-bb77-00a1a902ee42</t>
+  </si>
+  <si>
+    <t>relationship--c89c0b7a-f023-479e-9753-40097186f046</t>
+  </si>
+  <si>
+    <t>relationship--e04b5366-8c23-448d-9b88-fe56bd29942d</t>
+  </si>
+  <si>
+    <t>relationship--2ed74d6a-11c8-4f33-bd08-1ec2f25bd0b7</t>
+  </si>
+  <si>
+    <t>relationship--a785db23-c56a-4693-beda-7dcf166e6227</t>
+  </si>
+  <si>
+    <t>relationship--2f92b345-b9fc-4643-898b-3904e77069bf</t>
+  </si>
+  <si>
+    <t>relationship--b1c463fa-8f1a-4b77-9a65-16e5852c003c</t>
+  </si>
+  <si>
+    <t>relationship--d374ff17-73dd-4ac7-8381-62eed7137469</t>
+  </si>
+  <si>
+    <t>relationship--72d78c0d-8e6f-437f-92a7-4c076720dece</t>
+  </si>
+  <si>
+    <t>relationship--116a18fb-8c67-4fe1-a7ca-986001ce149f</t>
+  </si>
+  <si>
+    <t>relationship--53d0fca9-36f5-4eda-8632-d72031d8d198</t>
+  </si>
+  <si>
+    <t>relationship--a125c3e6-5ea4-416d-81b4-c0169bf5d36d</t>
+  </si>
+  <si>
+    <t>relationship--eda34a23-d83c-44f9-936c-c8e3107288a3</t>
+  </si>
+  <si>
+    <t>relationship--4f5120eb-12a6-4033-8c98-af20365d4fd1</t>
+  </si>
+  <si>
+    <t>relationship--3bc86575-0c4b-490a-b373-68bec683add4</t>
+  </si>
+  <si>
+    <t>relationship--f87d3aef-083b-4d69-8745-50345d6587f3</t>
+  </si>
+  <si>
+    <t>relationship--c90f8eeb-d6b2-44fd-9b02-e3e18e6db474</t>
+  </si>
+  <si>
+    <t>relationship--36650039-0241-4c19-9659-3ca5f72971de</t>
+  </si>
+  <si>
+    <t>relationship--18089baf-d9c4-482b-ac26-91bfd97eb777</t>
+  </si>
+  <si>
+    <t>relationship--fc13aee5-9eaa-449e-ae59-330eb32fea05</t>
+  </si>
+  <si>
+    <t>relationship--c947d95f-8656-4324-b486-cd13ca0927cc</t>
+  </si>
+  <si>
+    <t>relationship--b336cb42-3bb1-435c-846f-0c00febf1277</t>
+  </si>
+  <si>
+    <t>relationship--ce900a33-70c5-4a1a-9781-c87b88e967b2</t>
+  </si>
+  <si>
+    <t>relationship--933b2afa-e26f-4aa9-ad59-5e3f5125e589</t>
+  </si>
+  <si>
+    <t>relationship--18c57bf7-ae3c-4657-9739-d786015969e2</t>
+  </si>
+  <si>
+    <t>relationship--852be3d7-aa50-47cc-8650-4d1d96e5eada</t>
+  </si>
+  <si>
+    <t>relationship--fc878e7d-9269-4bc0-9a8d-5bd96a8a21e3</t>
+  </si>
+  <si>
+    <t>relationship--cea2cea0-ad64-4fb2-9ec3-2f0703d860fe</t>
+  </si>
+  <si>
+    <t>relationship--a1b44447-6383-44a1-8be5-4c130931885d</t>
+  </si>
+  <si>
+    <t>relationship--aa2208c4-3aa8-4b41-b43b-881b9da22239</t>
+  </si>
+  <si>
+    <t>relationship--660f2aca-acdb-4d7a-a623-c1c4bd072590</t>
+  </si>
+  <si>
+    <t>relationship--16250663-d5c7-44a0-b47d-51e08be54785</t>
+  </si>
+  <si>
+    <t>relationship--b21c33d5-2489-4693-bbc8-d90ac913967f</t>
+  </si>
+  <si>
+    <t>relationship--790eea08-3f25-4d6b-b2ca-194bd4040dbc</t>
+  </si>
+  <si>
+    <t>relationship--09747095-11f6-42fe-80c9-035fe244f624</t>
+  </si>
+  <si>
+    <t>relationship--678ca8eb-6f43-4ac7-9e5f-c0d16ada12cb</t>
+  </si>
+  <si>
+    <t>relationship--507287f7-225d-4c78-8250-18934f0ad3b0</t>
+  </si>
+  <si>
+    <t>relationship--4fa18265-9a9c-4b4b-9221-f87ee590b740</t>
+  </si>
+  <si>
+    <t>relationship--9974065b-d135-4983-bc93-6d4c8a41ccfa</t>
+  </si>
+  <si>
+    <t>relationship--366bb653-b0cb-4f76-a261-cc1acf7b2786</t>
+  </si>
+  <si>
+    <t>relationship--852dfeaa-f92c-4b07-b20b-6666060cb1f6</t>
+  </si>
+  <si>
+    <t>relationship--9dbb42b0-39e3-4c8f-a726-522c83944680</t>
+  </si>
+  <si>
+    <t>relationship--45bbf762-8c52-4374-a5f3-ae6ed92beacc</t>
+  </si>
+  <si>
+    <t>relationship--6451fe6f-8f1e-474b-b36c-37bfb8d171d3</t>
+  </si>
+  <si>
+    <t>relationship--52d6dae1-ae2a-413f-9b16-93ec199212fb</t>
+  </si>
+  <si>
+    <t>relationship--68afc738-9241-447a-b99e-c7d1fd301ed0</t>
+  </si>
+  <si>
+    <t>relationship--aba19d3c-eb07-4976-b2a8-3e5e01b1baf3</t>
+  </si>
+  <si>
+    <t>relationship--57d02153-c6a4-4528-a314-c22631dd526d</t>
+  </si>
+  <si>
+    <t>relationship--8922e0b6-24f5-451e-b25b-7792c71f272b</t>
+  </si>
+  <si>
+    <t>relationship--b79e8b45-b8c8-464a-a735-141b2bc48e92</t>
+  </si>
+  <si>
+    <t>relationship--d21e5e1f-dd33-41ec-8df7-4d2d800a09a8</t>
+  </si>
+  <si>
+    <t>relationship--677dfe65-b189-4f72-ab09-4df65c1c1d7b</t>
+  </si>
+  <si>
+    <t>relationship--7162dd20-7933-48a5-884d-00783ffe735d</t>
+  </si>
+  <si>
+    <t>relationship--502fed6c-2913-48a0-bef8-448cd530e753</t>
+  </si>
+  <si>
+    <t>relationship--3c219078-acd9-4d8b-8b01-326313855dc2</t>
+  </si>
+  <si>
+    <t>relationship--01c0f813-b9e4-4596-9e78-fd93563ca609</t>
+  </si>
+  <si>
+    <t>relationship--fe7ccf7a-c024-4340-8ba2-4e919213a8c6</t>
+  </si>
+  <si>
+    <t>relationship--8088ae80-0e2d-4653-a2e1-c1c29f777a4c</t>
+  </si>
+  <si>
+    <t>relationship--90a37a3a-9577-49fc-9989-771444e7c56a</t>
+  </si>
+  <si>
+    <t>relationship--9d0a828d-f81f-4601-9850-d3564b968a54</t>
+  </si>
+  <si>
+    <t>relationship--dd1598cd-ec13-4064-a1c7-e16f7a81aa74</t>
+  </si>
+  <si>
+    <t>relationship--ecd69714-1d25-43cd-a432-f70962a54b62</t>
+  </si>
+  <si>
+    <t>relationship--106ad2d5-ed5a-4680-b28d-e40e2c73fb1a</t>
+  </si>
+  <si>
+    <t>relationship--6aee2f28-8a03-4e64-9700-7f07e73500ba</t>
+  </si>
+  <si>
+    <t>relationship--d2f0e81a-2057-4e93-ab36-c61afef37fd7</t>
+  </si>
+  <si>
+    <t>relationship--40ec47e6-77e6-42b8-8a25-7853fe687141</t>
+  </si>
+  <si>
+    <t>relationship--5536f8ea-dade-4bfb-8665-3958d824469d</t>
+  </si>
+  <si>
+    <t>relationship--5b39901b-f285-4060-a711-77c092bbeeca</t>
+  </si>
+  <si>
+    <t>relationship--0d5d3c2a-9dd4-47c5-939d-3b1ada5f714b</t>
+  </si>
+  <si>
+    <t>relationship--c356afec-73f2-4a7c-b4ac-87686f124c98</t>
+  </si>
+  <si>
+    <t>relationship--d65586b6-8843-436b-868b-5643747c1458</t>
+  </si>
+  <si>
+    <t>relationship--c9514420-06b6-411d-b29d-698d7c0c32a5</t>
+  </si>
+  <si>
+    <t>relationship--8595d180-0b01-4d71-81fc-50c503a5cc7c</t>
+  </si>
+  <si>
+    <t>relationship--c9595494-ee98-4a68-8948-aae74bc0a24e</t>
+  </si>
+  <si>
+    <t>relationship--422c3b87-86fe-48d9-a056-fed6294e1b0c</t>
+  </si>
+  <si>
+    <t>relationship--fe24862b-3be8-4d94-a070-5f31d2561b03</t>
+  </si>
+  <si>
+    <t>relationship--10e845b5-afc8-47c4-898d-65db358fd2f9</t>
+  </si>
+  <si>
+    <t>relationship--d60c19e7-f755-4610-8537-2984ee4bc95b</t>
+  </si>
+  <si>
+    <t>relationship--460e3f22-5e70-4e1a-ae77-4d4e519fa881</t>
+  </si>
+  <si>
+    <t>relationship--4b4eeb4e-46d4-4f71-96d8-d0026bba1ed8</t>
+  </si>
+  <si>
+    <t>relationship--fb629e4a-e6f2-46bb-b4c0-49f44f821092</t>
+  </si>
+  <si>
+    <t>relationship--df1ce40a-dac8-45ed-b042-05dfc77c05bb</t>
+  </si>
+  <si>
+    <t>relationship--89e96d40-fea4-40bf-8ce4-85129bc59274</t>
+  </si>
+  <si>
+    <t>relationship--675aae63-9167-444e-bfe1-06d0b895a842</t>
+  </si>
+  <si>
+    <t>relationship--0283d952-9f00-413f-ba8f-8ee476a1dbc1</t>
+  </si>
+  <si>
+    <t>relationship--95ea5184-bb3b-43a1-8782-cd81e17d7263</t>
+  </si>
+  <si>
+    <t>relationship--2d86f586-095d-4616-9fe3-7a14d4e2cae2</t>
+  </si>
+  <si>
+    <t>relationship--11324577-43b4-4627-ad35-aa562a54c341</t>
+  </si>
+  <si>
+    <t>relationship--bfbbd33a-e5e1-4852-9306-1d7c43b641ee</t>
+  </si>
+  <si>
+    <t>relationship--f35ecf84-ea47-4385-a2b3-48d5e21387d8</t>
+  </si>
+  <si>
+    <t>relationship--7104efed-9524-4ecc-b0f9-a417774f8d6a</t>
+  </si>
+  <si>
+    <t>relationship--5e7fd10d-6c05-4c29-be4d-41386fa93ee2</t>
+  </si>
+  <si>
+    <t>relationship--26ae8fdd-f418-4e90-a1cb-0514e89f5396</t>
+  </si>
+  <si>
+    <t>relationship--0c8f00b9-4929-4a91-9e67-f2287a69961d</t>
+  </si>
+  <si>
+    <t>relationship--e1d35297-ead4-43c0-b8bd-886275c5b1a1</t>
+  </si>
+  <si>
+    <t>relationship--4e84a9a4-8941-4267-aa48-5d7635ccb758</t>
+  </si>
+  <si>
+    <t>relationship--992593de-3273-45fc-815b-0f71e42c59c3</t>
+  </si>
+  <si>
+    <t>relationship--d9d53a8e-ad3d-4ae1-8626-a2e101cb53bc</t>
+  </si>
+  <si>
+    <t>relationship--42dc016f-7e38-40f2-862b-d1407135e1ba</t>
+  </si>
+  <si>
+    <t>relationship--548c662b-e702-454d-894d-aa00bd15daee</t>
+  </si>
+  <si>
+    <t>relationship--3c8c661d-e662-420b-87c9-1e78cce48160</t>
+  </si>
+  <si>
+    <t>relationship--8d5ce96b-3e5a-46b5-986e-066f30e7d102</t>
+  </si>
+  <si>
+    <t>relationship--c9b11839-0972-4c4f-a08d-5ad4edcd08a8</t>
+  </si>
+  <si>
+    <t>relationship--0715ddc8-2bc3-4465-8dec-19f8a5fca47d</t>
+  </si>
+  <si>
+    <t>relationship--18e9ee37-32eb-40c7-ba80-6603163572a4</t>
+  </si>
+  <si>
+    <t>relationship--e38c7839-a190-4247-814f-b87bc7c09c4e</t>
+  </si>
+  <si>
+    <t>relationship--cb5bb378-e4f8-4018-894a-ba6e6eb56939</t>
+  </si>
+  <si>
+    <t>relationship--624b4a09-8d37-41e3-a5f5-4d7dd67fbd34</t>
+  </si>
+  <si>
+    <t>relationship--473143d3-de77-484c-8794-06621a40f738</t>
+  </si>
+  <si>
+    <t>relationship--96c1b3a1-7e12-4e2f-9d37-f6fae16a6c22</t>
+  </si>
+  <si>
+    <t>relationship--3cb7fc74-614e-4d58-a946-c344a9a8f7e1</t>
+  </si>
+  <si>
+    <t>relationship--b8fb19c3-7a18-4353-8692-77753d25b876</t>
+  </si>
+  <si>
+    <t>relationship--4e6e6dda-1ef8-48bc-9fec-6168a81ba00a</t>
+  </si>
+  <si>
+    <t>relationship--8264538f-bef4-4f84-bf9f-021cac6c2c6d</t>
+  </si>
+  <si>
+    <t>relationship--131c51bd-34b1-4f67-b7d8-fa840fc69750</t>
+  </si>
+  <si>
+    <t>relationship--33f9b731-538b-4627-930f-eec899282ce8</t>
+  </si>
+  <si>
+    <t>relationship--a8bbf553-d68c-416e-ab2e-db8d7b010d8c</t>
+  </si>
+  <si>
+    <t>relationship--79e705c1-4fd7-4e27-b889-0fe04825fd33</t>
+  </si>
+  <si>
+    <t>relationship--1194a81b-5134-4fe9-bba4-65b9b1d80a69</t>
+  </si>
+  <si>
+    <t>relationship--2572aa85-70c9-4048-af8e-a800a6b9019a</t>
+  </si>
+  <si>
+    <t>relationship--44c1b005-058c-4fc8-9fa6-4bfb6b77ab72</t>
+  </si>
+  <si>
+    <t>relationship--9379159d-ac2b-46a4-b4e1-446d885f0b8a</t>
+  </si>
+  <si>
+    <t>relationship--fd0c1b84-2b4b-4e53-bef5-c90ddd5bf36a</t>
+  </si>
+  <si>
+    <t>relationship--a8538c78-7fe9-4005-af59-b1cb97e9bbe6</t>
+  </si>
+  <si>
+    <t>relationship--fc975dd9-2a58-413d-bef4-8f326dadc42d</t>
+  </si>
+  <si>
+    <t>relationship--cf237a49-124f-450d-9f82-6687bf7c2bbd</t>
+  </si>
+  <si>
+    <t>relationship--34433b84-24b7-46db-8a89-69d5c1842212</t>
+  </si>
+  <si>
+    <t>relationship--1056ae9d-16ed-4245-936e-fb1f0ea739fc</t>
+  </si>
+  <si>
+    <t>relationship--bb17a815-48e7-41d2-a2d7-ced0649b6a72</t>
+  </si>
+  <si>
+    <t>relationship--88d66211-d6e8-43e0-bce4-73b5ccf11cfe</t>
+  </si>
+  <si>
+    <t>relationship--ad816f19-7ef4-42ad-a0d8-6f3cdc5dc7b5</t>
+  </si>
+  <si>
+    <t>relationship--b0b9fa79-b8c6-4d56-91af-e78ae8868a18</t>
+  </si>
+  <si>
+    <t>relationship--a65db1f2-21ff-424b-a521-2050ca1f3b09</t>
+  </si>
+  <si>
+    <t>relationship--cc771afe-611a-412f-a747-fc87cc56f804</t>
+  </si>
+  <si>
+    <t>relationship--f931f4cc-b4b2-4a74-bf94-42588c3b19b9</t>
+  </si>
+  <si>
+    <t>relationship--46cbb067-12a0-4002-affb-9787f3ae6286</t>
+  </si>
+  <si>
+    <t>relationship--03eaa6f9-e266-4cda-aa1f-8e47162842b0</t>
+  </si>
+  <si>
+    <t>relationship--79c0ba76-7d1e-4ce1-a4b7-adbe4dc0495f</t>
+  </si>
+  <si>
+    <t>relationship--81eaafe9-f9b7-4ce4-a525-fdb78fc968f3</t>
+  </si>
+  <si>
+    <t>relationship--d1a55c8c-6e2b-4faf-b8f3-de995fe69739</t>
+  </si>
+  <si>
+    <t>relationship--d9c02db0-bbab-4ea0-b9ae-c95bf97f8432</t>
+  </si>
+  <si>
+    <t>relationship--ba81173b-aefd-40d5-aac2-400c5329a8bf</t>
+  </si>
+  <si>
+    <t>relationship--431549c5-c30a-400a-a674-46bda0e54599</t>
+  </si>
+  <si>
+    <t>relationship--f05c1e28-7669-45a0-8ecb-8a24b74120d2</t>
+  </si>
+  <si>
+    <t>relationship--693adc63-b1db-4758-a2d7-d21c854c50a4</t>
+  </si>
+  <si>
+    <t>relationship--1ab306f6-f695-4873-b3fa-10c2176c1305</t>
+  </si>
+  <si>
+    <t>relationship--6a9f86b8-a71d-429c-b08f-84ccfae7f31b</t>
+  </si>
+  <si>
+    <t>relationship--df29b69f-0ced-4fc0-b6c8-94434e751e36</t>
+  </si>
+  <si>
+    <t>relationship--2f8a5ca2-f944-4f76-a6ff-435cc073cef6</t>
+  </si>
+  <si>
+    <t>relationship--c8c060f6-4af2-4b4b-8340-d5f24e6448fc</t>
+  </si>
+  <si>
+    <t>relationship--62ccfc5c-2e25-4fd4-82fd-1e09115778a5</t>
+  </si>
+  <si>
+    <t>relationship--a602df81-ddcb-4bc9-ada4-23b1daf04e19</t>
+  </si>
+  <si>
+    <t>relationship--48e7cb0d-f697-4853-93ca-855cf57b6b7f</t>
+  </si>
+  <si>
+    <t>relationship--71ceb742-b2c2-4c6e-93c4-b6396eb1203a</t>
+  </si>
+  <si>
+    <t>relationship--120f6ccb-a375-455f-8b5d-4660f7d8f703</t>
+  </si>
+  <si>
+    <t>relationship--b1cfc045-f959-45e5-8a1e-4e75a6a3ac06</t>
+  </si>
+  <si>
+    <t>relationship--3a7d524e-bc71-446e-8008-02a27f3537d7</t>
+  </si>
+  <si>
+    <t>relationship--3f7db20f-12f2-4e3e-83d9-c7039d9f2862</t>
+  </si>
+  <si>
+    <t>relationship--eb5ce8c1-f59b-4ad0-b0df-63feed62464d</t>
+  </si>
+  <si>
+    <t>relationship--af84b5a3-d24a-4407-8944-31ac8f69fa7d</t>
+  </si>
+  <si>
+    <t>relationship--374ef7fd-766a-4b89-9c40-7c85da4864aa</t>
+  </si>
+  <si>
+    <t>relationship--6c3336c0-2dec-46e9-a424-b86461f6719c</t>
+  </si>
+  <si>
+    <t>relationship--e8c953da-2943-46e0-b7ae-cffe3bf274b4</t>
+  </si>
+  <si>
+    <t>relationship--6b497a64-0f53-4b22-a8f3-b8c42489ff57</t>
+  </si>
+  <si>
+    <t>relationship--2b21c131-5910-4163-8e65-5cedc0d9a624</t>
+  </si>
+  <si>
+    <t>relationship--7d51687b-6630-4fea-be92-b2aa8af5a624</t>
+  </si>
+  <si>
+    <t>relationship--1e67e6e6-b2ca-4f65-a822-a322d24f1f34</t>
+  </si>
+  <si>
+    <t>relationship--5b5be8c6-1acd-4481-b4a5-6cfaf12bf30c</t>
+  </si>
+  <si>
+    <t>relationship--b6b93397-50d8-4cbc-aa34-5a4ae18fe1f6</t>
+  </si>
+  <si>
+    <t>relationship--449039e3-2d6c-4747-950f-150777d01333</t>
+  </si>
+  <si>
+    <t>relationship--c77fe291-d151-4070-9216-0a4c3cb6ab6d</t>
+  </si>
+  <si>
+    <t>relationship--60422152-5817-4023-9554-55b6804ab0b3</t>
+  </si>
+  <si>
+    <t>relationship--30720fdc-5bbe-47fb-977a-b11b297a5789</t>
+  </si>
+  <si>
+    <t>relationship--a8711592-b934-4a3b-869b-18e5476eab29</t>
+  </si>
+  <si>
+    <t>relationship--dd35529a-4997-46ec-a5dd-da669f251d73</t>
+  </si>
+  <si>
+    <t>relationship--88d3266c-359b-4c7b-8e8f-d7629066ae51</t>
+  </si>
+  <si>
+    <t>relationship--5db7225b-a9bc-4701-87eb-4e7dd112c8ba</t>
+  </si>
+  <si>
+    <t>relationship--2f5a4e73-7bad-4088-9e28-70f12bfdf432</t>
+  </si>
+  <si>
+    <t>relationship--8353609f-ce10-446d-84f7-8c21c9f7f096</t>
+  </si>
+  <si>
+    <t>relationship--23ccab69-3f81-4c46-80fe-33f7a22e1c62</t>
+  </si>
+  <si>
+    <t>relationship--cc29b464-6b26-4da3-8915-73f02e530701</t>
+  </si>
+  <si>
+    <t>relationship--f1a8948f-16ab-451c-acc1-3238d76022c1</t>
+  </si>
+  <si>
+    <t>relationship--6fda1ee2-0726-4007-b48a-1945a93298c2</t>
+  </si>
+  <si>
+    <t>relationship--fb5eb070-ce49-4baf-8088-567ec8758a73</t>
+  </si>
+  <si>
+    <t>relationship--c33588fa-3c04-41d7-880f-4d5ba3a62257</t>
+  </si>
+  <si>
+    <t>relationship--1b293662-380b-49c4-a5cf-82d5b88fb365</t>
+  </si>
+  <si>
+    <t>relationship--c356e43d-81d8-422a-a923-9440186d5da8</t>
+  </si>
+  <si>
+    <t>relationship--f7088fba-e1b9-40e8-80ab-74732a0142b7</t>
+  </si>
+  <si>
+    <t>relationship--784277fe-fbd4-4804-b281-b35b465246f2</t>
+  </si>
+  <si>
+    <t>relationship--6b0db16c-fe90-433b-9d21-1873f4107b5e</t>
+  </si>
+  <si>
+    <t>relationship--78496c31-9c7b-41f9-885d-a11935a3c801</t>
+  </si>
+  <si>
+    <t>relationship--f1dcf389-f9cb-4c56-933a-254856a5c22c</t>
+  </si>
+  <si>
+    <t>relationship--810487dc-e56a-4f46-9916-38ebc608b03f</t>
+  </si>
+  <si>
+    <t>relationship--f3376006-b855-4134-9112-259ce1e4f288</t>
+  </si>
+  <si>
+    <t>relationship--90dcc9ee-f45d-4ea8-8061-e9f01669e772</t>
+  </si>
+  <si>
+    <t>relationship--82c5ad2b-327a-48d2-9a27-6698ca60d175</t>
+  </si>
+  <si>
+    <t>relationship--43f6f3e4-1036-4136-a44f-ad84b138390e</t>
+  </si>
+  <si>
+    <t>relationship--08322f90-a8fc-426c-85d9-787500a60d63</t>
+  </si>
+  <si>
+    <t>relationship--f1cb7b2d-0e2f-4563-8b20-e4664fcc34bb</t>
+  </si>
+  <si>
+    <t>relationship--fbe68433-0c9f-4840-94e3-d5dcd921bb10</t>
+  </si>
+  <si>
+    <t>relationship--ed94bec6-c33a-4161-8f91-bcf071c6eb46</t>
+  </si>
+  <si>
+    <t>relationship--2acd4183-f1fe-48a6-8591-b5be8c2c1488</t>
+  </si>
+  <si>
+    <t>relationship--46db6129-0cf5-41c0-b746-870a9da6c6ca</t>
+  </si>
+  <si>
+    <t>relationship--bb438ef2-f8aa-459b-92e7-15f651028dc5</t>
+  </si>
+  <si>
+    <t>relationship--8dc26f58-662b-4697-a121-4f14c80f0be0</t>
+  </si>
+  <si>
+    <t>relationship--43158157-4152-4ba8-8e5e-fa2fe3e48843</t>
+  </si>
+  <si>
+    <t>relationship--4e006450-1794-40a0-b790-0426bf3f4f6e</t>
+  </si>
+  <si>
+    <t>relationship--20b2cbd3-7083-47d5-a549-7b97aa39bd94</t>
+  </si>
+  <si>
+    <t>relationship--0fb09034-a316-4985-a7be-a8b1b6f9f165</t>
+  </si>
+  <si>
+    <t>relationship--3635be6e-c8e2-40e3-a500-2c53ae904742</t>
+  </si>
+  <si>
+    <t>relationship--2339f969-9e4a-48cd-b14d-299aa821a93f</t>
+  </si>
+  <si>
+    <t>relationship--6bc3b7e8-4234-4413-ae0e-93fad72efc1b</t>
+  </si>
+  <si>
+    <t>relationship--474974cd-7096-4155-836a-3372bb9adef3</t>
+  </si>
+  <si>
+    <t>relationship--23a630c9-f4cf-4ce9-8e27-bf98c563755c</t>
+  </si>
+  <si>
+    <t>relationship--dcaa3cde-6bee-492b-97c8-93219168c428</t>
+  </si>
+  <si>
+    <t>relationship--fef63a3e-9e07-446a-8024-4189414ee178</t>
+  </si>
+  <si>
+    <t>relationship--fab72703-5abc-424a-a91c-600f9eeec639</t>
+  </si>
+  <si>
+    <t>relationship--8c9a605b-d389-4590-9f50-126b1476878b</t>
+  </si>
+  <si>
+    <t>relationship--05993f87-bf71-48b7-843d-65a2839b8038</t>
+  </si>
+  <si>
+    <t>relationship--340d16ba-6b7f-4fde-951a-0fb9bad84f14</t>
+  </si>
+  <si>
+    <t>relationship--f77f3771-804e-45c0-80f4-aa0ba8e33152</t>
+  </si>
+  <si>
+    <t>relationship--d494703e-bdbd-4f63-9e09-a860b0d04a45</t>
+  </si>
+  <si>
+    <t>relationship--f091b18f-7bbd-436d-b795-9853f63d2c06</t>
+  </si>
+  <si>
+    <t>relationship--113a4168-01dc-4c6c-b534-60e9b6103f40</t>
+  </si>
+  <si>
+    <t>relationship--56736bee-e40d-49ea-b8e4-8d28f52e7019</t>
+  </si>
+  <si>
+    <t>relationship--a95adb07-cba8-4748-a590-4fa4597cc2e0</t>
+  </si>
+  <si>
+    <t>relationship--5165809e-c747-4c3e-b8b5-187ebb59a4e1</t>
+  </si>
+  <si>
+    <t>relationship--fa984c1e-b337-45d2-9f9a-35d3da33bb84</t>
+  </si>
+  <si>
+    <t>relationship--6bd93943-6fb5-4944-b871-3cb306b0d8f5</t>
+  </si>
+  <si>
+    <t>relationship--f37ac11b-8ba3-4ed7-ab5c-779ab658ac71</t>
+  </si>
+  <si>
+    <t>relationship--234a532e-ce20-42ae-a7d3-b9ff7d26f67e</t>
+  </si>
+  <si>
+    <t>relationship--199c76ae-e3bb-43f0-80bf-cbcc8a279774</t>
+  </si>
+  <si>
+    <t>relationship--080f2018-4093-4255-8e61-fd187c804ddc</t>
+  </si>
+  <si>
+    <t>relationship--94abd5d6-363e-4bcb-b2ba-086a4e0efd34</t>
+  </si>
+  <si>
+    <t>relationship--d9a22fc3-bce5-46e7-bf71-d6a9dc72096e</t>
+  </si>
+  <si>
+    <t>relationship--634aecb6-4c9e-411c-85fc-65a86519645e</t>
+  </si>
+  <si>
+    <t>relationship--7a66b59e-63b3-44e3-8ab7-30fb93e70030</t>
+  </si>
+  <si>
+    <t>relationship--82b33b34-5a06-4928-bd23-5bc7b7877f2c</t>
+  </si>
+  <si>
+    <t>relationship--93ecb16d-3498-42b1-b96f-5b2f99e0066d</t>
+  </si>
+  <si>
+    <t>relationship--4d1bdeb5-c434-407b-9ec3-545b82703cdb</t>
+  </si>
+  <si>
+    <t>relationship--a6589388-5be1-469d-8283-ba853387ec2d</t>
+  </si>
+  <si>
+    <t>relationship--7d27df0e-2a93-48f7-8d2b-0779279990e7</t>
+  </si>
+  <si>
+    <t>relationship--aebeed5c-1b6f-4ddd-b270-80ed5a8fe855</t>
+  </si>
+  <si>
+    <t>relationship--858b9702-4376-47fe-8a89-25ef646ca9ec</t>
+  </si>
+  <si>
+    <t>relationship--33f740b8-88b6-479e-925a-1427d3974c96</t>
+  </si>
+  <si>
+    <t>relationship--aaf29cd8-ec5a-4f55-aae4-c4058fbad0b1</t>
+  </si>
+  <si>
+    <t>relationship--928ce81b-cdb4-4a64-b856-596f0237f31a</t>
+  </si>
+  <si>
+    <t>relationship--d511b6f2-e2bd-45c2-aa81-fab304c95498</t>
+  </si>
+  <si>
+    <t>relationship--c506a666-6acd-4ed3-8446-d208a9994676</t>
+  </si>
+  <si>
+    <t>relationship--5629044e-11ea-43ce-b553-d53ba7ceebfc</t>
+  </si>
+  <si>
+    <t>relationship--63209b40-aefd-465e-bb8c-292a6db66960</t>
+  </si>
+  <si>
+    <t>relationship--8f341786-757e-478b-8d08-c03f32a9dad6</t>
+  </si>
+  <si>
+    <t>relationship--78410111-368b-4bde-a7dc-75f718d0feac</t>
+  </si>
+  <si>
+    <t>relationship--19726ca7-9360-4b05-9bda-1597046cad49</t>
   </si>
   <si>
     <t>attributed-to</t>
@@ -5893,22 +5893,22 @@
     <t>Советская Россия (РСФСР)</t>
   </si>
   <si>
-    <t>intrusion-set--224aa639-ced9-4891-bc3c-72ee1592cf05</t>
-  </si>
-  <si>
-    <t>intrusion-set--243887eb-e4f8-4b0e-a6d2-843e9676f671</t>
-  </si>
-  <si>
-    <t>intrusion-set--e3bc6b24-7eb3-408b-af74-b5924d08cd07</t>
-  </si>
-  <si>
-    <t>intrusion-set--1be81b91-037a-46a1-8e5e-b282c40ea297</t>
-  </si>
-  <si>
-    <t>intrusion-set--3642f171-4667-4b82-b3c5-73f7f518396b</t>
-  </si>
-  <si>
-    <t>intrusion-set--8b5f0098-75af-4fcd-9c7f-88149768cd8b</t>
+    <t>intrusion-set--d5113a56-7d11-4ccf-b29b-db0230a3deb5</t>
+  </si>
+  <si>
+    <t>intrusion-set--efc55d3b-975e-4784-879d-5e1771bcdfb2</t>
+  </si>
+  <si>
+    <t>intrusion-set--ccad1a64-f9f9-4595-8650-92f87954b4a0</t>
+  </si>
+  <si>
+    <t>intrusion-set--763a114d-2942-4a6d-9907-1170a64fae86</t>
+  </si>
+  <si>
+    <t>intrusion-set--7b976569-98f0-4fa3-82fe-02d61389de3e</t>
+  </si>
+  <si>
+    <t>intrusion-set--d6cb53bb-bf87-46da-99d2-d218130dd4c9</t>
   </si>
   <si>
     <t>group</t>
@@ -5917,313 +5917,313 @@
     <t>Вторжение войск генерала Деникина под лозунгом восстановления «единой и неделимой России» и вооруженное вытеснение украинских частей из освобожденного ими Киева 31 августа 1919 года («Киевская катастрофа»), приведшее к развалу фронта. (Citation: Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013)</t>
   </si>
   <si>
-    <t>relationship--579007f9-28a0-48e4-9185-c1e2d0b17ae3</t>
-  </si>
-  <si>
-    <t>relationship--cbe422cd-9fe9-4132-84f1-96be195ac993</t>
-  </si>
-  <si>
-    <t>relationship--5667cd4d-ca36-46d4-a17a-9d54006f1f5b</t>
-  </si>
-  <si>
-    <t>relationship--f281ae66-2d30-4085-b524-194af26c8459</t>
-  </si>
-  <si>
-    <t>relationship--36dcc214-651c-4657-acdf-5a62bef3ec0f</t>
-  </si>
-  <si>
-    <t>relationship--13a0e8d5-cd26-41ad-989a-1ffb8a550016</t>
-  </si>
-  <si>
-    <t>relationship--2bf4f3c6-637c-41b5-b365-73fd8f1340fa</t>
-  </si>
-  <si>
-    <t>relationship--bc31601d-18b2-4aed-90e3-208e5d49b78a</t>
-  </si>
-  <si>
-    <t>relationship--9807e38f-6ad6-447a-ae60-a64f9f343370</t>
-  </si>
-  <si>
-    <t>relationship--8a514380-8a2d-4c81-9db0-93a248171fba</t>
-  </si>
-  <si>
-    <t>relationship--b2f79bb7-979e-4ea3-86ef-eebc886aaa6b</t>
-  </si>
-  <si>
-    <t>relationship--545039f1-fa7a-4f32-9e79-7584f9399a5a</t>
-  </si>
-  <si>
-    <t>relationship--bb7c01ba-b6d1-40f6-a6d0-3e4b0cdddbef</t>
-  </si>
-  <si>
-    <t>relationship--974dffe7-2fe4-45f0-bf21-5df9f49100d0</t>
-  </si>
-  <si>
-    <t>relationship--590d5394-a905-4b57-8ea4-38e941c36875</t>
-  </si>
-  <si>
-    <t>relationship--c76b1d3c-c2e5-45d1-a417-d580c9825105</t>
-  </si>
-  <si>
-    <t>relationship--3037be7e-2186-4f85-beb4-bfc477eef251</t>
-  </si>
-  <si>
-    <t>relationship--ceeb598f-298b-4fdd-aa06-06c66f75cb93</t>
-  </si>
-  <si>
-    <t>relationship--6e2eee1c-1d01-4aa2-b34b-1ce62806dae9</t>
-  </si>
-  <si>
-    <t>relationship--c347dbcd-3768-45bb-85b5-ee75069b5731</t>
-  </si>
-  <si>
-    <t>relationship--eacab9fe-e01f-49fc-a53a-bdbdacec0a5d</t>
-  </si>
-  <si>
-    <t>relationship--0a00c5e3-fc83-48cd-8ddb-09ef4bbedfe0</t>
-  </si>
-  <si>
-    <t>relationship--0ee2ab17-a17d-488c-a01f-4cc29fa47acc</t>
-  </si>
-  <si>
-    <t>relationship--72e5cce2-bbff-48a2-b689-589ad7bde2fb</t>
-  </si>
-  <si>
-    <t>relationship--d3b4874f-ecb2-4381-9b8d-7927f05858d0</t>
-  </si>
-  <si>
-    <t>relationship--ca5afe22-bac2-4077-b67b-337995a60f43</t>
-  </si>
-  <si>
-    <t>relationship--77b67bf7-363d-4a9d-9f8b-9742086db6c6</t>
-  </si>
-  <si>
-    <t>relationship--63fe6e4d-581d-431b-8116-9e090e8a745c</t>
-  </si>
-  <si>
-    <t>relationship--94908fc4-bb5b-4683-805a-dbd8dc5e4999</t>
-  </si>
-  <si>
-    <t>relationship--d9fe5d2b-3357-4241-901b-39166dd33941</t>
-  </si>
-  <si>
-    <t>relationship--035ae41a-01e9-4155-9738-28abee46fa01</t>
-  </si>
-  <si>
-    <t>relationship--22ee9109-c21a-4017-a011-8847cb95d8af</t>
-  </si>
-  <si>
-    <t>relationship--de151bf0-ed08-4e2c-924e-d1e4fcd66047</t>
-  </si>
-  <si>
-    <t>relationship--1b8dfcb3-509e-4b06-a3eb-15219d4b259f</t>
-  </si>
-  <si>
-    <t>relationship--d9c1c0f7-5386-45dd-90f5-cdcf145f2c40</t>
-  </si>
-  <si>
-    <t>relationship--a7369f3d-8b80-46e3-bb86-52408e4d0a70</t>
-  </si>
-  <si>
-    <t>relationship--924eeef7-4ac6-4094-a9d7-36befeac2c17</t>
-  </si>
-  <si>
-    <t>relationship--4135c852-a440-4feb-a662-d639156221ad</t>
-  </si>
-  <si>
-    <t>relationship--b50f9c63-ba9d-4a49-a4f7-45d9b53d8ef0</t>
-  </si>
-  <si>
-    <t>relationship--02f7b89f-53fa-478f-a1b5-7b61d8dcbff2</t>
-  </si>
-  <si>
-    <t>relationship--64360548-9a83-41f8-90e4-d73d3eb2c33a</t>
-  </si>
-  <si>
-    <t>relationship--8283b0e0-32c7-4708-9057-d42e6598176b</t>
-  </si>
-  <si>
-    <t>relationship--c1c921d9-699e-4928-8506-67dcd2061170</t>
-  </si>
-  <si>
-    <t>relationship--f2726f56-5487-4b4f-af8a-7031b19d1d76</t>
-  </si>
-  <si>
-    <t>relationship--d84105e6-4a04-4cf4-8a2c-c4a12e5dea08</t>
-  </si>
-  <si>
-    <t>relationship--3b452af0-3666-4c28-974e-a4fb53bbf295</t>
-  </si>
-  <si>
-    <t>relationship--f8ab7e5a-e300-48c9-b77c-8e67a4d7df27</t>
-  </si>
-  <si>
-    <t>relationship--40666857-41f2-4d46-bf70-47aa0c34dcc7</t>
-  </si>
-  <si>
-    <t>relationship--771548ba-7416-4cde-95d1-c788b08aaa71</t>
-  </si>
-  <si>
-    <t>relationship--779d583e-d222-4b26-956a-1e19ac4b77e2</t>
-  </si>
-  <si>
-    <t>relationship--d82e2525-0fdd-49cb-b3f1-1f2efa99ee08</t>
-  </si>
-  <si>
-    <t>relationship--31777070-381d-45d3-b313-00646e092c07</t>
-  </si>
-  <si>
-    <t>relationship--0f4de468-fd2f-4285-9db2-740ef8555069</t>
-  </si>
-  <si>
-    <t>relationship--24ad6afb-6426-413a-a29f-38668ad6ff90</t>
-  </si>
-  <si>
-    <t>relationship--946d5ae9-8056-4e22-9cd4-417de7f38d82</t>
-  </si>
-  <si>
-    <t>relationship--2a1f9d54-b16b-46ad-a923-604adfe79e1e</t>
-  </si>
-  <si>
-    <t>relationship--9a57978d-fe99-4297-8eb2-9746f0966990</t>
-  </si>
-  <si>
-    <t>relationship--366127f5-ecfd-431d-8baa-60078e576cef</t>
-  </si>
-  <si>
-    <t>relationship--835e8e03-39f2-4a00-a970-4f85d13ecae3</t>
-  </si>
-  <si>
-    <t>relationship--8a4a0c57-9338-42e3-8d0f-f04cc7e4970f</t>
-  </si>
-  <si>
-    <t>relationship--13eee957-a48f-466d-833c-b05db7b68537</t>
-  </si>
-  <si>
-    <t>relationship--5c8531a1-d41b-4b0b-8a4e-dfae8afcfa13</t>
-  </si>
-  <si>
-    <t>relationship--823a5587-50a0-40bc-9bde-70e3c2182300</t>
-  </si>
-  <si>
-    <t>relationship--293ad61a-8091-43f2-9fdc-e1adb4c75bc9</t>
-  </si>
-  <si>
-    <t>relationship--08e3ea95-b7f8-4937-b29c-4a1672614f9c</t>
-  </si>
-  <si>
-    <t>relationship--49edb497-7c42-44fc-bb53-870ca69c42d0</t>
-  </si>
-  <si>
-    <t>relationship--2051eeb2-4f36-497b-b503-5da4e20d78a0</t>
-  </si>
-  <si>
-    <t>relationship--30d0c38d-f5e6-4c94-a312-bb0202c53235</t>
-  </si>
-  <si>
-    <t>relationship--a372bff6-e803-4af7-ba39-d0996ef7de00</t>
-  </si>
-  <si>
-    <t>relationship--16bf97f2-e1ac-451b-93db-61a5ca25cfa5</t>
-  </si>
-  <si>
-    <t>relationship--b4456713-6f1a-423c-9417-3fd9318794b5</t>
-  </si>
-  <si>
-    <t>relationship--7368aac6-f55d-45e8-bcd2-0150164725c0</t>
-  </si>
-  <si>
-    <t>relationship--8fa92939-0395-495a-a2cc-25920befafd6</t>
-  </si>
-  <si>
-    <t>relationship--7f8c1d68-a431-4053-a40c-08397553d9f8</t>
-  </si>
-  <si>
-    <t>relationship--fe830b39-4d93-4844-92e9-630d112bb1cc</t>
-  </si>
-  <si>
-    <t>relationship--ba30d8c0-0a8a-43e3-884e-9ebc68c8b18b</t>
-  </si>
-  <si>
-    <t>relationship--a9ada7e1-57e6-4aba-95c7-33f97a61382d</t>
-  </si>
-  <si>
-    <t>relationship--4e5af6b1-7d02-4647-843f-917014cbfee5</t>
-  </si>
-  <si>
-    <t>relationship--a41e87ab-e2f0-472e-8b8b-b96ee2a8dbfb</t>
-  </si>
-  <si>
-    <t>relationship--7a731bc9-9092-4523-8921-dd7a3d94426f</t>
-  </si>
-  <si>
-    <t>relationship--b2beb81b-3b22-4e86-9770-beb7bcb9e418</t>
-  </si>
-  <si>
-    <t>relationship--eba89ba0-a62f-4d7a-aac2-58639ab713f8</t>
-  </si>
-  <si>
-    <t>relationship--cd2cd507-1be3-4d9a-b9fc-fcbddeac37be</t>
-  </si>
-  <si>
-    <t>relationship--0cfbf64b-f9a8-4961-bdcc-328c9364a656</t>
-  </si>
-  <si>
-    <t>relationship--3db40fe1-6e0d-4323-8da9-f0359cfa8be7</t>
-  </si>
-  <si>
-    <t>relationship--077d87d9-6da7-4b46-9cfc-4c84e7f788af</t>
-  </si>
-  <si>
-    <t>relationship--86e9c863-5ae5-46bf-b0e4-b02eaa185bd7</t>
-  </si>
-  <si>
-    <t>relationship--434ffa6e-8e3f-42bf-8887-3b685da7afe2</t>
-  </si>
-  <si>
-    <t>relationship--61560840-331e-4982-ab6f-90edf192c51f</t>
-  </si>
-  <si>
-    <t>relationship--5ed32bcc-ffac-41fb-ade7-6baf29882120</t>
-  </si>
-  <si>
-    <t>relationship--abce58d8-6877-4dcb-a877-9e213452f4b6</t>
-  </si>
-  <si>
-    <t>relationship--0b3c0a27-bbc5-4005-ac5d-bb05a255a1fd</t>
-  </si>
-  <si>
-    <t>relationship--9f3989ee-e8dd-48ba-a582-6a1fb2c277cf</t>
-  </si>
-  <si>
-    <t>relationship--5f947b73-c283-438a-b661-e922ef128815</t>
-  </si>
-  <si>
-    <t>relationship--f2028f92-96ba-481d-a719-e43200be30eb</t>
-  </si>
-  <si>
-    <t>relationship--9b0772cb-acd9-4f8a-82b1-c429efd3c3fc</t>
-  </si>
-  <si>
-    <t>relationship--cf2a8f50-c042-4978-8ac9-040f681a0902</t>
-  </si>
-  <si>
-    <t>relationship--dd0249b1-41cf-49f2-8b39-909edba54fbb</t>
-  </si>
-  <si>
-    <t>relationship--0863f965-e8ec-4d07-86db-37554adca29b</t>
-  </si>
-  <si>
-    <t>relationship--e86d43ec-a735-4d99-ad60-b0135dbfb42f</t>
-  </si>
-  <si>
-    <t>relationship--fc6c0597-d0d4-4933-8519-4d7a7c7297f6</t>
-  </si>
-  <si>
-    <t>relationship--27d3b66b-60c5-4691-884a-af621f775026</t>
-  </si>
-  <si>
-    <t>relationship--653d9b5d-056b-4633-8ccb-46dd884fe269</t>
+    <t>relationship--a95066fb-1718-46d3-8e6e-49e87d4751b7</t>
+  </si>
+  <si>
+    <t>relationship--e9a22d2b-cb0b-4938-9005-5533000e7b38</t>
+  </si>
+  <si>
+    <t>relationship--565adc13-b06e-47cd-ba71-049604f1c97e</t>
+  </si>
+  <si>
+    <t>relationship--1c284d41-421a-4be5-9678-bb2ac621c866</t>
+  </si>
+  <si>
+    <t>relationship--32210d72-5a5a-447f-bc97-012c21a9d180</t>
+  </si>
+  <si>
+    <t>relationship--48fe585f-60a2-4e8c-8063-2ef406ecabbc</t>
+  </si>
+  <si>
+    <t>relationship--1aa6f707-5ad2-4cee-9940-beb43e0bbd57</t>
+  </si>
+  <si>
+    <t>relationship--6810df1c-387a-422d-8a88-f1e5ac631c8c</t>
+  </si>
+  <si>
+    <t>relationship--ebf45aa9-ab01-471e-989c-cf1348b5d70a</t>
+  </si>
+  <si>
+    <t>relationship--4807f9f0-92c6-446d-9180-7913879270a1</t>
+  </si>
+  <si>
+    <t>relationship--2fd65693-90a1-4f44-8274-b473a3bb173f</t>
+  </si>
+  <si>
+    <t>relationship--a0e6d595-4668-4dda-806b-b016e035a696</t>
+  </si>
+  <si>
+    <t>relationship--d47a8fb4-6c97-4b93-a1d6-61eb3f535597</t>
+  </si>
+  <si>
+    <t>relationship--f5c06e1b-f14f-492b-95e0-e82889dcc877</t>
+  </si>
+  <si>
+    <t>relationship--11eee327-9c1f-4151-931a-fbeb9b35bb4c</t>
+  </si>
+  <si>
+    <t>relationship--e435b9fd-332a-4d75-9476-d406f9c37a61</t>
+  </si>
+  <si>
+    <t>relationship--c13f714f-67f4-4e3f-a5fb-410a7d86df85</t>
+  </si>
+  <si>
+    <t>relationship--34d5c786-e1a6-4953-8f03-d138258da3d4</t>
+  </si>
+  <si>
+    <t>relationship--ed0e4c1e-4a29-4e56-99b3-c40191c272cc</t>
+  </si>
+  <si>
+    <t>relationship--dc8be056-141e-4424-80c7-a593fb2736fb</t>
+  </si>
+  <si>
+    <t>relationship--7ba58dbe-7676-4d12-a9da-718738083fe5</t>
+  </si>
+  <si>
+    <t>relationship--fc74cc6a-7592-4289-985b-94d3f359ade3</t>
+  </si>
+  <si>
+    <t>relationship--5541fa16-864d-4d8f-bdd9-8f442103ea16</t>
+  </si>
+  <si>
+    <t>relationship--7d115ed9-39e7-4def-b4a0-79972420802d</t>
+  </si>
+  <si>
+    <t>relationship--1bca7e42-1da9-4ea3-bb66-afa4c1df3443</t>
+  </si>
+  <si>
+    <t>relationship--bbdcb1e8-692d-41fe-88e1-d1fc06f4a8d5</t>
+  </si>
+  <si>
+    <t>relationship--dfb42873-75dc-45b8-8abd-96f5da31a2fa</t>
+  </si>
+  <si>
+    <t>relationship--48aaa29f-ac3e-47ee-982c-8541c26117c5</t>
+  </si>
+  <si>
+    <t>relationship--30d03301-95c7-4a01-86ab-fc56fab12bd0</t>
+  </si>
+  <si>
+    <t>relationship--33c28a36-b522-4c5c-b33c-28d4390bd800</t>
+  </si>
+  <si>
+    <t>relationship--463bd61c-a8d3-40ab-ace9-4515dfa76476</t>
+  </si>
+  <si>
+    <t>relationship--32ff96a6-0b0a-4ca7-8f19-3ed9dce19f80</t>
+  </si>
+  <si>
+    <t>relationship--f743c22a-ebef-4a93-847b-3b6e3122b994</t>
+  </si>
+  <si>
+    <t>relationship--619ee101-358b-4aad-b5d0-14bced2f13c8</t>
+  </si>
+  <si>
+    <t>relationship--abf8a785-6875-4d28-8fe5-01247f5425d9</t>
+  </si>
+  <si>
+    <t>relationship--0eadb0af-59ea-46cf-929c-73d9b9764492</t>
+  </si>
+  <si>
+    <t>relationship--261854c3-1617-45ff-baa8-6dbe52976c77</t>
+  </si>
+  <si>
+    <t>relationship--b027ab64-92aa-4d21-af4e-2337894240b5</t>
+  </si>
+  <si>
+    <t>relationship--b58f403d-9810-45d5-86d3-41e89f270bcf</t>
+  </si>
+  <si>
+    <t>relationship--f56b40d8-819a-40bc-a68e-c60d01db7f0f</t>
+  </si>
+  <si>
+    <t>relationship--3ef446d6-bbb7-433b-af9a-46857a3bc555</t>
+  </si>
+  <si>
+    <t>relationship--0cfbc2d3-05dd-44a8-bc82-7887467e3928</t>
+  </si>
+  <si>
+    <t>relationship--646e8a40-ca48-4925-9031-204da00b650e</t>
+  </si>
+  <si>
+    <t>relationship--a5959dbf-f0f2-45a0-bb14-5e41bdb8e585</t>
+  </si>
+  <si>
+    <t>relationship--e634e455-5505-4898-b305-982f72306fc4</t>
+  </si>
+  <si>
+    <t>relationship--3ae42177-2839-483a-80ef-2f3a2d15803c</t>
+  </si>
+  <si>
+    <t>relationship--79f23e7a-d1dc-44a2-bc4c-6d7c0604d9d9</t>
+  </si>
+  <si>
+    <t>relationship--41d16cff-028a-45b7-9773-b7ed73ac0855</t>
+  </si>
+  <si>
+    <t>relationship--26683c7f-b18d-4f0b-8240-1474c128b1ed</t>
+  </si>
+  <si>
+    <t>relationship--1116351d-6972-444b-90a0-1f8e7e66d75e</t>
+  </si>
+  <si>
+    <t>relationship--8c0281e5-c7a7-4e8c-a340-f4c9c0e727e9</t>
+  </si>
+  <si>
+    <t>relationship--9cedb62b-574a-4771-bf01-3eb83d2c19e7</t>
+  </si>
+  <si>
+    <t>relationship--2c051a16-4463-4ce0-8045-05edbecdb96e</t>
+  </si>
+  <si>
+    <t>relationship--cb40224b-fde2-4bd9-b5f4-1c7fca7631b9</t>
+  </si>
+  <si>
+    <t>relationship--ce3e3dce-c741-4765-a1f3-44e4543d4b3d</t>
+  </si>
+  <si>
+    <t>relationship--58d301f9-9b44-47c3-8013-ae1ec11c5913</t>
+  </si>
+  <si>
+    <t>relationship--97129600-dfdc-46fc-87ea-0815c54c2726</t>
+  </si>
+  <si>
+    <t>relationship--bfea3bd1-1ce5-4d9e-b016-73478a483537</t>
+  </si>
+  <si>
+    <t>relationship--87f2faef-e5fd-49df-99d1-3d1b54ca7640</t>
+  </si>
+  <si>
+    <t>relationship--fab8f5da-e65c-435e-8311-720b6c9eeabf</t>
+  </si>
+  <si>
+    <t>relationship--3aa6ec34-f393-430c-9cbd-4841f9920f0e</t>
+  </si>
+  <si>
+    <t>relationship--31366991-d83e-4eaf-88ba-c26255847e3f</t>
+  </si>
+  <si>
+    <t>relationship--d87ce476-23f9-4fc6-b13c-047097357dcf</t>
+  </si>
+  <si>
+    <t>relationship--5badbe27-c263-478a-b68d-c0c28b4f8ef1</t>
+  </si>
+  <si>
+    <t>relationship--a351e0a9-ae44-4578-8b4d-c6b47da74308</t>
+  </si>
+  <si>
+    <t>relationship--a56ff3ba-96e6-4973-bcd0-c4bef23b5d38</t>
+  </si>
+  <si>
+    <t>relationship--0ce7bddd-50d5-48be-afb7-d3e06b285ef0</t>
+  </si>
+  <si>
+    <t>relationship--05e4c4c5-0966-4337-8275-c4907b8d4673</t>
+  </si>
+  <si>
+    <t>relationship--565130fe-3386-42b6-b475-f02f8474bd39</t>
+  </si>
+  <si>
+    <t>relationship--cef88e9a-6cb7-49e6-9b5b-ba08c8ca6b88</t>
+  </si>
+  <si>
+    <t>relationship--e1ac74fc-d530-4cc3-a105-56087b595c2c</t>
+  </si>
+  <si>
+    <t>relationship--516e3400-7942-4d72-b4b0-e3b39d62f9e7</t>
+  </si>
+  <si>
+    <t>relationship--df7ec859-d883-4c8f-8b0e-372570d2a736</t>
+  </si>
+  <si>
+    <t>relationship--da299c4e-9630-4b38-b717-b6583dbe26fc</t>
+  </si>
+  <si>
+    <t>relationship--c8edbb88-14ff-4d8e-9c74-b2712da0ab11</t>
+  </si>
+  <si>
+    <t>relationship--278b8d8c-0a20-4a8f-9bad-a72df718c17c</t>
+  </si>
+  <si>
+    <t>relationship--ed38512a-db10-4611-b123-d56d3b981c1e</t>
+  </si>
+  <si>
+    <t>relationship--83dd8b38-931f-40f7-bc4b-d56173bcfe73</t>
+  </si>
+  <si>
+    <t>relationship--7f6d56c5-6612-489c-9b18-8c24dc75af58</t>
+  </si>
+  <si>
+    <t>relationship--118c7ea5-f1e1-495b-a5a2-963b25933ac6</t>
+  </si>
+  <si>
+    <t>relationship--b7c59cd1-369f-4de9-a3a4-5b5cdae3d166</t>
+  </si>
+  <si>
+    <t>relationship--b907d83f-4982-4baa-b5f8-fc364e9b33cc</t>
+  </si>
+  <si>
+    <t>relationship--7c44d0bb-7378-48de-af57-28bbb3af8b8b</t>
+  </si>
+  <si>
+    <t>relationship--eda1dbd4-3b39-44ff-90c1-96e6046320fc</t>
+  </si>
+  <si>
+    <t>relationship--3b210ccc-f8be-470c-adc2-cd060d11ffbe</t>
+  </si>
+  <si>
+    <t>relationship--7bf4e691-2470-49cd-a172-5df8af2263c5</t>
+  </si>
+  <si>
+    <t>relationship--57227651-67a7-4ede-b3bd-9309c9dede53</t>
+  </si>
+  <si>
+    <t>relationship--692ea191-a544-4a50-9449-6ac7d09a1930</t>
+  </si>
+  <si>
+    <t>relationship--6e0c35a5-3a68-4c67-af6d-bd0866e51274</t>
+  </si>
+  <si>
+    <t>relationship--c4285b2d-5078-4331-9d59-fe17df33e8d0</t>
+  </si>
+  <si>
+    <t>relationship--c55f3f86-c5b9-4fc3-82f3-3ef59966c26b</t>
+  </si>
+  <si>
+    <t>relationship--a2a349c4-fcd3-47cf-913c-db97245ac089</t>
+  </si>
+  <si>
+    <t>relationship--d12e139d-c65a-4553-832b-62ec4ad574ca</t>
+  </si>
+  <si>
+    <t>relationship--80d2485a-1628-48d9-bb5f-e5b985c816ef</t>
+  </si>
+  <si>
+    <t>relationship--c0eb327a-d351-41c7-ad63-def80454e574</t>
+  </si>
+  <si>
+    <t>relationship--b8166e54-71e5-4ec9-b871-e2bfa18c5cbf</t>
+  </si>
+  <si>
+    <t>relationship--859a06b7-36a7-4ff8-bf25-dd0593d202f3</t>
+  </si>
+  <si>
+    <t>relationship--8c419d72-e7d3-43ef-abcc-b264990cc673</t>
+  </si>
+  <si>
+    <t>relationship--7eac7055-d3e2-4b34-9559-1360309757c9</t>
+  </si>
+  <si>
+    <t>relationship--cd9f0e86-64ce-438f-9767-6b4081d8079f</t>
+  </si>
+  <si>
+    <t>relationship--22ace871-0cc2-4b40-901d-51c4fd38aebd</t>
+  </si>
+  <si>
+    <t>relationship--2ebd7677-4776-4837-9240-39ff6493c0d9</t>
+  </si>
+  <si>
+    <t>relationship--123596cd-c28b-46e5-a300-7400a612cb67</t>
   </si>
   <si>
     <t>reference</t>
@@ -6397,19 +6397,58 @@
     <t>Чорносотенці — Вікіпедія 2026</t>
   </si>
   <si>
+    <t>Польское восстание (1863—1864) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Російсько-українська війна (з 2014) — Вікіпедія 2026</t>
+  </si>
+  <si>
     <t>Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.) 2013</t>
   </si>
   <si>
     <t>Україна й українці в постімперську добу (1917—1939) 2021</t>
   </si>
   <si>
-    <t>Російсько-українська війна (з 2014) — Вікіпедія 2026</t>
+    <t>Перепис населення Російської імперії (1897) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Переяславські статті (1659) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Листопадове повстання (1830—1831) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Аннексия Бессарабии Российской империей (1812) — Википедия 2026</t>
+  </si>
+  <si>
+    <t>Ліквідація Запорозької Січі (1775) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Повстання бузьких козаків (1817) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Московські статті (1665) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Антикріпосницький рух в Україні (1789-1861) — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія 2026</t>
   </si>
   <si>
     <t>Московсько-українська війна (1658—1659) — Вікіпедія 2026</t>
   </si>
   <si>
-    <t>Антикріпосницький рух в Україні (1789-1861) — Вікіпедія 2026</t>
+    <t>ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026</t>
+  </si>
+  <si>
+    <t>Анексія Кримського ханства — Вікіпедія 2026</t>
+  </si>
+  <si>
+    <t>Русско-турецкая война (1768—1774) — Википедия 2026</t>
   </si>
   <si>
     <t>Русско-турецкая война (1877—1878) — Википедия 2026</t>
@@ -6418,42 +6457,6 @@
     <t>Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1) 1998</t>
   </si>
   <si>
-    <t>Русско-турецкая война (1768—1774) — Википедия 2026</t>
-  </si>
-  <si>
-    <t>Перепис населення Російської імперії (1897) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Ліквідація Запорозької Січі (1775) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Московські статті (1665) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Листопадове повстання (1830—1831) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Польское восстание (1863—1864) — Википедия 2026</t>
-  </si>
-  <si>
-    <t>Анексія Кримського ханства — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Переяславські статті (1659) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987) 2026</t>
-  </si>
-  <si>
-    <t>Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія 2026</t>
-  </si>
-  <si>
-    <t>Аннексия Бессарабии Российской империей (1812) — Википедия 2026</t>
-  </si>
-  <si>
     <t>MITRE ATT&amp;CK®. (2023). 2015 Ukraine Electric Power Attack | MITRE ATT&amp;CK®.</t>
   </si>
   <si>
@@ -6619,19 +6622,58 @@
     <t>Википедия. (2026). Чорносотенці — Вікіпедія.</t>
   </si>
   <si>
+    <t>Википедия. (2026). Польское восстание (1863—1864) — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Російсько-українська війна (з 2014) — Вікіпедія.</t>
+  </si>
+  <si>
     <t>Лариса Якубова, большая команда. (2013). Відносини держави, суспільства і особи під час створення радянського ладу в Україні (1917 – 1938 рр.).</t>
   </si>
   <si>
     <t>Єфіменко Г. Г., Кульчицький С. В., Пиріг Р. Я., Скальський В. В., Якубова Л. Д.. (2021). Україна й українці в постімперську добу (1917—1939).</t>
   </si>
   <si>
-    <t>Вікіпедія. (2026). Російсько-українська війна (з 2014) — Вікіпедія.</t>
+    <t>Вікіпедія. (2026). Перепис населення Російської імперії (1897) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Переяславські статті (1659) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Листопадове повстання (1830—1831) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Аннексия Бессарабии Российской империей (1812) — Википедия.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Ліквідація Запорозької Січі (1775) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Повстання бузьких козаків (1817) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Московські статті (1665) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Антикріпосницький рух в Україні (1789-1861) — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія.</t>
   </si>
   <si>
     <t>Википедия. (2026). Московсько-українська війна (1658—1659) — Вікіпедія.</t>
   </si>
   <si>
-    <t>Вікіпедія. (2026). Антикріпосницький рух в Україні (1789-1861) — Вікіпедія.</t>
+    <t>Евгений Захаров, Харьковская правозащитная группа. (2026). ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987).</t>
+  </si>
+  <si>
+    <t>Википедия. (2026). Анексія Кримського ханства — Вікіпедія.</t>
+  </si>
+  <si>
+    <t>Вікіпедія. (2026). Русско-турецкая война (1768—1774) — Википедия.</t>
   </si>
   <si>
     <t>Википедия. (2026). Русско-турецкая война (1877—1878) — Википедия.</t>
@@ -6640,42 +6682,6 @@
     <t>Лариса Якубова. (1998). Національно-культурне життя етнічних меншостей України ( 20-30-ті роки ): коренізація і денаціоналізація (1).</t>
   </si>
   <si>
-    <t>Вікіпедія. (2026). Русско-турецкая война (1768—1774) — Википедия.</t>
-  </si>
-  <si>
-    <t>Вікіпедія. (2026). Перепис населення Російської імперії (1897) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Вікіпедія. (2026). Ліквідація Запорозької Січі (1775) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Вікіпедія. (2026). Московські статті (1665) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Вікіпедія. (2026). Листопадове повстання (1830—1831) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Википедия. (2026). Польское восстание (1863—1864) — Википедия.</t>
-  </si>
-  <si>
-    <t>Википедия. (2026). Анексія Кримського ханства — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Википедия. (2026). Переяславські статті (1659) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Вікіпедія. (2026). Ліквідація козацтва на Правобережній Україні (1699) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Евгений Захаров, Харьковская правозащитная группа. (2026). ДИССИДЕНТСКОЕ ДВИЖЕНИЕ В УКРАИНЕ (1954 – 1987).</t>
-  </si>
-  <si>
-    <t>Вікіпедія. (2026). Похід Пилипа Орлика на Правобережну Україну (1711) — Вікіпедія.</t>
-  </si>
-  <si>
-    <t>Википедия. (2026). Аннексия Бессарабии Российской империей (1812) — Википедия.</t>
-  </si>
-  <si>
     <t>https://attack.mitre.org/campaigns/C0028/</t>
   </si>
   <si>
@@ -6826,58 +6832,61 @@
     <t>https://uk.wikipedia.org/wiki/%25D0%25A7%25D0%25BE%25D1%2580%25D0%25BD%25D0%25BE%25D1%2581%25D0%25BE%25D1%2582%25D0%25B5%25D0%25BD%25D1%2586%25D1%2596</t>
   </si>
   <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%281863%25E2%2580%25941864%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%28%25D0%25B7_2014%29</t>
+  </si>
+  <si>
     <t>http://resource.history.org.ua/item/0016476</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE-%25D1%2583%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2581%25D1%258C%25D0%25BA%25D0%25B0_%25D0%25B2%25D1%2596%25D0%25B9%25D0%25BD%25D0%25B0_%28%25D0%25B7_2014%29</t>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BF%25D0%25B8%25D1%2581_%25D0%25BD%25D0%25B0%25D1%2581%25D0%25B5%25D0%25BB%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D1%2596%25D1%2597_%281897%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96_%281659%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D0%25B8%25D1%2581%25D1%2582%25D0%25BE%25D0%25BF%25D0%25B0%25D0%25B4%25D0%25BE%25D0%25B2%25D0%25B5_%25D0%25BF%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%281830%25E2%2580%25941831%29</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D0%25B8%25D1%258F_%25D0%2591%25D0%25B5%25D1%2581%25D1%2581%25D0%25B0%25D1%2580%25D0%25B0%25D0%25B1%25D0%25B8%25D0%25B8_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D0%25B8%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B8%25D0%25B5%25D0%25B9_%281812%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25A1%25D1%2596%25D1%2587%25D1%2596_%281775%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25B1%25D1%2583%25D0%25B7%25D1%258C%25D0%25BA%25D0%25B8%25D1%2585_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D0%25BA%25D1%2596%25D0%25B2_%281817%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596_%281665%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%2582%25D0%25B2%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281699%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D1%2582%25D0%25B8%25D0%25BA%25D1%2580%25D1%2596%25D0%25BF%25D0%25BE%25D1%2581%25D0%25BD%25D0%25B8%25D1%2586%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25B2_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281789-1861%29</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D1%2585%25D1%2596%25D0%25B4_%25D0%259F%25D0%25B8%25D0%25BB%25D0%25B8%25D0%25BF%25D0%25B0_%25D0%259E%25D1%2580%25D0%25BB%25D0%25B8%25D0%25BA%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2583_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2583_%281711%29</t>
   </si>
   <si>
     <t>https://uk.wikipedia.org/wiki/%D0%9C%D0%BE%D1%81%D0%BA%D0%BE%D0%B2%D1%81%D1%8C%D0%BA%D0%BE-%D1%83%D0%BA%D1%80%D0%B0%D1%97%D0%BD%D1%81%D1%8C%D0%BA%D0%B0_%D0%B2%D1%96%D0%B9%D0%BD%D0%B0_%281658%E2%80%941659%29</t>
   </si>
   <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D1%2582%25D0%25B8%25D0%25BA%25D1%2580%25D1%2596%25D0%25BF%25D0%25BE%25D1%2581%25D0%25BD%25D0%25B8%25D1%2586%25D1%258C%25D0%25BA%25D0%25B8%25D0%25B9_%25D1%2580%25D1%2583%25D1%2585_%25D0%25B2_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281789-1861%29</t>
+    <t>https://museum.khpg.org/ru/1628664422</t>
+  </si>
+  <si>
+    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D1%2580%25D0%25B8%25D0%25BC%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2585%25D0%25B0%25D0%25BD%25D1%2581%25D1%2582%25D0%25B2%25D0%25B0</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281768%25E2%2580%25941774%29</t>
   </si>
   <si>
     <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281877%25E2%2580%25941878%29</t>
   </si>
   <si>
     <t>http://resource.history.org.ua/publ/journal_1998_6_22</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%25A0%25D1%2583%25D1%2581%25D1%2581%25D0%25BA%25D0%25BE-%25D1%2582%25D1%2583%25D1%2580%25D0%25B5%25D1%2586%25D0%25BA%25D0%25B0%25D1%258F_%25D0%25B2%25D0%25BE%25D0%25B9%25D0%25BD%25D0%25B0_%281768%25E2%2580%25941774%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25B5%25D1%2580%25D0%25B5%25D0%25BF%25D0%25B8%25D1%2581_%25D0%25BD%25D0%25B0%25D1%2581%25D0%25B5%25D0%25BB%25D0%25B5%25D0%25BD%25D0%25BD%25D1%258F_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2596%25D0%25B9%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D1%2596%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D1%2596%25D1%2597_%281897%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%2597%25D0%25B0%25D0%25BF%25D0%25BE%25D1%2580%25D0%25BE%25D0%25B7%25D1%258C%25D0%25BA%25D0%25BE%25D1%2597_%25D0%25A1%25D1%2596%25D1%2587%25D1%2596_%281775%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259C%25D0%25BE%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B2%25D1%2581%25D1%258C%25D0%25BA%25D1%2596_%25D1%2581%25D1%2582%25D0%25B0%25D1%2582%25D1%2582%25D1%2596_%281665%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D0%25B8%25D1%2581%25D1%2582%25D0%25BE%25D0%25BF%25D0%25B0%25D0%25B4%25D0%25BE%25D0%25B2%25D0%25B5_%25D0%25BF%25D0%25BE%25D0%25B2%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25BD%25D1%258F_%281830%25E2%2580%25941831%29</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D0%25BB%25D1%258C%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B5_%25D0%25B2%25D0%25BE%25D1%2581%25D1%2581%25D1%2582%25D0%25B0%25D0%25BD%25D0%25B8%25D0%25B5_%281863%25E2%2580%25941864%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D1%2596%25D1%258F_%25D0%259A%25D1%2580%25D0%25B8%25D0%25BC%25D1%2581%25D1%258C%25D0%25BA%25D0%25BE%25D0%25B3%25D0%25BE_%25D1%2585%25D0%25B0%25D0%25BD%25D1%2581%25D1%2582%25D0%25B2%25D0%25B0</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%D0%9F%D0%B5%D1%80%D0%B5%D1%8F%D1%81%D0%BB%D0%B0%D0%B2%D1%81%D1%8C%D0%BA%D1%96_%D1%81%D1%82%D0%B0%D1%82%D1%82%D1%96_%281659%29</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259B%25D1%2596%25D0%25BA%25D0%25B2%25D1%2596%25D0%25B4%25D0%25B0%25D1%2586%25D1%2596%25D1%258F_%25D0%25BA%25D0%25BE%25D0%25B7%25D0%25B0%25D1%2586%25D1%2582%25D0%25B2%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2596%25D0%25B9_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2596_%281699%29</t>
-  </si>
-  <si>
-    <t>https://museum.khpg.org/ru/1628664422</t>
-  </si>
-  <si>
-    <t>https://uk.wikipedia.org/wiki/%25D0%259F%25D0%25BE%25D1%2585%25D1%2596%25D0%25B4_%25D0%259F%25D0%25B8%25D0%25BB%25D0%25B8%25D0%25BF%25D0%25B0_%25D0%259E%25D1%2580%25D0%25BB%25D0%25B8%25D0%25BA%25D0%25B0_%25D0%25BD%25D0%25B0_%25D0%259F%25D1%2580%25D0%25B0%25D0%25B2%25D0%25BE%25D0%25B1%25D0%25B5%25D1%2580%25D0%25B5%25D0%25B6%25D0%25BD%25D1%2583_%25D0%25A3%25D0%25BA%25D1%2580%25D0%25B0%25D1%2597%25D0%25BD%25D1%2583_%281711%29</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%25D0%2590%25D0%25BD%25D0%25BD%25D0%25B5%25D0%25BA%25D1%2581%25D0%25B8%25D1%258F_%25D0%2591%25D0%25B5%25D1%2581%25D1%2581%25D0%25B0%25D1%2580%25D0%25B0%25D0%25B1%25D0%25B8%25D0%25B8_%25D0%25A0%25D0%25BE%25D1%2581%25D1%2581%25D0%25B8%25D0%25B9%25D1%2581%25D0%25BA%25D0%25BE%25D0%25B9_%25D0%25B8%25D0%25BC%25D0%25BF%25D0%25B5%25D1%2580%25D0%25B8%25D0%25B5%25D0%25B9_%281812%29</t>
   </si>
 </sst>
 </file>
@@ -37728,7 +37737,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -37747,10 +37756,10 @@
         <v>2070</v>
       </c>
       <c r="B2" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -37758,10 +37767,10 @@
         <v>2071</v>
       </c>
       <c r="B3" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -37769,10 +37778,10 @@
         <v>2072</v>
       </c>
       <c r="B4" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -37780,10 +37789,10 @@
         <v>2073</v>
       </c>
       <c r="B5" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -37791,10 +37800,10 @@
         <v>2074</v>
       </c>
       <c r="B6" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -37802,10 +37811,10 @@
         <v>2075</v>
       </c>
       <c r="B7" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -37813,10 +37822,10 @@
         <v>2076</v>
       </c>
       <c r="B8" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -37824,10 +37833,10 @@
         <v>2077</v>
       </c>
       <c r="B9" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -37835,10 +37844,10 @@
         <v>2078</v>
       </c>
       <c r="B10" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -37846,10 +37855,10 @@
         <v>2079</v>
       </c>
       <c r="B11" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -37857,10 +37866,10 @@
         <v>2080</v>
       </c>
       <c r="B12" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -37868,7 +37877,7 @@
         <v>2081</v>
       </c>
       <c r="B13" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -37876,7 +37885,7 @@
         <v>2082</v>
       </c>
       <c r="B14" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -37884,10 +37893,10 @@
         <v>2083</v>
       </c>
       <c r="B15" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -37895,10 +37904,10 @@
         <v>2084</v>
       </c>
       <c r="B16" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -37906,10 +37915,10 @@
         <v>2085</v>
       </c>
       <c r="B17" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -37917,10 +37926,10 @@
         <v>2086</v>
       </c>
       <c r="B18" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -37928,10 +37937,10 @@
         <v>2087</v>
       </c>
       <c r="B19" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -37939,10 +37948,10 @@
         <v>2088</v>
       </c>
       <c r="B20" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -37950,7 +37959,7 @@
         <v>2089</v>
       </c>
       <c r="B21" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -37958,10 +37967,10 @@
         <v>2090</v>
       </c>
       <c r="B22" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -37969,10 +37978,10 @@
         <v>2091</v>
       </c>
       <c r="B23" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -37980,10 +37989,10 @@
         <v>2092</v>
       </c>
       <c r="B24" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -37991,10 +38000,10 @@
         <v>2093</v>
       </c>
       <c r="B25" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -38002,10 +38011,10 @@
         <v>2094</v>
       </c>
       <c r="B26" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -38013,10 +38022,10 @@
         <v>2095</v>
       </c>
       <c r="B27" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -38024,10 +38033,10 @@
         <v>2096</v>
       </c>
       <c r="B28" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -38035,10 +38044,10 @@
         <v>2097</v>
       </c>
       <c r="B29" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -38046,10 +38055,10 @@
         <v>2098</v>
       </c>
       <c r="B30" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -38057,7 +38066,7 @@
         <v>2099</v>
       </c>
       <c r="B31" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -38065,10 +38074,10 @@
         <v>2100</v>
       </c>
       <c r="B32" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -38076,10 +38085,10 @@
         <v>2101</v>
       </c>
       <c r="B33" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -38087,10 +38096,10 @@
         <v>2102</v>
       </c>
       <c r="B34" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -38098,10 +38107,10 @@
         <v>2103</v>
       </c>
       <c r="B35" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -38109,10 +38118,10 @@
         <v>2104</v>
       </c>
       <c r="B36" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -38120,10 +38129,10 @@
         <v>2105</v>
       </c>
       <c r="B37" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -38131,10 +38140,10 @@
         <v>2106</v>
       </c>
       <c r="B38" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -38142,10 +38151,10 @@
         <v>2107</v>
       </c>
       <c r="B39" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -38153,10 +38162,10 @@
         <v>2108</v>
       </c>
       <c r="B40" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -38164,7 +38173,7 @@
         <v>2109</v>
       </c>
       <c r="B41" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -38172,10 +38181,10 @@
         <v>2110</v>
       </c>
       <c r="B42" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -38183,10 +38192,10 @@
         <v>2111</v>
       </c>
       <c r="B43" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -38194,10 +38203,10 @@
         <v>2112</v>
       </c>
       <c r="B44" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -38205,10 +38214,10 @@
         <v>2113</v>
       </c>
       <c r="B45" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -38216,10 +38225,10 @@
         <v>2114</v>
       </c>
       <c r="B46" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -38227,10 +38236,10 @@
         <v>2115</v>
       </c>
       <c r="B47" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -38238,10 +38247,10 @@
         <v>2116</v>
       </c>
       <c r="B48" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -38249,10 +38258,10 @@
         <v>2117</v>
       </c>
       <c r="B49" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -38260,10 +38269,10 @@
         <v>2118</v>
       </c>
       <c r="B50" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -38271,10 +38280,10 @@
         <v>2119</v>
       </c>
       <c r="B51" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -38282,10 +38291,10 @@
         <v>2120</v>
       </c>
       <c r="B52" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -38293,10 +38302,10 @@
         <v>2121</v>
       </c>
       <c r="B53" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -38304,10 +38313,10 @@
         <v>2122</v>
       </c>
       <c r="B54" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -38315,10 +38324,10 @@
         <v>2123</v>
       </c>
       <c r="B55" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -38326,256 +38335,256 @@
         <v>2124</v>
       </c>
       <c r="B56" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>2125</v>
+        <v>2082</v>
       </c>
       <c r="B57" t="s">
-        <v>2199</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>2082</v>
+        <v>2125</v>
       </c>
       <c r="B58" t="s">
-        <v>2156</v>
+        <v>2200</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2270</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>2123</v>
+        <v>2089</v>
       </c>
       <c r="B59" t="s">
-        <v>2197</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>2266</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>2112</v>
+        <v>2088</v>
       </c>
       <c r="B60" t="s">
-        <v>2186</v>
+        <v>2163</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2255</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>2077</v>
+        <v>2126</v>
       </c>
       <c r="B61" t="s">
-        <v>2151</v>
+        <v>2201</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>2225</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>2126</v>
+        <v>2109</v>
       </c>
       <c r="B62" t="s">
-        <v>2200</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>2268</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>2089</v>
+        <v>2077</v>
       </c>
       <c r="B63" t="s">
-        <v>2163</v>
+        <v>2152</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2227</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>2088</v>
+        <v>2127</v>
       </c>
       <c r="B64" t="s">
-        <v>2162</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>2234</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>2113</v>
+        <v>2128</v>
       </c>
       <c r="B65" t="s">
-        <v>2187</v>
+        <v>2203</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>2256</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2109</v>
+        <v>2100</v>
       </c>
       <c r="B66" t="s">
-        <v>2183</v>
+        <v>2175</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>2246</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>2093</v>
+        <v>2099</v>
       </c>
       <c r="B67" t="s">
-        <v>2167</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>2238</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="B68" t="s">
-        <v>2198</v>
+        <v>2204</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>2267</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="B69" t="s">
-        <v>2181</v>
+        <v>2188</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>2251</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>2127</v>
+        <v>2115</v>
       </c>
       <c r="B70" t="s">
-        <v>2201</v>
+        <v>2190</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>2269</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>2098</v>
+        <v>2117</v>
       </c>
       <c r="B71" t="s">
-        <v>2172</v>
+        <v>2192</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>2243</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>2086</v>
+        <v>2119</v>
       </c>
       <c r="B72" t="s">
-        <v>2160</v>
+        <v>2194</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>2232</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>2084</v>
+        <v>2098</v>
       </c>
       <c r="B73" t="s">
-        <v>2158</v>
+        <v>2173</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>2230</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>2114</v>
+        <v>2086</v>
       </c>
       <c r="B74" t="s">
-        <v>2188</v>
+        <v>2161</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>2257</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>2128</v>
+        <v>2092</v>
       </c>
       <c r="B75" t="s">
-        <v>2202</v>
+        <v>2167</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>2270</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>2122</v>
+        <v>2130</v>
       </c>
       <c r="B76" t="s">
-        <v>2196</v>
+        <v>2205</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>2265</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>2079</v>
+        <v>2104</v>
       </c>
       <c r="B77" t="s">
-        <v>2153</v>
+        <v>2179</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>2227</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>2099</v>
+        <v>2091</v>
       </c>
       <c r="B78" t="s">
-        <v>2173</v>
+        <v>2166</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>2238</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>2129</v>
+        <v>2108</v>
       </c>
       <c r="B79" t="s">
-        <v>2203</v>
+        <v>2183</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>2271</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="B80" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>2244</v>
@@ -38583,384 +38592,406 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="B81" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B82" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>2081</v>
+        <v>2112</v>
       </c>
       <c r="B83" t="s">
-        <v>2155</v>
+        <v>2187</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>2257</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>2078</v>
+        <v>2133</v>
       </c>
       <c r="B84" t="s">
-        <v>2152</v>
+        <v>2208</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>2226</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>2092</v>
+        <v>2110</v>
       </c>
       <c r="B85" t="s">
-        <v>2166</v>
+        <v>2185</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>2237</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>2090</v>
+        <v>2123</v>
       </c>
       <c r="B86" t="s">
-        <v>2164</v>
+        <v>2198</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>2235</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>2117</v>
+        <v>2134</v>
       </c>
       <c r="B87" t="s">
-        <v>2191</v>
+        <v>2209</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>2260</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>2132</v>
+        <v>2087</v>
       </c>
       <c r="B88" t="s">
-        <v>2206</v>
+        <v>2162</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>2274</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>2133</v>
+        <v>2121</v>
       </c>
       <c r="B89" t="s">
-        <v>2207</v>
+        <v>2196</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>2275</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B90" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>2119</v>
+        <v>2079</v>
       </c>
       <c r="B91" t="s">
-        <v>2193</v>
+        <v>2154</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>2262</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="B92" t="s">
-        <v>2209</v>
+        <v>2199</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>2095</v>
+        <v>2136</v>
       </c>
       <c r="B93" t="s">
-        <v>2169</v>
+        <v>2211</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>2240</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>2110</v>
+        <v>2137</v>
       </c>
       <c r="B94" t="s">
-        <v>2184</v>
+        <v>2212</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>2253</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>2136</v>
+        <v>2105</v>
       </c>
       <c r="B95" t="s">
-        <v>2210</v>
+        <v>2180</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>2278</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>2115</v>
+        <v>2138</v>
       </c>
       <c r="B96" t="s">
-        <v>2189</v>
+        <v>2213</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>2101</v>
+        <v>2114</v>
       </c>
       <c r="B97" t="s">
-        <v>2175</v>
+        <v>2189</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>2245</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="B98" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>2108</v>
+        <v>2122</v>
       </c>
       <c r="B99" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>2252</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="B100" t="s">
         <v>2171</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>2118</v>
+        <v>2094</v>
       </c>
       <c r="B101" t="s">
-        <v>2192</v>
+        <v>2169</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>2261</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>2096</v>
+        <v>2107</v>
       </c>
       <c r="B102" t="s">
-        <v>2170</v>
+        <v>2182</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>2241</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>2094</v>
+        <v>2106</v>
       </c>
       <c r="B103" t="s">
-        <v>2168</v>
+        <v>2181</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>2239</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>2121</v>
+        <v>2140</v>
       </c>
       <c r="B104" t="s">
-        <v>2195</v>
+        <v>2215</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>2264</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>2138</v>
+        <v>2078</v>
       </c>
       <c r="B105" t="s">
-        <v>2212</v>
+        <v>2153</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>2280</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B106" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="B107" t="s">
-        <v>2178</v>
+        <v>2168</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>2248</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B108" t="s">
         <v>2165</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>2105</v>
+        <v>2142</v>
       </c>
       <c r="B109" t="s">
-        <v>2179</v>
+        <v>2217</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>2249</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="B110" t="s">
-        <v>2214</v>
+        <v>2218</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>2282</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>2106</v>
+        <v>2118</v>
       </c>
       <c r="B111" t="s">
-        <v>2180</v>
+        <v>2193</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>2250</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>2141</v>
+        <v>2095</v>
       </c>
       <c r="B112" t="s">
-        <v>2215</v>
+        <v>2170</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>2283</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>2102</v>
+        <v>2084</v>
       </c>
       <c r="B113" t="s">
-        <v>2176</v>
+        <v>2159</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>2246</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="B114" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>2143</v>
+        <v>2081</v>
       </c>
       <c r="B115" t="s">
-        <v>2217</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>2285</v>
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>2247</v>
       </c>
     </row>
   </sheetData>
@@ -39015,59 +39046,61 @@
     <hyperlink ref="C54" r:id="rId48"/>
     <hyperlink ref="C55" r:id="rId49"/>
     <hyperlink ref="C56" r:id="rId50"/>
-    <hyperlink ref="C59" r:id="rId51"/>
+    <hyperlink ref="C58" r:id="rId51"/>
     <hyperlink ref="C60" r:id="rId52"/>
     <hyperlink ref="C61" r:id="rId53"/>
-    <hyperlink ref="C62" r:id="rId54"/>
-    <hyperlink ref="C64" r:id="rId55"/>
-    <hyperlink ref="C65" r:id="rId56"/>
-    <hyperlink ref="C67" r:id="rId57"/>
-    <hyperlink ref="C68" r:id="rId58"/>
-    <hyperlink ref="C69" r:id="rId59"/>
-    <hyperlink ref="C70" r:id="rId60"/>
-    <hyperlink ref="C71" r:id="rId61"/>
-    <hyperlink ref="C72" r:id="rId62"/>
-    <hyperlink ref="C73" r:id="rId63"/>
-    <hyperlink ref="C74" r:id="rId64"/>
-    <hyperlink ref="C75" r:id="rId65"/>
-    <hyperlink ref="C76" r:id="rId66"/>
-    <hyperlink ref="C77" r:id="rId67"/>
+    <hyperlink ref="C63" r:id="rId54"/>
+    <hyperlink ref="C65" r:id="rId55"/>
+    <hyperlink ref="C66" r:id="rId56"/>
+    <hyperlink ref="C68" r:id="rId57"/>
+    <hyperlink ref="C69" r:id="rId58"/>
+    <hyperlink ref="C70" r:id="rId59"/>
+    <hyperlink ref="C71" r:id="rId60"/>
+    <hyperlink ref="C72" r:id="rId61"/>
+    <hyperlink ref="C73" r:id="rId62"/>
+    <hyperlink ref="C74" r:id="rId63"/>
+    <hyperlink ref="C75" r:id="rId64"/>
+    <hyperlink ref="C76" r:id="rId65"/>
+    <hyperlink ref="C77" r:id="rId66"/>
+    <hyperlink ref="C78" r:id="rId67"/>
     <hyperlink ref="C79" r:id="rId68"/>
     <hyperlink ref="C80" r:id="rId69"/>
     <hyperlink ref="C81" r:id="rId70"/>
     <hyperlink ref="C82" r:id="rId71"/>
-    <hyperlink ref="C84" r:id="rId72"/>
-    <hyperlink ref="C85" r:id="rId73"/>
-    <hyperlink ref="C86" r:id="rId74"/>
-    <hyperlink ref="C87" r:id="rId75"/>
-    <hyperlink ref="C88" r:id="rId76"/>
-    <hyperlink ref="C89" r:id="rId77"/>
-    <hyperlink ref="C90" r:id="rId78"/>
-    <hyperlink ref="C91" r:id="rId79"/>
-    <hyperlink ref="C92" r:id="rId80"/>
-    <hyperlink ref="C93" r:id="rId81"/>
-    <hyperlink ref="C94" r:id="rId82"/>
-    <hyperlink ref="C95" r:id="rId83"/>
-    <hyperlink ref="C96" r:id="rId84"/>
-    <hyperlink ref="C97" r:id="rId85"/>
-    <hyperlink ref="C98" r:id="rId86"/>
-    <hyperlink ref="C99" r:id="rId87"/>
-    <hyperlink ref="C100" r:id="rId88"/>
-    <hyperlink ref="C101" r:id="rId89"/>
-    <hyperlink ref="C102" r:id="rId90"/>
-    <hyperlink ref="C103" r:id="rId91"/>
-    <hyperlink ref="C104" r:id="rId92"/>
-    <hyperlink ref="C105" r:id="rId93"/>
-    <hyperlink ref="C106" r:id="rId94"/>
-    <hyperlink ref="C107" r:id="rId95"/>
-    <hyperlink ref="C108" r:id="rId96"/>
-    <hyperlink ref="C109" r:id="rId97"/>
-    <hyperlink ref="C110" r:id="rId98"/>
-    <hyperlink ref="C111" r:id="rId99"/>
-    <hyperlink ref="C112" r:id="rId100"/>
-    <hyperlink ref="C113" r:id="rId101"/>
-    <hyperlink ref="C114" r:id="rId102"/>
-    <hyperlink ref="C115" r:id="rId103"/>
+    <hyperlink ref="C83" r:id="rId72"/>
+    <hyperlink ref="C84" r:id="rId73"/>
+    <hyperlink ref="C85" r:id="rId74"/>
+    <hyperlink ref="C86" r:id="rId75"/>
+    <hyperlink ref="C87" r:id="rId76"/>
+    <hyperlink ref="C88" r:id="rId77"/>
+    <hyperlink ref="C89" r:id="rId78"/>
+    <hyperlink ref="C90" r:id="rId79"/>
+    <hyperlink ref="C91" r:id="rId80"/>
+    <hyperlink ref="C92" r:id="rId81"/>
+    <hyperlink ref="C93" r:id="rId82"/>
+    <hyperlink ref="C94" r:id="rId83"/>
+    <hyperlink ref="C95" r:id="rId84"/>
+    <hyperlink ref="C96" r:id="rId85"/>
+    <hyperlink ref="C97" r:id="rId86"/>
+    <hyperlink ref="C98" r:id="rId87"/>
+    <hyperlink ref="C99" r:id="rId88"/>
+    <hyperlink ref="C100" r:id="rId89"/>
+    <hyperlink ref="C101" r:id="rId90"/>
+    <hyperlink ref="C102" r:id="rId91"/>
+    <hyperlink ref="C103" r:id="rId92"/>
+    <hyperlink ref="C104" r:id="rId93"/>
+    <hyperlink ref="C105" r:id="rId94"/>
+    <hyperlink ref="C106" r:id="rId95"/>
+    <hyperlink ref="C107" r:id="rId96"/>
+    <hyperlink ref="C108" r:id="rId97"/>
+    <hyperlink ref="C109" r:id="rId98"/>
+    <hyperlink ref="C110" r:id="rId99"/>
+    <hyperlink ref="C111" r:id="rId100"/>
+    <hyperlink ref="C112" r:id="rId101"/>
+    <hyperlink ref="C113" r:id="rId102"/>
+    <hyperlink ref="C114" r:id="rId103"/>
+    <hyperlink ref="C116" r:id="rId104"/>
+    <hyperlink ref="C117" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
